--- a/artfynd/A 32573-2024 artfynd.xlsx
+++ b/artfynd/A 32573-2024 artfynd.xlsx
@@ -12300,10 +12300,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120819508</v>
+        <v>120827484</v>
       </c>
       <c r="B115" t="n">
-        <v>77982</v>
+        <v>57348</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12316,37 +12316,45 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Risåsen, Risåsen, Tännäs, Hjd</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>380437</v>
+        <v>380187</v>
       </c>
       <c r="R115" t="n">
-        <v>6920374</v>
+        <v>6920068</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12402,10 +12410,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120818809</v>
+        <v>120819508</v>
       </c>
       <c r="B116" t="n">
-        <v>74705</v>
+        <v>77982</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12418,34 +12426,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>380379</v>
+        <v>380437</v>
       </c>
       <c r="R116" t="n">
-        <v>6920117</v>
+        <v>6920374</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12504,10 +12512,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120827484</v>
+        <v>120818809</v>
       </c>
       <c r="B117" t="n">
-        <v>57348</v>
+        <v>74705</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12520,45 +12528,37 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Risåsen, Risåsen, Tännäs, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>380187</v>
+        <v>380379</v>
       </c>
       <c r="R117" t="n">
-        <v>6920068</v>
+        <v>6920117</v>
       </c>
       <c r="S117" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13948,10 +13948,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120817582</v>
+        <v>120819997</v>
       </c>
       <c r="B131" t="n">
-        <v>74705</v>
+        <v>90705</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -13964,21 +13964,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13988,10 +13988,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>380239</v>
+        <v>380169</v>
       </c>
       <c r="R131" t="n">
-        <v>6920211</v>
+        <v>6920084</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14050,7 +14050,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120818107</v>
+        <v>120817582</v>
       </c>
       <c r="B132" t="n">
         <v>74705</v>
@@ -14090,10 +14090,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>380241</v>
+        <v>380239</v>
       </c>
       <c r="R132" t="n">
-        <v>6920149</v>
+        <v>6920211</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14152,10 +14152,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120819997</v>
+        <v>120818107</v>
       </c>
       <c r="B133" t="n">
-        <v>90705</v>
+        <v>74705</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14168,21 +14168,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14192,10 +14192,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>380169</v>
+        <v>380241</v>
       </c>
       <c r="R133" t="n">
-        <v>6920084</v>
+        <v>6920149</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>

--- a/artfynd/A 32573-2024 artfynd.xlsx
+++ b/artfynd/A 32573-2024 artfynd.xlsx
@@ -11994,10 +11994,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120817498</v>
+        <v>120818809</v>
       </c>
       <c r="B112" t="n">
-        <v>74705</v>
+        <v>74708</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12034,10 +12034,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>380253</v>
+        <v>380379</v>
       </c>
       <c r="R112" t="n">
-        <v>6920258</v>
+        <v>6920117</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12096,10 +12096,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120817117</v>
+        <v>120817445</v>
       </c>
       <c r="B113" t="n">
-        <v>74705</v>
+        <v>74708</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12136,10 +12136,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>380229</v>
+        <v>380272</v>
       </c>
       <c r="R113" t="n">
-        <v>6920310</v>
+        <v>6920269</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12198,10 +12198,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120819131</v>
+        <v>120819340</v>
       </c>
       <c r="B114" t="n">
-        <v>77939</v>
+        <v>74708</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12210,25 +12210,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>498</v>
+        <v>6440</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12238,10 +12238,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>380487</v>
+        <v>380508</v>
       </c>
       <c r="R114" t="n">
-        <v>6920278</v>
+        <v>6920337</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12300,10 +12300,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120827484</v>
+        <v>120827462</v>
       </c>
       <c r="B115" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12348,10 +12348,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>380187</v>
+        <v>380225</v>
       </c>
       <c r="R115" t="n">
-        <v>6920068</v>
+        <v>6920029</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12410,10 +12410,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120819508</v>
+        <v>120817298</v>
       </c>
       <c r="B116" t="n">
-        <v>77982</v>
+        <v>74708</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12426,34 +12426,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>380437</v>
+        <v>380275</v>
       </c>
       <c r="R116" t="n">
-        <v>6920374</v>
+        <v>6920296</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12512,10 +12512,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120818809</v>
+        <v>120816914</v>
       </c>
       <c r="B117" t="n">
-        <v>74705</v>
+        <v>74708</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12552,10 +12552,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>380379</v>
+        <v>380182</v>
       </c>
       <c r="R117" t="n">
-        <v>6920117</v>
+        <v>6920292</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12614,10 +12614,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120818308</v>
+        <v>120818608</v>
       </c>
       <c r="B118" t="n">
-        <v>74705</v>
+        <v>78601</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12630,21 +12630,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12654,7 +12654,7 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>380298</v>
+        <v>380350</v>
       </c>
       <c r="R118" t="n">
         <v>6920123</v>
@@ -12716,10 +12716,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120817440</v>
+        <v>120818107</v>
       </c>
       <c r="B119" t="n">
-        <v>77982</v>
+        <v>74708</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12732,21 +12732,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12756,10 +12756,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>380272</v>
+        <v>380241</v>
       </c>
       <c r="R119" t="n">
-        <v>6920269</v>
+        <v>6920149</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12818,10 +12818,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120818909</v>
+        <v>120819131</v>
       </c>
       <c r="B120" t="n">
-        <v>90705</v>
+        <v>77942</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12830,38 +12830,38 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5432</v>
+        <v>498</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>380419</v>
+        <v>380487</v>
       </c>
       <c r="R120" t="n">
-        <v>6920164</v>
+        <v>6920278</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12920,10 +12920,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120819340</v>
+        <v>120819092</v>
       </c>
       <c r="B121" t="n">
-        <v>74705</v>
+        <v>57351</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -12936,37 +12936,42 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>380508</v>
+        <v>380492</v>
       </c>
       <c r="R121" t="n">
-        <v>6920337</v>
+        <v>6920257</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13022,10 +13027,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120818887</v>
+        <v>120819559</v>
       </c>
       <c r="B122" t="n">
-        <v>77939</v>
+        <v>74708</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13034,38 +13039,38 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>498</v>
+        <v>6440</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>380400</v>
+        <v>380312</v>
       </c>
       <c r="R122" t="n">
-        <v>6920126</v>
+        <v>6920269</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13124,10 +13129,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120819133</v>
+        <v>120819439</v>
       </c>
       <c r="B123" t="n">
-        <v>74705</v>
+        <v>74708</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13164,10 +13169,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>380487</v>
+        <v>380480</v>
       </c>
       <c r="R123" t="n">
-        <v>6920278</v>
+        <v>6920366</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13226,10 +13231,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120819137</v>
+        <v>120818661</v>
       </c>
       <c r="B124" t="n">
-        <v>90705</v>
+        <v>78700</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13242,34 +13247,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5432</v>
+        <v>967</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>380487</v>
+        <v>380350</v>
       </c>
       <c r="R124" t="n">
-        <v>6920278</v>
+        <v>6920123</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13328,10 +13333,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120827462</v>
+        <v>120817582</v>
       </c>
       <c r="B125" t="n">
-        <v>57348</v>
+        <v>74708</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13344,45 +13349,37 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Risåsen, Risåsen, Tännäs, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>380225</v>
+        <v>380239</v>
       </c>
       <c r="R125" t="n">
-        <v>6920029</v>
+        <v>6920211</v>
       </c>
       <c r="S125" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13438,10 +13435,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120817002</v>
+        <v>120817117</v>
       </c>
       <c r="B126" t="n">
-        <v>74705</v>
+        <v>74708</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13478,10 +13475,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>380205</v>
+        <v>380229</v>
       </c>
       <c r="R126" t="n">
-        <v>6920296</v>
+        <v>6920310</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13540,10 +13537,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120819057</v>
+        <v>120817141</v>
       </c>
       <c r="B127" t="n">
-        <v>90652</v>
+        <v>78601</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13552,38 +13549,38 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>380472</v>
+        <v>380229</v>
       </c>
       <c r="R127" t="n">
-        <v>6920251</v>
+        <v>6920310</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13642,10 +13639,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120817256</v>
+        <v>120817498</v>
       </c>
       <c r="B128" t="n">
-        <v>77939</v>
+        <v>74708</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13654,25 +13651,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>498</v>
+        <v>6440</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13682,10 +13679,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>380250</v>
+        <v>380253</v>
       </c>
       <c r="R128" t="n">
-        <v>6920331</v>
+        <v>6920258</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13744,10 +13741,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120819439</v>
+        <v>120818909</v>
       </c>
       <c r="B129" t="n">
-        <v>74705</v>
+        <v>90715</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13760,34 +13757,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>380480</v>
+        <v>380419</v>
       </c>
       <c r="R129" t="n">
-        <v>6920366</v>
+        <v>6920164</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13846,10 +13843,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120817445</v>
+        <v>120819508</v>
       </c>
       <c r="B130" t="n">
-        <v>74705</v>
+        <v>77985</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13862,34 +13859,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>380272</v>
+        <v>380437</v>
       </c>
       <c r="R130" t="n">
-        <v>6920269</v>
+        <v>6920374</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13948,10 +13945,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120819997</v>
+        <v>120818308</v>
       </c>
       <c r="B131" t="n">
-        <v>90705</v>
+        <v>74708</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -13964,21 +13961,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13988,10 +13985,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>380169</v>
+        <v>380298</v>
       </c>
       <c r="R131" t="n">
-        <v>6920084</v>
+        <v>6920123</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14050,10 +14047,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120817582</v>
+        <v>120817440</v>
       </c>
       <c r="B132" t="n">
-        <v>74705</v>
+        <v>77985</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14066,21 +14063,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14090,10 +14087,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>380239</v>
+        <v>380272</v>
       </c>
       <c r="R132" t="n">
-        <v>6920211</v>
+        <v>6920269</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14152,10 +14149,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120818107</v>
+        <v>120818244</v>
       </c>
       <c r="B133" t="n">
-        <v>74705</v>
+        <v>57351</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14168,37 +14165,42 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>380241</v>
+        <v>380276</v>
       </c>
       <c r="R133" t="n">
-        <v>6920149</v>
+        <v>6920119</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14254,10 +14256,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120819676</v>
+        <v>120818856</v>
       </c>
       <c r="B134" t="n">
-        <v>74705</v>
+        <v>77942</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14266,38 +14268,38 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6440</v>
+        <v>498</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>380292</v>
+        <v>380400</v>
       </c>
       <c r="R134" t="n">
-        <v>6920288</v>
+        <v>6920126</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14356,10 +14358,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120817963</v>
+        <v>120817002</v>
       </c>
       <c r="B135" t="n">
-        <v>74705</v>
+        <v>74708</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14396,10 +14398,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>380238</v>
+        <v>380205</v>
       </c>
       <c r="R135" t="n">
-        <v>6920182</v>
+        <v>6920296</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14458,10 +14460,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120817559</v>
+        <v>120817256</v>
       </c>
       <c r="B136" t="n">
-        <v>57348</v>
+        <v>77942</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14470,43 +14472,38 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>380253</v>
+        <v>380250</v>
       </c>
       <c r="R136" t="n">
-        <v>6920258</v>
+        <v>6920331</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14565,10 +14562,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120817433</v>
+        <v>120818044</v>
       </c>
       <c r="B137" t="n">
-        <v>77530</v>
+        <v>74708</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14581,21 +14578,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6487</v>
+        <v>6440</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14605,10 +14602,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>380272</v>
+        <v>380257</v>
       </c>
       <c r="R137" t="n">
-        <v>6920269</v>
+        <v>6920161</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14670,7 +14667,7 @@
         <v>120819496</v>
       </c>
       <c r="B138" t="n">
-        <v>77530</v>
+        <v>77533</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14769,10 +14766,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120817712</v>
+        <v>120818721</v>
       </c>
       <c r="B139" t="n">
-        <v>74705</v>
+        <v>78601</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14785,21 +14782,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14809,10 +14806,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>380212</v>
+        <v>380365</v>
       </c>
       <c r="R139" t="n">
-        <v>6920214</v>
+        <v>6920138</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14871,10 +14868,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120817141</v>
+        <v>120817963</v>
       </c>
       <c r="B140" t="n">
-        <v>78598</v>
+        <v>74708</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -14887,21 +14884,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14911,10 +14908,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>380229</v>
+        <v>380238</v>
       </c>
       <c r="R140" t="n">
-        <v>6920310</v>
+        <v>6920182</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14973,10 +14970,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120818044</v>
+        <v>120827484</v>
       </c>
       <c r="B141" t="n">
-        <v>74705</v>
+        <v>57351</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -14989,37 +14986,45 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Risåsen, Tännäs, Hjd</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>380257</v>
+        <v>380187</v>
       </c>
       <c r="R141" t="n">
-        <v>6920161</v>
+        <v>6920068</v>
       </c>
       <c r="S141" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15075,10 +15080,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>120817298</v>
+        <v>120819137</v>
       </c>
       <c r="B142" t="n">
-        <v>74705</v>
+        <v>90715</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15091,34 +15096,34 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>380275</v>
+        <v>380487</v>
       </c>
       <c r="R142" t="n">
-        <v>6920296</v>
+        <v>6920278</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15177,10 +15182,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>120816914</v>
+        <v>120816961</v>
       </c>
       <c r="B143" t="n">
-        <v>74705</v>
+        <v>90715</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15193,21 +15198,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15217,10 +15222,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>380182</v>
+        <v>380202</v>
       </c>
       <c r="R143" t="n">
-        <v>6920292</v>
+        <v>6920286</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15279,10 +15284,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>120819092</v>
+        <v>120819133</v>
       </c>
       <c r="B144" t="n">
-        <v>57348</v>
+        <v>74708</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15295,42 +15300,37 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>380492</v>
+        <v>380487</v>
       </c>
       <c r="R144" t="n">
-        <v>6920257</v>
+        <v>6920278</v>
       </c>
       <c r="S144" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15386,10 +15386,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>120818244</v>
+        <v>120817559</v>
       </c>
       <c r="B145" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15422,7 +15422,7 @@
       <c r="I145" t="inlineStr"/>
       <c r="M145" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -15431,13 +15431,13 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>380276</v>
+        <v>380253</v>
       </c>
       <c r="R145" t="n">
-        <v>6920119</v>
+        <v>6920258</v>
       </c>
       <c r="S145" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -15493,10 +15493,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>120818973</v>
+        <v>120817433</v>
       </c>
       <c r="B146" t="n">
-        <v>90705</v>
+        <v>77533</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15509,34 +15509,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>5432</v>
+        <v>6487</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>380420</v>
+        <v>380272</v>
       </c>
       <c r="R146" t="n">
-        <v>6920187</v>
+        <v>6920269</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15595,10 +15595,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>120816961</v>
+        <v>120819057</v>
       </c>
       <c r="B147" t="n">
-        <v>90705</v>
+        <v>90662</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15607,38 +15607,38 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>380202</v>
+        <v>380472</v>
       </c>
       <c r="R147" t="n">
-        <v>6920286</v>
+        <v>6920251</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15697,10 +15697,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>120818661</v>
+        <v>120819997</v>
       </c>
       <c r="B148" t="n">
-        <v>78697</v>
+        <v>90715</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15713,21 +15713,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>967</v>
+        <v>5432</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15737,10 +15737,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>380350</v>
+        <v>380169</v>
       </c>
       <c r="R148" t="n">
-        <v>6920123</v>
+        <v>6920084</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15799,10 +15799,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>120818608</v>
+        <v>120818973</v>
       </c>
       <c r="B149" t="n">
-        <v>78598</v>
+        <v>90715</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15815,34 +15815,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>380350</v>
+        <v>380420</v>
       </c>
       <c r="R149" t="n">
-        <v>6920123</v>
+        <v>6920187</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15901,10 +15901,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>120819559</v>
+        <v>120819676</v>
       </c>
       <c r="B150" t="n">
-        <v>74705</v>
+        <v>74708</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -15941,10 +15941,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>380312</v>
+        <v>380292</v>
       </c>
       <c r="R150" t="n">
-        <v>6920269</v>
+        <v>6920288</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16003,10 +16003,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>120818721</v>
+        <v>120817712</v>
       </c>
       <c r="B151" t="n">
-        <v>78598</v>
+        <v>74708</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16019,21 +16019,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16043,10 +16043,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>380365</v>
+        <v>380212</v>
       </c>
       <c r="R151" t="n">
-        <v>6920138</v>
+        <v>6920214</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>

--- a/artfynd/A 32573-2024 artfynd.xlsx
+++ b/artfynd/A 32573-2024 artfynd.xlsx
@@ -14149,10 +14149,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120818244</v>
+        <v>120818856</v>
       </c>
       <c r="B133" t="n">
-        <v>57351</v>
+        <v>77942</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14161,46 +14161,41 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>380276</v>
+        <v>380400</v>
       </c>
       <c r="R133" t="n">
-        <v>6920119</v>
+        <v>6920126</v>
       </c>
       <c r="S133" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14256,10 +14251,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120818856</v>
+        <v>120818244</v>
       </c>
       <c r="B134" t="n">
-        <v>77942</v>
+        <v>57351</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14268,41 +14263,46 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>498</v>
+        <v>100109</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>380400</v>
+        <v>380276</v>
       </c>
       <c r="R134" t="n">
-        <v>6920126</v>
+        <v>6920119</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15386,10 +15386,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>120817559</v>
+        <v>120817433</v>
       </c>
       <c r="B145" t="n">
-        <v>57351</v>
+        <v>77533</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15402,39 +15402,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>380253</v>
+        <v>380272</v>
       </c>
       <c r="R145" t="n">
-        <v>6920258</v>
+        <v>6920269</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15493,10 +15488,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>120817433</v>
+        <v>120817559</v>
       </c>
       <c r="B146" t="n">
-        <v>77533</v>
+        <v>57351</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15509,34 +15504,39 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6487</v>
+        <v>100109</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>380272</v>
+        <v>380253</v>
       </c>
       <c r="R146" t="n">
-        <v>6920269</v>
+        <v>6920258</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>

--- a/artfynd/A 32573-2024 artfynd.xlsx
+++ b/artfynd/A 32573-2024 artfynd.xlsx
@@ -3957,11 +3957,11 @@
         <v>119314931</v>
       </c>
       <c r="B34" t="n">
-        <v>57326</v>
+        <v>57494</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">

--- a/artfynd/A 32573-2024 artfynd.xlsx
+++ b/artfynd/A 32573-2024 artfynd.xlsx
@@ -3957,7 +3957,7 @@
         <v>119314931</v>
       </c>
       <c r="B34" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>

--- a/artfynd/A 32573-2024 artfynd.xlsx
+++ b/artfynd/A 32573-2024 artfynd.xlsx
@@ -3957,7 +3957,7 @@
         <v>119314931</v>
       </c>
       <c r="B34" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>

--- a/artfynd/A 32573-2024 artfynd.xlsx
+++ b/artfynd/A 32573-2024 artfynd.xlsx
@@ -16105,10 +16105,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>124464047</v>
+        <v>124464970</v>
       </c>
       <c r="B152" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16121,37 +16121,42 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>380267</v>
+        <v>380255</v>
       </c>
       <c r="R152" t="n">
-        <v>6919731</v>
+        <v>6919561</v>
       </c>
       <c r="S152" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16207,10 +16212,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>124467947</v>
+        <v>124471016</v>
       </c>
       <c r="B153" t="n">
-        <v>78194</v>
+        <v>57513</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16223,34 +16228,39 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>380361</v>
+        <v>380506</v>
       </c>
       <c r="R153" t="n">
-        <v>6919740</v>
+        <v>6920061</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16283,11 +16293,6 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16314,10 +16319,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>124470184</v>
+        <v>124465863</v>
       </c>
       <c r="B154" t="n">
-        <v>91030</v>
+        <v>78151</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16326,38 +16331,38 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>5432</v>
+        <v>498</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>380516</v>
+        <v>380296</v>
       </c>
       <c r="R154" t="n">
-        <v>6920004</v>
+        <v>6919585</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16416,10 +16421,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>124452423</v>
+        <v>124457866</v>
       </c>
       <c r="B155" t="n">
-        <v>56725</v>
+        <v>78151</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16428,43 +16433,38 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>102613</v>
+        <v>498</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>380227</v>
+        <v>380537</v>
       </c>
       <c r="R155" t="n">
-        <v>6920340</v>
+        <v>6920199</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16511,22 +16511,22 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>124466494</v>
+        <v>124454979</v>
       </c>
       <c r="B156" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16539,42 +16539,37 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>380344</v>
+        <v>380289</v>
       </c>
       <c r="R156" t="n">
-        <v>6919654</v>
+        <v>6920290</v>
       </c>
       <c r="S156" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -16604,6 +16599,11 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16618,22 +16618,22 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>124464121</v>
+        <v>124450578</v>
       </c>
       <c r="B157" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16646,39 +16646,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>380419</v>
+        <v>380227</v>
       </c>
       <c r="R157" t="n">
-        <v>6919960</v>
+        <v>6920340</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16737,10 +16732,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>124457866</v>
+        <v>124452423</v>
       </c>
       <c r="B158" t="n">
-        <v>78151</v>
+        <v>56725</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16749,38 +16744,43 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>498</v>
+        <v>102613</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>380537</v>
+        <v>380227</v>
       </c>
       <c r="R158" t="n">
-        <v>6920199</v>
+        <v>6920340</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16827,22 +16827,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>124450737</v>
+        <v>124466302</v>
       </c>
       <c r="B159" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16855,37 +16855,42 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>380210</v>
+        <v>380345</v>
       </c>
       <c r="R159" t="n">
-        <v>6920378</v>
+        <v>6919632</v>
       </c>
       <c r="S159" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -16941,10 +16946,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>124470397</v>
+        <v>124450845</v>
       </c>
       <c r="B160" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -16957,34 +16962,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>380506</v>
+        <v>380205</v>
       </c>
       <c r="R160" t="n">
-        <v>6920061</v>
+        <v>6920378</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17031,22 +17036,22 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>124451172</v>
+        <v>124470404</v>
       </c>
       <c r="B161" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17059,34 +17064,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>380184</v>
+        <v>380471</v>
       </c>
       <c r="R161" t="n">
-        <v>6920434</v>
+        <v>6920069</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17145,10 +17150,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>124452261</v>
+        <v>124464121</v>
       </c>
       <c r="B162" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17161,34 +17166,39 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>380227</v>
+        <v>380419</v>
       </c>
       <c r="R162" t="n">
-        <v>6920340</v>
+        <v>6919960</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17247,10 +17257,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>124470732</v>
+        <v>124451984</v>
       </c>
       <c r="B163" t="n">
-        <v>74901</v>
+        <v>79399</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17263,34 +17273,34 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>380372</v>
+        <v>380203</v>
       </c>
       <c r="R163" t="n">
-        <v>6920042</v>
+        <v>6920482</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17349,10 +17359,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>124464471</v>
+        <v>124464466</v>
       </c>
       <c r="B164" t="n">
-        <v>78194</v>
+        <v>78905</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17365,21 +17375,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6437</v>
+        <v>967</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17451,10 +17461,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>124451574</v>
+        <v>124457601</v>
       </c>
       <c r="B165" t="n">
-        <v>79428</v>
+        <v>78151</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17463,38 +17473,38 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6453</v>
+        <v>498</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>380184</v>
+        <v>380544</v>
       </c>
       <c r="R165" t="n">
-        <v>6920434</v>
+        <v>6920188</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17553,10 +17563,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>124470555</v>
+        <v>124460965</v>
       </c>
       <c r="B166" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17569,34 +17579,34 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>380431</v>
+        <v>380307</v>
       </c>
       <c r="R166" t="n">
-        <v>6920068</v>
+        <v>6919967</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17655,10 +17665,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>124471016</v>
+        <v>124463640</v>
       </c>
       <c r="B167" t="n">
-        <v>57513</v>
+        <v>79428</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17671,39 +17681,34 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>380506</v>
+        <v>380218</v>
       </c>
       <c r="R167" t="n">
-        <v>6920061</v>
+        <v>6919722</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17750,12 +17755,12 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
@@ -17864,10 +17869,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>124451837</v>
+        <v>124455206</v>
       </c>
       <c r="B169" t="n">
-        <v>78194</v>
+        <v>91030</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -17880,21 +17885,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6437</v>
+        <v>5432</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17904,10 +17909,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>380197</v>
+        <v>380311</v>
       </c>
       <c r="R169" t="n">
-        <v>6920479</v>
+        <v>6920231</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17966,10 +17971,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>124468547</v>
+        <v>124470555</v>
       </c>
       <c r="B170" t="n">
-        <v>74901</v>
+        <v>82597</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -17982,34 +17987,34 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>380356</v>
+        <v>380431</v>
       </c>
       <c r="R170" t="n">
-        <v>6919817</v>
+        <v>6920068</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18068,10 +18073,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>124450518</v>
+        <v>124454876</v>
       </c>
       <c r="B171" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18084,34 +18089,34 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>380202</v>
+        <v>380290</v>
       </c>
       <c r="R171" t="n">
-        <v>6920332</v>
+        <v>6920272</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18170,10 +18175,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>124456697</v>
+        <v>124464047</v>
       </c>
       <c r="B172" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18186,21 +18191,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18210,10 +18215,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>380443</v>
+        <v>380267</v>
       </c>
       <c r="R172" t="n">
-        <v>6920118</v>
+        <v>6919731</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18272,10 +18277,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>124460224</v>
+        <v>124470598</v>
       </c>
       <c r="B173" t="n">
-        <v>57513</v>
+        <v>79428</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18288,39 +18293,34 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P173" t="inlineStr">
         <is>
           <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>380374</v>
+        <v>380506</v>
       </c>
       <c r="R173" t="n">
-        <v>6919982</v>
+        <v>6920061</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18353,6 +18353,11 @@
       <c r="AA173" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18379,10 +18384,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>124459048</v>
+        <v>124458743</v>
       </c>
       <c r="B174" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18395,29 +18400,24 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P174" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
@@ -18460,6 +18460,11 @@
       <c r="AA174" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18486,10 +18491,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>124459456</v>
+        <v>124455220</v>
       </c>
       <c r="B175" t="n">
-        <v>91032</v>
+        <v>74901</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -18502,34 +18507,34 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>5442</v>
+        <v>6440</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>380561</v>
+        <v>380311</v>
       </c>
       <c r="R175" t="n">
-        <v>6919930</v>
+        <v>6920231</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18576,22 +18581,22 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>124450666</v>
+        <v>124470299</v>
       </c>
       <c r="B176" t="n">
-        <v>74901</v>
+        <v>56722</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -18600,38 +18605,43 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6440</v>
+        <v>100138</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>380227</v>
+        <v>380495</v>
       </c>
       <c r="R176" t="n">
-        <v>6920340</v>
+        <v>6920029</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18678,22 +18688,22 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>124469915</v>
+        <v>124457605</v>
       </c>
       <c r="B177" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -18706,34 +18716,39 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>380521</v>
+        <v>380542</v>
       </c>
       <c r="R177" t="n">
-        <v>6919962</v>
+        <v>6920184</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18768,6 +18783,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området.</t>
+        </is>
+      </c>
       <c r="AD177" t="b">
         <v>0</v>
       </c>
@@ -18780,22 +18800,22 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>124464681</v>
+        <v>124458282</v>
       </c>
       <c r="B178" t="n">
-        <v>79399</v>
+        <v>78151</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -18804,25 +18824,25 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>229821</v>
+        <v>498</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18832,10 +18852,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>380264</v>
+        <v>380588</v>
       </c>
       <c r="R178" t="n">
-        <v>6919665</v>
+        <v>6920110</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18894,10 +18914,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>124468916</v>
+        <v>124467914</v>
       </c>
       <c r="B179" t="n">
-        <v>78151</v>
+        <v>77738</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -18906,38 +18926,38 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>498</v>
+        <v>6487</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>380343</v>
+        <v>380361</v>
       </c>
       <c r="R179" t="n">
-        <v>6919896</v>
+        <v>6919740</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18972,6 +18992,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD179" t="b">
         <v>0</v>
       </c>
@@ -18984,22 +19009,22 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>124460951</v>
+        <v>124465167</v>
       </c>
       <c r="B180" t="n">
-        <v>74901</v>
+        <v>78194</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -19012,34 +19037,34 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>380307</v>
+        <v>380244</v>
       </c>
       <c r="R180" t="n">
-        <v>6919967</v>
+        <v>6919577</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19086,22 +19111,22 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>124452491</v>
+        <v>124459134</v>
       </c>
       <c r="B181" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -19114,34 +19139,34 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>380208</v>
+        <v>380559</v>
       </c>
       <c r="R181" t="n">
-        <v>6920481</v>
+        <v>6919947</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19200,10 +19225,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124458651</v>
+        <v>124470146</v>
       </c>
       <c r="B182" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -19216,37 +19241,42 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>380569</v>
+        <v>380527</v>
       </c>
       <c r="R182" t="n">
-        <v>6920058</v>
+        <v>6919988</v>
       </c>
       <c r="S182" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -19409,10 +19439,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124464292</v>
+        <v>124464651</v>
       </c>
       <c r="B184" t="n">
-        <v>57513</v>
+        <v>79399</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -19425,39 +19455,34 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P184" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>380275</v>
+        <v>380251</v>
       </c>
       <c r="R184" t="n">
-        <v>6919775</v>
+        <v>6919658</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19504,19 +19529,19 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124454876</v>
+        <v>124456372</v>
       </c>
       <c r="B185" t="n">
         <v>74901</v>
@@ -19552,14 +19577,14 @@
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>380290</v>
+        <v>380368</v>
       </c>
       <c r="R185" t="n">
-        <v>6920272</v>
+        <v>6920107</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19618,7 +19643,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124458046</v>
+        <v>124470732</v>
       </c>
       <c r="B186" t="n">
         <v>74901</v>
@@ -19654,14 +19679,14 @@
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>380533</v>
+        <v>380372</v>
       </c>
       <c r="R186" t="n">
-        <v>6920142</v>
+        <v>6920042</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19720,10 +19745,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124455220</v>
+        <v>124452261</v>
       </c>
       <c r="B187" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -19736,21 +19761,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19760,10 +19785,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>380311</v>
+        <v>380227</v>
       </c>
       <c r="R187" t="n">
-        <v>6920231</v>
+        <v>6920340</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19810,22 +19835,22 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124470485</v>
+        <v>124451885</v>
       </c>
       <c r="B188" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -19838,34 +19863,34 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>380446</v>
+        <v>380189</v>
       </c>
       <c r="R188" t="n">
-        <v>6920059</v>
+        <v>6920488</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19924,10 +19949,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124452627</v>
+        <v>124456046</v>
       </c>
       <c r="B189" t="n">
-        <v>74901</v>
+        <v>91032</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -19940,21 +19965,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6440</v>
+        <v>5442</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19964,10 +19989,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>380217</v>
+        <v>380326</v>
       </c>
       <c r="R189" t="n">
-        <v>6920440</v>
+        <v>6920218</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20002,6 +20027,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området.</t>
+        </is>
+      </c>
       <c r="AD189" t="b">
         <v>0</v>
       </c>
@@ -20014,22 +20044,22 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>124456502</v>
+        <v>124450300</v>
       </c>
       <c r="B190" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20042,34 +20072,34 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>380385</v>
+        <v>380182</v>
       </c>
       <c r="R190" t="n">
-        <v>6920091</v>
+        <v>6920316</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20104,11 +20134,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området.</t>
-        </is>
-      </c>
       <c r="AD190" t="b">
         <v>0</v>
       </c>
@@ -20121,19 +20146,19 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>124464842</v>
+        <v>124460258</v>
       </c>
       <c r="B191" t="n">
         <v>79428</v>
@@ -20169,14 +20194,14 @@
       <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>380237</v>
+        <v>380365</v>
       </c>
       <c r="R191" t="n">
-        <v>6919621</v>
+        <v>6919996</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20235,10 +20260,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>124465526</v>
+        <v>124469907</v>
       </c>
       <c r="B192" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20251,34 +20276,34 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Risåsvallen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>380252</v>
+        <v>380452</v>
       </c>
       <c r="R192" t="n">
-        <v>6919535</v>
+        <v>6919913</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20325,19 +20350,19 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>124468302</v>
+        <v>124456676</v>
       </c>
       <c r="B193" t="n">
         <v>57513</v>
@@ -20382,10 +20407,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>380265</v>
+        <v>380434</v>
       </c>
       <c r="R193" t="n">
-        <v>6919774</v>
+        <v>6920123</v>
       </c>
       <c r="S193" t="n">
         <v>15</v>
@@ -20444,10 +20469,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>124470146</v>
+        <v>124466026</v>
       </c>
       <c r="B194" t="n">
-        <v>57513</v>
+        <v>79399</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -20460,42 +20485,37 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P194" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>380527</v>
+        <v>380303</v>
       </c>
       <c r="R194" t="n">
-        <v>6919988</v>
+        <v>6919598</v>
       </c>
       <c r="S194" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -20525,6 +20545,11 @@
       <c r="AA194" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20539,22 +20564,22 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>124457601</v>
+        <v>124455776</v>
       </c>
       <c r="B195" t="n">
-        <v>78151</v>
+        <v>57513</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -20563,38 +20588,43 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>498</v>
+        <v>100109</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>380544</v>
+        <v>380326</v>
       </c>
       <c r="R195" t="n">
-        <v>6920188</v>
+        <v>6920218</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20641,22 +20671,22 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>124459042</v>
+        <v>124470806</v>
       </c>
       <c r="B196" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -20669,37 +20699,42 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>380571</v>
+        <v>380340</v>
       </c>
       <c r="R196" t="n">
-        <v>6919993</v>
+        <v>6920036</v>
       </c>
       <c r="S196" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -20755,10 +20790,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>124463640</v>
+        <v>124470070</v>
       </c>
       <c r="B197" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -20771,21 +20806,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20795,10 +20830,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>380218</v>
+        <v>380533</v>
       </c>
       <c r="R197" t="n">
-        <v>6919722</v>
+        <v>6919979</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20857,10 +20892,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>124457836</v>
+        <v>124459456</v>
       </c>
       <c r="B198" t="n">
-        <v>78810</v>
+        <v>91032</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -20873,34 +20908,34 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>380542</v>
+        <v>380561</v>
       </c>
       <c r="R198" t="n">
-        <v>6920184</v>
+        <v>6919930</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20959,10 +20994,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>124460258</v>
+        <v>124470397</v>
       </c>
       <c r="B199" t="n">
-        <v>79428</v>
+        <v>74901</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -20975,34 +21010,34 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>380365</v>
+        <v>380506</v>
       </c>
       <c r="R199" t="n">
-        <v>6919996</v>
+        <v>6920061</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21049,22 +21084,22 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>124464901</v>
+        <v>124458651</v>
       </c>
       <c r="B200" t="n">
-        <v>79399</v>
+        <v>91030</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -21077,21 +21112,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>229821</v>
+        <v>5432</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -21101,10 +21136,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>380249</v>
+        <v>380569</v>
       </c>
       <c r="R200" t="n">
-        <v>6919607</v>
+        <v>6920058</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21163,10 +21198,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>124464466</v>
+        <v>124468547</v>
       </c>
       <c r="B201" t="n">
-        <v>78905</v>
+        <v>74901</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -21179,34 +21214,34 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>967</v>
+        <v>6440</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>380243</v>
+        <v>380356</v>
       </c>
       <c r="R201" t="n">
-        <v>6919687</v>
+        <v>6919817</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21265,10 +21300,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>124469547</v>
+        <v>124451802</v>
       </c>
       <c r="B202" t="n">
-        <v>88359</v>
+        <v>79428</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -21281,34 +21316,34 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>510</v>
+        <v>6453</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>380452</v>
+        <v>380197</v>
       </c>
       <c r="R202" t="n">
-        <v>6919913</v>
+        <v>6920479</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21355,22 +21390,22 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>124456676</v>
+        <v>124464842</v>
       </c>
       <c r="B203" t="n">
-        <v>57513</v>
+        <v>79428</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -21383,42 +21418,37 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P203" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>380434</v>
+        <v>380237</v>
       </c>
       <c r="R203" t="n">
-        <v>6920123</v>
+        <v>6919621</v>
       </c>
       <c r="S203" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -21474,10 +21504,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>124466026</v>
+        <v>124470184</v>
       </c>
       <c r="B204" t="n">
-        <v>79399</v>
+        <v>91030</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -21490,21 +21520,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>229821</v>
+        <v>5432</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -21514,10 +21544,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>380303</v>
+        <v>380516</v>
       </c>
       <c r="R204" t="n">
-        <v>6919598</v>
+        <v>6920004</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21552,11 +21582,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD204" t="b">
         <v>0</v>
       </c>
@@ -21569,22 +21594,22 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>124456372</v>
+        <v>124456129</v>
       </c>
       <c r="B205" t="n">
-        <v>74901</v>
+        <v>78905</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -21597,34 +21622,34 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6440</v>
+        <v>967</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>380368</v>
+        <v>380326</v>
       </c>
       <c r="R205" t="n">
-        <v>6920107</v>
+        <v>6920218</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21671,22 +21696,22 @@
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>124469751</v>
+        <v>124464681</v>
       </c>
       <c r="B206" t="n">
-        <v>74901</v>
+        <v>79399</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -21699,34 +21724,34 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>380490</v>
+        <v>380264</v>
       </c>
       <c r="R206" t="n">
-        <v>6919937</v>
+        <v>6919665</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21785,10 +21810,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>124470070</v>
+        <v>124461477</v>
       </c>
       <c r="B207" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -21801,34 +21826,34 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>380533</v>
+        <v>380285</v>
       </c>
       <c r="R207" t="n">
-        <v>6919979</v>
+        <v>6919895</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21887,10 +21912,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>124470737</v>
+        <v>124450518</v>
       </c>
       <c r="B208" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -21903,34 +21928,34 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>380506</v>
+        <v>380202</v>
       </c>
       <c r="R208" t="n">
-        <v>6920061</v>
+        <v>6920332</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21977,19 +22002,19 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>124458282</v>
+        <v>124458172</v>
       </c>
       <c r="B209" t="n">
         <v>78151</v>
@@ -22029,10 +22054,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>380588</v>
+        <v>380562</v>
       </c>
       <c r="R209" t="n">
-        <v>6920110</v>
+        <v>6920118</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -22091,10 +22116,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>124465863</v>
+        <v>124459815</v>
       </c>
       <c r="B210" t="n">
-        <v>78151</v>
+        <v>79428</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -22103,38 +22128,38 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>498</v>
+        <v>6453</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Risåsvallen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>380296</v>
+        <v>380445</v>
       </c>
       <c r="R210" t="n">
-        <v>6919585</v>
+        <v>6919917</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22193,7 +22218,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>124458476</v>
+        <v>124461736</v>
       </c>
       <c r="B211" t="n">
         <v>74901</v>
@@ -22233,10 +22258,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>380581</v>
+        <v>380232</v>
       </c>
       <c r="R211" t="n">
-        <v>6920056</v>
+        <v>6919808</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22295,10 +22320,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>124451893</v>
+        <v>124450666</v>
       </c>
       <c r="B212" t="n">
-        <v>5196</v>
+        <v>74901</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -22307,25 +22332,25 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>105930</v>
+        <v>6440</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -22397,10 +22422,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>124451984</v>
+        <v>124450415</v>
       </c>
       <c r="B213" t="n">
-        <v>79399</v>
+        <v>74901</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -22413,34 +22438,34 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>380203</v>
+        <v>380202</v>
       </c>
       <c r="R213" t="n">
-        <v>6920482</v>
+        <v>6920332</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22499,10 +22524,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>124464493</v>
+        <v>124464329</v>
       </c>
       <c r="B214" t="n">
-        <v>79399</v>
+        <v>78194</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -22515,21 +22540,21 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -22539,10 +22564,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>380243</v>
+        <v>380268</v>
       </c>
       <c r="R214" t="n">
-        <v>6919687</v>
+        <v>6919685</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22601,10 +22626,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>124464559</v>
+        <v>124470742</v>
       </c>
       <c r="B215" t="n">
-        <v>79399</v>
+        <v>57513</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -22617,37 +22642,42 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>380236</v>
+        <v>380369</v>
       </c>
       <c r="R215" t="n">
-        <v>6919671</v>
+        <v>6920032</v>
       </c>
       <c r="S215" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -22703,10 +22733,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>124465009</v>
+        <v>124459287</v>
       </c>
       <c r="B216" t="n">
-        <v>79399</v>
+        <v>57513</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -22719,34 +22749,39 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>380267</v>
+        <v>380561</v>
       </c>
       <c r="R216" t="n">
-        <v>6919764</v>
+        <v>6919930</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22779,11 +22814,6 @@
       <c r="AA216" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC216" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -22810,10 +22840,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>124454979</v>
+        <v>124458357</v>
       </c>
       <c r="B217" t="n">
-        <v>91030</v>
+        <v>57666</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -22826,37 +22856,42 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>380289</v>
+        <v>380586</v>
       </c>
       <c r="R217" t="n">
-        <v>6920290</v>
+        <v>6920100</v>
       </c>
       <c r="S217" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -22886,11 +22921,6 @@
       <c r="AA217" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC217" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -22905,19 +22935,19 @@
       <c r="AT217" t="inlineStr"/>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>124455206</v>
+        <v>124456697</v>
       </c>
       <c r="B218" t="n">
         <v>91030</v>
@@ -22953,14 +22983,14 @@
       <c r="I218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>380311</v>
+        <v>380443</v>
       </c>
       <c r="R218" t="n">
-        <v>6920231</v>
+        <v>6920118</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23019,10 +23049,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>124454665</v>
+        <v>124456704</v>
       </c>
       <c r="B219" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -23035,34 +23065,34 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>380258</v>
+        <v>380385</v>
       </c>
       <c r="R219" t="n">
-        <v>6920309</v>
+        <v>6920091</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23097,6 +23127,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD219" t="b">
         <v>0</v>
       </c>
@@ -23109,22 +23144,22 @@
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>124455022</v>
+        <v>124464471</v>
       </c>
       <c r="B220" t="n">
-        <v>79428</v>
+        <v>78194</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -23137,34 +23172,34 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>380292</v>
+        <v>380243</v>
       </c>
       <c r="R220" t="n">
-        <v>6920288</v>
+        <v>6919687</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23325,7 +23360,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>124455774</v>
+        <v>124454665</v>
       </c>
       <c r="B222" t="n">
         <v>74901</v>
@@ -23361,14 +23396,14 @@
       <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>380356</v>
+        <v>380258</v>
       </c>
       <c r="R222" t="n">
-        <v>6920172</v>
+        <v>6920309</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23427,10 +23462,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>124450415</v>
+        <v>124460611</v>
       </c>
       <c r="B223" t="n">
-        <v>74901</v>
+        <v>78905</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -23443,34 +23478,34 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6440</v>
+        <v>967</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>380202</v>
+        <v>380335</v>
       </c>
       <c r="R223" t="n">
-        <v>6920332</v>
+        <v>6920000</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23517,22 +23552,22 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>124459134</v>
+        <v>124470695</v>
       </c>
       <c r="B224" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -23545,21 +23580,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -23569,10 +23604,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>380559</v>
+        <v>380506</v>
       </c>
       <c r="R224" t="n">
-        <v>6919947</v>
+        <v>6920061</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23607,6 +23642,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD224" t="b">
         <v>0</v>
       </c>
@@ -23619,22 +23659,22 @@
       <c r="AT224" t="inlineStr"/>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>124450902</v>
+        <v>124470485</v>
       </c>
       <c r="B225" t="n">
-        <v>57529</v>
+        <v>74901</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -23647,39 +23687,34 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
-      <c r="M225" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>380227</v>
+        <v>380446</v>
       </c>
       <c r="R225" t="n">
-        <v>6920340</v>
+        <v>6920059</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23714,11 +23749,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC225" t="inlineStr">
-        <is>
-          <t>Troligen spillkråka.</t>
-        </is>
-      </c>
       <c r="AD225" t="b">
         <v>0</v>
       </c>
@@ -23731,22 +23761,22 @@
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>124470404</v>
+        <v>124458046</v>
       </c>
       <c r="B226" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -23759,21 +23789,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -23783,10 +23813,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>380471</v>
+        <v>380533</v>
       </c>
       <c r="R226" t="n">
-        <v>6920069</v>
+        <v>6920142</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23845,7 +23875,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>124461646</v>
+        <v>124468302</v>
       </c>
       <c r="B227" t="n">
         <v>57513</v>
@@ -23890,10 +23920,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>380239</v>
+        <v>380265</v>
       </c>
       <c r="R227" t="n">
-        <v>6919828</v>
+        <v>6919774</v>
       </c>
       <c r="S227" t="n">
         <v>15</v>
@@ -23952,10 +23982,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>124464970</v>
+        <v>124465009</v>
       </c>
       <c r="B228" t="n">
-        <v>57513</v>
+        <v>79399</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -23968,42 +23998,37 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>380255</v>
+        <v>380267</v>
       </c>
       <c r="R228" t="n">
-        <v>6919561</v>
+        <v>6919764</v>
       </c>
       <c r="S228" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -24033,6 +24058,11 @@
       <c r="AA228" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC228" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -24047,22 +24077,22 @@
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>124468469</v>
+        <v>124464901</v>
       </c>
       <c r="B229" t="n">
-        <v>57513</v>
+        <v>79399</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -24075,42 +24105,37 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P229" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>380324</v>
+        <v>380249</v>
       </c>
       <c r="R229" t="n">
-        <v>6919803</v>
+        <v>6919607</v>
       </c>
       <c r="S229" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T229" t="inlineStr">
         <is>
@@ -24166,10 +24191,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>124459815</v>
+        <v>124451569</v>
       </c>
       <c r="B230" t="n">
-        <v>79428</v>
+        <v>79399</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -24182,21 +24207,21 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -24206,10 +24231,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>380445</v>
+        <v>380184</v>
       </c>
       <c r="R230" t="n">
-        <v>6919917</v>
+        <v>6920434</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24268,10 +24293,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>124450300</v>
+        <v>124463365</v>
       </c>
       <c r="B231" t="n">
-        <v>74901</v>
+        <v>79399</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -24284,21 +24309,21 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -24308,10 +24333,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>380182</v>
+        <v>380199</v>
       </c>
       <c r="R231" t="n">
-        <v>6920316</v>
+        <v>6919723</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24370,10 +24395,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>124464321</v>
+        <v>124468916</v>
       </c>
       <c r="B232" t="n">
-        <v>77738</v>
+        <v>78151</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -24382,38 +24407,38 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>6487</v>
+        <v>498</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>380268</v>
+        <v>380343</v>
       </c>
       <c r="R232" t="n">
-        <v>6919685</v>
+        <v>6919896</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24472,7 +24497,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>124451885</v>
+        <v>124470646</v>
       </c>
       <c r="B233" t="n">
         <v>91030</v>
@@ -24508,14 +24533,14 @@
       <c r="I233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>380189</v>
+        <v>380402</v>
       </c>
       <c r="R233" t="n">
-        <v>6920488</v>
+        <v>6920044</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -24574,10 +24599,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>124456704</v>
+        <v>124452491</v>
       </c>
       <c r="B234" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -24590,21 +24615,21 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -24614,10 +24639,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>380385</v>
+        <v>380208</v>
       </c>
       <c r="R234" t="n">
-        <v>6920091</v>
+        <v>6920481</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -24652,11 +24677,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC234" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
-        </is>
-      </c>
       <c r="AD234" t="b">
         <v>0</v>
       </c>
@@ -24669,22 +24689,22 @@
       <c r="AT234" t="inlineStr"/>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>124461477</v>
+        <v>124457836</v>
       </c>
       <c r="B235" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -24697,34 +24717,34 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>380285</v>
+        <v>380542</v>
       </c>
       <c r="R235" t="n">
-        <v>6919895</v>
+        <v>6920184</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -24771,22 +24791,22 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>124458172</v>
+        <v>124467947</v>
       </c>
       <c r="B236" t="n">
-        <v>78151</v>
+        <v>78194</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -24795,25 +24815,25 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>498</v>
+        <v>6437</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -24823,10 +24843,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>380562</v>
+        <v>380361</v>
       </c>
       <c r="R236" t="n">
-        <v>6920118</v>
+        <v>6919740</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24861,6 +24881,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC236" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD236" t="b">
         <v>0</v>
       </c>
@@ -24873,22 +24898,22 @@
       <c r="AT236" t="inlineStr"/>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>124460611</v>
+        <v>124464292</v>
       </c>
       <c r="B237" t="n">
-        <v>78905</v>
+        <v>57513</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -24901,34 +24926,39 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>967</v>
+        <v>100109</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>380335</v>
+        <v>380275</v>
       </c>
       <c r="R237" t="n">
-        <v>6920000</v>
+        <v>6919775</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -24987,10 +25017,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>124460965</v>
+        <v>124458476</v>
       </c>
       <c r="B238" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -25003,34 +25033,34 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>380307</v>
+        <v>380581</v>
       </c>
       <c r="R238" t="n">
-        <v>6919967</v>
+        <v>6920056</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -25089,10 +25119,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>124465167</v>
+        <v>124456502</v>
       </c>
       <c r="B239" t="n">
-        <v>78194</v>
+        <v>78810</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -25105,34 +25135,34 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>380244</v>
+        <v>380385</v>
       </c>
       <c r="R239" t="n">
-        <v>6919577</v>
+        <v>6920091</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -25165,6 +25195,11 @@
       <c r="AA239" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC239" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -25191,10 +25226,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>124456046</v>
+        <v>124461108</v>
       </c>
       <c r="B240" t="n">
-        <v>91032</v>
+        <v>74901</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -25207,21 +25242,21 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>5442</v>
+        <v>6440</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -25231,10 +25266,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>380326</v>
+        <v>380308</v>
       </c>
       <c r="R240" t="n">
-        <v>6920218</v>
+        <v>6919925</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -25271,7 +25306,7 @@
       </c>
       <c r="AC240" t="inlineStr">
         <is>
-          <t>Miljöbilder för området.</t>
+          <t>På basen avsågad gran. Grov stubbe</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -25286,12 +25321,12 @@
       <c r="AT240" t="inlineStr"/>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
@@ -25400,10 +25435,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>124469907</v>
+        <v>124468469</v>
       </c>
       <c r="B242" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -25416,37 +25451,42 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>380452</v>
+        <v>380324</v>
       </c>
       <c r="R242" t="n">
-        <v>6919913</v>
+        <v>6919803</v>
       </c>
       <c r="S242" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -25490,22 +25530,22 @@
       <c r="AT242" t="inlineStr"/>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>124451569</v>
+        <v>124470707</v>
       </c>
       <c r="B243" t="n">
-        <v>79399</v>
+        <v>57513</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -25518,37 +25558,42 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>380184</v>
+        <v>380367</v>
       </c>
       <c r="R243" t="n">
-        <v>6920434</v>
+        <v>6920058</v>
       </c>
       <c r="S243" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -25604,10 +25649,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>124470742</v>
+        <v>124464493</v>
       </c>
       <c r="B244" t="n">
-        <v>57513</v>
+        <v>79399</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -25620,42 +25665,37 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
-      <c r="M244" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>380369</v>
+        <v>380243</v>
       </c>
       <c r="R244" t="n">
-        <v>6920032</v>
+        <v>6919687</v>
       </c>
       <c r="S244" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
@@ -25711,10 +25751,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>124455456</v>
+        <v>124464559</v>
       </c>
       <c r="B245" t="n">
-        <v>74901</v>
+        <v>79399</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -25727,34 +25767,34 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
       <c r="P245" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>380314</v>
+        <v>380236</v>
       </c>
       <c r="R245" t="n">
-        <v>6920201</v>
+        <v>6919671</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25813,10 +25853,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>124467914</v>
+        <v>124465389</v>
       </c>
       <c r="B246" t="n">
-        <v>77738</v>
+        <v>79399</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -25829,21 +25869,21 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -25853,10 +25893,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>380361</v>
+        <v>380244</v>
       </c>
       <c r="R246" t="n">
-        <v>6919740</v>
+        <v>6919577</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25889,11 +25929,6 @@
       <c r="AA246" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC246" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -25920,10 +25955,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>124470299</v>
+        <v>124465526</v>
       </c>
       <c r="B247" t="n">
-        <v>56722</v>
+        <v>79399</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -25932,43 +25967,38 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
-      <c r="M247" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>380495</v>
+        <v>380252</v>
       </c>
       <c r="R247" t="n">
-        <v>6920029</v>
+        <v>6919535</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -26027,10 +26057,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>124470707</v>
+        <v>124469547</v>
       </c>
       <c r="B248" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -26043,42 +26073,37 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
-      <c r="M248" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P248" t="inlineStr">
         <is>
           <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>380367</v>
+        <v>380452</v>
       </c>
       <c r="R248" t="n">
-        <v>6920058</v>
+        <v>6919913</v>
       </c>
       <c r="S248" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T248" t="inlineStr">
         <is>
@@ -26122,22 +26147,22 @@
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>124459060</v>
+        <v>124470234</v>
       </c>
       <c r="B249" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -26150,39 +26175,34 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
-      <c r="M249" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P249" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>380571</v>
+        <v>380506</v>
       </c>
       <c r="R249" t="n">
-        <v>6919993</v>
+        <v>6920009</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -26241,10 +26261,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>124463365</v>
+        <v>124460224</v>
       </c>
       <c r="B250" t="n">
-        <v>79399</v>
+        <v>57513</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -26257,34 +26277,39 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>380199</v>
+        <v>380374</v>
       </c>
       <c r="R250" t="n">
-        <v>6919723</v>
+        <v>6919982</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -26331,22 +26356,22 @@
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>124470646</v>
+        <v>124466494</v>
       </c>
       <c r="B251" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -26359,37 +26384,42 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P251" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>380402</v>
+        <v>380344</v>
       </c>
       <c r="R251" t="n">
-        <v>6920044</v>
+        <v>6919654</v>
       </c>
       <c r="S251" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T251" t="inlineStr">
         <is>
@@ -26445,10 +26475,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>124458357</v>
+        <v>124459060</v>
       </c>
       <c r="B252" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -26461,27 +26491,27 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
       <c r="M252" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P252" t="inlineStr">
@@ -26490,13 +26520,13 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>380586</v>
+        <v>380571</v>
       </c>
       <c r="R252" t="n">
-        <v>6920100</v>
+        <v>6919993</v>
       </c>
       <c r="S252" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T252" t="inlineStr">
         <is>
@@ -26552,10 +26582,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>124463210</v>
+        <v>124455096</v>
       </c>
       <c r="B253" t="n">
-        <v>79428</v>
+        <v>5196</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -26564,38 +26594,43 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>6453</v>
+        <v>105930</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>380189</v>
+        <v>380323</v>
       </c>
       <c r="R253" t="n">
-        <v>6919766</v>
+        <v>6920260</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -26654,10 +26689,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>124451802</v>
+        <v>124460951</v>
       </c>
       <c r="B254" t="n">
-        <v>79428</v>
+        <v>74901</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -26670,34 +26705,34 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>380197</v>
+        <v>380307</v>
       </c>
       <c r="R254" t="n">
-        <v>6920479</v>
+        <v>6919967</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26756,7 +26791,7 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>124455453</v>
+        <v>124452627</v>
       </c>
       <c r="B255" t="n">
         <v>74901</v>
@@ -26796,10 +26831,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>380326</v>
+        <v>380217</v>
       </c>
       <c r="R255" t="n">
-        <v>6920218</v>
+        <v>6920440</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26846,22 +26881,22 @@
       <c r="AT255" t="inlineStr"/>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>124450578</v>
+        <v>124463210</v>
       </c>
       <c r="B256" t="n">
-        <v>91030</v>
+        <v>79428</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -26874,34 +26909,34 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
       <c r="P256" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>380227</v>
+        <v>380189</v>
       </c>
       <c r="R256" t="n">
-        <v>6920340</v>
+        <v>6919766</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -26948,22 +26983,22 @@
       <c r="AT256" t="inlineStr"/>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>124470806</v>
+        <v>124455453</v>
       </c>
       <c r="B257" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -26976,42 +27011,37 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
-      <c r="M257" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>380340</v>
+        <v>380326</v>
       </c>
       <c r="R257" t="n">
-        <v>6920036</v>
+        <v>6920218</v>
       </c>
       <c r="S257" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T257" t="inlineStr">
         <is>
@@ -27055,22 +27085,22 @@
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>124459287</v>
+        <v>124455022</v>
       </c>
       <c r="B258" t="n">
-        <v>57513</v>
+        <v>79428</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -27083,39 +27113,34 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
-      <c r="M258" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P258" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>380561</v>
+        <v>380292</v>
       </c>
       <c r="R258" t="n">
-        <v>6919930</v>
+        <v>6920288</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -27162,22 +27187,22 @@
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>124455096</v>
+        <v>124450737</v>
       </c>
       <c r="B259" t="n">
-        <v>5196</v>
+        <v>74901</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -27186,43 +27211,38 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>105930</v>
+        <v>6440</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
-      <c r="M259" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P259" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>380323</v>
+        <v>380210</v>
       </c>
       <c r="R259" t="n">
-        <v>6920260</v>
+        <v>6920378</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -27281,10 +27301,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>124464651</v>
+        <v>124451172</v>
       </c>
       <c r="B260" t="n">
-        <v>79399</v>
+        <v>74901</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -27297,34 +27317,34 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>380251</v>
+        <v>380184</v>
       </c>
       <c r="R260" t="n">
-        <v>6919658</v>
+        <v>6920434</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -27383,10 +27403,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>124456129</v>
+        <v>124469088</v>
       </c>
       <c r="B261" t="n">
-        <v>78905</v>
+        <v>78810</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -27399,34 +27419,34 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
       <c r="P261" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>380326</v>
+        <v>380352</v>
       </c>
       <c r="R261" t="n">
-        <v>6920218</v>
+        <v>6919913</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -27473,22 +27493,22 @@
       <c r="AT261" t="inlineStr"/>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>124470234</v>
+        <v>124464321</v>
       </c>
       <c r="B262" t="n">
-        <v>82597</v>
+        <v>77738</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -27501,21 +27521,21 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>1312</v>
+        <v>6487</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -27525,10 +27545,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>380506</v>
+        <v>380268</v>
       </c>
       <c r="R262" t="n">
-        <v>6920009</v>
+        <v>6919685</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -27587,10 +27607,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>124458743</v>
+        <v>124469915</v>
       </c>
       <c r="B263" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -27603,34 +27623,34 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>380542</v>
+        <v>380521</v>
       </c>
       <c r="R263" t="n">
-        <v>6920184</v>
+        <v>6919962</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -27665,11 +27685,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC263" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
-        </is>
-      </c>
       <c r="AD263" t="b">
         <v>0</v>
       </c>
@@ -27682,22 +27697,22 @@
       <c r="AT263" t="inlineStr"/>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>124466302</v>
+        <v>124455774</v>
       </c>
       <c r="B264" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -27710,42 +27725,37 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
-      <c r="M264" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P264" t="inlineStr">
         <is>
           <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>380345</v>
+        <v>380356</v>
       </c>
       <c r="R264" t="n">
-        <v>6919632</v>
+        <v>6920172</v>
       </c>
       <c r="S264" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T264" t="inlineStr">
         <is>
@@ -27801,10 +27811,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>124465389</v>
+        <v>124469751</v>
       </c>
       <c r="B265" t="n">
-        <v>79399</v>
+        <v>74901</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -27817,34 +27827,34 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>380244</v>
+        <v>380490</v>
       </c>
       <c r="R265" t="n">
-        <v>6919577</v>
+        <v>6919937</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27891,22 +27901,22 @@
       <c r="AT265" t="inlineStr"/>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>124461736</v>
+        <v>124451574</v>
       </c>
       <c r="B266" t="n">
-        <v>74901</v>
+        <v>79428</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -27919,34 +27929,34 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>380232</v>
+        <v>380184</v>
       </c>
       <c r="R266" t="n">
-        <v>6919808</v>
+        <v>6920434</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -28005,10 +28015,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>124469088</v>
+        <v>124450902</v>
       </c>
       <c r="B267" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -28021,34 +28031,39 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P267" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>380352</v>
+        <v>380227</v>
       </c>
       <c r="R267" t="n">
-        <v>6919913</v>
+        <v>6920340</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -28083,6 +28098,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC267" t="inlineStr">
+        <is>
+          <t>Troligen spillkråka.</t>
+        </is>
+      </c>
       <c r="AD267" t="b">
         <v>0</v>
       </c>
@@ -28095,22 +28115,22 @@
       <c r="AT267" t="inlineStr"/>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>124464329</v>
+        <v>124461646</v>
       </c>
       <c r="B268" t="n">
-        <v>78194</v>
+        <v>57513</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -28123,37 +28143,42 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P268" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>380268</v>
+        <v>380239</v>
       </c>
       <c r="R268" t="n">
-        <v>6919685</v>
+        <v>6919828</v>
       </c>
       <c r="S268" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T268" t="inlineStr">
         <is>
@@ -28209,10 +28234,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>124470598</v>
+        <v>124451893</v>
       </c>
       <c r="B269" t="n">
-        <v>79428</v>
+        <v>5196</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -28221,38 +28246,38 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>6453</v>
+        <v>105930</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
       <c r="P269" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>380506</v>
+        <v>380227</v>
       </c>
       <c r="R269" t="n">
-        <v>6920061</v>
+        <v>6920340</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -28285,11 +28310,6 @@
       <c r="AA269" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC269" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -28316,10 +28336,10 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>124450845</v>
+        <v>124455456</v>
       </c>
       <c r="B270" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -28332,34 +28352,34 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
       <c r="P270" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>380205</v>
+        <v>380314</v>
       </c>
       <c r="R270" t="n">
-        <v>6920378</v>
+        <v>6920201</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -28418,7 +28438,7 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>124461108</v>
+        <v>124459042</v>
       </c>
       <c r="B271" t="n">
         <v>74901</v>
@@ -28454,14 +28474,14 @@
       <c r="I271" t="inlineStr"/>
       <c r="P271" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>380308</v>
+        <v>380571</v>
       </c>
       <c r="R271" t="n">
-        <v>6919925</v>
+        <v>6919993</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -28494,11 +28514,6 @@
       <c r="AA271" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC271" t="inlineStr">
-        <is>
-          <t>På basen avsågad gran. Grov stubbe</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -28525,10 +28540,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>124455776</v>
+        <v>124451837</v>
       </c>
       <c r="B272" t="n">
-        <v>57513</v>
+        <v>78194</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -28541,39 +28556,34 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
-      <c r="M272" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P272" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>380326</v>
+        <v>380197</v>
       </c>
       <c r="R272" t="n">
-        <v>6920218</v>
+        <v>6920479</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -28620,12 +28630,12 @@
       <c r="AT272" t="inlineStr"/>
       <c r="AW272" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>

--- a/artfynd/A 32573-2024 artfynd.xlsx
+++ b/artfynd/A 32573-2024 artfynd.xlsx
@@ -16105,10 +16105,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>124464970</v>
+        <v>124467914</v>
       </c>
       <c r="B152" t="n">
-        <v>57513</v>
+        <v>77738</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16121,42 +16121,37 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>380255</v>
+        <v>380361</v>
       </c>
       <c r="R152" t="n">
-        <v>6919561</v>
+        <v>6919740</v>
       </c>
       <c r="S152" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16186,6 +16181,11 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16200,22 +16200,22 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>124471016</v>
+        <v>124463210</v>
       </c>
       <c r="B153" t="n">
-        <v>57513</v>
+        <v>79428</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16228,39 +16228,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>380506</v>
+        <v>380189</v>
       </c>
       <c r="R153" t="n">
-        <v>6920061</v>
+        <v>6919766</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16307,22 +16302,22 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>124465863</v>
+        <v>124458509</v>
       </c>
       <c r="B154" t="n">
-        <v>78151</v>
+        <v>57513</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16331,38 +16326,43 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>498</v>
+        <v>100109</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Risåsvallen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>380296</v>
+        <v>380542</v>
       </c>
       <c r="R154" t="n">
-        <v>6919585</v>
+        <v>6920184</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16397,6 +16397,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>Miljöbilder, talltita.</t>
+        </is>
+      </c>
       <c r="AD154" t="b">
         <v>0</v>
       </c>
@@ -16409,22 +16414,22 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>124457866</v>
+        <v>124452423</v>
       </c>
       <c r="B155" t="n">
-        <v>78151</v>
+        <v>56725</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16433,38 +16438,43 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>498</v>
+        <v>102613</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>380537</v>
+        <v>380227</v>
       </c>
       <c r="R155" t="n">
-        <v>6920199</v>
+        <v>6920340</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16511,22 +16521,22 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>124454979</v>
+        <v>124469547</v>
       </c>
       <c r="B156" t="n">
-        <v>91030</v>
+        <v>88359</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16539,34 +16549,34 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>380289</v>
+        <v>380452</v>
       </c>
       <c r="R156" t="n">
-        <v>6920290</v>
+        <v>6919913</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16599,11 +16609,6 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16630,10 +16635,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>124450578</v>
+        <v>124460611</v>
       </c>
       <c r="B157" t="n">
-        <v>91030</v>
+        <v>78905</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16646,34 +16651,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>5432</v>
+        <v>967</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>380227</v>
+        <v>380335</v>
       </c>
       <c r="R157" t="n">
-        <v>6920340</v>
+        <v>6920000</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16732,10 +16737,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>124452423</v>
+        <v>124455096</v>
       </c>
       <c r="B158" t="n">
-        <v>56725</v>
+        <v>5196</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16748,16 +16753,16 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>102613</v>
+        <v>105930</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -16768,7 +16773,7 @@
       <c r="I158" t="inlineStr"/>
       <c r="M158" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
@@ -16777,10 +16782,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>380227</v>
+        <v>380323</v>
       </c>
       <c r="R158" t="n">
-        <v>6920340</v>
+        <v>6920260</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16827,19 +16832,19 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>124466302</v>
+        <v>124459287</v>
       </c>
       <c r="B159" t="n">
         <v>57513</v>
@@ -16875,7 +16880,7 @@
       <c r="I159" t="inlineStr"/>
       <c r="M159" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
@@ -16884,13 +16889,13 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>380345</v>
+        <v>380561</v>
       </c>
       <c r="R159" t="n">
-        <v>6919632</v>
+        <v>6919930</v>
       </c>
       <c r="S159" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -16934,22 +16939,22 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>124450845</v>
+        <v>124455456</v>
       </c>
       <c r="B160" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -16962,34 +16967,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>380205</v>
+        <v>380314</v>
       </c>
       <c r="R160" t="n">
-        <v>6920378</v>
+        <v>6920201</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17048,10 +17053,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>124470404</v>
+        <v>124470732</v>
       </c>
       <c r="B161" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17064,34 +17069,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>380471</v>
+        <v>380372</v>
       </c>
       <c r="R161" t="n">
-        <v>6920069</v>
+        <v>6920042</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17150,10 +17155,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>124464121</v>
+        <v>124464321</v>
       </c>
       <c r="B162" t="n">
-        <v>57513</v>
+        <v>77738</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17166,39 +17171,34 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>380419</v>
+        <v>380268</v>
       </c>
       <c r="R162" t="n">
-        <v>6919960</v>
+        <v>6919685</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17245,22 +17245,22 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>124451984</v>
+        <v>124470646</v>
       </c>
       <c r="B163" t="n">
-        <v>79399</v>
+        <v>91030</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17273,34 +17273,34 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>229821</v>
+        <v>5432</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>380203</v>
+        <v>380402</v>
       </c>
       <c r="R163" t="n">
-        <v>6920482</v>
+        <v>6920044</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17359,10 +17359,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>124464466</v>
+        <v>124456697</v>
       </c>
       <c r="B164" t="n">
-        <v>78905</v>
+        <v>91030</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17375,21 +17375,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>967</v>
+        <v>5432</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17399,10 +17399,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>380243</v>
+        <v>380443</v>
       </c>
       <c r="R164" t="n">
-        <v>6919687</v>
+        <v>6920118</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17461,10 +17461,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>124457601</v>
+        <v>124454876</v>
       </c>
       <c r="B165" t="n">
-        <v>78151</v>
+        <v>74901</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17473,38 +17473,38 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>498</v>
+        <v>6440</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>380544</v>
+        <v>380290</v>
       </c>
       <c r="R165" t="n">
-        <v>6920188</v>
+        <v>6920272</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17563,10 +17563,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>124460965</v>
+        <v>124470695</v>
       </c>
       <c r="B166" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17579,34 +17579,34 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>380307</v>
+        <v>380506</v>
       </c>
       <c r="R166" t="n">
-        <v>6919967</v>
+        <v>6920061</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17641,6 +17641,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD166" t="b">
         <v>0</v>
       </c>
@@ -17653,22 +17658,22 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>124463640</v>
+        <v>124461646</v>
       </c>
       <c r="B167" t="n">
-        <v>79428</v>
+        <v>57513</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17681,37 +17686,42 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>380218</v>
+        <v>380239</v>
       </c>
       <c r="R167" t="n">
-        <v>6919722</v>
+        <v>6919828</v>
       </c>
       <c r="S167" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -17767,10 +17777,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>124457317</v>
+        <v>124465009</v>
       </c>
       <c r="B168" t="n">
-        <v>79428</v>
+        <v>79399</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -17783,21 +17793,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17807,10 +17817,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>380547</v>
+        <v>380267</v>
       </c>
       <c r="R168" t="n">
-        <v>6920163</v>
+        <v>6919764</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17845,6 +17855,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD168" t="b">
         <v>0</v>
       </c>
@@ -17857,22 +17872,22 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>124455206</v>
+        <v>124458282</v>
       </c>
       <c r="B169" t="n">
-        <v>91030</v>
+        <v>78151</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -17881,38 +17896,38 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5432</v>
+        <v>498</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>380311</v>
+        <v>380588</v>
       </c>
       <c r="R169" t="n">
-        <v>6920231</v>
+        <v>6920110</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17971,10 +17986,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>124470555</v>
+        <v>124465863</v>
       </c>
       <c r="B170" t="n">
-        <v>82597</v>
+        <v>78151</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -17983,38 +17998,38 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1312</v>
+        <v>498</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>380431</v>
+        <v>380296</v>
       </c>
       <c r="R170" t="n">
-        <v>6920068</v>
+        <v>6919585</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18073,10 +18088,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>124454876</v>
+        <v>124456704</v>
       </c>
       <c r="B171" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18089,21 +18104,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18113,10 +18128,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>380290</v>
+        <v>380385</v>
       </c>
       <c r="R171" t="n">
-        <v>6920272</v>
+        <v>6920091</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18151,6 +18166,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD171" t="b">
         <v>0</v>
       </c>
@@ -18163,22 +18183,22 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>124464047</v>
+        <v>124451837</v>
       </c>
       <c r="B172" t="n">
-        <v>78810</v>
+        <v>78194</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18191,34 +18211,34 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>380267</v>
+        <v>380197</v>
       </c>
       <c r="R172" t="n">
-        <v>6919731</v>
+        <v>6920479</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18277,10 +18297,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>124470598</v>
+        <v>124456046</v>
       </c>
       <c r="B173" t="n">
-        <v>79428</v>
+        <v>91032</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18293,34 +18313,34 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>380506</v>
+        <v>380326</v>
       </c>
       <c r="R173" t="n">
-        <v>6920061</v>
+        <v>6920218</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18357,7 +18377,7 @@
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18384,10 +18404,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>124458743</v>
+        <v>124468547</v>
       </c>
       <c r="B174" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18400,21 +18420,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18424,10 +18444,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>380542</v>
+        <v>380356</v>
       </c>
       <c r="R174" t="n">
-        <v>6920184</v>
+        <v>6919817</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18462,11 +18482,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
-        </is>
-      </c>
       <c r="AD174" t="b">
         <v>0</v>
       </c>
@@ -18479,22 +18494,22 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>124455220</v>
+        <v>124464901</v>
       </c>
       <c r="B175" t="n">
-        <v>74901</v>
+        <v>79399</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -18507,34 +18522,34 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>380311</v>
+        <v>380249</v>
       </c>
       <c r="R175" t="n">
-        <v>6920231</v>
+        <v>6919607</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18593,10 +18608,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>124470299</v>
+        <v>124460965</v>
       </c>
       <c r="B176" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -18605,43 +18620,38 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>380495</v>
+        <v>380307</v>
       </c>
       <c r="R176" t="n">
-        <v>6920029</v>
+        <v>6919967</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18700,10 +18710,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>124457605</v>
+        <v>124456372</v>
       </c>
       <c r="B177" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -18716,39 +18726,34 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>380542</v>
+        <v>380368</v>
       </c>
       <c r="R177" t="n">
-        <v>6920184</v>
+        <v>6920107</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18783,11 +18788,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området.</t>
-        </is>
-      </c>
       <c r="AD177" t="b">
         <v>0</v>
       </c>
@@ -18800,22 +18800,22 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>124458282</v>
+        <v>124450578</v>
       </c>
       <c r="B178" t="n">
-        <v>78151</v>
+        <v>91030</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -18824,38 +18824,38 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>498</v>
+        <v>5432</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>380588</v>
+        <v>380227</v>
       </c>
       <c r="R178" t="n">
-        <v>6920110</v>
+        <v>6920340</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18902,22 +18902,22 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>124467914</v>
+        <v>124470806</v>
       </c>
       <c r="B179" t="n">
-        <v>77738</v>
+        <v>57513</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -18930,37 +18930,42 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6487</v>
+        <v>100109</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>380361</v>
+        <v>380340</v>
       </c>
       <c r="R179" t="n">
-        <v>6919740</v>
+        <v>6920036</v>
       </c>
       <c r="S179" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -18990,11 +18995,6 @@
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19009,22 +19009,22 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>124465167</v>
+        <v>124456676</v>
       </c>
       <c r="B180" t="n">
-        <v>78194</v>
+        <v>57513</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -19037,37 +19037,42 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P180" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>380244</v>
+        <v>380434</v>
       </c>
       <c r="R180" t="n">
-        <v>6919577</v>
+        <v>6920123</v>
       </c>
       <c r="S180" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -19111,22 +19116,22 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>124459134</v>
+        <v>124470742</v>
       </c>
       <c r="B181" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -19139,37 +19144,42 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P181" t="inlineStr">
         <is>
           <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>380559</v>
+        <v>380369</v>
       </c>
       <c r="R181" t="n">
-        <v>6919947</v>
+        <v>6920032</v>
       </c>
       <c r="S181" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -19225,10 +19235,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124470146</v>
+        <v>124458172</v>
       </c>
       <c r="B182" t="n">
-        <v>57513</v>
+        <v>78151</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -19237,46 +19247,41 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>380527</v>
+        <v>380562</v>
       </c>
       <c r="R182" t="n">
-        <v>6919988</v>
+        <v>6920118</v>
       </c>
       <c r="S182" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -19332,10 +19337,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124451326</v>
+        <v>124458476</v>
       </c>
       <c r="B183" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -19348,39 +19353,34 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>380227</v>
+        <v>380581</v>
       </c>
       <c r="R183" t="n">
-        <v>6920340</v>
+        <v>6920056</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19427,22 +19427,22 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124464651</v>
+        <v>124451574</v>
       </c>
       <c r="B184" t="n">
-        <v>79399</v>
+        <v>79428</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -19455,34 +19455,34 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>380251</v>
+        <v>380184</v>
       </c>
       <c r="R184" t="n">
-        <v>6919658</v>
+        <v>6920434</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19541,10 +19541,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124456372</v>
+        <v>124464121</v>
       </c>
       <c r="B185" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -19557,34 +19557,39 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P185" t="inlineStr">
         <is>
           <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>380368</v>
+        <v>380419</v>
       </c>
       <c r="R185" t="n">
-        <v>6920107</v>
+        <v>6919960</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19631,22 +19636,22 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124470732</v>
+        <v>124468469</v>
       </c>
       <c r="B186" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -19659,37 +19664,42 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>380372</v>
+        <v>380324</v>
       </c>
       <c r="R186" t="n">
-        <v>6920042</v>
+        <v>6919803</v>
       </c>
       <c r="S186" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -19745,10 +19755,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124452261</v>
+        <v>124470146</v>
       </c>
       <c r="B187" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -19761,37 +19771,42 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>380227</v>
+        <v>380527</v>
       </c>
       <c r="R187" t="n">
-        <v>6920340</v>
+        <v>6919988</v>
       </c>
       <c r="S187" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -19835,19 +19850,19 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124451885</v>
+        <v>124454979</v>
       </c>
       <c r="B188" t="n">
         <v>91030</v>
@@ -19887,10 +19902,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>380189</v>
+        <v>380289</v>
       </c>
       <c r="R188" t="n">
-        <v>6920488</v>
+        <v>6920290</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19925,6 +19940,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD188" t="b">
         <v>0</v>
       </c>
@@ -19937,22 +19957,22 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124456046</v>
+        <v>124459815</v>
       </c>
       <c r="B189" t="n">
-        <v>91032</v>
+        <v>79428</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -19965,21 +19985,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19989,10 +20009,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>380326</v>
+        <v>380445</v>
       </c>
       <c r="R189" t="n">
-        <v>6920218</v>
+        <v>6919917</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20027,11 +20047,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området.</t>
-        </is>
-      </c>
       <c r="AD189" t="b">
         <v>0</v>
       </c>
@@ -20044,22 +20059,22 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>124450300</v>
+        <v>124450845</v>
       </c>
       <c r="B190" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20072,21 +20087,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20096,10 +20111,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>380182</v>
+        <v>380205</v>
       </c>
       <c r="R190" t="n">
-        <v>6920316</v>
+        <v>6920378</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20158,10 +20173,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>124460258</v>
+        <v>124450666</v>
       </c>
       <c r="B191" t="n">
-        <v>79428</v>
+        <v>74901</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20174,34 +20189,34 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>380365</v>
+        <v>380227</v>
       </c>
       <c r="R191" t="n">
-        <v>6919996</v>
+        <v>6920340</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20248,22 +20263,22 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>124469907</v>
+        <v>124455134</v>
       </c>
       <c r="B192" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20276,34 +20291,34 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>380452</v>
+        <v>380311</v>
       </c>
       <c r="R192" t="n">
-        <v>6919913</v>
+        <v>6920245</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20350,22 +20365,22 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>124456676</v>
+        <v>124458743</v>
       </c>
       <c r="B193" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -20378,42 +20393,37 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
-      <c r="M193" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>380434</v>
+        <v>380542</v>
       </c>
       <c r="R193" t="n">
-        <v>6920123</v>
+        <v>6920184</v>
       </c>
       <c r="S193" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -20443,6 +20453,11 @@
       <c r="AA193" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20457,22 +20472,22 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>124466026</v>
+        <v>124451802</v>
       </c>
       <c r="B194" t="n">
-        <v>79399</v>
+        <v>79428</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -20485,34 +20500,34 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>380303</v>
+        <v>380197</v>
       </c>
       <c r="R194" t="n">
-        <v>6919598</v>
+        <v>6920479</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20547,11 +20562,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD194" t="b">
         <v>0</v>
       </c>
@@ -20564,22 +20574,22 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>124455776</v>
+        <v>124469751</v>
       </c>
       <c r="B195" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -20592,39 +20602,34 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>380326</v>
+        <v>380490</v>
       </c>
       <c r="R195" t="n">
-        <v>6920218</v>
+        <v>6919937</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20671,22 +20676,22 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>124470806</v>
+        <v>124469907</v>
       </c>
       <c r="B196" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -20699,42 +20704,37 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>380340</v>
+        <v>380452</v>
       </c>
       <c r="R196" t="n">
-        <v>6920036</v>
+        <v>6919913</v>
       </c>
       <c r="S196" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -20778,22 +20778,22 @@
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>124470070</v>
+        <v>124470184</v>
       </c>
       <c r="B197" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -20806,21 +20806,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20830,10 +20830,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>380533</v>
+        <v>380516</v>
       </c>
       <c r="R197" t="n">
-        <v>6919979</v>
+        <v>6920004</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20892,10 +20892,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>124459456</v>
+        <v>124470707</v>
       </c>
       <c r="B198" t="n">
-        <v>91032</v>
+        <v>57513</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -20908,37 +20908,42 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>380561</v>
+        <v>380367</v>
       </c>
       <c r="R198" t="n">
-        <v>6919930</v>
+        <v>6920058</v>
       </c>
       <c r="S198" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -20982,22 +20987,22 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>124470397</v>
+        <v>124464970</v>
       </c>
       <c r="B199" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -21010,37 +21015,42 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>380506</v>
+        <v>380255</v>
       </c>
       <c r="R199" t="n">
-        <v>6920061</v>
+        <v>6919561</v>
       </c>
       <c r="S199" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -21084,22 +21094,22 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>124458651</v>
+        <v>124463365</v>
       </c>
       <c r="B200" t="n">
-        <v>91030</v>
+        <v>79399</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -21112,21 +21122,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>5432</v>
+        <v>229821</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -21136,10 +21146,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>380569</v>
+        <v>380199</v>
       </c>
       <c r="R200" t="n">
-        <v>6920058</v>
+        <v>6919723</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21198,10 +21208,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>124468547</v>
+        <v>124451984</v>
       </c>
       <c r="B201" t="n">
-        <v>74901</v>
+        <v>79399</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -21214,21 +21224,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -21238,10 +21248,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>380356</v>
+        <v>380203</v>
       </c>
       <c r="R201" t="n">
-        <v>6919817</v>
+        <v>6920482</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21300,10 +21310,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>124451802</v>
+        <v>124464651</v>
       </c>
       <c r="B202" t="n">
-        <v>79428</v>
+        <v>79399</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -21316,34 +21326,34 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>380197</v>
+        <v>380251</v>
       </c>
       <c r="R202" t="n">
-        <v>6920479</v>
+        <v>6919658</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21402,10 +21412,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>124464842</v>
+        <v>124451569</v>
       </c>
       <c r="B203" t="n">
-        <v>79428</v>
+        <v>79399</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -21418,34 +21428,34 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>380237</v>
+        <v>380184</v>
       </c>
       <c r="R203" t="n">
-        <v>6919621</v>
+        <v>6920434</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21504,10 +21514,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>124470184</v>
+        <v>124468916</v>
       </c>
       <c r="B204" t="n">
-        <v>91030</v>
+        <v>78151</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -21516,38 +21526,38 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>5432</v>
+        <v>498</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>380516</v>
+        <v>380343</v>
       </c>
       <c r="R204" t="n">
-        <v>6920004</v>
+        <v>6919896</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21606,10 +21616,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>124456129</v>
+        <v>124457866</v>
       </c>
       <c r="B205" t="n">
-        <v>78905</v>
+        <v>78151</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -21618,38 +21628,38 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>967</v>
+        <v>498</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>380326</v>
+        <v>380537</v>
       </c>
       <c r="R205" t="n">
-        <v>6920218</v>
+        <v>6920199</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21696,22 +21706,22 @@
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>124464681</v>
+        <v>124464471</v>
       </c>
       <c r="B206" t="n">
-        <v>79399</v>
+        <v>78194</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -21724,21 +21734,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -21748,10 +21758,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>380264</v>
+        <v>380243</v>
       </c>
       <c r="R206" t="n">
-        <v>6919665</v>
+        <v>6919687</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21810,10 +21820,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>124461477</v>
+        <v>124458651</v>
       </c>
       <c r="B207" t="n">
-        <v>79399</v>
+        <v>91030</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -21826,34 +21836,34 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>229821</v>
+        <v>5432</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>380285</v>
+        <v>380569</v>
       </c>
       <c r="R207" t="n">
-        <v>6919895</v>
+        <v>6920058</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21912,10 +21922,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>124450518</v>
+        <v>124455206</v>
       </c>
       <c r="B208" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -21928,34 +21938,34 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>380202</v>
+        <v>380311</v>
       </c>
       <c r="R208" t="n">
-        <v>6920332</v>
+        <v>6920231</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22014,10 +22024,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>124458172</v>
+        <v>124465526</v>
       </c>
       <c r="B209" t="n">
-        <v>78151</v>
+        <v>79399</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -22026,38 +22036,38 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>498</v>
+        <v>229821</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>380562</v>
+        <v>380252</v>
       </c>
       <c r="R209" t="n">
-        <v>6920118</v>
+        <v>6919535</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -22116,10 +22126,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>124459815</v>
+        <v>124464493</v>
       </c>
       <c r="B210" t="n">
-        <v>79428</v>
+        <v>79399</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -22132,34 +22142,34 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>380445</v>
+        <v>380243</v>
       </c>
       <c r="R210" t="n">
-        <v>6919917</v>
+        <v>6919687</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22218,10 +22228,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>124461736</v>
+        <v>124464559</v>
       </c>
       <c r="B211" t="n">
-        <v>74901</v>
+        <v>79399</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -22234,21 +22244,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -22258,10 +22268,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>380232</v>
+        <v>380236</v>
       </c>
       <c r="R211" t="n">
-        <v>6919808</v>
+        <v>6919671</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22320,10 +22330,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>124450666</v>
+        <v>124470299</v>
       </c>
       <c r="B212" t="n">
-        <v>74901</v>
+        <v>56722</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -22332,38 +22342,43 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6440</v>
+        <v>100138</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>380227</v>
+        <v>380495</v>
       </c>
       <c r="R212" t="n">
-        <v>6920340</v>
+        <v>6920029</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22410,19 +22425,19 @@
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>124450415</v>
+        <v>124454665</v>
       </c>
       <c r="B213" t="n">
         <v>74901</v>
@@ -22462,10 +22477,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>380202</v>
+        <v>380258</v>
       </c>
       <c r="R213" t="n">
-        <v>6920332</v>
+        <v>6920309</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22524,10 +22539,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>124464329</v>
+        <v>124470070</v>
       </c>
       <c r="B214" t="n">
-        <v>78194</v>
+        <v>78810</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -22540,21 +22555,21 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -22564,10 +22579,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>380268</v>
+        <v>380533</v>
       </c>
       <c r="R214" t="n">
-        <v>6919685</v>
+        <v>6919979</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22626,10 +22641,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>124470742</v>
+        <v>124455453</v>
       </c>
       <c r="B215" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -22642,42 +22657,37 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
-      <c r="M215" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>380369</v>
+        <v>380326</v>
       </c>
       <c r="R215" t="n">
-        <v>6920032</v>
+        <v>6920218</v>
       </c>
       <c r="S215" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -22721,22 +22731,22 @@
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>124459287</v>
+        <v>124456129</v>
       </c>
       <c r="B216" t="n">
-        <v>57513</v>
+        <v>78905</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -22749,39 +22759,34 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>100109</v>
+        <v>967</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
-      <c r="M216" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>380561</v>
+        <v>380326</v>
       </c>
       <c r="R216" t="n">
-        <v>6919930</v>
+        <v>6920218</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22840,10 +22845,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>124458357</v>
+        <v>124452491</v>
       </c>
       <c r="B217" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -22856,42 +22861,37 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
-      <c r="M217" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>380586</v>
+        <v>380208</v>
       </c>
       <c r="R217" t="n">
-        <v>6920100</v>
+        <v>6920481</v>
       </c>
       <c r="S217" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -22947,10 +22947,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>124456697</v>
+        <v>124464466</v>
       </c>
       <c r="B218" t="n">
-        <v>91030</v>
+        <v>78905</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -22963,21 +22963,21 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>5432</v>
+        <v>967</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -22987,10 +22987,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>380443</v>
+        <v>380243</v>
       </c>
       <c r="R218" t="n">
-        <v>6920118</v>
+        <v>6919687</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23049,10 +23049,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>124456704</v>
+        <v>124470397</v>
       </c>
       <c r="B219" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -23065,34 +23065,34 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>380385</v>
+        <v>380506</v>
       </c>
       <c r="R219" t="n">
-        <v>6920091</v>
+        <v>6920061</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23125,11 +23125,6 @@
       <c r="AA219" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC219" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -23156,10 +23151,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>124464471</v>
+        <v>124457317</v>
       </c>
       <c r="B220" t="n">
-        <v>78194</v>
+        <v>79428</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -23172,21 +23167,21 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -23196,10 +23191,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>380243</v>
+        <v>380547</v>
       </c>
       <c r="R220" t="n">
-        <v>6919687</v>
+        <v>6920163</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23258,10 +23253,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>124455134</v>
+        <v>124455022</v>
       </c>
       <c r="B221" t="n">
-        <v>74901</v>
+        <v>79428</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -23274,21 +23269,21 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -23298,10 +23293,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>380311</v>
+        <v>380292</v>
       </c>
       <c r="R221" t="n">
-        <v>6920245</v>
+        <v>6920288</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23360,10 +23355,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>124454665</v>
+        <v>124461477</v>
       </c>
       <c r="B222" t="n">
-        <v>74901</v>
+        <v>79399</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -23376,34 +23371,34 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>380258</v>
+        <v>380285</v>
       </c>
       <c r="R222" t="n">
-        <v>6920309</v>
+        <v>6919895</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23462,10 +23457,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>124460611</v>
+        <v>124470598</v>
       </c>
       <c r="B223" t="n">
-        <v>78905</v>
+        <v>79428</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -23478,21 +23473,21 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>967</v>
+        <v>6453</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -23502,10 +23497,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>380335</v>
+        <v>380506</v>
       </c>
       <c r="R223" t="n">
-        <v>6920000</v>
+        <v>6920061</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23538,6 +23533,11 @@
       <c r="AA223" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -23564,10 +23564,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>124470695</v>
+        <v>124469088</v>
       </c>
       <c r="B224" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -23580,34 +23580,34 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>380506</v>
+        <v>380352</v>
       </c>
       <c r="R224" t="n">
-        <v>6920061</v>
+        <v>6919913</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23642,11 +23642,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC224" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
-        </is>
-      </c>
       <c r="AD224" t="b">
         <v>0</v>
       </c>
@@ -23659,22 +23654,22 @@
       <c r="AT224" t="inlineStr"/>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>124470485</v>
+        <v>124457836</v>
       </c>
       <c r="B225" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -23687,34 +23682,34 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>380446</v>
+        <v>380542</v>
       </c>
       <c r="R225" t="n">
-        <v>6920059</v>
+        <v>6920184</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23761,22 +23756,22 @@
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>124458046</v>
+        <v>124460258</v>
       </c>
       <c r="B226" t="n">
-        <v>74901</v>
+        <v>79428</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -23789,34 +23784,34 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>380533</v>
+        <v>380365</v>
       </c>
       <c r="R226" t="n">
-        <v>6920142</v>
+        <v>6919996</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23982,7 +23977,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>124465009</v>
+        <v>124466026</v>
       </c>
       <c r="B228" t="n">
         <v>79399</v>
@@ -24022,10 +24017,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>380267</v>
+        <v>380303</v>
       </c>
       <c r="R228" t="n">
-        <v>6919764</v>
+        <v>6919598</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24089,10 +24084,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>124464901</v>
+        <v>124463640</v>
       </c>
       <c r="B229" t="n">
-        <v>79399</v>
+        <v>79428</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -24105,21 +24100,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -24129,10 +24124,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>380249</v>
+        <v>380218</v>
       </c>
       <c r="R229" t="n">
-        <v>6919607</v>
+        <v>6919722</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24191,10 +24186,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>124451569</v>
+        <v>124450300</v>
       </c>
       <c r="B230" t="n">
-        <v>79399</v>
+        <v>74901</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -24207,34 +24202,34 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>380184</v>
+        <v>380182</v>
       </c>
       <c r="R230" t="n">
-        <v>6920434</v>
+        <v>6920316</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24293,10 +24288,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>124463365</v>
+        <v>124455774</v>
       </c>
       <c r="B231" t="n">
-        <v>79399</v>
+        <v>74901</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -24309,34 +24304,34 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>380199</v>
+        <v>380356</v>
       </c>
       <c r="R231" t="n">
-        <v>6919723</v>
+        <v>6920172</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24395,10 +24390,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>124468916</v>
+        <v>124464329</v>
       </c>
       <c r="B232" t="n">
-        <v>78151</v>
+        <v>78194</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -24407,38 +24402,38 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>498</v>
+        <v>6437</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>380343</v>
+        <v>380268</v>
       </c>
       <c r="R232" t="n">
-        <v>6919896</v>
+        <v>6919685</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24497,10 +24492,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>124470646</v>
+        <v>124466494</v>
       </c>
       <c r="B233" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -24513,37 +24508,42 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>380402</v>
+        <v>380344</v>
       </c>
       <c r="R233" t="n">
-        <v>6920044</v>
+        <v>6919654</v>
       </c>
       <c r="S233" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -24599,10 +24599,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>124452491</v>
+        <v>124459060</v>
       </c>
       <c r="B234" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -24615,34 +24615,39 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>380208</v>
+        <v>380571</v>
       </c>
       <c r="R234" t="n">
-        <v>6920481</v>
+        <v>6919993</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -24701,10 +24706,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>124457836</v>
+        <v>124459456</v>
       </c>
       <c r="B235" t="n">
-        <v>78810</v>
+        <v>91032</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -24717,34 +24722,34 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>380542</v>
+        <v>380561</v>
       </c>
       <c r="R235" t="n">
-        <v>6920184</v>
+        <v>6919930</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -24803,10 +24808,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>124467947</v>
+        <v>124456502</v>
       </c>
       <c r="B236" t="n">
-        <v>78194</v>
+        <v>78810</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -24819,34 +24824,34 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>380361</v>
+        <v>380385</v>
       </c>
       <c r="R236" t="n">
-        <v>6919740</v>
+        <v>6920091</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24883,7 +24888,7 @@
       </c>
       <c r="AC236" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -24910,10 +24915,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>124464292</v>
+        <v>124450415</v>
       </c>
       <c r="B237" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -24926,39 +24931,34 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
-      <c r="M237" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P237" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>380275</v>
+        <v>380202</v>
       </c>
       <c r="R237" t="n">
-        <v>6919775</v>
+        <v>6920332</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -25005,19 +25005,19 @@
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>124458476</v>
+        <v>124469377</v>
       </c>
       <c r="B238" t="n">
         <v>74901</v>
@@ -25053,14 +25053,14 @@
       <c r="I238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>380581</v>
+        <v>380435</v>
       </c>
       <c r="R238" t="n">
-        <v>6920056</v>
+        <v>6919916</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -25119,10 +25119,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>124456502</v>
+        <v>124471016</v>
       </c>
       <c r="B239" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -25135,34 +25135,39 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>380385</v>
+        <v>380506</v>
       </c>
       <c r="R239" t="n">
-        <v>6920091</v>
+        <v>6920061</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -25195,11 +25200,6 @@
       <c r="AA239" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC239" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -25226,10 +25226,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>124461108</v>
+        <v>124451326</v>
       </c>
       <c r="B240" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -25242,34 +25242,39 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P240" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>380308</v>
+        <v>380227</v>
       </c>
       <c r="R240" t="n">
-        <v>6919925</v>
+        <v>6920340</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -25304,11 +25309,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC240" t="inlineStr">
-        <is>
-          <t>På basen avsågad gran. Grov stubbe</t>
-        </is>
-      </c>
       <c r="AD240" t="b">
         <v>0</v>
       </c>
@@ -25321,22 +25321,22 @@
       <c r="AT240" t="inlineStr"/>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>124469377</v>
+        <v>124450902</v>
       </c>
       <c r="B241" t="n">
-        <v>74901</v>
+        <v>57529</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -25349,34 +25349,39 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P241" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>380435</v>
+        <v>380227</v>
       </c>
       <c r="R241" t="n">
-        <v>6919916</v>
+        <v>6920340</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -25411,6 +25416,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC241" t="inlineStr">
+        <is>
+          <t>Troligen spillkråka.</t>
+        </is>
+      </c>
       <c r="AD241" t="b">
         <v>0</v>
       </c>
@@ -25423,22 +25433,22 @@
       <c r="AT241" t="inlineStr"/>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>124468469</v>
+        <v>124458357</v>
       </c>
       <c r="B242" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -25451,27 +25461,27 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
       <c r="M242" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
@@ -25480,13 +25490,13 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>380324</v>
+        <v>380586</v>
       </c>
       <c r="R242" t="n">
-        <v>6919803</v>
+        <v>6920100</v>
       </c>
       <c r="S242" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -25542,10 +25552,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>124470707</v>
+        <v>124464047</v>
       </c>
       <c r="B243" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -25558,42 +25568,37 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
-      <c r="M243" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>380367</v>
+        <v>380267</v>
       </c>
       <c r="R243" t="n">
-        <v>6920058</v>
+        <v>6919731</v>
       </c>
       <c r="S243" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -25649,10 +25654,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>124464493</v>
+        <v>124455220</v>
       </c>
       <c r="B244" t="n">
-        <v>79399</v>
+        <v>74901</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -25665,34 +25670,34 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>380243</v>
+        <v>380311</v>
       </c>
       <c r="R244" t="n">
-        <v>6919687</v>
+        <v>6920231</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25751,10 +25756,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>124464559</v>
+        <v>124465167</v>
       </c>
       <c r="B245" t="n">
-        <v>79399</v>
+        <v>78194</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -25767,21 +25772,21 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -25791,10 +25796,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>380236</v>
+        <v>380244</v>
       </c>
       <c r="R245" t="n">
-        <v>6919671</v>
+        <v>6919577</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25841,22 +25846,22 @@
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>124465389</v>
+        <v>124452627</v>
       </c>
       <c r="B246" t="n">
-        <v>79399</v>
+        <v>74901</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -25869,34 +25874,34 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>380244</v>
+        <v>380217</v>
       </c>
       <c r="R246" t="n">
-        <v>6919577</v>
+        <v>6920440</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25943,22 +25948,22 @@
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>124465526</v>
+        <v>124470234</v>
       </c>
       <c r="B247" t="n">
-        <v>79399</v>
+        <v>82597</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -25971,34 +25976,34 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>229821</v>
+        <v>1312</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Risåsvallen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>380252</v>
+        <v>380506</v>
       </c>
       <c r="R247" t="n">
-        <v>6919535</v>
+        <v>6920009</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -26057,10 +26062,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>124469547</v>
+        <v>124459134</v>
       </c>
       <c r="B248" t="n">
-        <v>88359</v>
+        <v>74901</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -26073,21 +26078,21 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -26097,10 +26102,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>380452</v>
+        <v>380559</v>
       </c>
       <c r="R248" t="n">
-        <v>6919913</v>
+        <v>6919947</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -26147,22 +26152,22 @@
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>124470234</v>
+        <v>124451893</v>
       </c>
       <c r="B249" t="n">
-        <v>82597</v>
+        <v>5196</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -26171,38 +26176,38 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>1312</v>
+        <v>105930</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>380506</v>
+        <v>380227</v>
       </c>
       <c r="R249" t="n">
-        <v>6920009</v>
+        <v>6920340</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -26249,22 +26254,22 @@
       <c r="AT249" t="inlineStr"/>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>124460224</v>
+        <v>124459042</v>
       </c>
       <c r="B250" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -26277,39 +26282,34 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
-      <c r="M250" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>380374</v>
+        <v>380571</v>
       </c>
       <c r="R250" t="n">
-        <v>6919982</v>
+        <v>6919993</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -26356,22 +26356,22 @@
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>124466494</v>
+        <v>124470555</v>
       </c>
       <c r="B251" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -26384,42 +26384,37 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
-      <c r="M251" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P251" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>380344</v>
+        <v>380431</v>
       </c>
       <c r="R251" t="n">
-        <v>6919654</v>
+        <v>6920068</v>
       </c>
       <c r="S251" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T251" t="inlineStr">
         <is>
@@ -26475,10 +26470,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>124459060</v>
+        <v>124458046</v>
       </c>
       <c r="B252" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -26491,39 +26486,34 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
-      <c r="M252" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P252" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>380571</v>
+        <v>380533</v>
       </c>
       <c r="R252" t="n">
-        <v>6919993</v>
+        <v>6920142</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -26582,10 +26572,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>124455096</v>
+        <v>124461108</v>
       </c>
       <c r="B253" t="n">
-        <v>5196</v>
+        <v>74901</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -26594,43 +26584,38 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>105930</v>
+        <v>6440</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
-      <c r="M253" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P253" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>380323</v>
+        <v>380308</v>
       </c>
       <c r="R253" t="n">
-        <v>6920260</v>
+        <v>6919925</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -26663,6 +26648,11 @@
       <c r="AA253" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC253" t="inlineStr">
+        <is>
+          <t>På basen avsågad gran. Grov stubbe</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -26689,10 +26679,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>124460951</v>
+        <v>124464842</v>
       </c>
       <c r="B254" t="n">
-        <v>74901</v>
+        <v>79428</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -26705,34 +26695,34 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>380307</v>
+        <v>380237</v>
       </c>
       <c r="R254" t="n">
-        <v>6919967</v>
+        <v>6919621</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26791,10 +26781,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>124452627</v>
+        <v>124455776</v>
       </c>
       <c r="B255" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -26807,34 +26797,39 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P255" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>380217</v>
+        <v>380326</v>
       </c>
       <c r="R255" t="n">
-        <v>6920440</v>
+        <v>6920218</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26881,22 +26876,22 @@
       <c r="AT255" t="inlineStr"/>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>124463210</v>
+        <v>124466302</v>
       </c>
       <c r="B256" t="n">
-        <v>79428</v>
+        <v>57513</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -26909,37 +26904,42 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P256" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>380189</v>
+        <v>380345</v>
       </c>
       <c r="R256" t="n">
-        <v>6919766</v>
+        <v>6919632</v>
       </c>
       <c r="S256" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T256" t="inlineStr">
         <is>
@@ -26995,10 +26995,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>124455453</v>
+        <v>124465389</v>
       </c>
       <c r="B257" t="n">
-        <v>74901</v>
+        <v>79399</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -27011,34 +27011,34 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
       <c r="P257" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>380326</v>
+        <v>380244</v>
       </c>
       <c r="R257" t="n">
-        <v>6920218</v>
+        <v>6919577</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -27097,10 +27097,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>124455022</v>
+        <v>124464681</v>
       </c>
       <c r="B258" t="n">
-        <v>79428</v>
+        <v>79399</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -27113,34 +27113,34 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>380292</v>
+        <v>380264</v>
       </c>
       <c r="R258" t="n">
-        <v>6920288</v>
+        <v>6919665</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -27301,7 +27301,7 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>124451172</v>
+        <v>124461736</v>
       </c>
       <c r="B260" t="n">
         <v>74901</v>
@@ -27337,14 +27337,14 @@
       <c r="I260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>380184</v>
+        <v>380232</v>
       </c>
       <c r="R260" t="n">
-        <v>6920434</v>
+        <v>6919808</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -27403,7 +27403,7 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>124469088</v>
+        <v>124452261</v>
       </c>
       <c r="B261" t="n">
         <v>78810</v>
@@ -27439,14 +27439,14 @@
       <c r="I261" t="inlineStr"/>
       <c r="P261" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>380352</v>
+        <v>380227</v>
       </c>
       <c r="R261" t="n">
-        <v>6919913</v>
+        <v>6920340</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -27493,22 +27493,22 @@
       <c r="AT261" t="inlineStr"/>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>124464321</v>
+        <v>124470404</v>
       </c>
       <c r="B262" t="n">
-        <v>77738</v>
+        <v>91030</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -27521,21 +27521,21 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>6487</v>
+        <v>5432</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -27545,10 +27545,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>380268</v>
+        <v>380471</v>
       </c>
       <c r="R262" t="n">
-        <v>6919685</v>
+        <v>6920069</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -27607,10 +27607,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>124469915</v>
+        <v>124451885</v>
       </c>
       <c r="B263" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -27623,34 +27623,34 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>380521</v>
+        <v>380189</v>
       </c>
       <c r="R263" t="n">
-        <v>6919962</v>
+        <v>6920488</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -27709,7 +27709,7 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>124455774</v>
+        <v>124451172</v>
       </c>
       <c r="B264" t="n">
         <v>74901</v>
@@ -27745,14 +27745,14 @@
       <c r="I264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>380356</v>
+        <v>380184</v>
       </c>
       <c r="R264" t="n">
-        <v>6920172</v>
+        <v>6920434</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27811,7 +27811,7 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>124469751</v>
+        <v>124470485</v>
       </c>
       <c r="B265" t="n">
         <v>74901</v>
@@ -27847,14 +27847,14 @@
       <c r="I265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>380490</v>
+        <v>380446</v>
       </c>
       <c r="R265" t="n">
-        <v>6919937</v>
+        <v>6920059</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27913,10 +27913,10 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>124451574</v>
+        <v>124469915</v>
       </c>
       <c r="B266" t="n">
-        <v>79428</v>
+        <v>74901</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -27929,34 +27929,34 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>380184</v>
+        <v>380521</v>
       </c>
       <c r="R266" t="n">
-        <v>6920434</v>
+        <v>6919962</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -28015,10 +28015,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>124450902</v>
+        <v>124467947</v>
       </c>
       <c r="B267" t="n">
-        <v>57529</v>
+        <v>78194</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -28031,39 +28031,34 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>100049</v>
+        <v>6437</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
-      <c r="M267" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P267" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>380227</v>
+        <v>380361</v>
       </c>
       <c r="R267" t="n">
-        <v>6920340</v>
+        <v>6919740</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -28100,7 +28095,7 @@
       </c>
       <c r="AC267" t="inlineStr">
         <is>
-          <t>Troligen spillkråka.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -28127,10 +28122,10 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>124461646</v>
+        <v>124450518</v>
       </c>
       <c r="B268" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -28143,42 +28138,37 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
-      <c r="M268" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P268" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>380239</v>
+        <v>380202</v>
       </c>
       <c r="R268" t="n">
-        <v>6919828</v>
+        <v>6920332</v>
       </c>
       <c r="S268" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T268" t="inlineStr">
         <is>
@@ -28234,10 +28224,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>124451893</v>
+        <v>124464292</v>
       </c>
       <c r="B269" t="n">
-        <v>5196</v>
+        <v>57513</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -28246,20 +28236,20 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>105930</v>
+        <v>100109</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -28268,16 +28258,21 @@
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>380227</v>
+        <v>380275</v>
       </c>
       <c r="R269" t="n">
-        <v>6920340</v>
+        <v>6919775</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -28336,10 +28331,10 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>124455456</v>
+        <v>124460224</v>
       </c>
       <c r="B270" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -28352,34 +28347,39 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P270" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>380314</v>
+        <v>380374</v>
       </c>
       <c r="R270" t="n">
-        <v>6920201</v>
+        <v>6919982</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -28426,22 +28426,22 @@
       <c r="AT270" t="inlineStr"/>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>124459042</v>
+        <v>124457601</v>
       </c>
       <c r="B271" t="n">
-        <v>74901</v>
+        <v>78151</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -28450,25 +28450,25 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>6440</v>
+        <v>498</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
@@ -28478,10 +28478,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>380571</v>
+        <v>380544</v>
       </c>
       <c r="R271" t="n">
-        <v>6919993</v>
+        <v>6920188</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -28540,10 +28540,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>124451837</v>
+        <v>124460951</v>
       </c>
       <c r="B272" t="n">
-        <v>78194</v>
+        <v>74901</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -28556,34 +28556,34 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
       <c r="P272" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>380197</v>
+        <v>380307</v>
       </c>
       <c r="R272" t="n">
-        <v>6920479</v>
+        <v>6919967</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -28642,10 +28642,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>124588108</v>
+        <v>124589633</v>
       </c>
       <c r="B273" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -28658,42 +28658,37 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
-      <c r="M273" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P273" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>380223</v>
+        <v>380181</v>
       </c>
       <c r="R273" t="n">
-        <v>6920277</v>
+        <v>6920018</v>
       </c>
       <c r="S273" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T273" t="inlineStr">
         <is>
@@ -28749,10 +28744,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>124589633</v>
+        <v>124588108</v>
       </c>
       <c r="B274" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -28765,37 +28760,42 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P274" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>380181</v>
+        <v>380223</v>
       </c>
       <c r="R274" t="n">
-        <v>6920018</v>
+        <v>6920277</v>
       </c>
       <c r="S274" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T274" t="inlineStr">
         <is>

--- a/artfynd/A 32573-2024 artfynd.xlsx
+++ b/artfynd/A 32573-2024 artfynd.xlsx
@@ -16105,10 +16105,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>124467914</v>
+        <v>124461477</v>
       </c>
       <c r="B152" t="n">
-        <v>77738</v>
+        <v>79399</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16121,34 +16121,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>380361</v>
+        <v>380285</v>
       </c>
       <c r="R152" t="n">
-        <v>6919740</v>
+        <v>6919895</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16183,11 +16183,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD152" t="b">
         <v>0</v>
       </c>
@@ -16200,22 +16195,22 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>124463210</v>
+        <v>124451569</v>
       </c>
       <c r="B153" t="n">
-        <v>79428</v>
+        <v>79399</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16228,34 +16223,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>380189</v>
+        <v>380184</v>
       </c>
       <c r="R153" t="n">
-        <v>6919766</v>
+        <v>6920434</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16314,7 +16309,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>124458509</v>
+        <v>124468182</v>
       </c>
       <c r="B154" t="n">
         <v>57513</v>
@@ -16355,17 +16350,17 @@
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>380542</v>
+        <v>380265</v>
       </c>
       <c r="R154" t="n">
-        <v>6920184</v>
+        <v>6919774</v>
       </c>
       <c r="S154" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -16395,11 +16390,6 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>Miljöbilder, talltita.</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16414,22 +16404,22 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>124452423</v>
+        <v>124456046</v>
       </c>
       <c r="B155" t="n">
-        <v>56725</v>
+        <v>91032</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16438,43 +16428,38 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>102613</v>
+        <v>5442</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>380227</v>
+        <v>380326</v>
       </c>
       <c r="R155" t="n">
-        <v>6920340</v>
+        <v>6920218</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16507,6 +16492,11 @@
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16533,10 +16523,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>124469547</v>
+        <v>124451574</v>
       </c>
       <c r="B156" t="n">
-        <v>88359</v>
+        <v>79428</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16549,34 +16539,34 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>510</v>
+        <v>6453</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>380452</v>
+        <v>380184</v>
       </c>
       <c r="R156" t="n">
-        <v>6919913</v>
+        <v>6920434</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16623,22 +16613,22 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>124460611</v>
+        <v>124468916</v>
       </c>
       <c r="B157" t="n">
-        <v>78905</v>
+        <v>78151</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16647,38 +16637,38 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>967</v>
+        <v>498</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>380335</v>
+        <v>380343</v>
       </c>
       <c r="R157" t="n">
-        <v>6920000</v>
+        <v>6919896</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16725,22 +16715,22 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>124455096</v>
+        <v>124457317</v>
       </c>
       <c r="B158" t="n">
-        <v>5196</v>
+        <v>79428</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16749,43 +16739,38 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>105930</v>
+        <v>6453</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>380323</v>
+        <v>380547</v>
       </c>
       <c r="R158" t="n">
-        <v>6920260</v>
+        <v>6920163</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16844,10 +16829,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>124459287</v>
+        <v>124470485</v>
       </c>
       <c r="B159" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16860,39 +16845,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>380561</v>
+        <v>380446</v>
       </c>
       <c r="R159" t="n">
-        <v>6919930</v>
+        <v>6920059</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16939,19 +16919,19 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>124455456</v>
+        <v>124450666</v>
       </c>
       <c r="B160" t="n">
         <v>74901</v>
@@ -16991,10 +16971,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>380314</v>
+        <v>380227</v>
       </c>
       <c r="R160" t="n">
-        <v>6920201</v>
+        <v>6920340</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17041,22 +17021,22 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>124470732</v>
+        <v>124458357</v>
       </c>
       <c r="B161" t="n">
-        <v>74901</v>
+        <v>57666</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17069,37 +17049,42 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>380372</v>
+        <v>380586</v>
       </c>
       <c r="R161" t="n">
-        <v>6920042</v>
+        <v>6920100</v>
       </c>
       <c r="S161" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -17155,10 +17140,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>124464321</v>
+        <v>124458172</v>
       </c>
       <c r="B162" t="n">
-        <v>77738</v>
+        <v>78151</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17167,25 +17152,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6487</v>
+        <v>498</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17195,10 +17180,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>380268</v>
+        <v>380562</v>
       </c>
       <c r="R162" t="n">
-        <v>6919685</v>
+        <v>6920118</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17257,10 +17242,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>124470646</v>
+        <v>124470732</v>
       </c>
       <c r="B163" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17273,34 +17258,34 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>380402</v>
+        <v>380372</v>
       </c>
       <c r="R163" t="n">
-        <v>6920044</v>
+        <v>6920042</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17359,10 +17344,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>124456697</v>
+        <v>124463210</v>
       </c>
       <c r="B164" t="n">
-        <v>91030</v>
+        <v>79428</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17375,21 +17360,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17399,10 +17384,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>380443</v>
+        <v>380189</v>
       </c>
       <c r="R164" t="n">
-        <v>6920118</v>
+        <v>6919766</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17461,7 +17446,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>124454876</v>
+        <v>124450415</v>
       </c>
       <c r="B165" t="n">
         <v>74901</v>
@@ -17497,14 +17482,14 @@
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>380290</v>
+        <v>380202</v>
       </c>
       <c r="R165" t="n">
-        <v>6920272</v>
+        <v>6920332</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17563,10 +17548,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>124470695</v>
+        <v>124451802</v>
       </c>
       <c r="B166" t="n">
-        <v>91030</v>
+        <v>79428</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17579,34 +17564,34 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>380506</v>
+        <v>380197</v>
       </c>
       <c r="R166" t="n">
-        <v>6920061</v>
+        <v>6920479</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17641,11 +17626,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
-        </is>
-      </c>
       <c r="AD166" t="b">
         <v>0</v>
       </c>
@@ -17658,22 +17638,22 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>124461646</v>
+        <v>124464493</v>
       </c>
       <c r="B167" t="n">
-        <v>57513</v>
+        <v>79399</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17686,42 +17666,37 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P167" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>380239</v>
+        <v>380243</v>
       </c>
       <c r="R167" t="n">
-        <v>6919828</v>
+        <v>6919687</v>
       </c>
       <c r="S167" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -17777,7 +17752,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>124465009</v>
+        <v>124465526</v>
       </c>
       <c r="B168" t="n">
         <v>79399</v>
@@ -17813,14 +17788,14 @@
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>380267</v>
+        <v>380252</v>
       </c>
       <c r="R168" t="n">
-        <v>6919764</v>
+        <v>6919535</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17855,11 +17830,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD168" t="b">
         <v>0</v>
       </c>
@@ -17872,22 +17842,22 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>124458282</v>
+        <v>124470234</v>
       </c>
       <c r="B169" t="n">
-        <v>78151</v>
+        <v>82597</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -17896,25 +17866,25 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>498</v>
+        <v>1312</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17924,10 +17894,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>380588</v>
+        <v>380506</v>
       </c>
       <c r="R169" t="n">
-        <v>6920110</v>
+        <v>6920009</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17986,10 +17956,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>124465863</v>
+        <v>124464466</v>
       </c>
       <c r="B170" t="n">
-        <v>78151</v>
+        <v>78905</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -17998,38 +17968,38 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>498</v>
+        <v>967</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Risåsvallen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>380296</v>
+        <v>380243</v>
       </c>
       <c r="R170" t="n">
-        <v>6919585</v>
+        <v>6919687</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18088,10 +18058,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>124456704</v>
+        <v>124456129</v>
       </c>
       <c r="B171" t="n">
-        <v>91030</v>
+        <v>78905</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18104,21 +18074,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5432</v>
+        <v>967</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18128,10 +18098,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>380385</v>
+        <v>380326</v>
       </c>
       <c r="R171" t="n">
-        <v>6920091</v>
+        <v>6920218</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18164,11 +18134,6 @@
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18195,10 +18160,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>124451837</v>
+        <v>124470299</v>
       </c>
       <c r="B172" t="n">
-        <v>78194</v>
+        <v>56722</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18207,38 +18172,43 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6437</v>
+        <v>100138</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>380197</v>
+        <v>380495</v>
       </c>
       <c r="R172" t="n">
-        <v>6920479</v>
+        <v>6920029</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18297,10 +18267,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>124456046</v>
+        <v>124451326</v>
       </c>
       <c r="B173" t="n">
-        <v>91032</v>
+        <v>57513</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18313,34 +18283,39 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P173" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>380326</v>
+        <v>380227</v>
       </c>
       <c r="R173" t="n">
-        <v>6920218</v>
+        <v>6920340</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18373,11 +18348,6 @@
       <c r="AA173" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC173" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18404,10 +18374,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>124468547</v>
+        <v>124459456</v>
       </c>
       <c r="B174" t="n">
-        <v>74901</v>
+        <v>91032</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18420,34 +18390,34 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6440</v>
+        <v>5442</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>380356</v>
+        <v>380561</v>
       </c>
       <c r="R174" t="n">
-        <v>6919817</v>
+        <v>6919930</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18494,22 +18464,22 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>124464901</v>
+        <v>124456704</v>
       </c>
       <c r="B175" t="n">
-        <v>79399</v>
+        <v>91030</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -18522,34 +18492,34 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>229821</v>
+        <v>5432</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>380249</v>
+        <v>380385</v>
       </c>
       <c r="R175" t="n">
-        <v>6919607</v>
+        <v>6920091</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18584,6 +18554,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD175" t="b">
         <v>0</v>
       </c>
@@ -18596,22 +18571,22 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>124460965</v>
+        <v>124458743</v>
       </c>
       <c r="B176" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -18624,34 +18599,34 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>380307</v>
+        <v>380542</v>
       </c>
       <c r="R176" t="n">
-        <v>6919967</v>
+        <v>6920184</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18686,6 +18661,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD176" t="b">
         <v>0</v>
       </c>
@@ -18698,22 +18678,22 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>124456372</v>
+        <v>124467914</v>
       </c>
       <c r="B177" t="n">
-        <v>74901</v>
+        <v>77738</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -18726,34 +18706,34 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6440</v>
+        <v>6487</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>380368</v>
+        <v>380361</v>
       </c>
       <c r="R177" t="n">
-        <v>6920107</v>
+        <v>6919740</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18788,6 +18768,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD177" t="b">
         <v>0</v>
       </c>
@@ -18800,22 +18785,22 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>124450578</v>
+        <v>124455220</v>
       </c>
       <c r="B178" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -18828,21 +18813,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18852,10 +18837,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>380227</v>
+        <v>380311</v>
       </c>
       <c r="R178" t="n">
-        <v>6920340</v>
+        <v>6920231</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18902,22 +18887,22 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>124470806</v>
+        <v>124455774</v>
       </c>
       <c r="B179" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -18930,42 +18915,37 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P179" t="inlineStr">
         <is>
           <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>380340</v>
+        <v>380356</v>
       </c>
       <c r="R179" t="n">
-        <v>6920036</v>
+        <v>6920172</v>
       </c>
       <c r="S179" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -19021,10 +19001,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>124456676</v>
+        <v>124452261</v>
       </c>
       <c r="B180" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -19037,42 +19017,37 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>380434</v>
+        <v>380227</v>
       </c>
       <c r="R180" t="n">
-        <v>6920123</v>
+        <v>6920340</v>
       </c>
       <c r="S180" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -19116,19 +19091,19 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>124470742</v>
+        <v>124468469</v>
       </c>
       <c r="B181" t="n">
         <v>57513</v>
@@ -19169,14 +19144,14 @@
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>380369</v>
+        <v>380324</v>
       </c>
       <c r="R181" t="n">
-        <v>6920032</v>
+        <v>6919803</v>
       </c>
       <c r="S181" t="n">
         <v>15</v>
@@ -19235,7 +19210,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124458172</v>
+        <v>124465863</v>
       </c>
       <c r="B182" t="n">
         <v>78151</v>
@@ -19271,14 +19246,14 @@
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>380562</v>
+        <v>380296</v>
       </c>
       <c r="R182" t="n">
-        <v>6920118</v>
+        <v>6919585</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19337,10 +19312,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124458476</v>
+        <v>124464681</v>
       </c>
       <c r="B183" t="n">
-        <v>74901</v>
+        <v>79399</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -19353,21 +19328,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19377,10 +19352,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>380581</v>
+        <v>380264</v>
       </c>
       <c r="R183" t="n">
-        <v>6920056</v>
+        <v>6919665</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19439,10 +19414,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124451574</v>
+        <v>124457605</v>
       </c>
       <c r="B184" t="n">
-        <v>79428</v>
+        <v>57513</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -19455,34 +19430,39 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P184" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>380184</v>
+        <v>380542</v>
       </c>
       <c r="R184" t="n">
-        <v>6920434</v>
+        <v>6920184</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19517,6 +19497,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området.</t>
+        </is>
+      </c>
       <c r="AD184" t="b">
         <v>0</v>
       </c>
@@ -19529,22 +19514,22 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124464121</v>
+        <v>124455096</v>
       </c>
       <c r="B185" t="n">
-        <v>57513</v>
+        <v>5196</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -19553,20 +19538,20 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>100109</v>
+        <v>105930</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -19577,19 +19562,19 @@
       <c r="I185" t="inlineStr"/>
       <c r="M185" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>380419</v>
+        <v>380323</v>
       </c>
       <c r="R185" t="n">
-        <v>6919960</v>
+        <v>6920260</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19636,22 +19621,22 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124468469</v>
+        <v>124454979</v>
       </c>
       <c r="B186" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -19664,42 +19649,37 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>380324</v>
+        <v>380289</v>
       </c>
       <c r="R186" t="n">
-        <v>6919803</v>
+        <v>6920290</v>
       </c>
       <c r="S186" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -19729,6 +19709,11 @@
       <c r="AA186" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -19743,22 +19728,22 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124470146</v>
+        <v>124470404</v>
       </c>
       <c r="B187" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -19771,42 +19756,37 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P187" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>380527</v>
+        <v>380471</v>
       </c>
       <c r="R187" t="n">
-        <v>6919988</v>
+        <v>6920069</v>
       </c>
       <c r="S187" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -19862,7 +19842,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124454979</v>
+        <v>124470737</v>
       </c>
       <c r="B188" t="n">
         <v>91030</v>
@@ -19898,14 +19878,14 @@
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>380289</v>
+        <v>380506</v>
       </c>
       <c r="R188" t="n">
-        <v>6920290</v>
+        <v>6920061</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19938,11 +19918,6 @@
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC188" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -19969,10 +19944,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124459815</v>
+        <v>124469088</v>
       </c>
       <c r="B189" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -19985,34 +19960,34 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>380445</v>
+        <v>380352</v>
       </c>
       <c r="R189" t="n">
-        <v>6919917</v>
+        <v>6919913</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20071,10 +20046,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>124450845</v>
+        <v>124458046</v>
       </c>
       <c r="B190" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20087,21 +20062,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20111,10 +20086,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>380205</v>
+        <v>380533</v>
       </c>
       <c r="R190" t="n">
-        <v>6920378</v>
+        <v>6920142</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20173,7 +20148,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>124450666</v>
+        <v>124460951</v>
       </c>
       <c r="B191" t="n">
         <v>74901</v>
@@ -20209,14 +20184,14 @@
       <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>380227</v>
+        <v>380307</v>
       </c>
       <c r="R191" t="n">
-        <v>6920340</v>
+        <v>6919967</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20263,19 +20238,19 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>124455134</v>
+        <v>124461736</v>
       </c>
       <c r="B192" t="n">
         <v>74901</v>
@@ -20311,14 +20286,14 @@
       <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>380311</v>
+        <v>380232</v>
       </c>
       <c r="R192" t="n">
-        <v>6920245</v>
+        <v>6919808</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20377,10 +20352,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>124458743</v>
+        <v>124455453</v>
       </c>
       <c r="B193" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -20393,21 +20368,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20417,10 +20392,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>380542</v>
+        <v>380326</v>
       </c>
       <c r="R193" t="n">
-        <v>6920184</v>
+        <v>6920218</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20453,11 +20428,6 @@
       <c r="AA193" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20484,10 +20454,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>124451802</v>
+        <v>124464292</v>
       </c>
       <c r="B194" t="n">
-        <v>79428</v>
+        <v>57513</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -20500,34 +20470,39 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>380197</v>
+        <v>380275</v>
       </c>
       <c r="R194" t="n">
-        <v>6920479</v>
+        <v>6919775</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20574,22 +20549,22 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>124469751</v>
+        <v>124451885</v>
       </c>
       <c r="B195" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -20602,34 +20577,34 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>380490</v>
+        <v>380189</v>
       </c>
       <c r="R195" t="n">
-        <v>6919937</v>
+        <v>6920488</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20688,10 +20663,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>124469907</v>
+        <v>124456832</v>
       </c>
       <c r="B196" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -20704,34 +20679,34 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>380452</v>
+        <v>380443</v>
       </c>
       <c r="R196" t="n">
-        <v>6919913</v>
+        <v>6920118</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20778,22 +20753,22 @@
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>124470184</v>
+        <v>124470555</v>
       </c>
       <c r="B197" t="n">
-        <v>91030</v>
+        <v>82597</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -20806,21 +20781,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20830,10 +20805,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>380516</v>
+        <v>380431</v>
       </c>
       <c r="R197" t="n">
-        <v>6920004</v>
+        <v>6920068</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20892,10 +20867,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>124470707</v>
+        <v>124469547</v>
       </c>
       <c r="B198" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -20908,42 +20883,37 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>380367</v>
+        <v>380452</v>
       </c>
       <c r="R198" t="n">
-        <v>6920058</v>
+        <v>6919913</v>
       </c>
       <c r="S198" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -20987,22 +20957,22 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>124464970</v>
+        <v>124459815</v>
       </c>
       <c r="B199" t="n">
-        <v>57513</v>
+        <v>79428</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -21015,42 +20985,37 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>380255</v>
+        <v>380445</v>
       </c>
       <c r="R199" t="n">
-        <v>6919561</v>
+        <v>6919917</v>
       </c>
       <c r="S199" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -21106,10 +21071,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>124463365</v>
+        <v>124468547</v>
       </c>
       <c r="B200" t="n">
-        <v>79399</v>
+        <v>74901</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -21122,34 +21087,34 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>380199</v>
+        <v>380356</v>
       </c>
       <c r="R200" t="n">
-        <v>6919723</v>
+        <v>6919817</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21208,10 +21173,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>124451984</v>
+        <v>124459134</v>
       </c>
       <c r="B201" t="n">
-        <v>79399</v>
+        <v>74901</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -21224,34 +21189,34 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>380203</v>
+        <v>380559</v>
       </c>
       <c r="R201" t="n">
-        <v>6920482</v>
+        <v>6919947</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21310,10 +21275,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>124464651</v>
+        <v>124450578</v>
       </c>
       <c r="B202" t="n">
-        <v>79399</v>
+        <v>91030</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -21326,34 +21291,34 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>229821</v>
+        <v>5432</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>380251</v>
+        <v>380227</v>
       </c>
       <c r="R202" t="n">
-        <v>6919658</v>
+        <v>6920340</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21400,22 +21365,22 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>124451569</v>
+        <v>124458651</v>
       </c>
       <c r="B203" t="n">
-        <v>79399</v>
+        <v>91030</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -21428,34 +21393,34 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>229821</v>
+        <v>5432</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>380184</v>
+        <v>380569</v>
       </c>
       <c r="R203" t="n">
-        <v>6920434</v>
+        <v>6920058</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21514,10 +21479,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>124468916</v>
+        <v>124465167</v>
       </c>
       <c r="B204" t="n">
-        <v>78151</v>
+        <v>78194</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -21526,38 +21491,38 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>498</v>
+        <v>6437</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>380343</v>
+        <v>380244</v>
       </c>
       <c r="R204" t="n">
-        <v>6919896</v>
+        <v>6919577</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21604,22 +21569,22 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>124457866</v>
+        <v>124452627</v>
       </c>
       <c r="B205" t="n">
-        <v>78151</v>
+        <v>74901</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -21628,38 +21593,38 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>498</v>
+        <v>6440</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>380537</v>
+        <v>380217</v>
       </c>
       <c r="R205" t="n">
-        <v>6920199</v>
+        <v>6920440</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21718,10 +21683,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>124464471</v>
+        <v>124454665</v>
       </c>
       <c r="B206" t="n">
-        <v>78194</v>
+        <v>74901</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -21734,21 +21699,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -21758,10 +21723,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>380243</v>
+        <v>380258</v>
       </c>
       <c r="R206" t="n">
-        <v>6919687</v>
+        <v>6920309</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21820,10 +21785,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>124458651</v>
+        <v>124450300</v>
       </c>
       <c r="B207" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -21836,21 +21801,21 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -21860,10 +21825,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>380569</v>
+        <v>380182</v>
       </c>
       <c r="R207" t="n">
-        <v>6920058</v>
+        <v>6920316</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21922,10 +21887,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>124455206</v>
+        <v>124457836</v>
       </c>
       <c r="B208" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -21938,21 +21903,21 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -21962,10 +21927,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>380311</v>
+        <v>380542</v>
       </c>
       <c r="R208" t="n">
-        <v>6920231</v>
+        <v>6920184</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22012,22 +21977,22 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>124465526</v>
+        <v>124450902</v>
       </c>
       <c r="B209" t="n">
-        <v>79399</v>
+        <v>57529</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -22040,34 +22005,39 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Risåsvallen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>380252</v>
+        <v>380227</v>
       </c>
       <c r="R209" t="n">
-        <v>6919535</v>
+        <v>6920340</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -22102,6 +22072,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>Troligen spillkråka.</t>
+        </is>
+      </c>
       <c r="AD209" t="b">
         <v>0</v>
       </c>
@@ -22114,19 +22089,19 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>124464493</v>
+        <v>124465389</v>
       </c>
       <c r="B210" t="n">
         <v>79399</v>
@@ -22166,10 +22141,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>380243</v>
+        <v>380244</v>
       </c>
       <c r="R210" t="n">
-        <v>6919687</v>
+        <v>6919577</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22216,19 +22191,19 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>124464559</v>
+        <v>124464901</v>
       </c>
       <c r="B211" t="n">
         <v>79399</v>
@@ -22268,10 +22243,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>380236</v>
+        <v>380249</v>
       </c>
       <c r="R211" t="n">
-        <v>6919671</v>
+        <v>6919607</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22330,10 +22305,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>124470299</v>
+        <v>124470184</v>
       </c>
       <c r="B212" t="n">
-        <v>56722</v>
+        <v>91030</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -22342,43 +22317,38 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P212" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>380495</v>
+        <v>380516</v>
       </c>
       <c r="R212" t="n">
-        <v>6920029</v>
+        <v>6920004</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22437,7 +22407,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>124454665</v>
+        <v>124450737</v>
       </c>
       <c r="B213" t="n">
         <v>74901</v>
@@ -22473,14 +22443,14 @@
       <c r="I213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>380258</v>
+        <v>380210</v>
       </c>
       <c r="R213" t="n">
-        <v>6920309</v>
+        <v>6920378</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22539,10 +22509,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>124470070</v>
+        <v>124470397</v>
       </c>
       <c r="B214" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -22555,34 +22525,34 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>380533</v>
+        <v>380506</v>
       </c>
       <c r="R214" t="n">
-        <v>6919979</v>
+        <v>6920061</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22629,19 +22599,19 @@
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>124455453</v>
+        <v>124455134</v>
       </c>
       <c r="B215" t="n">
         <v>74901</v>
@@ -22681,10 +22651,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>380326</v>
+        <v>380311</v>
       </c>
       <c r="R215" t="n">
-        <v>6920218</v>
+        <v>6920245</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22731,22 +22701,22 @@
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>124456129</v>
+        <v>124458476</v>
       </c>
       <c r="B216" t="n">
-        <v>78905</v>
+        <v>74901</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -22759,34 +22729,34 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>967</v>
+        <v>6440</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>380326</v>
+        <v>380581</v>
       </c>
       <c r="R216" t="n">
-        <v>6920218</v>
+        <v>6920056</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22833,22 +22803,22 @@
       <c r="AT216" t="inlineStr"/>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>124452491</v>
+        <v>124467947</v>
       </c>
       <c r="B217" t="n">
-        <v>78810</v>
+        <v>78194</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -22861,34 +22831,34 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>380208</v>
+        <v>380361</v>
       </c>
       <c r="R217" t="n">
-        <v>6920481</v>
+        <v>6919740</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22923,6 +22893,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD217" t="b">
         <v>0</v>
       </c>
@@ -22935,22 +22910,22 @@
       <c r="AT217" t="inlineStr"/>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>124464466</v>
+        <v>124464121</v>
       </c>
       <c r="B218" t="n">
-        <v>78905</v>
+        <v>57513</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -22963,34 +22938,39 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>967</v>
+        <v>100109</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>380243</v>
+        <v>380419</v>
       </c>
       <c r="R218" t="n">
-        <v>6919687</v>
+        <v>6919960</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23037,22 +23017,22 @@
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>124470397</v>
+        <v>124460224</v>
       </c>
       <c r="B219" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -23065,34 +23045,39 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P219" t="inlineStr">
         <is>
           <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>380506</v>
+        <v>380374</v>
       </c>
       <c r="R219" t="n">
-        <v>6920061</v>
+        <v>6919982</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23151,10 +23136,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>124457317</v>
+        <v>124459042</v>
       </c>
       <c r="B220" t="n">
-        <v>79428</v>
+        <v>74901</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -23167,21 +23152,21 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -23191,10 +23176,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>380547</v>
+        <v>380571</v>
       </c>
       <c r="R220" t="n">
-        <v>6920163</v>
+        <v>6919993</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23253,7 +23238,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>124455022</v>
+        <v>124470598</v>
       </c>
       <c r="B221" t="n">
         <v>79428</v>
@@ -23289,14 +23274,14 @@
       <c r="I221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>380292</v>
+        <v>380506</v>
       </c>
       <c r="R221" t="n">
-        <v>6920288</v>
+        <v>6920061</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23331,6 +23316,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD221" t="b">
         <v>0</v>
       </c>
@@ -23343,22 +23333,22 @@
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>124461477</v>
+        <v>124469751</v>
       </c>
       <c r="B222" t="n">
-        <v>79399</v>
+        <v>74901</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -23371,21 +23361,21 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -23395,10 +23385,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>380285</v>
+        <v>380490</v>
       </c>
       <c r="R222" t="n">
-        <v>6919895</v>
+        <v>6919937</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23457,10 +23447,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>124470598</v>
+        <v>124463365</v>
       </c>
       <c r="B223" t="n">
-        <v>79428</v>
+        <v>79399</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -23473,34 +23463,34 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>380506</v>
+        <v>380199</v>
       </c>
       <c r="R223" t="n">
-        <v>6920061</v>
+        <v>6919723</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23535,11 +23525,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC223" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD223" t="b">
         <v>0</v>
       </c>
@@ -23552,22 +23537,22 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>124469088</v>
+        <v>124471016</v>
       </c>
       <c r="B224" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -23580,34 +23565,39 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>380352</v>
+        <v>380506</v>
       </c>
       <c r="R224" t="n">
-        <v>6919913</v>
+        <v>6920061</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23654,22 +23644,22 @@
       <c r="AT224" t="inlineStr"/>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>124457836</v>
+        <v>124452423</v>
       </c>
       <c r="B225" t="n">
-        <v>78810</v>
+        <v>56725</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -23678,38 +23668,43 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P225" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>380542</v>
+        <v>380227</v>
       </c>
       <c r="R225" t="n">
-        <v>6920184</v>
+        <v>6920340</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23768,10 +23763,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>124460258</v>
+        <v>124455776</v>
       </c>
       <c r="B226" t="n">
-        <v>79428</v>
+        <v>57513</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -23784,34 +23779,39 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>380365</v>
+        <v>380326</v>
       </c>
       <c r="R226" t="n">
-        <v>6919996</v>
+        <v>6920218</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23858,19 +23858,19 @@
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>124468302</v>
+        <v>124470707</v>
       </c>
       <c r="B227" t="n">
         <v>57513</v>
@@ -23911,14 +23911,14 @@
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>380265</v>
+        <v>380367</v>
       </c>
       <c r="R227" t="n">
-        <v>6919774</v>
+        <v>6920058</v>
       </c>
       <c r="S227" t="n">
         <v>15</v>
@@ -23977,10 +23977,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>124466026</v>
+        <v>124459060</v>
       </c>
       <c r="B228" t="n">
-        <v>79399</v>
+        <v>57513</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -23993,34 +23993,39 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>380303</v>
+        <v>380571</v>
       </c>
       <c r="R228" t="n">
-        <v>6919598</v>
+        <v>6919993</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24055,11 +24060,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC228" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD228" t="b">
         <v>0</v>
       </c>
@@ -24072,22 +24072,22 @@
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>124463640</v>
+        <v>124464047</v>
       </c>
       <c r="B229" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -24100,21 +24100,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -24124,10 +24124,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>380218</v>
+        <v>380267</v>
       </c>
       <c r="R229" t="n">
-        <v>6919722</v>
+        <v>6919731</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24186,10 +24186,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>124450300</v>
+        <v>124455206</v>
       </c>
       <c r="B230" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -24202,34 +24202,34 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>380182</v>
+        <v>380311</v>
       </c>
       <c r="R230" t="n">
-        <v>6920316</v>
+        <v>6920231</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24288,7 +24288,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>124455774</v>
+        <v>124455456</v>
       </c>
       <c r="B231" t="n">
         <v>74901</v>
@@ -24324,14 +24324,14 @@
       <c r="I231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>380356</v>
+        <v>380314</v>
       </c>
       <c r="R231" t="n">
-        <v>6920172</v>
+        <v>6920201</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24390,10 +24390,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>124464329</v>
+        <v>124463640</v>
       </c>
       <c r="B232" t="n">
-        <v>78194</v>
+        <v>79428</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -24406,21 +24406,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -24430,10 +24430,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>380268</v>
+        <v>380218</v>
       </c>
       <c r="R232" t="n">
-        <v>6919685</v>
+        <v>6919722</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24492,10 +24492,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>124466494</v>
+        <v>124450518</v>
       </c>
       <c r="B233" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -24508,42 +24508,37 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
-      <c r="M233" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>380344</v>
+        <v>380202</v>
       </c>
       <c r="R233" t="n">
-        <v>6919654</v>
+        <v>6920332</v>
       </c>
       <c r="S233" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -24599,10 +24594,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>124459060</v>
+        <v>124458282</v>
       </c>
       <c r="B234" t="n">
-        <v>57513</v>
+        <v>78151</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -24611,43 +24606,38 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
-      <c r="M234" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P234" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>380571</v>
+        <v>380588</v>
       </c>
       <c r="R234" t="n">
-        <v>6919993</v>
+        <v>6920110</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -24706,10 +24696,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>124459456</v>
+        <v>124451984</v>
       </c>
       <c r="B235" t="n">
-        <v>91032</v>
+        <v>79399</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -24722,34 +24712,34 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>5442</v>
+        <v>229821</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>380561</v>
+        <v>380203</v>
       </c>
       <c r="R235" t="n">
-        <v>6919930</v>
+        <v>6920482</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -24796,12 +24786,12 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
@@ -24915,7 +24905,7 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>124450415</v>
+        <v>124461108</v>
       </c>
       <c r="B237" t="n">
         <v>74901</v>
@@ -24951,14 +24941,14 @@
       <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>380202</v>
+        <v>380308</v>
       </c>
       <c r="R237" t="n">
-        <v>6920332</v>
+        <v>6919925</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -24991,6 +24981,11 @@
       <c r="AA237" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC237" t="inlineStr">
+        <is>
+          <t>På basen avsågad gran. Grov stubbe</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -25017,10 +25012,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>124469377</v>
+        <v>124455022</v>
       </c>
       <c r="B238" t="n">
-        <v>74901</v>
+        <v>79428</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -25033,34 +25028,34 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>380435</v>
+        <v>380292</v>
       </c>
       <c r="R238" t="n">
-        <v>6919916</v>
+        <v>6920288</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -25119,10 +25114,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>124471016</v>
+        <v>124469915</v>
       </c>
       <c r="B239" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -25135,39 +25130,34 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
-      <c r="M239" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>380506</v>
+        <v>380521</v>
       </c>
       <c r="R239" t="n">
-        <v>6920061</v>
+        <v>6919962</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -25214,22 +25204,22 @@
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>124451326</v>
+        <v>124469377</v>
       </c>
       <c r="B240" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -25242,39 +25232,34 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
-      <c r="M240" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>380227</v>
+        <v>380435</v>
       </c>
       <c r="R240" t="n">
-        <v>6920340</v>
+        <v>6919916</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -25321,22 +25306,22 @@
       <c r="AT240" t="inlineStr"/>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>124450902</v>
+        <v>124469907</v>
       </c>
       <c r="B241" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -25349,39 +25334,34 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
-      <c r="M241" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P241" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>380227</v>
+        <v>380452</v>
       </c>
       <c r="R241" t="n">
-        <v>6920340</v>
+        <v>6919913</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -25414,11 +25394,6 @@
       <c r="AA241" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC241" t="inlineStr">
-        <is>
-          <t>Troligen spillkråka.</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -25445,10 +25420,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>124458357</v>
+        <v>124456372</v>
       </c>
       <c r="B242" t="n">
-        <v>57666</v>
+        <v>74901</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -25461,42 +25436,37 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
-      <c r="M242" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>380586</v>
+        <v>380368</v>
       </c>
       <c r="R242" t="n">
-        <v>6920100</v>
+        <v>6920107</v>
       </c>
       <c r="S242" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -25552,7 +25522,7 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>124464047</v>
+        <v>124452491</v>
       </c>
       <c r="B243" t="n">
         <v>78810</v>
@@ -25588,14 +25558,14 @@
       <c r="I243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>380267</v>
+        <v>380208</v>
       </c>
       <c r="R243" t="n">
-        <v>6919731</v>
+        <v>6920481</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -25654,10 +25624,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>124455220</v>
+        <v>124457601</v>
       </c>
       <c r="B244" t="n">
-        <v>74901</v>
+        <v>78151</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -25666,38 +25636,38 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>6440</v>
+        <v>498</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>380311</v>
+        <v>380544</v>
       </c>
       <c r="R244" t="n">
-        <v>6920231</v>
+        <v>6920188</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25756,10 +25726,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>124465167</v>
+        <v>124450845</v>
       </c>
       <c r="B245" t="n">
-        <v>78194</v>
+        <v>78810</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -25772,21 +25742,21 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -25796,10 +25766,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>380244</v>
+        <v>380205</v>
       </c>
       <c r="R245" t="n">
-        <v>6919577</v>
+        <v>6920378</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25846,22 +25816,22 @@
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>124452627</v>
+        <v>124466026</v>
       </c>
       <c r="B246" t="n">
-        <v>74901</v>
+        <v>79399</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -25874,34 +25844,34 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>380217</v>
+        <v>380303</v>
       </c>
       <c r="R246" t="n">
-        <v>6920440</v>
+        <v>6919598</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25936,6 +25906,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC246" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD246" t="b">
         <v>0</v>
       </c>
@@ -25948,22 +25923,22 @@
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>124470234</v>
+        <v>124465009</v>
       </c>
       <c r="B247" t="n">
-        <v>82597</v>
+        <v>79399</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -25976,21 +25951,21 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>1312</v>
+        <v>229821</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -26000,10 +25975,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>380506</v>
+        <v>380267</v>
       </c>
       <c r="R247" t="n">
-        <v>6920009</v>
+        <v>6919764</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -26038,6 +26013,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC247" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD247" t="b">
         <v>0</v>
       </c>
@@ -26050,22 +26030,22 @@
       <c r="AT247" t="inlineStr"/>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>124459134</v>
+        <v>124460965</v>
       </c>
       <c r="B248" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -26078,34 +26058,34 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>380559</v>
+        <v>380307</v>
       </c>
       <c r="R248" t="n">
-        <v>6919947</v>
+        <v>6919967</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -26164,10 +26144,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>124451893</v>
+        <v>124464321</v>
       </c>
       <c r="B249" t="n">
-        <v>5196</v>
+        <v>77738</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -26176,38 +26156,38 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>105930</v>
+        <v>6487</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>380227</v>
+        <v>380268</v>
       </c>
       <c r="R249" t="n">
-        <v>6920340</v>
+        <v>6919685</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -26254,22 +26234,22 @@
       <c r="AT249" t="inlineStr"/>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>124459042</v>
+        <v>124460258</v>
       </c>
       <c r="B250" t="n">
-        <v>74901</v>
+        <v>79428</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -26282,34 +26262,34 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>380571</v>
+        <v>380365</v>
       </c>
       <c r="R250" t="n">
-        <v>6919993</v>
+        <v>6919996</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -26368,10 +26348,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>124470555</v>
+        <v>124464329</v>
       </c>
       <c r="B251" t="n">
-        <v>82597</v>
+        <v>78194</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -26384,21 +26364,21 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>1312</v>
+        <v>6437</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -26408,10 +26388,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>380431</v>
+        <v>380268</v>
       </c>
       <c r="R251" t="n">
-        <v>6920068</v>
+        <v>6919685</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -26470,10 +26450,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>124458046</v>
+        <v>124451893</v>
       </c>
       <c r="B252" t="n">
-        <v>74901</v>
+        <v>5196</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -26482,38 +26462,38 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>6440</v>
+        <v>105930</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
       <c r="P252" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>380533</v>
+        <v>380227</v>
       </c>
       <c r="R252" t="n">
-        <v>6920142</v>
+        <v>6920340</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -26560,22 +26540,22 @@
       <c r="AT252" t="inlineStr"/>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>124461108</v>
+        <v>124470646</v>
       </c>
       <c r="B253" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -26588,34 +26568,34 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>380308</v>
+        <v>380402</v>
       </c>
       <c r="R253" t="n">
-        <v>6919925</v>
+        <v>6920044</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -26648,11 +26628,6 @@
       <c r="AA253" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC253" t="inlineStr">
-        <is>
-          <t>På basen avsågad gran. Grov stubbe</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -26679,10 +26654,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>124464842</v>
+        <v>124457866</v>
       </c>
       <c r="B254" t="n">
-        <v>79428</v>
+        <v>78151</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -26691,25 +26666,25 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>6453</v>
+        <v>498</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -26719,10 +26694,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>380237</v>
+        <v>380537</v>
       </c>
       <c r="R254" t="n">
-        <v>6919621</v>
+        <v>6920199</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26781,10 +26756,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>124455776</v>
+        <v>124460611</v>
       </c>
       <c r="B255" t="n">
-        <v>57513</v>
+        <v>78905</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -26797,39 +26772,34 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>100109</v>
+        <v>967</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
-      <c r="M255" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>380326</v>
+        <v>380335</v>
       </c>
       <c r="R255" t="n">
-        <v>6920218</v>
+        <v>6920000</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26888,7 +26858,7 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>124466302</v>
+        <v>124461646</v>
       </c>
       <c r="B256" t="n">
         <v>57513</v>
@@ -26929,14 +26899,14 @@
       </c>
       <c r="P256" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>380345</v>
+        <v>380239</v>
       </c>
       <c r="R256" t="n">
-        <v>6919632</v>
+        <v>6919828</v>
       </c>
       <c r="S256" t="n">
         <v>15</v>
@@ -26995,10 +26965,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>124465389</v>
+        <v>124470742</v>
       </c>
       <c r="B257" t="n">
-        <v>79399</v>
+        <v>57513</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -27011,37 +26981,42 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>380244</v>
+        <v>380369</v>
       </c>
       <c r="R257" t="n">
-        <v>6919577</v>
+        <v>6920032</v>
       </c>
       <c r="S257" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T257" t="inlineStr">
         <is>
@@ -27085,22 +27060,22 @@
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>124464681</v>
+        <v>124470806</v>
       </c>
       <c r="B258" t="n">
-        <v>79399</v>
+        <v>57513</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -27113,37 +27088,42 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P258" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>380264</v>
+        <v>380340</v>
       </c>
       <c r="R258" t="n">
-        <v>6919665</v>
+        <v>6920036</v>
       </c>
       <c r="S258" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T258" t="inlineStr">
         <is>
@@ -27199,10 +27179,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>124450737</v>
+        <v>124466302</v>
       </c>
       <c r="B259" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -27215,37 +27195,42 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>380210</v>
+        <v>380345</v>
       </c>
       <c r="R259" t="n">
-        <v>6920378</v>
+        <v>6919632</v>
       </c>
       <c r="S259" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T259" t="inlineStr">
         <is>
@@ -27301,10 +27286,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>124461736</v>
+        <v>124459287</v>
       </c>
       <c r="B260" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -27317,34 +27302,39 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>380232</v>
+        <v>380561</v>
       </c>
       <c r="R260" t="n">
-        <v>6919808</v>
+        <v>6919930</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -27391,22 +27381,22 @@
       <c r="AT260" t="inlineStr"/>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>124452261</v>
+        <v>124451172</v>
       </c>
       <c r="B261" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -27419,21 +27409,21 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -27443,10 +27433,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>380227</v>
+        <v>380184</v>
       </c>
       <c r="R261" t="n">
-        <v>6920340</v>
+        <v>6920434</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -27493,22 +27483,22 @@
       <c r="AT261" t="inlineStr"/>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>124470404</v>
+        <v>124464471</v>
       </c>
       <c r="B262" t="n">
-        <v>91030</v>
+        <v>78194</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -27521,21 +27511,21 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>5432</v>
+        <v>6437</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -27545,10 +27535,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>380471</v>
+        <v>380243</v>
       </c>
       <c r="R262" t="n">
-        <v>6920069</v>
+        <v>6919687</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -27607,10 +27597,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>124451885</v>
+        <v>124451837</v>
       </c>
       <c r="B263" t="n">
-        <v>91030</v>
+        <v>78194</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -27623,21 +27613,21 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>5432</v>
+        <v>6437</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
@@ -27647,10 +27637,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>380189</v>
+        <v>380197</v>
       </c>
       <c r="R263" t="n">
-        <v>6920488</v>
+        <v>6920479</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -27709,10 +27699,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>124451172</v>
+        <v>124464651</v>
       </c>
       <c r="B264" t="n">
-        <v>74901</v>
+        <v>79399</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -27725,34 +27715,34 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>380184</v>
+        <v>380251</v>
       </c>
       <c r="R264" t="n">
-        <v>6920434</v>
+        <v>6919658</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27811,10 +27801,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>124470485</v>
+        <v>124456676</v>
       </c>
       <c r="B265" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -27827,37 +27817,42 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P265" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>380446</v>
+        <v>380434</v>
       </c>
       <c r="R265" t="n">
-        <v>6920059</v>
+        <v>6920123</v>
       </c>
       <c r="S265" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T265" t="inlineStr">
         <is>
@@ -27913,10 +27908,10 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>124469915</v>
+        <v>124470146</v>
       </c>
       <c r="B266" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -27929,37 +27924,42 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P266" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>380521</v>
+        <v>380527</v>
       </c>
       <c r="R266" t="n">
-        <v>6919962</v>
+        <v>6919988</v>
       </c>
       <c r="S266" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T266" t="inlineStr">
         <is>
@@ -28015,10 +28015,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>124467947</v>
+        <v>124464559</v>
       </c>
       <c r="B267" t="n">
-        <v>78194</v>
+        <v>79399</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -28031,21 +28031,21 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
@@ -28055,10 +28055,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>380361</v>
+        <v>380236</v>
       </c>
       <c r="R267" t="n">
-        <v>6919740</v>
+        <v>6919671</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -28093,11 +28093,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC267" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD267" t="b">
         <v>0</v>
       </c>
@@ -28110,22 +28105,22 @@
       <c r="AT267" t="inlineStr"/>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>124450518</v>
+        <v>124464970</v>
       </c>
       <c r="B268" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -28138,37 +28133,42 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P268" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>380202</v>
+        <v>380255</v>
       </c>
       <c r="R268" t="n">
-        <v>6920332</v>
+        <v>6919561</v>
       </c>
       <c r="S268" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T268" t="inlineStr">
         <is>
@@ -28224,7 +28224,7 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>124464292</v>
+        <v>124466494</v>
       </c>
       <c r="B269" t="n">
         <v>57513</v>
@@ -28265,17 +28265,17 @@
       </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>380275</v>
+        <v>380344</v>
       </c>
       <c r="R269" t="n">
-        <v>6919775</v>
+        <v>6919654</v>
       </c>
       <c r="S269" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T269" t="inlineStr">
         <is>
@@ -28319,22 +28319,22 @@
       <c r="AT269" t="inlineStr"/>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>124460224</v>
+        <v>124454876</v>
       </c>
       <c r="B270" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -28347,39 +28347,34 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
-      <c r="M270" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P270" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>380374</v>
+        <v>380290</v>
       </c>
       <c r="R270" t="n">
-        <v>6919982</v>
+        <v>6920272</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -28426,22 +28421,22 @@
       <c r="AT270" t="inlineStr"/>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>124457601</v>
+        <v>124464842</v>
       </c>
       <c r="B271" t="n">
-        <v>78151</v>
+        <v>79428</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -28450,25 +28445,25 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>498</v>
+        <v>6453</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
@@ -28478,10 +28473,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>380544</v>
+        <v>380237</v>
       </c>
       <c r="R271" t="n">
-        <v>6920188</v>
+        <v>6919621</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -28540,10 +28535,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>124460951</v>
+        <v>124470070</v>
       </c>
       <c r="B272" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -28556,34 +28551,34 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
       <c r="P272" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>380307</v>
+        <v>380533</v>
       </c>
       <c r="R272" t="n">
-        <v>6919967</v>
+        <v>6919979</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -28744,7 +28739,7 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>124588108</v>
+        <v>124588913</v>
       </c>
       <c r="B274" t="n">
         <v>57513</v>
@@ -28780,19 +28775,19 @@
       <c r="I274" t="inlineStr"/>
       <c r="M274" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P274" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>380223</v>
+        <v>380140</v>
       </c>
       <c r="R274" t="n">
-        <v>6920277</v>
+        <v>6919839</v>
       </c>
       <c r="S274" t="n">
         <v>15</v>
@@ -28851,7 +28846,7 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>124588913</v>
+        <v>124588108</v>
       </c>
       <c r="B275" t="n">
         <v>57513</v>
@@ -28887,19 +28882,19 @@
       <c r="I275" t="inlineStr"/>
       <c r="M275" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P275" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>380140</v>
+        <v>380223</v>
       </c>
       <c r="R275" t="n">
-        <v>6919839</v>
+        <v>6920277</v>
       </c>
       <c r="S275" t="n">
         <v>15</v>

--- a/artfynd/A 32573-2024 artfynd.xlsx
+++ b/artfynd/A 32573-2024 artfynd.xlsx
@@ -16105,10 +16105,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>124461477</v>
+        <v>124470555</v>
       </c>
       <c r="B152" t="n">
-        <v>79399</v>
+        <v>82597</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16121,34 +16121,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>229821</v>
+        <v>1312</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>380285</v>
+        <v>380431</v>
       </c>
       <c r="R152" t="n">
-        <v>6919895</v>
+        <v>6920068</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16207,10 +16207,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>124451569</v>
+        <v>124465863</v>
       </c>
       <c r="B153" t="n">
-        <v>79399</v>
+        <v>78151</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16219,38 +16219,38 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>229821</v>
+        <v>498</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Risåsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>380184</v>
+        <v>380296</v>
       </c>
       <c r="R153" t="n">
-        <v>6920434</v>
+        <v>6919585</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16309,10 +16309,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>124468182</v>
+        <v>124455134</v>
       </c>
       <c r="B154" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16325,42 +16325,37 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>380265</v>
+        <v>380311</v>
       </c>
       <c r="R154" t="n">
-        <v>6919774</v>
+        <v>6920245</v>
       </c>
       <c r="S154" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -16416,10 +16411,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>124456046</v>
+        <v>124465389</v>
       </c>
       <c r="B155" t="n">
-        <v>91032</v>
+        <v>79399</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16432,34 +16427,34 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>5442</v>
+        <v>229821</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>380326</v>
+        <v>380244</v>
       </c>
       <c r="R155" t="n">
-        <v>6920218</v>
+        <v>6919577</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16492,11 +16487,6 @@
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16523,10 +16513,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>124451574</v>
+        <v>124464493</v>
       </c>
       <c r="B156" t="n">
-        <v>79428</v>
+        <v>79399</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16539,34 +16529,34 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>380184</v>
+        <v>380243</v>
       </c>
       <c r="R156" t="n">
-        <v>6920434</v>
+        <v>6919687</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16625,7 +16615,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>124468916</v>
+        <v>124457601</v>
       </c>
       <c r="B157" t="n">
         <v>78151</v>
@@ -16661,14 +16651,14 @@
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>380343</v>
+        <v>380544</v>
       </c>
       <c r="R157" t="n">
-        <v>6919896</v>
+        <v>6920188</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16727,10 +16717,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>124457317</v>
+        <v>124450737</v>
       </c>
       <c r="B158" t="n">
-        <v>79428</v>
+        <v>74901</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16743,34 +16733,34 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>380547</v>
+        <v>380210</v>
       </c>
       <c r="R158" t="n">
-        <v>6920163</v>
+        <v>6920378</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16829,7 +16819,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>124470485</v>
+        <v>124458046</v>
       </c>
       <c r="B159" t="n">
         <v>74901</v>
@@ -16869,10 +16859,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>380446</v>
+        <v>380533</v>
       </c>
       <c r="R159" t="n">
-        <v>6920059</v>
+        <v>6920142</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16931,7 +16921,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>124450666</v>
+        <v>124460951</v>
       </c>
       <c r="B160" t="n">
         <v>74901</v>
@@ -16967,14 +16957,14 @@
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>380227</v>
+        <v>380307</v>
       </c>
       <c r="R160" t="n">
-        <v>6920340</v>
+        <v>6919967</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17021,22 +17011,22 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>124458357</v>
+        <v>124464292</v>
       </c>
       <c r="B161" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17049,27 +17039,27 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="M161" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
@@ -17078,13 +17068,13 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>380586</v>
+        <v>380275</v>
       </c>
       <c r="R161" t="n">
-        <v>6920100</v>
+        <v>6919775</v>
       </c>
       <c r="S161" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -17128,22 +17118,22 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>124458172</v>
+        <v>124464681</v>
       </c>
       <c r="B162" t="n">
-        <v>78151</v>
+        <v>79399</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17152,25 +17142,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>498</v>
+        <v>229821</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17180,10 +17170,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>380562</v>
+        <v>380264</v>
       </c>
       <c r="R162" t="n">
-        <v>6920118</v>
+        <v>6919665</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17242,10 +17232,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>124470732</v>
+        <v>124458282</v>
       </c>
       <c r="B163" t="n">
-        <v>74901</v>
+        <v>78151</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17254,38 +17244,38 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6440</v>
+        <v>498</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>380372</v>
+        <v>380588</v>
       </c>
       <c r="R163" t="n">
-        <v>6920042</v>
+        <v>6920110</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17344,10 +17334,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>124463210</v>
+        <v>124450666</v>
       </c>
       <c r="B164" t="n">
-        <v>79428</v>
+        <v>74901</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17360,34 +17350,34 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>380189</v>
+        <v>380227</v>
       </c>
       <c r="R164" t="n">
-        <v>6919766</v>
+        <v>6920340</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17434,22 +17424,22 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>124450415</v>
+        <v>124467947</v>
       </c>
       <c r="B165" t="n">
-        <v>74901</v>
+        <v>78194</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17462,21 +17452,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17486,10 +17476,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>380202</v>
+        <v>380361</v>
       </c>
       <c r="R165" t="n">
-        <v>6920332</v>
+        <v>6919740</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17524,6 +17514,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD165" t="b">
         <v>0</v>
       </c>
@@ -17536,22 +17531,22 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>124451802</v>
+        <v>124464901</v>
       </c>
       <c r="B166" t="n">
-        <v>79428</v>
+        <v>79399</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17564,34 +17559,34 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>380197</v>
+        <v>380249</v>
       </c>
       <c r="R166" t="n">
-        <v>6920479</v>
+        <v>6919607</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17650,10 +17645,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>124464493</v>
+        <v>124470146</v>
       </c>
       <c r="B167" t="n">
-        <v>79399</v>
+        <v>57513</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17666,37 +17661,42 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>380243</v>
+        <v>380527</v>
       </c>
       <c r="R167" t="n">
-        <v>6919687</v>
+        <v>6919988</v>
       </c>
       <c r="S167" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -17752,10 +17752,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>124465526</v>
+        <v>124458509</v>
       </c>
       <c r="B168" t="n">
-        <v>79399</v>
+        <v>57513</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -17768,34 +17768,39 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Risåsvallen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>380252</v>
+        <v>380542</v>
       </c>
       <c r="R168" t="n">
-        <v>6919535</v>
+        <v>6920184</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17830,6 +17835,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>Miljöbilder, talltita.</t>
+        </is>
+      </c>
       <c r="AD168" t="b">
         <v>0</v>
       </c>
@@ -17842,22 +17852,22 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>124470234</v>
+        <v>124459456</v>
       </c>
       <c r="B169" t="n">
-        <v>82597</v>
+        <v>91032</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -17870,34 +17880,34 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>1312</v>
+        <v>5442</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>380506</v>
+        <v>380561</v>
       </c>
       <c r="R169" t="n">
-        <v>6920009</v>
+        <v>6919930</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17944,22 +17954,22 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>124464466</v>
+        <v>124458743</v>
       </c>
       <c r="B170" t="n">
-        <v>78905</v>
+        <v>91030</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -17972,34 +17982,34 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>967</v>
+        <v>5432</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>380243</v>
+        <v>380542</v>
       </c>
       <c r="R170" t="n">
-        <v>6919687</v>
+        <v>6920184</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18034,6 +18044,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD170" t="b">
         <v>0</v>
       </c>
@@ -18046,22 +18061,22 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>124456129</v>
+        <v>124458651</v>
       </c>
       <c r="B171" t="n">
-        <v>78905</v>
+        <v>91030</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18074,34 +18089,34 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>967</v>
+        <v>5432</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>380326</v>
+        <v>380569</v>
       </c>
       <c r="R171" t="n">
-        <v>6920218</v>
+        <v>6920058</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18148,22 +18163,22 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>124470299</v>
+        <v>124469377</v>
       </c>
       <c r="B172" t="n">
-        <v>56722</v>
+        <v>74901</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18172,43 +18187,38 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>100138</v>
+        <v>6440</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>380495</v>
+        <v>380435</v>
       </c>
       <c r="R172" t="n">
-        <v>6920029</v>
+        <v>6919916</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18267,10 +18277,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>124451326</v>
+        <v>124454876</v>
       </c>
       <c r="B173" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18283,39 +18293,34 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P173" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>380227</v>
+        <v>380290</v>
       </c>
       <c r="R173" t="n">
-        <v>6920340</v>
+        <v>6920272</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18362,22 +18367,22 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>124459456</v>
+        <v>124451802</v>
       </c>
       <c r="B174" t="n">
-        <v>91032</v>
+        <v>79428</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18390,34 +18395,34 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>380561</v>
+        <v>380197</v>
       </c>
       <c r="R174" t="n">
-        <v>6919930</v>
+        <v>6920479</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18464,22 +18469,22 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>124456704</v>
+        <v>124459060</v>
       </c>
       <c r="B175" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -18492,34 +18497,39 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>380385</v>
+        <v>380571</v>
       </c>
       <c r="R175" t="n">
-        <v>6920091</v>
+        <v>6919993</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18554,11 +18564,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
-        </is>
-      </c>
       <c r="AD175" t="b">
         <v>0</v>
       </c>
@@ -18571,22 +18576,22 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>124458743</v>
+        <v>124452423</v>
       </c>
       <c r="B176" t="n">
-        <v>91030</v>
+        <v>56725</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -18595,38 +18600,43 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>5432</v>
+        <v>102613</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P176" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>380542</v>
+        <v>380227</v>
       </c>
       <c r="R176" t="n">
-        <v>6920184</v>
+        <v>6920340</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18659,11 +18669,6 @@
       <c r="AA176" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -18690,10 +18695,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>124467914</v>
+        <v>124456129</v>
       </c>
       <c r="B177" t="n">
-        <v>77738</v>
+        <v>78905</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -18706,34 +18711,34 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6487</v>
+        <v>967</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>380361</v>
+        <v>380326</v>
       </c>
       <c r="R177" t="n">
-        <v>6919740</v>
+        <v>6920218</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18766,11 +18771,6 @@
       <c r="AA177" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -18797,10 +18797,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>124455220</v>
+        <v>124466026</v>
       </c>
       <c r="B178" t="n">
-        <v>74901</v>
+        <v>79399</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -18813,34 +18813,34 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>380311</v>
+        <v>380303</v>
       </c>
       <c r="R178" t="n">
-        <v>6920231</v>
+        <v>6919598</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18875,6 +18875,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD178" t="b">
         <v>0</v>
       </c>
@@ -18887,22 +18892,22 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>124455774</v>
+        <v>124470646</v>
       </c>
       <c r="B179" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -18915,34 +18920,34 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>380356</v>
+        <v>380402</v>
       </c>
       <c r="R179" t="n">
-        <v>6920172</v>
+        <v>6920044</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19001,10 +19006,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>124452261</v>
+        <v>124454979</v>
       </c>
       <c r="B180" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -19017,21 +19022,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19041,10 +19046,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>380227</v>
+        <v>380289</v>
       </c>
       <c r="R180" t="n">
-        <v>6920340</v>
+        <v>6920290</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19077,6 +19082,11 @@
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19103,10 +19113,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>124468469</v>
+        <v>124460611</v>
       </c>
       <c r="B181" t="n">
-        <v>57513</v>
+        <v>78905</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -19119,42 +19129,37 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100109</v>
+        <v>967</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>380324</v>
+        <v>380335</v>
       </c>
       <c r="R181" t="n">
-        <v>6919803</v>
+        <v>6920000</v>
       </c>
       <c r="S181" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -19198,22 +19203,22 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124465863</v>
+        <v>124451326</v>
       </c>
       <c r="B182" t="n">
-        <v>78151</v>
+        <v>57513</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -19222,38 +19227,43 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>498</v>
+        <v>100109</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Risåsvallen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>380296</v>
+        <v>380227</v>
       </c>
       <c r="R182" t="n">
-        <v>6919585</v>
+        <v>6920340</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19300,22 +19310,22 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124464681</v>
+        <v>124471016</v>
       </c>
       <c r="B183" t="n">
-        <v>79399</v>
+        <v>57513</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -19328,34 +19338,39 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>380264</v>
+        <v>380506</v>
       </c>
       <c r="R183" t="n">
-        <v>6919665</v>
+        <v>6920061</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19402,22 +19417,22 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124457605</v>
+        <v>124456697</v>
       </c>
       <c r="B184" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -19430,39 +19445,34 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>380542</v>
+        <v>380443</v>
       </c>
       <c r="R184" t="n">
-        <v>6920184</v>
+        <v>6920118</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19497,11 +19507,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området.</t>
-        </is>
-      </c>
       <c r="AD184" t="b">
         <v>0</v>
       </c>
@@ -19514,22 +19519,22 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124455096</v>
+        <v>124456046</v>
       </c>
       <c r="B185" t="n">
-        <v>5196</v>
+        <v>91032</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -19538,43 +19543,38 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>105930</v>
+        <v>5442</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P185" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>380323</v>
+        <v>380326</v>
       </c>
       <c r="R185" t="n">
-        <v>6920260</v>
+        <v>6920218</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19609,6 +19609,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området.</t>
+        </is>
+      </c>
       <c r="AD185" t="b">
         <v>0</v>
       </c>
@@ -19621,22 +19626,22 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124454979</v>
+        <v>124455220</v>
       </c>
       <c r="B186" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -19649,21 +19654,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19673,10 +19678,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>380289</v>
+        <v>380311</v>
       </c>
       <c r="R186" t="n">
-        <v>6920290</v>
+        <v>6920231</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19711,11 +19716,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC186" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
-        </is>
-      </c>
       <c r="AD186" t="b">
         <v>0</v>
       </c>
@@ -19728,22 +19728,22 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124470404</v>
+        <v>124467914</v>
       </c>
       <c r="B187" t="n">
-        <v>91030</v>
+        <v>77738</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -19756,21 +19756,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>5432</v>
+        <v>6487</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19780,10 +19780,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>380471</v>
+        <v>380361</v>
       </c>
       <c r="R187" t="n">
-        <v>6920069</v>
+        <v>6919740</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19818,6 +19818,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD187" t="b">
         <v>0</v>
       </c>
@@ -19830,22 +19835,22 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124470737</v>
+        <v>124450902</v>
       </c>
       <c r="B188" t="n">
-        <v>91030</v>
+        <v>57529</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -19858,34 +19863,39 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>380506</v>
+        <v>380227</v>
       </c>
       <c r="R188" t="n">
-        <v>6920061</v>
+        <v>6920340</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19918,6 +19928,11 @@
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>Troligen spillkråka.</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -19944,10 +19959,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124469088</v>
+        <v>124465526</v>
       </c>
       <c r="B189" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -19960,34 +19975,34 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Risåsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>380352</v>
+        <v>380252</v>
       </c>
       <c r="R189" t="n">
-        <v>6919913</v>
+        <v>6919535</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20046,10 +20061,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>124458046</v>
+        <v>124464559</v>
       </c>
       <c r="B190" t="n">
-        <v>74901</v>
+        <v>79399</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20062,21 +20077,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20086,10 +20101,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>380533</v>
+        <v>380236</v>
       </c>
       <c r="R190" t="n">
-        <v>6920142</v>
+        <v>6919671</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20148,10 +20163,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>124460951</v>
+        <v>124460052</v>
       </c>
       <c r="B191" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20164,34 +20179,39 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>380307</v>
+        <v>380419</v>
       </c>
       <c r="R191" t="n">
-        <v>6919967</v>
+        <v>6919960</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20238,22 +20258,22 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>124461736</v>
+        <v>124468182</v>
       </c>
       <c r="B192" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20266,37 +20286,42 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P192" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>380232</v>
+        <v>380265</v>
       </c>
       <c r="R192" t="n">
-        <v>6919808</v>
+        <v>6919774</v>
       </c>
       <c r="S192" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -20352,10 +20377,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>124455453</v>
+        <v>124470070</v>
       </c>
       <c r="B193" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -20368,34 +20393,34 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>380326</v>
+        <v>380533</v>
       </c>
       <c r="R193" t="n">
-        <v>6920218</v>
+        <v>6919979</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20442,22 +20467,22 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>124464292</v>
+        <v>124457866</v>
       </c>
       <c r="B194" t="n">
-        <v>57513</v>
+        <v>78151</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -20466,43 +20491,38 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P194" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>380275</v>
+        <v>380537</v>
       </c>
       <c r="R194" t="n">
-        <v>6919775</v>
+        <v>6920199</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20549,22 +20569,22 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>124451885</v>
+        <v>124458172</v>
       </c>
       <c r="B195" t="n">
-        <v>91030</v>
+        <v>78151</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -20573,38 +20593,38 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>5432</v>
+        <v>498</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>380189</v>
+        <v>380562</v>
       </c>
       <c r="R195" t="n">
-        <v>6920488</v>
+        <v>6920118</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20663,10 +20683,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>124456832</v>
+        <v>124454665</v>
       </c>
       <c r="B196" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -20679,21 +20699,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20703,10 +20723,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>380443</v>
+        <v>380258</v>
       </c>
       <c r="R196" t="n">
-        <v>6920118</v>
+        <v>6920309</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20765,10 +20785,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>124470555</v>
+        <v>124455096</v>
       </c>
       <c r="B197" t="n">
-        <v>82597</v>
+        <v>5196</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -20777,38 +20797,43 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>1312</v>
+        <v>105930</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>380431</v>
+        <v>380323</v>
       </c>
       <c r="R197" t="n">
-        <v>6920068</v>
+        <v>6920260</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20867,10 +20892,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>124469547</v>
+        <v>124470485</v>
       </c>
       <c r="B198" t="n">
-        <v>88359</v>
+        <v>74901</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -20883,34 +20908,34 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>380452</v>
+        <v>380446</v>
       </c>
       <c r="R198" t="n">
-        <v>6919913</v>
+        <v>6920059</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20957,22 +20982,22 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>124459815</v>
+        <v>124450415</v>
       </c>
       <c r="B199" t="n">
-        <v>79428</v>
+        <v>74901</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -20985,34 +21010,34 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>380445</v>
+        <v>380202</v>
       </c>
       <c r="R199" t="n">
-        <v>6919917</v>
+        <v>6920332</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21071,7 +21096,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>124468547</v>
+        <v>124458476</v>
       </c>
       <c r="B200" t="n">
         <v>74901</v>
@@ -21107,14 +21132,14 @@
       <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>380356</v>
+        <v>380581</v>
       </c>
       <c r="R200" t="n">
-        <v>6919817</v>
+        <v>6920056</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21173,7 +21198,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>124459134</v>
+        <v>124451172</v>
       </c>
       <c r="B201" t="n">
         <v>74901</v>
@@ -21209,14 +21234,14 @@
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>380559</v>
+        <v>380184</v>
       </c>
       <c r="R201" t="n">
-        <v>6919947</v>
+        <v>6920434</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21275,10 +21300,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>124450578</v>
+        <v>124470598</v>
       </c>
       <c r="B202" t="n">
-        <v>91030</v>
+        <v>79428</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -21291,34 +21316,34 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>380227</v>
+        <v>380506</v>
       </c>
       <c r="R202" t="n">
-        <v>6920340</v>
+        <v>6920061</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21351,6 +21376,11 @@
       <c r="AA202" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -21377,10 +21407,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>124458651</v>
+        <v>124456676</v>
       </c>
       <c r="B203" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -21393,37 +21423,42 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P203" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>380569</v>
+        <v>380434</v>
       </c>
       <c r="R203" t="n">
-        <v>6920058</v>
+        <v>6920123</v>
       </c>
       <c r="S203" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -21479,10 +21514,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>124465167</v>
+        <v>124460258</v>
       </c>
       <c r="B204" t="n">
-        <v>78194</v>
+        <v>79428</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -21495,34 +21530,34 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>380244</v>
+        <v>380365</v>
       </c>
       <c r="R204" t="n">
-        <v>6919577</v>
+        <v>6919996</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21569,19 +21604,19 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>124452627</v>
+        <v>124450300</v>
       </c>
       <c r="B205" t="n">
         <v>74901</v>
@@ -21617,14 +21652,14 @@
       <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>380217</v>
+        <v>380182</v>
       </c>
       <c r="R205" t="n">
-        <v>6920440</v>
+        <v>6920316</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21683,10 +21718,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>124454665</v>
+        <v>124457836</v>
       </c>
       <c r="B206" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -21699,34 +21734,34 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>380258</v>
+        <v>380542</v>
       </c>
       <c r="R206" t="n">
-        <v>6920309</v>
+        <v>6920184</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21773,22 +21808,22 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>124450300</v>
+        <v>124466494</v>
       </c>
       <c r="B207" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -21801,37 +21836,42 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>380182</v>
+        <v>380344</v>
       </c>
       <c r="R207" t="n">
-        <v>6920316</v>
+        <v>6919654</v>
       </c>
       <c r="S207" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -21887,10 +21927,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>124457836</v>
+        <v>124463365</v>
       </c>
       <c r="B208" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -21903,34 +21943,34 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>380542</v>
+        <v>380199</v>
       </c>
       <c r="R208" t="n">
-        <v>6920184</v>
+        <v>6919723</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21977,22 +22017,22 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>124450902</v>
+        <v>124470404</v>
       </c>
       <c r="B209" t="n">
-        <v>57529</v>
+        <v>91030</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -22005,39 +22045,34 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
-      <c r="M209" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>380227</v>
+        <v>380471</v>
       </c>
       <c r="R209" t="n">
-        <v>6920340</v>
+        <v>6920069</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -22072,11 +22107,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>Troligen spillkråka.</t>
-        </is>
-      </c>
       <c r="AD209" t="b">
         <v>0</v>
       </c>
@@ -22089,22 +22119,22 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>124465389</v>
+        <v>124469751</v>
       </c>
       <c r="B210" t="n">
-        <v>79399</v>
+        <v>74901</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -22117,34 +22147,34 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>380244</v>
+        <v>380490</v>
       </c>
       <c r="R210" t="n">
-        <v>6919577</v>
+        <v>6919937</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22191,22 +22221,22 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>124464901</v>
+        <v>124469088</v>
       </c>
       <c r="B211" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -22219,34 +22249,34 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>380249</v>
+        <v>380352</v>
       </c>
       <c r="R211" t="n">
-        <v>6919607</v>
+        <v>6919913</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22305,10 +22335,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>124470184</v>
+        <v>124451984</v>
       </c>
       <c r="B212" t="n">
-        <v>91030</v>
+        <v>79399</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -22321,34 +22351,34 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>5432</v>
+        <v>229821</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>380516</v>
+        <v>380203</v>
       </c>
       <c r="R212" t="n">
-        <v>6920004</v>
+        <v>6920482</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22407,10 +22437,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>124450737</v>
+        <v>124456704</v>
       </c>
       <c r="B213" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -22423,21 +22453,21 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -22447,10 +22477,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>380210</v>
+        <v>380385</v>
       </c>
       <c r="R213" t="n">
-        <v>6920378</v>
+        <v>6920091</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22485,6 +22515,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD213" t="b">
         <v>0</v>
       </c>
@@ -22497,22 +22532,22 @@
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>124470397</v>
+        <v>124470737</v>
       </c>
       <c r="B214" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -22525,21 +22560,21 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -22611,10 +22646,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>124455134</v>
+        <v>124470184</v>
       </c>
       <c r="B215" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -22627,34 +22662,34 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>380311</v>
+        <v>380516</v>
       </c>
       <c r="R215" t="n">
-        <v>6920245</v>
+        <v>6920004</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22713,10 +22748,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>124458476</v>
+        <v>124464466</v>
       </c>
       <c r="B216" t="n">
-        <v>74901</v>
+        <v>78905</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -22729,21 +22764,21 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>6440</v>
+        <v>967</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -22753,10 +22788,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>380581</v>
+        <v>380243</v>
       </c>
       <c r="R216" t="n">
-        <v>6920056</v>
+        <v>6919687</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22815,10 +22850,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>124467947</v>
+        <v>124463640</v>
       </c>
       <c r="B217" t="n">
-        <v>78194</v>
+        <v>79428</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -22831,21 +22866,21 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -22855,10 +22890,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>380361</v>
+        <v>380218</v>
       </c>
       <c r="R217" t="n">
-        <v>6919740</v>
+        <v>6919722</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22893,11 +22928,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC217" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD217" t="b">
         <v>0</v>
       </c>
@@ -22910,22 +22940,22 @@
       <c r="AT217" t="inlineStr"/>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>124464121</v>
+        <v>124451574</v>
       </c>
       <c r="B218" t="n">
-        <v>57513</v>
+        <v>79428</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -22938,39 +22968,34 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
-      <c r="M218" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>380419</v>
+        <v>380184</v>
       </c>
       <c r="R218" t="n">
-        <v>6919960</v>
+        <v>6920434</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23017,22 +23042,22 @@
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>124460224</v>
+        <v>124455453</v>
       </c>
       <c r="B219" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -23045,39 +23070,34 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>380374</v>
+        <v>380326</v>
       </c>
       <c r="R219" t="n">
-        <v>6919982</v>
+        <v>6920218</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23136,10 +23156,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>124459042</v>
+        <v>124451893</v>
       </c>
       <c r="B220" t="n">
-        <v>74901</v>
+        <v>5196</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -23148,38 +23168,38 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6440</v>
+        <v>105930</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>380571</v>
+        <v>380227</v>
       </c>
       <c r="R220" t="n">
-        <v>6919993</v>
+        <v>6920340</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23226,22 +23246,22 @@
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>124470598</v>
+        <v>124465009</v>
       </c>
       <c r="B221" t="n">
-        <v>79428</v>
+        <v>79399</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -23254,34 +23274,34 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>380506</v>
+        <v>380267</v>
       </c>
       <c r="R221" t="n">
-        <v>6920061</v>
+        <v>6919764</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23345,10 +23365,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>124469751</v>
+        <v>124451885</v>
       </c>
       <c r="B222" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -23361,34 +23381,34 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>380490</v>
+        <v>380189</v>
       </c>
       <c r="R222" t="n">
-        <v>6919937</v>
+        <v>6920488</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23447,10 +23467,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>124463365</v>
+        <v>124450845</v>
       </c>
       <c r="B223" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -23463,21 +23483,21 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -23487,10 +23507,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>380199</v>
+        <v>380205</v>
       </c>
       <c r="R223" t="n">
-        <v>6919723</v>
+        <v>6920378</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23549,10 +23569,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>124471016</v>
+        <v>124469547</v>
       </c>
       <c r="B224" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -23565,39 +23585,34 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
-      <c r="M224" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P224" t="inlineStr">
         <is>
           <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>380506</v>
+        <v>380452</v>
       </c>
       <c r="R224" t="n">
-        <v>6920061</v>
+        <v>6919913</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23656,10 +23671,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>124452423</v>
+        <v>124459815</v>
       </c>
       <c r="B225" t="n">
-        <v>56725</v>
+        <v>79428</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -23668,43 +23683,38 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>102613</v>
+        <v>6453</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
-      <c r="M225" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P225" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>380227</v>
+        <v>380445</v>
       </c>
       <c r="R225" t="n">
-        <v>6920340</v>
+        <v>6919917</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23751,22 +23761,22 @@
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>124455776</v>
+        <v>124465167</v>
       </c>
       <c r="B226" t="n">
-        <v>57513</v>
+        <v>78194</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -23779,39 +23789,34 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
-      <c r="M226" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>380326</v>
+        <v>380244</v>
       </c>
       <c r="R226" t="n">
-        <v>6920218</v>
+        <v>6919577</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23870,10 +23875,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>124470707</v>
+        <v>124470732</v>
       </c>
       <c r="B227" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -23886,42 +23891,37 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P227" t="inlineStr">
         <is>
           <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>380367</v>
+        <v>380372</v>
       </c>
       <c r="R227" t="n">
-        <v>6920058</v>
+        <v>6920042</v>
       </c>
       <c r="S227" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -23977,10 +23977,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>124459060</v>
+        <v>124464471</v>
       </c>
       <c r="B228" t="n">
-        <v>57513</v>
+        <v>78194</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -23993,39 +23993,34 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>380571</v>
+        <v>380243</v>
       </c>
       <c r="R228" t="n">
-        <v>6919993</v>
+        <v>6919687</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24084,10 +24079,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>124464047</v>
+        <v>124455456</v>
       </c>
       <c r="B229" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -24100,34 +24095,34 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>380267</v>
+        <v>380314</v>
       </c>
       <c r="R229" t="n">
-        <v>6919731</v>
+        <v>6920201</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24186,10 +24181,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>124455206</v>
+        <v>124452491</v>
       </c>
       <c r="B230" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -24202,21 +24197,21 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -24226,10 +24221,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>380311</v>
+        <v>380208</v>
       </c>
       <c r="R230" t="n">
-        <v>6920231</v>
+        <v>6920481</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24288,10 +24283,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>124455456</v>
+        <v>124451837</v>
       </c>
       <c r="B231" t="n">
-        <v>74901</v>
+        <v>78194</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -24304,21 +24299,21 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -24328,10 +24323,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>380314</v>
+        <v>380197</v>
       </c>
       <c r="R231" t="n">
-        <v>6920201</v>
+        <v>6920479</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24390,10 +24385,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>124463640</v>
+        <v>124469907</v>
       </c>
       <c r="B232" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -24406,34 +24401,34 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>380218</v>
+        <v>380452</v>
       </c>
       <c r="R232" t="n">
-        <v>6919722</v>
+        <v>6919913</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24480,22 +24475,22 @@
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>124450518</v>
+        <v>124470397</v>
       </c>
       <c r="B233" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -24508,34 +24503,34 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>380202</v>
+        <v>380506</v>
       </c>
       <c r="R233" t="n">
-        <v>6920332</v>
+        <v>6920061</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -24582,22 +24577,22 @@
       <c r="AT233" t="inlineStr"/>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>124458282</v>
+        <v>124455774</v>
       </c>
       <c r="B234" t="n">
-        <v>78151</v>
+        <v>74901</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -24606,38 +24601,38 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>498</v>
+        <v>6440</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>380588</v>
+        <v>380356</v>
       </c>
       <c r="R234" t="n">
-        <v>6920110</v>
+        <v>6920172</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -24696,10 +24691,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>124451984</v>
+        <v>124452261</v>
       </c>
       <c r="B235" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -24712,21 +24707,21 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -24736,10 +24731,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>380203</v>
+        <v>380227</v>
       </c>
       <c r="R235" t="n">
-        <v>6920482</v>
+        <v>6920340</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -24786,22 +24781,22 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>124456502</v>
+        <v>124461736</v>
       </c>
       <c r="B236" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -24814,34 +24809,34 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>380385</v>
+        <v>380232</v>
       </c>
       <c r="R236" t="n">
-        <v>6920091</v>
+        <v>6919808</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24876,11 +24871,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC236" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området.</t>
-        </is>
-      </c>
       <c r="AD236" t="b">
         <v>0</v>
       </c>
@@ -24893,22 +24883,22 @@
       <c r="AT236" t="inlineStr"/>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>124461108</v>
+        <v>124455206</v>
       </c>
       <c r="B237" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -24921,21 +24911,21 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -24945,10 +24935,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>380308</v>
+        <v>380311</v>
       </c>
       <c r="R237" t="n">
-        <v>6919925</v>
+        <v>6920231</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -24981,11 +24971,6 @@
       <c r="AA237" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC237" t="inlineStr">
-        <is>
-          <t>På basen avsågad gran. Grov stubbe</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -25012,10 +24997,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>124455022</v>
+        <v>124450518</v>
       </c>
       <c r="B238" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -25028,34 +25013,34 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>380292</v>
+        <v>380202</v>
       </c>
       <c r="R238" t="n">
-        <v>6920288</v>
+        <v>6920332</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -25114,7 +25099,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>124469915</v>
+        <v>124459134</v>
       </c>
       <c r="B239" t="n">
         <v>74901</v>
@@ -25150,14 +25135,14 @@
       <c r="I239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>380521</v>
+        <v>380559</v>
       </c>
       <c r="R239" t="n">
-        <v>6919962</v>
+        <v>6919947</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -25216,7 +25201,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>124469377</v>
+        <v>124456372</v>
       </c>
       <c r="B240" t="n">
         <v>74901</v>
@@ -25252,14 +25237,14 @@
       <c r="I240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>380435</v>
+        <v>380368</v>
       </c>
       <c r="R240" t="n">
-        <v>6919916</v>
+        <v>6920107</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -25318,10 +25303,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>124469907</v>
+        <v>124459287</v>
       </c>
       <c r="B241" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -25334,34 +25319,39 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P241" t="inlineStr">
         <is>
           <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>380452</v>
+        <v>380561</v>
       </c>
       <c r="R241" t="n">
-        <v>6919913</v>
+        <v>6919930</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -25420,10 +25410,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>124456372</v>
+        <v>124458357</v>
       </c>
       <c r="B242" t="n">
-        <v>74901</v>
+        <v>57666</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -25436,37 +25426,42 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>380368</v>
+        <v>380586</v>
       </c>
       <c r="R242" t="n">
-        <v>6920107</v>
+        <v>6920100</v>
       </c>
       <c r="S242" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -25522,10 +25517,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>124452491</v>
+        <v>124463210</v>
       </c>
       <c r="B243" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -25538,34 +25533,34 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>380208</v>
+        <v>380189</v>
       </c>
       <c r="R243" t="n">
-        <v>6920481</v>
+        <v>6919766</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -25624,10 +25619,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>124457601</v>
+        <v>124470707</v>
       </c>
       <c r="B244" t="n">
-        <v>78151</v>
+        <v>57513</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -25636,41 +25631,46 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>498</v>
+        <v>100109</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>380544</v>
+        <v>380367</v>
       </c>
       <c r="R244" t="n">
-        <v>6920188</v>
+        <v>6920058</v>
       </c>
       <c r="S244" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
@@ -25726,10 +25726,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>124450845</v>
+        <v>124470806</v>
       </c>
       <c r="B245" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -25742,37 +25742,42 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>380205</v>
+        <v>380340</v>
       </c>
       <c r="R245" t="n">
-        <v>6920378</v>
+        <v>6920036</v>
       </c>
       <c r="S245" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -25828,10 +25833,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>124466026</v>
+        <v>124468469</v>
       </c>
       <c r="B246" t="n">
-        <v>79399</v>
+        <v>57513</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -25844,37 +25849,42 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P246" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>380303</v>
+        <v>380324</v>
       </c>
       <c r="R246" t="n">
-        <v>6919598</v>
+        <v>6919803</v>
       </c>
       <c r="S246" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -25904,11 +25914,6 @@
       <c r="AA246" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC246" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -25923,22 +25928,22 @@
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>124465009</v>
+        <v>124470299</v>
       </c>
       <c r="B247" t="n">
-        <v>79399</v>
+        <v>56722</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -25947,38 +25952,43 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P247" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>380267</v>
+        <v>380495</v>
       </c>
       <c r="R247" t="n">
-        <v>6919764</v>
+        <v>6920029</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -26013,11 +26023,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC247" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD247" t="b">
         <v>0</v>
       </c>
@@ -26030,12 +26035,12 @@
       <c r="AT247" t="inlineStr"/>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
@@ -26144,10 +26149,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>124464321</v>
+        <v>124468916</v>
       </c>
       <c r="B249" t="n">
-        <v>77738</v>
+        <v>78151</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -26156,38 +26161,38 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>6487</v>
+        <v>498</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>380268</v>
+        <v>380343</v>
       </c>
       <c r="R249" t="n">
-        <v>6919685</v>
+        <v>6919896</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -26246,10 +26251,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>124460258</v>
+        <v>124464329</v>
       </c>
       <c r="B250" t="n">
-        <v>79428</v>
+        <v>78194</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -26262,34 +26267,34 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>380365</v>
+        <v>380268</v>
       </c>
       <c r="R250" t="n">
-        <v>6919996</v>
+        <v>6919685</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -26348,10 +26353,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>124464329</v>
+        <v>124451569</v>
       </c>
       <c r="B251" t="n">
-        <v>78194</v>
+        <v>79399</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -26364,34 +26369,34 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
       <c r="P251" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>380268</v>
+        <v>380184</v>
       </c>
       <c r="R251" t="n">
-        <v>6919685</v>
+        <v>6920434</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -26450,10 +26455,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>124451893</v>
+        <v>124464321</v>
       </c>
       <c r="B252" t="n">
-        <v>5196</v>
+        <v>77738</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -26462,38 +26467,38 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>105930</v>
+        <v>6487</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
       <c r="P252" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>380227</v>
+        <v>380268</v>
       </c>
       <c r="R252" t="n">
-        <v>6920340</v>
+        <v>6919685</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -26540,22 +26545,22 @@
       <c r="AT252" t="inlineStr"/>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>124470646</v>
+        <v>124461646</v>
       </c>
       <c r="B253" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -26568,37 +26573,42 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>380402</v>
+        <v>380239</v>
       </c>
       <c r="R253" t="n">
-        <v>6920044</v>
+        <v>6919828</v>
       </c>
       <c r="S253" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T253" t="inlineStr">
         <is>
@@ -26654,10 +26664,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>124457866</v>
+        <v>124466302</v>
       </c>
       <c r="B254" t="n">
-        <v>78151</v>
+        <v>57513</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -26666,41 +26676,46 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>498</v>
+        <v>100109</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P254" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>380537</v>
+        <v>380345</v>
       </c>
       <c r="R254" t="n">
-        <v>6920199</v>
+        <v>6919632</v>
       </c>
       <c r="S254" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T254" t="inlineStr">
         <is>
@@ -26756,10 +26771,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>124460611</v>
+        <v>124468547</v>
       </c>
       <c r="B255" t="n">
-        <v>78905</v>
+        <v>74901</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -26772,34 +26787,34 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>967</v>
+        <v>6440</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>380335</v>
+        <v>380356</v>
       </c>
       <c r="R255" t="n">
-        <v>6920000</v>
+        <v>6919817</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26846,22 +26861,22 @@
       <c r="AT255" t="inlineStr"/>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>124461646</v>
+        <v>124461108</v>
       </c>
       <c r="B256" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -26874,42 +26889,37 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
-      <c r="M256" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P256" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>380239</v>
+        <v>380308</v>
       </c>
       <c r="R256" t="n">
-        <v>6919828</v>
+        <v>6919925</v>
       </c>
       <c r="S256" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T256" t="inlineStr">
         <is>
@@ -26939,6 +26949,11 @@
       <c r="AA256" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC256" t="inlineStr">
+        <is>
+          <t>På basen avsågad gran. Grov stubbe</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -26965,10 +26980,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>124470742</v>
+        <v>124457317</v>
       </c>
       <c r="B257" t="n">
-        <v>57513</v>
+        <v>79428</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -26981,42 +26996,37 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
-      <c r="M257" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>380369</v>
+        <v>380547</v>
       </c>
       <c r="R257" t="n">
-        <v>6920032</v>
+        <v>6920163</v>
       </c>
       <c r="S257" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T257" t="inlineStr">
         <is>
@@ -27072,10 +27082,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>124470806</v>
+        <v>124464651</v>
       </c>
       <c r="B258" t="n">
-        <v>57513</v>
+        <v>79399</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -27088,42 +27098,37 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
-      <c r="M258" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P258" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>380340</v>
+        <v>380251</v>
       </c>
       <c r="R258" t="n">
-        <v>6920036</v>
+        <v>6919658</v>
       </c>
       <c r="S258" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T258" t="inlineStr">
         <is>
@@ -27179,7 +27184,7 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>124466302</v>
+        <v>124470742</v>
       </c>
       <c r="B259" t="n">
         <v>57513</v>
@@ -27224,10 +27229,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>380345</v>
+        <v>380369</v>
       </c>
       <c r="R259" t="n">
-        <v>6919632</v>
+        <v>6920032</v>
       </c>
       <c r="S259" t="n">
         <v>15</v>
@@ -27286,7 +27291,7 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>124459287</v>
+        <v>124460224</v>
       </c>
       <c r="B260" t="n">
         <v>57513</v>
@@ -27322,7 +27327,7 @@
       <c r="I260" t="inlineStr"/>
       <c r="M260" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P260" t="inlineStr">
@@ -27331,10 +27336,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>380561</v>
+        <v>380374</v>
       </c>
       <c r="R260" t="n">
-        <v>6919930</v>
+        <v>6919982</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -27393,10 +27398,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>124451172</v>
+        <v>124470234</v>
       </c>
       <c r="B261" t="n">
-        <v>74901</v>
+        <v>82597</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -27409,34 +27414,34 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
       <c r="P261" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>380184</v>
+        <v>380506</v>
       </c>
       <c r="R261" t="n">
-        <v>6920434</v>
+        <v>6920009</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -27495,10 +27500,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>124464471</v>
+        <v>124456502</v>
       </c>
       <c r="B262" t="n">
-        <v>78194</v>
+        <v>78810</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -27511,34 +27516,34 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>380243</v>
+        <v>380385</v>
       </c>
       <c r="R262" t="n">
-        <v>6919687</v>
+        <v>6920091</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -27573,6 +27578,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC262" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området.</t>
+        </is>
+      </c>
       <c r="AD262" t="b">
         <v>0</v>
       </c>
@@ -27585,22 +27595,22 @@
       <c r="AT262" t="inlineStr"/>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>124451837</v>
+        <v>124459042</v>
       </c>
       <c r="B263" t="n">
-        <v>78194</v>
+        <v>74901</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -27613,34 +27623,34 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>380197</v>
+        <v>380571</v>
       </c>
       <c r="R263" t="n">
-        <v>6920479</v>
+        <v>6919993</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -27699,10 +27709,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>124464651</v>
+        <v>124469915</v>
       </c>
       <c r="B264" t="n">
-        <v>79399</v>
+        <v>74901</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -27715,21 +27725,21 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
@@ -27739,10 +27749,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>380251</v>
+        <v>380521</v>
       </c>
       <c r="R264" t="n">
-        <v>6919658</v>
+        <v>6919962</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27801,10 +27811,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>124456676</v>
+        <v>124464842</v>
       </c>
       <c r="B265" t="n">
-        <v>57513</v>
+        <v>79428</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -27817,42 +27827,37 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
-      <c r="M265" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P265" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>380434</v>
+        <v>380237</v>
       </c>
       <c r="R265" t="n">
-        <v>6920123</v>
+        <v>6919621</v>
       </c>
       <c r="S265" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T265" t="inlineStr">
         <is>
@@ -27908,10 +27913,10 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>124470146</v>
+        <v>124464047</v>
       </c>
       <c r="B266" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -27924,42 +27929,37 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
-      <c r="M266" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P266" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>380527</v>
+        <v>380267</v>
       </c>
       <c r="R266" t="n">
-        <v>6919988</v>
+        <v>6919731</v>
       </c>
       <c r="S266" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T266" t="inlineStr">
         <is>
@@ -28015,10 +28015,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>124464559</v>
+        <v>124450578</v>
       </c>
       <c r="B267" t="n">
-        <v>79399</v>
+        <v>91030</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -28031,34 +28031,34 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>229821</v>
+        <v>5432</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
       <c r="P267" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>380236</v>
+        <v>380227</v>
       </c>
       <c r="R267" t="n">
-        <v>6919671</v>
+        <v>6920340</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -28105,22 +28105,22 @@
       <c r="AT267" t="inlineStr"/>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>124464970</v>
+        <v>124455022</v>
       </c>
       <c r="B268" t="n">
-        <v>57513</v>
+        <v>79428</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -28133,42 +28133,37 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
-      <c r="M268" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P268" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>380255</v>
+        <v>380292</v>
       </c>
       <c r="R268" t="n">
-        <v>6919561</v>
+        <v>6920288</v>
       </c>
       <c r="S268" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T268" t="inlineStr">
         <is>
@@ -28224,10 +28219,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>124466494</v>
+        <v>124452627</v>
       </c>
       <c r="B269" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -28240,42 +28235,37 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
-      <c r="M269" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>380344</v>
+        <v>380217</v>
       </c>
       <c r="R269" t="n">
-        <v>6919654</v>
+        <v>6920440</v>
       </c>
       <c r="S269" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T269" t="inlineStr">
         <is>
@@ -28331,10 +28321,10 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>124454876</v>
+        <v>124455776</v>
       </c>
       <c r="B270" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -28347,34 +28337,39 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P270" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>380290</v>
+        <v>380326</v>
       </c>
       <c r="R270" t="n">
-        <v>6920272</v>
+        <v>6920218</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -28421,22 +28416,22 @@
       <c r="AT270" t="inlineStr"/>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>124464842</v>
+        <v>124464970</v>
       </c>
       <c r="B271" t="n">
-        <v>79428</v>
+        <v>57513</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -28449,37 +28444,42 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P271" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>380237</v>
+        <v>380255</v>
       </c>
       <c r="R271" t="n">
-        <v>6919621</v>
+        <v>6919561</v>
       </c>
       <c r="S271" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T271" t="inlineStr">
         <is>
@@ -28535,10 +28535,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>124470070</v>
+        <v>124461477</v>
       </c>
       <c r="B272" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -28551,34 +28551,34 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
       <c r="P272" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>380533</v>
+        <v>380285</v>
       </c>
       <c r="R272" t="n">
-        <v>6919979</v>
+        <v>6919895</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -28637,10 +28637,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>124589633</v>
+        <v>124588108</v>
       </c>
       <c r="B273" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -28653,37 +28653,42 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P273" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>380181</v>
+        <v>380223</v>
       </c>
       <c r="R273" t="n">
-        <v>6920018</v>
+        <v>6920277</v>
       </c>
       <c r="S273" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T273" t="inlineStr">
         <is>
@@ -28846,10 +28851,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>124588108</v>
+        <v>124589633</v>
       </c>
       <c r="B275" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -28862,42 +28867,37 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
-      <c r="M275" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P275" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>380223</v>
+        <v>380181</v>
       </c>
       <c r="R275" t="n">
-        <v>6920277</v>
+        <v>6920018</v>
       </c>
       <c r="S275" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T275" t="inlineStr">
         <is>

--- a/artfynd/A 32573-2024 artfynd.xlsx
+++ b/artfynd/A 32573-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY275"/>
+  <dimension ref="A1:AY289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17232,10 +17232,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>124458282</v>
+        <v>124450666</v>
       </c>
       <c r="B163" t="n">
-        <v>78151</v>
+        <v>74901</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17244,38 +17244,38 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>498</v>
+        <v>6440</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>380588</v>
+        <v>380227</v>
       </c>
       <c r="R163" t="n">
-        <v>6920110</v>
+        <v>6920340</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17322,22 +17322,22 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>124450666</v>
+        <v>124467947</v>
       </c>
       <c r="B164" t="n">
-        <v>74901</v>
+        <v>78194</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17350,34 +17350,34 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>380227</v>
+        <v>380361</v>
       </c>
       <c r="R164" t="n">
-        <v>6920340</v>
+        <v>6919740</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17410,6 +17410,11 @@
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17436,10 +17441,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>124467947</v>
+        <v>124458743</v>
       </c>
       <c r="B165" t="n">
-        <v>78194</v>
+        <v>91030</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17452,34 +17457,34 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6437</v>
+        <v>5432</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>380361</v>
+        <v>380542</v>
       </c>
       <c r="R165" t="n">
-        <v>6919740</v>
+        <v>6920184</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17516,7 +17521,7 @@
       </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17543,10 +17548,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>124464901</v>
+        <v>124459456</v>
       </c>
       <c r="B166" t="n">
-        <v>79399</v>
+        <v>91032</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17559,34 +17564,34 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>229821</v>
+        <v>5442</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>380249</v>
+        <v>380561</v>
       </c>
       <c r="R166" t="n">
-        <v>6919607</v>
+        <v>6919930</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17633,22 +17638,22 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>124470146</v>
+        <v>124458282</v>
       </c>
       <c r="B167" t="n">
-        <v>57513</v>
+        <v>78151</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17657,46 +17662,41 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P167" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>380527</v>
+        <v>380588</v>
       </c>
       <c r="R167" t="n">
-        <v>6919988</v>
+        <v>6920110</v>
       </c>
       <c r="S167" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>124458509</v>
+        <v>124470146</v>
       </c>
       <c r="B168" t="n">
         <v>57513</v>
@@ -17788,22 +17788,22 @@
       <c r="I168" t="inlineStr"/>
       <c r="M168" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>380542</v>
+        <v>380527</v>
       </c>
       <c r="R168" t="n">
-        <v>6920184</v>
+        <v>6919988</v>
       </c>
       <c r="S168" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -17833,11 +17833,6 @@
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>Miljöbilder, talltita.</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -17852,22 +17847,22 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>124459456</v>
+        <v>124458509</v>
       </c>
       <c r="B169" t="n">
-        <v>91032</v>
+        <v>57513</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -17880,34 +17875,39 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>380561</v>
+        <v>380542</v>
       </c>
       <c r="R169" t="n">
-        <v>6919930</v>
+        <v>6920184</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17940,6 +17940,11 @@
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>Miljöbilder, talltita.</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17966,10 +17971,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>124458743</v>
+        <v>124464901</v>
       </c>
       <c r="B170" t="n">
-        <v>91030</v>
+        <v>79399</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -17982,34 +17987,34 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>5432</v>
+        <v>229821</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>380542</v>
+        <v>380249</v>
       </c>
       <c r="R170" t="n">
-        <v>6920184</v>
+        <v>6919607</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18044,11 +18049,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
-        </is>
-      </c>
       <c r="AD170" t="b">
         <v>0</v>
       </c>
@@ -18061,12 +18061,12 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
@@ -19113,10 +19113,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>124460611</v>
+        <v>124456697</v>
       </c>
       <c r="B181" t="n">
-        <v>78905</v>
+        <v>91030</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -19129,34 +19129,34 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>967</v>
+        <v>5432</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>380335</v>
+        <v>380443</v>
       </c>
       <c r="R181" t="n">
-        <v>6920000</v>
+        <v>6920118</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19203,22 +19203,22 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124451326</v>
+        <v>124456046</v>
       </c>
       <c r="B182" t="n">
-        <v>57513</v>
+        <v>91032</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -19231,39 +19231,34 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>380227</v>
+        <v>380326</v>
       </c>
       <c r="R182" t="n">
-        <v>6920340</v>
+        <v>6920218</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19296,6 +19291,11 @@
       <c r="AA182" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19322,10 +19322,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124471016</v>
+        <v>124460611</v>
       </c>
       <c r="B183" t="n">
-        <v>57513</v>
+        <v>78905</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -19338,39 +19338,34 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>100109</v>
+        <v>967</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P183" t="inlineStr">
         <is>
           <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>380506</v>
+        <v>380335</v>
       </c>
       <c r="R183" t="n">
-        <v>6920061</v>
+        <v>6920000</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19429,10 +19424,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124456697</v>
+        <v>124455220</v>
       </c>
       <c r="B184" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -19445,34 +19440,34 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>380443</v>
+        <v>380311</v>
       </c>
       <c r="R184" t="n">
-        <v>6920118</v>
+        <v>6920231</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19531,10 +19526,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124456046</v>
+        <v>124467914</v>
       </c>
       <c r="B185" t="n">
-        <v>91032</v>
+        <v>77738</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -19547,34 +19542,34 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>5442</v>
+        <v>6487</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>380326</v>
+        <v>380361</v>
       </c>
       <c r="R185" t="n">
-        <v>6920218</v>
+        <v>6919740</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19611,7 +19606,7 @@
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>Miljöbilder för området.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19638,10 +19633,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124455220</v>
+        <v>124451326</v>
       </c>
       <c r="B186" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -19654,34 +19649,39 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P186" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>380311</v>
+        <v>380227</v>
       </c>
       <c r="R186" t="n">
-        <v>6920231</v>
+        <v>6920340</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19728,22 +19728,22 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124467914</v>
+        <v>124450902</v>
       </c>
       <c r="B187" t="n">
-        <v>77738</v>
+        <v>57529</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -19756,34 +19756,39 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6487</v>
+        <v>100049</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>380361</v>
+        <v>380227</v>
       </c>
       <c r="R187" t="n">
-        <v>6919740</v>
+        <v>6920340</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19820,7 +19825,7 @@
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Troligen spillkråka.</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -19847,10 +19852,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124450902</v>
+        <v>124471016</v>
       </c>
       <c r="B188" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -19863,16 +19868,16 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -19888,14 +19893,14 @@
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>380227</v>
+        <v>380506</v>
       </c>
       <c r="R188" t="n">
-        <v>6920340</v>
+        <v>6920061</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19928,11 +19933,6 @@
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC188" t="inlineStr">
-        <is>
-          <t>Troligen spillkråka.</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20163,10 +20163,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>124460052</v>
+        <v>124470070</v>
       </c>
       <c r="B191" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20179,39 +20179,34 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>380419</v>
+        <v>380533</v>
       </c>
       <c r="R191" t="n">
-        <v>6919960</v>
+        <v>6919979</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20258,22 +20253,22 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>124468182</v>
+        <v>124457866</v>
       </c>
       <c r="B192" t="n">
-        <v>57513</v>
+        <v>78151</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20282,46 +20277,41 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P192" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>380265</v>
+        <v>380537</v>
       </c>
       <c r="R192" t="n">
-        <v>6919774</v>
+        <v>6920199</v>
       </c>
       <c r="S192" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -20377,10 +20367,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>124470070</v>
+        <v>124458172</v>
       </c>
       <c r="B193" t="n">
-        <v>78810</v>
+        <v>78151</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -20389,25 +20379,25 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6425</v>
+        <v>498</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20417,10 +20407,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>380533</v>
+        <v>380562</v>
       </c>
       <c r="R193" t="n">
-        <v>6919979</v>
+        <v>6920118</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20479,10 +20469,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>124457866</v>
+        <v>124454665</v>
       </c>
       <c r="B194" t="n">
-        <v>78151</v>
+        <v>74901</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -20491,25 +20481,25 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>498</v>
+        <v>6440</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20519,10 +20509,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>380537</v>
+        <v>380258</v>
       </c>
       <c r="R194" t="n">
-        <v>6920199</v>
+        <v>6920309</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20581,10 +20571,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>124458172</v>
+        <v>124460052</v>
       </c>
       <c r="B195" t="n">
-        <v>78151</v>
+        <v>57513</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -20593,38 +20583,43 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>498</v>
+        <v>100109</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>380562</v>
+        <v>380419</v>
       </c>
       <c r="R195" t="n">
-        <v>6920118</v>
+        <v>6919960</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20671,22 +20666,22 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>124454665</v>
+        <v>124468182</v>
       </c>
       <c r="B196" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -20699,37 +20694,42 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>380258</v>
+        <v>380265</v>
       </c>
       <c r="R196" t="n">
-        <v>6920309</v>
+        <v>6919774</v>
       </c>
       <c r="S196" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -20785,10 +20785,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>124455096</v>
+        <v>124456676</v>
       </c>
       <c r="B197" t="n">
-        <v>5196</v>
+        <v>57513</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -20797,20 +20797,20 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>105930</v>
+        <v>100109</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -20821,22 +20821,22 @@
       <c r="I197" t="inlineStr"/>
       <c r="M197" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>380323</v>
+        <v>380434</v>
       </c>
       <c r="R197" t="n">
-        <v>6920260</v>
+        <v>6920123</v>
       </c>
       <c r="S197" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -21407,10 +21407,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>124456676</v>
+        <v>124455096</v>
       </c>
       <c r="B203" t="n">
-        <v>57513</v>
+        <v>5196</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -21419,20 +21419,20 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>100109</v>
+        <v>105930</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -21443,22 +21443,22 @@
       <c r="I203" t="inlineStr"/>
       <c r="M203" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>380434</v>
+        <v>380323</v>
       </c>
       <c r="R203" t="n">
-        <v>6920123</v>
+        <v>6920260</v>
       </c>
       <c r="S203" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -22029,10 +22029,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>124470404</v>
+        <v>124451984</v>
       </c>
       <c r="B209" t="n">
-        <v>91030</v>
+        <v>79399</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -22045,34 +22045,34 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>5432</v>
+        <v>229821</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>380471</v>
+        <v>380203</v>
       </c>
       <c r="R209" t="n">
-        <v>6920069</v>
+        <v>6920482</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -22335,10 +22335,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>124451984</v>
+        <v>124470404</v>
       </c>
       <c r="B212" t="n">
-        <v>79399</v>
+        <v>91030</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -22351,34 +22351,34 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>229821</v>
+        <v>5432</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>380203</v>
+        <v>380471</v>
       </c>
       <c r="R212" t="n">
-        <v>6920482</v>
+        <v>6920069</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23569,10 +23569,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>124469547</v>
+        <v>124459815</v>
       </c>
       <c r="B224" t="n">
-        <v>88359</v>
+        <v>79428</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -23585,34 +23585,34 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>510</v>
+        <v>6453</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>380452</v>
+        <v>380445</v>
       </c>
       <c r="R224" t="n">
-        <v>6919913</v>
+        <v>6919917</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23659,22 +23659,22 @@
       <c r="AT224" t="inlineStr"/>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>124459815</v>
+        <v>124465167</v>
       </c>
       <c r="B225" t="n">
-        <v>79428</v>
+        <v>78194</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -23687,34 +23687,34 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>380445</v>
+        <v>380244</v>
       </c>
       <c r="R225" t="n">
-        <v>6919917</v>
+        <v>6919577</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23761,22 +23761,22 @@
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>124465167</v>
+        <v>124470732</v>
       </c>
       <c r="B226" t="n">
-        <v>78194</v>
+        <v>74901</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -23789,34 +23789,34 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>380244</v>
+        <v>380372</v>
       </c>
       <c r="R226" t="n">
-        <v>6919577</v>
+        <v>6920042</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23863,22 +23863,22 @@
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>124470732</v>
+        <v>124469547</v>
       </c>
       <c r="B227" t="n">
-        <v>74901</v>
+        <v>88359</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -23891,21 +23891,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -23915,10 +23915,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>380372</v>
+        <v>380452</v>
       </c>
       <c r="R227" t="n">
-        <v>6920042</v>
+        <v>6919913</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23965,12 +23965,12 @@
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
@@ -25517,10 +25517,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>124463210</v>
+        <v>124470707</v>
       </c>
       <c r="B243" t="n">
-        <v>79428</v>
+        <v>57513</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -25533,37 +25533,42 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>380189</v>
+        <v>380367</v>
       </c>
       <c r="R243" t="n">
-        <v>6919766</v>
+        <v>6920058</v>
       </c>
       <c r="S243" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -25619,7 +25624,7 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>124470707</v>
+        <v>124470806</v>
       </c>
       <c r="B244" t="n">
         <v>57513</v>
@@ -25664,10 +25669,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>380367</v>
+        <v>380340</v>
       </c>
       <c r="R244" t="n">
-        <v>6920058</v>
+        <v>6920036</v>
       </c>
       <c r="S244" t="n">
         <v>15</v>
@@ -25726,7 +25731,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>124470806</v>
+        <v>124468469</v>
       </c>
       <c r="B245" t="n">
         <v>57513</v>
@@ -25767,14 +25772,14 @@
       </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>380340</v>
+        <v>380324</v>
       </c>
       <c r="R245" t="n">
-        <v>6920036</v>
+        <v>6919803</v>
       </c>
       <c r="S245" t="n">
         <v>15</v>
@@ -25833,10 +25838,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>124468469</v>
+        <v>124463210</v>
       </c>
       <c r="B246" t="n">
-        <v>57513</v>
+        <v>79428</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -25849,42 +25854,37 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
-      <c r="M246" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P246" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>380324</v>
+        <v>380189</v>
       </c>
       <c r="R246" t="n">
-        <v>6919803</v>
+        <v>6919766</v>
       </c>
       <c r="S246" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -27082,10 +27082,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>124464651</v>
+        <v>124470234</v>
       </c>
       <c r="B258" t="n">
-        <v>79399</v>
+        <v>82597</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -27098,21 +27098,21 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>229821</v>
+        <v>1312</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -27122,10 +27122,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>380251</v>
+        <v>380506</v>
       </c>
       <c r="R258" t="n">
-        <v>6919658</v>
+        <v>6920009</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -27184,10 +27184,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>124470742</v>
+        <v>124456502</v>
       </c>
       <c r="B259" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -27200,42 +27200,37 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
-      <c r="M259" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>380369</v>
+        <v>380385</v>
       </c>
       <c r="R259" t="n">
-        <v>6920032</v>
+        <v>6920091</v>
       </c>
       <c r="S259" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T259" t="inlineStr">
         <is>
@@ -27265,6 +27260,11 @@
       <c r="AA259" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC259" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -27279,22 +27279,22 @@
       <c r="AT259" t="inlineStr"/>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>124460224</v>
+        <v>124459042</v>
       </c>
       <c r="B260" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -27307,39 +27307,34 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
-      <c r="M260" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>380374</v>
+        <v>380571</v>
       </c>
       <c r="R260" t="n">
-        <v>6919982</v>
+        <v>6919993</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -27386,22 +27381,22 @@
       <c r="AT260" t="inlineStr"/>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>124470234</v>
+        <v>124469915</v>
       </c>
       <c r="B261" t="n">
-        <v>82597</v>
+        <v>74901</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -27414,21 +27409,21 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -27438,10 +27433,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>380506</v>
+        <v>380521</v>
       </c>
       <c r="R261" t="n">
-        <v>6920009</v>
+        <v>6919962</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -27500,10 +27495,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>124456502</v>
+        <v>124464842</v>
       </c>
       <c r="B262" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -27516,34 +27511,34 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>380385</v>
+        <v>380237</v>
       </c>
       <c r="R262" t="n">
-        <v>6920091</v>
+        <v>6919621</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -27578,11 +27573,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC262" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området.</t>
-        </is>
-      </c>
       <c r="AD262" t="b">
         <v>0</v>
       </c>
@@ -27595,22 +27585,22 @@
       <c r="AT262" t="inlineStr"/>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>124459042</v>
+        <v>124470742</v>
       </c>
       <c r="B263" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -27623,37 +27613,42 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>380571</v>
+        <v>380369</v>
       </c>
       <c r="R263" t="n">
-        <v>6919993</v>
+        <v>6920032</v>
       </c>
       <c r="S263" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T263" t="inlineStr">
         <is>
@@ -27709,10 +27704,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>124469915</v>
+        <v>124460224</v>
       </c>
       <c r="B264" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -27725,34 +27720,39 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P264" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>380521</v>
+        <v>380374</v>
       </c>
       <c r="R264" t="n">
-        <v>6919962</v>
+        <v>6919982</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27799,22 +27799,22 @@
       <c r="AT264" t="inlineStr"/>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>124464842</v>
+        <v>124464651</v>
       </c>
       <c r="B265" t="n">
-        <v>79428</v>
+        <v>79399</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -27827,21 +27827,21 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
@@ -27851,10 +27851,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>380237</v>
+        <v>380251</v>
       </c>
       <c r="R265" t="n">
-        <v>6919621</v>
+        <v>6919658</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27913,10 +27913,10 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>124464047</v>
+        <v>124455022</v>
       </c>
       <c r="B266" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -27929,34 +27929,34 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>380267</v>
+        <v>380292</v>
       </c>
       <c r="R266" t="n">
-        <v>6919731</v>
+        <v>6920288</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -28015,10 +28015,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>124450578</v>
+        <v>124455776</v>
       </c>
       <c r="B267" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -28031,34 +28031,39 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P267" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>380227</v>
+        <v>380326</v>
       </c>
       <c r="R267" t="n">
-        <v>6920340</v>
+        <v>6920218</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -28117,10 +28122,10 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>124455022</v>
+        <v>124464970</v>
       </c>
       <c r="B268" t="n">
-        <v>79428</v>
+        <v>57513</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -28133,37 +28138,42 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P268" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>380292</v>
+        <v>380255</v>
       </c>
       <c r="R268" t="n">
-        <v>6920288</v>
+        <v>6919561</v>
       </c>
       <c r="S268" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T268" t="inlineStr">
         <is>
@@ -28219,10 +28229,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>124452627</v>
+        <v>124464047</v>
       </c>
       <c r="B269" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -28235,34 +28245,34 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
       <c r="P269" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>380217</v>
+        <v>380267</v>
       </c>
       <c r="R269" t="n">
-        <v>6920440</v>
+        <v>6919731</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -28321,10 +28331,10 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>124455776</v>
+        <v>124450578</v>
       </c>
       <c r="B270" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -28337,39 +28347,34 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
-      <c r="M270" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P270" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>380326</v>
+        <v>380227</v>
       </c>
       <c r="R270" t="n">
-        <v>6920218</v>
+        <v>6920340</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -28428,10 +28433,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>124464970</v>
+        <v>124452627</v>
       </c>
       <c r="B271" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -28444,42 +28449,37 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
-      <c r="M271" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P271" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>380255</v>
+        <v>380217</v>
       </c>
       <c r="R271" t="n">
-        <v>6919561</v>
+        <v>6920440</v>
       </c>
       <c r="S271" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T271" t="inlineStr">
         <is>
@@ -28951,6 +28951,1479 @@
       </c>
       <c r="AY275" t="inlineStr"/>
     </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>124871232</v>
+      </c>
+      <c r="B276" t="n">
+        <v>74901</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E276" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr"/>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>Risåsen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q276" t="n">
+        <v>380202</v>
+      </c>
+      <c r="R276" t="n">
+        <v>6920072</v>
+      </c>
+      <c r="S276" t="n">
+        <v>10</v>
+      </c>
+      <c r="T276" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V276" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W276" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y276" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AD276" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE276" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG276" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT276" t="inlineStr"/>
+      <c r="AW276" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX276" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>124870881</v>
+      </c>
+      <c r="B277" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E277" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr"/>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>Lill-Långtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q277" t="n">
+        <v>380067</v>
+      </c>
+      <c r="R277" t="n">
+        <v>6919860</v>
+      </c>
+      <c r="S277" t="n">
+        <v>15</v>
+      </c>
+      <c r="T277" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V277" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W277" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y277" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AD277" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE277" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG277" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT277" t="inlineStr"/>
+      <c r="AW277" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX277" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>124870654</v>
+      </c>
+      <c r="B278" t="n">
+        <v>74901</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E278" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr"/>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>Lill-Långtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q278" t="n">
+        <v>380093</v>
+      </c>
+      <c r="R278" t="n">
+        <v>6919795</v>
+      </c>
+      <c r="S278" t="n">
+        <v>10</v>
+      </c>
+      <c r="T278" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V278" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W278" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y278" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AD278" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE278" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG278" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT278" t="inlineStr"/>
+      <c r="AW278" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX278" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>124870920</v>
+      </c>
+      <c r="B279" t="n">
+        <v>91030</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E279" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr"/>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>Risåsen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q279" t="n">
+        <v>380097</v>
+      </c>
+      <c r="R279" t="n">
+        <v>6919882</v>
+      </c>
+      <c r="S279" t="n">
+        <v>10</v>
+      </c>
+      <c r="T279" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V279" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W279" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y279" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AD279" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE279" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG279" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT279" t="inlineStr"/>
+      <c r="AW279" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX279" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>124870424</v>
+      </c>
+      <c r="B280" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E280" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr"/>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>Lill-Långtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q280" t="n">
+        <v>380098</v>
+      </c>
+      <c r="R280" t="n">
+        <v>6919759</v>
+      </c>
+      <c r="S280" t="n">
+        <v>15</v>
+      </c>
+      <c r="T280" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V280" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W280" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y280" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AD280" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE280" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG280" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT280" t="inlineStr"/>
+      <c r="AW280" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX280" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>124870262</v>
+      </c>
+      <c r="B281" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E281" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr"/>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>Risåsen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q281" t="n">
+        <v>380196</v>
+      </c>
+      <c r="R281" t="n">
+        <v>6919970</v>
+      </c>
+      <c r="S281" t="n">
+        <v>15</v>
+      </c>
+      <c r="T281" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V281" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W281" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y281" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AD281" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE281" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG281" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT281" t="inlineStr"/>
+      <c r="AW281" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX281" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>124870829</v>
+      </c>
+      <c r="B282" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E282" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr"/>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>Lill-Långtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q282" t="n">
+        <v>380045</v>
+      </c>
+      <c r="R282" t="n">
+        <v>6919831</v>
+      </c>
+      <c r="S282" t="n">
+        <v>15</v>
+      </c>
+      <c r="T282" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V282" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W282" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y282" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AD282" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE282" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG282" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT282" t="inlineStr"/>
+      <c r="AW282" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX282" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>124870503</v>
+      </c>
+      <c r="B283" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E283" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr"/>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>Lill-Långtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q283" t="n">
+        <v>380108</v>
+      </c>
+      <c r="R283" t="n">
+        <v>6919741</v>
+      </c>
+      <c r="S283" t="n">
+        <v>15</v>
+      </c>
+      <c r="T283" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V283" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W283" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y283" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AD283" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE283" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG283" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT283" t="inlineStr"/>
+      <c r="AW283" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX283" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>124871057</v>
+      </c>
+      <c r="B284" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E284" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr"/>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P284" t="inlineStr">
+        <is>
+          <t>Risåsen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q284" t="n">
+        <v>380132</v>
+      </c>
+      <c r="R284" t="n">
+        <v>6919977</v>
+      </c>
+      <c r="S284" t="n">
+        <v>15</v>
+      </c>
+      <c r="T284" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V284" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W284" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y284" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AD284" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE284" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG284" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT284" t="inlineStr"/>
+      <c r="AW284" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX284" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>124871117</v>
+      </c>
+      <c r="B285" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E285" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr"/>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>Risåsen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q285" t="n">
+        <v>380204</v>
+      </c>
+      <c r="R285" t="n">
+        <v>6920043</v>
+      </c>
+      <c r="S285" t="n">
+        <v>15</v>
+      </c>
+      <c r="T285" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V285" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W285" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y285" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AD285" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE285" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG285" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT285" t="inlineStr"/>
+      <c r="AW285" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX285" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>124870943</v>
+      </c>
+      <c r="B286" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E286" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr"/>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>Risåsen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q286" t="n">
+        <v>380093</v>
+      </c>
+      <c r="R286" t="n">
+        <v>6919892</v>
+      </c>
+      <c r="S286" t="n">
+        <v>15</v>
+      </c>
+      <c r="T286" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V286" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W286" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y286" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AD286" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE286" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG286" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT286" t="inlineStr"/>
+      <c r="AW286" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX286" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>124870851</v>
+      </c>
+      <c r="B287" t="n">
+        <v>79399</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E287" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr"/>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>Lill-Långtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q287" t="n">
+        <v>380051</v>
+      </c>
+      <c r="R287" t="n">
+        <v>6919850</v>
+      </c>
+      <c r="S287" t="n">
+        <v>10</v>
+      </c>
+      <c r="T287" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V287" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W287" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y287" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AD287" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE287" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG287" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT287" t="inlineStr"/>
+      <c r="AW287" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX287" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>124871081</v>
+      </c>
+      <c r="B288" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E288" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr"/>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>Risåsen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q288" t="n">
+        <v>380173</v>
+      </c>
+      <c r="R288" t="n">
+        <v>6920011</v>
+      </c>
+      <c r="S288" t="n">
+        <v>15</v>
+      </c>
+      <c r="T288" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V288" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W288" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y288" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AD288" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE288" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG288" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT288" t="inlineStr"/>
+      <c r="AW288" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX288" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>124870693</v>
+      </c>
+      <c r="B289" t="n">
+        <v>96354</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E289" t="n">
+        <v>53</v>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr"/>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>Lill-Långtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q289" t="n">
+        <v>380072</v>
+      </c>
+      <c r="R289" t="n">
+        <v>6919810</v>
+      </c>
+      <c r="S289" t="n">
+        <v>10</v>
+      </c>
+      <c r="T289" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U289" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V289" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W289" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y289" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA289" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AD289" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE289" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG289" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT289" t="inlineStr"/>
+      <c r="AW289" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX289" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY289" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32573-2024 artfynd.xlsx
+++ b/artfynd/A 32573-2024 artfynd.xlsx
@@ -16105,10 +16105,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>124470555</v>
+        <v>124456704</v>
       </c>
       <c r="B152" t="n">
-        <v>82597</v>
+        <v>91030</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16121,34 +16121,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>380431</v>
+        <v>380385</v>
       </c>
       <c r="R152" t="n">
-        <v>6920068</v>
+        <v>6920091</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16183,6 +16183,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD152" t="b">
         <v>0</v>
       </c>
@@ -16195,22 +16200,22 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>124465863</v>
+        <v>124452627</v>
       </c>
       <c r="B153" t="n">
-        <v>78151</v>
+        <v>74901</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16219,38 +16224,38 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>498</v>
+        <v>6440</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Risåsvallen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>380296</v>
+        <v>380217</v>
       </c>
       <c r="R153" t="n">
-        <v>6919585</v>
+        <v>6920440</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16309,10 +16314,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>124455134</v>
+        <v>124460258</v>
       </c>
       <c r="B154" t="n">
-        <v>74901</v>
+        <v>79428</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16325,34 +16330,34 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>380311</v>
+        <v>380365</v>
       </c>
       <c r="R154" t="n">
-        <v>6920245</v>
+        <v>6919996</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16411,10 +16416,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>124465389</v>
+        <v>124460611</v>
       </c>
       <c r="B155" t="n">
-        <v>79399</v>
+        <v>78905</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16427,34 +16432,34 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>229821</v>
+        <v>967</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>380244</v>
+        <v>380335</v>
       </c>
       <c r="R155" t="n">
-        <v>6919577</v>
+        <v>6920000</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16513,10 +16518,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>124464493</v>
+        <v>124457601</v>
       </c>
       <c r="B156" t="n">
-        <v>79399</v>
+        <v>78151</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16525,25 +16530,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>229821</v>
+        <v>498</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16553,10 +16558,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>380243</v>
+        <v>380544</v>
       </c>
       <c r="R156" t="n">
-        <v>6919687</v>
+        <v>6920188</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16615,10 +16620,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>124457601</v>
+        <v>124470555</v>
       </c>
       <c r="B157" t="n">
-        <v>78151</v>
+        <v>82597</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16627,25 +16632,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>498</v>
+        <v>1312</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16655,10 +16660,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>380544</v>
+        <v>380431</v>
       </c>
       <c r="R157" t="n">
-        <v>6920188</v>
+        <v>6920068</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16717,10 +16722,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>124450737</v>
+        <v>124455206</v>
       </c>
       <c r="B158" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16733,21 +16738,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16757,10 +16762,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>380210</v>
+        <v>380311</v>
       </c>
       <c r="R158" t="n">
-        <v>6920378</v>
+        <v>6920231</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16819,10 +16824,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>124458046</v>
+        <v>124470598</v>
       </c>
       <c r="B159" t="n">
-        <v>74901</v>
+        <v>79428</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16835,34 +16840,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>380533</v>
+        <v>380506</v>
       </c>
       <c r="R159" t="n">
-        <v>6920142</v>
+        <v>6920061</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16897,6 +16902,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD159" t="b">
         <v>0</v>
       </c>
@@ -16909,22 +16919,22 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>124460951</v>
+        <v>124450902</v>
       </c>
       <c r="B160" t="n">
-        <v>74901</v>
+        <v>57529</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -16937,34 +16947,39 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>380307</v>
+        <v>380227</v>
       </c>
       <c r="R160" t="n">
-        <v>6919967</v>
+        <v>6920340</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16999,6 +17014,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>Troligen spillkråka.</t>
+        </is>
+      </c>
       <c r="AD160" t="b">
         <v>0</v>
       </c>
@@ -17011,19 +17031,19 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>124464292</v>
+        <v>124470742</v>
       </c>
       <c r="B161" t="n">
         <v>57513</v>
@@ -17064,17 +17084,17 @@
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>380275</v>
+        <v>380369</v>
       </c>
       <c r="R161" t="n">
-        <v>6919775</v>
+        <v>6920032</v>
       </c>
       <c r="S161" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -17118,22 +17138,22 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>124464681</v>
+        <v>124460965</v>
       </c>
       <c r="B162" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17146,34 +17166,34 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>380264</v>
+        <v>380307</v>
       </c>
       <c r="R162" t="n">
-        <v>6919665</v>
+        <v>6919967</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17232,10 +17252,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>124450666</v>
+        <v>124450845</v>
       </c>
       <c r="B163" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17248,34 +17268,34 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>380227</v>
+        <v>380205</v>
       </c>
       <c r="R163" t="n">
-        <v>6920340</v>
+        <v>6920378</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17322,22 +17342,22 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>124467947</v>
+        <v>124460951</v>
       </c>
       <c r="B164" t="n">
-        <v>78194</v>
+        <v>74901</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17350,34 +17370,34 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>380361</v>
+        <v>380307</v>
       </c>
       <c r="R164" t="n">
-        <v>6919740</v>
+        <v>6919967</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17412,11 +17432,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD164" t="b">
         <v>0</v>
       </c>
@@ -17429,22 +17444,22 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>124458743</v>
+        <v>124459815</v>
       </c>
       <c r="B165" t="n">
-        <v>91030</v>
+        <v>79428</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17457,21 +17472,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17481,10 +17496,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>380542</v>
+        <v>380445</v>
       </c>
       <c r="R165" t="n">
-        <v>6920184</v>
+        <v>6919917</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17519,11 +17534,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
-        </is>
-      </c>
       <c r="AD165" t="b">
         <v>0</v>
       </c>
@@ -17536,22 +17546,22 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>124459456</v>
+        <v>124458046</v>
       </c>
       <c r="B166" t="n">
-        <v>91032</v>
+        <v>74901</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17564,34 +17574,34 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>5442</v>
+        <v>6440</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>380561</v>
+        <v>380533</v>
       </c>
       <c r="R166" t="n">
-        <v>6919930</v>
+        <v>6920142</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17638,22 +17648,22 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>124458282</v>
+        <v>124468547</v>
       </c>
       <c r="B167" t="n">
-        <v>78151</v>
+        <v>74901</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17662,38 +17672,38 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>498</v>
+        <v>6440</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>380588</v>
+        <v>380356</v>
       </c>
       <c r="R167" t="n">
-        <v>6920110</v>
+        <v>6919817</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17752,10 +17762,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>124470146</v>
+        <v>124455022</v>
       </c>
       <c r="B168" t="n">
-        <v>57513</v>
+        <v>79428</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -17768,42 +17778,37 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>380527</v>
+        <v>380292</v>
       </c>
       <c r="R168" t="n">
-        <v>6919988</v>
+        <v>6920288</v>
       </c>
       <c r="S168" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -17859,7 +17864,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>124458509</v>
+        <v>124470146</v>
       </c>
       <c r="B169" t="n">
         <v>57513</v>
@@ -17895,22 +17900,22 @@
       <c r="I169" t="inlineStr"/>
       <c r="M169" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>380542</v>
+        <v>380527</v>
       </c>
       <c r="R169" t="n">
-        <v>6920184</v>
+        <v>6919988</v>
       </c>
       <c r="S169" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -17940,11 +17945,6 @@
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>Miljöbilder, talltita.</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17959,19 +17959,19 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>124464901</v>
+        <v>124465526</v>
       </c>
       <c r="B170" t="n">
         <v>79399</v>
@@ -18007,14 +18007,14 @@
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>380249</v>
+        <v>380252</v>
       </c>
       <c r="R170" t="n">
-        <v>6919607</v>
+        <v>6919535</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18073,10 +18073,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>124458651</v>
+        <v>124468302</v>
       </c>
       <c r="B171" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18089,37 +18089,42 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>380569</v>
+        <v>380265</v>
       </c>
       <c r="R171" t="n">
-        <v>6920058</v>
+        <v>6919774</v>
       </c>
       <c r="S171" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -18175,10 +18180,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>124469377</v>
+        <v>124460052</v>
       </c>
       <c r="B172" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18191,34 +18196,39 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>380435</v>
+        <v>380419</v>
       </c>
       <c r="R172" t="n">
-        <v>6919916</v>
+        <v>6919960</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18265,22 +18275,22 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>124454876</v>
+        <v>124454979</v>
       </c>
       <c r="B173" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18293,21 +18303,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18317,10 +18327,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>380290</v>
+        <v>380289</v>
       </c>
       <c r="R173" t="n">
-        <v>6920272</v>
+        <v>6920290</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18355,6 +18365,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD173" t="b">
         <v>0</v>
       </c>
@@ -18367,22 +18382,22 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>124451802</v>
+        <v>124459134</v>
       </c>
       <c r="B174" t="n">
-        <v>79428</v>
+        <v>74901</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18395,34 +18410,34 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>380197</v>
+        <v>380559</v>
       </c>
       <c r="R174" t="n">
-        <v>6920479</v>
+        <v>6919947</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18481,10 +18496,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>124459060</v>
+        <v>124455453</v>
       </c>
       <c r="B175" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -18497,39 +18512,34 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>380571</v>
+        <v>380326</v>
       </c>
       <c r="R175" t="n">
-        <v>6919993</v>
+        <v>6920218</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18576,22 +18586,22 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>124452423</v>
+        <v>124461477</v>
       </c>
       <c r="B176" t="n">
-        <v>56725</v>
+        <v>79399</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -18600,43 +18610,38 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>102613</v>
+        <v>229821</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>380227</v>
+        <v>380285</v>
       </c>
       <c r="R176" t="n">
-        <v>6920340</v>
+        <v>6919895</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18683,22 +18688,22 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>124456129</v>
+        <v>124465389</v>
       </c>
       <c r="B177" t="n">
-        <v>78905</v>
+        <v>79399</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -18711,34 +18716,34 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>967</v>
+        <v>229821</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>380326</v>
+        <v>380244</v>
       </c>
       <c r="R177" t="n">
-        <v>6920218</v>
+        <v>6919577</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18797,10 +18802,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>124466026</v>
+        <v>124458282</v>
       </c>
       <c r="B178" t="n">
-        <v>79399</v>
+        <v>78151</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -18809,25 +18814,25 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>229821</v>
+        <v>498</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18837,10 +18842,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>380303</v>
+        <v>380588</v>
       </c>
       <c r="R178" t="n">
-        <v>6919598</v>
+        <v>6920110</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18875,11 +18880,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD178" t="b">
         <v>0</v>
       </c>
@@ -18892,22 +18892,22 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>124470646</v>
+        <v>124451326</v>
       </c>
       <c r="B179" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -18920,34 +18920,39 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>380402</v>
+        <v>380227</v>
       </c>
       <c r="R179" t="n">
-        <v>6920044</v>
+        <v>6920340</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18994,22 +18999,22 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>124454979</v>
+        <v>124452261</v>
       </c>
       <c r="B180" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -19022,21 +19027,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19046,10 +19051,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>380289</v>
+        <v>380227</v>
       </c>
       <c r="R180" t="n">
-        <v>6920290</v>
+        <v>6920340</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19082,11 +19087,6 @@
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19113,10 +19113,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>124456697</v>
+        <v>124469751</v>
       </c>
       <c r="B181" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -19129,34 +19129,34 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>380443</v>
+        <v>380490</v>
       </c>
       <c r="R181" t="n">
-        <v>6920118</v>
+        <v>6919937</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19215,10 +19215,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124456046</v>
+        <v>124467947</v>
       </c>
       <c r="B182" t="n">
-        <v>91032</v>
+        <v>78194</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -19231,34 +19231,34 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>5442</v>
+        <v>6437</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>380326</v>
+        <v>380361</v>
       </c>
       <c r="R182" t="n">
-        <v>6920218</v>
+        <v>6919740</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19295,7 +19295,7 @@
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>Miljöbilder för området.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19322,10 +19322,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124460611</v>
+        <v>124464842</v>
       </c>
       <c r="B183" t="n">
-        <v>78905</v>
+        <v>79428</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -19338,34 +19338,34 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>967</v>
+        <v>6453</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>380335</v>
+        <v>380237</v>
       </c>
       <c r="R183" t="n">
-        <v>6920000</v>
+        <v>6919621</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19412,22 +19412,22 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124455220</v>
+        <v>124464651</v>
       </c>
       <c r="B184" t="n">
-        <v>74901</v>
+        <v>79399</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -19440,34 +19440,34 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>380311</v>
+        <v>380251</v>
       </c>
       <c r="R184" t="n">
-        <v>6920231</v>
+        <v>6919658</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19526,10 +19526,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124467914</v>
+        <v>124458357</v>
       </c>
       <c r="B185" t="n">
-        <v>77738</v>
+        <v>57666</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -19542,37 +19542,42 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6487</v>
+        <v>103021</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P185" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>380361</v>
+        <v>380586</v>
       </c>
       <c r="R185" t="n">
-        <v>6919740</v>
+        <v>6920100</v>
       </c>
       <c r="S185" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -19602,11 +19607,6 @@
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19621,22 +19621,22 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124451326</v>
+        <v>124455096</v>
       </c>
       <c r="B186" t="n">
-        <v>57513</v>
+        <v>5196</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -19645,20 +19645,20 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>100109</v>
+        <v>105930</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -19669,7 +19669,7 @@
       <c r="I186" t="inlineStr"/>
       <c r="M186" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
@@ -19678,10 +19678,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>380227</v>
+        <v>380323</v>
       </c>
       <c r="R186" t="n">
-        <v>6920340</v>
+        <v>6920260</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19728,22 +19728,22 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124450902</v>
+        <v>124459287</v>
       </c>
       <c r="B187" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -19756,16 +19756,16 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -19776,19 +19776,19 @@
       <c r="I187" t="inlineStr"/>
       <c r="M187" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>380227</v>
+        <v>380561</v>
       </c>
       <c r="R187" t="n">
-        <v>6920340</v>
+        <v>6919930</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19821,11 +19821,6 @@
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC187" t="inlineStr">
-        <is>
-          <t>Troligen spillkråka.</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -19852,10 +19847,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124471016</v>
+        <v>124469088</v>
       </c>
       <c r="B188" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -19868,39 +19863,34 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
-      <c r="M188" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>380506</v>
+        <v>380352</v>
       </c>
       <c r="R188" t="n">
-        <v>6920061</v>
+        <v>6919913</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19947,22 +19937,22 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124465526</v>
+        <v>124470184</v>
       </c>
       <c r="B189" t="n">
-        <v>79399</v>
+        <v>91030</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -19975,34 +19965,34 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>229821</v>
+        <v>5432</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Risåsvallen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>380252</v>
+        <v>380516</v>
       </c>
       <c r="R189" t="n">
-        <v>6919535</v>
+        <v>6920004</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20061,10 +20051,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>124464559</v>
+        <v>124450518</v>
       </c>
       <c r="B190" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20077,21 +20067,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20101,10 +20091,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>380236</v>
+        <v>380202</v>
       </c>
       <c r="R190" t="n">
-        <v>6919671</v>
+        <v>6920332</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20163,10 +20153,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>124470070</v>
+        <v>124461108</v>
       </c>
       <c r="B191" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20179,34 +20169,34 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>380533</v>
+        <v>380308</v>
       </c>
       <c r="R191" t="n">
-        <v>6919979</v>
+        <v>6919925</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20239,6 +20229,11 @@
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>På basen avsågad gran. Grov stubbe</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20265,10 +20260,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>124457866</v>
+        <v>124464466</v>
       </c>
       <c r="B192" t="n">
-        <v>78151</v>
+        <v>78905</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20277,25 +20272,25 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>498</v>
+        <v>967</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20305,10 +20300,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>380537</v>
+        <v>380243</v>
       </c>
       <c r="R192" t="n">
-        <v>6920199</v>
+        <v>6919687</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20367,10 +20362,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>124458172</v>
+        <v>124454876</v>
       </c>
       <c r="B193" t="n">
-        <v>78151</v>
+        <v>74901</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -20379,38 +20374,38 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>498</v>
+        <v>6440</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>380562</v>
+        <v>380290</v>
       </c>
       <c r="R193" t="n">
-        <v>6920118</v>
+        <v>6920272</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20469,10 +20464,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>124454665</v>
+        <v>124465167</v>
       </c>
       <c r="B194" t="n">
-        <v>74901</v>
+        <v>78194</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -20485,21 +20480,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20509,10 +20504,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>380258</v>
+        <v>380244</v>
       </c>
       <c r="R194" t="n">
-        <v>6920309</v>
+        <v>6919577</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20559,22 +20554,22 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>124460052</v>
+        <v>124451837</v>
       </c>
       <c r="B195" t="n">
-        <v>57513</v>
+        <v>78194</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -20587,39 +20582,34 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>380419</v>
+        <v>380197</v>
       </c>
       <c r="R195" t="n">
-        <v>6919960</v>
+        <v>6920479</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20666,22 +20656,22 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>124468182</v>
+        <v>124470485</v>
       </c>
       <c r="B196" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -20694,42 +20684,37 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>380265</v>
+        <v>380446</v>
       </c>
       <c r="R196" t="n">
-        <v>6919774</v>
+        <v>6920059</v>
       </c>
       <c r="S196" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -20785,10 +20770,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>124456676</v>
+        <v>124470646</v>
       </c>
       <c r="B197" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -20801,42 +20786,37 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>380434</v>
+        <v>380402</v>
       </c>
       <c r="R197" t="n">
-        <v>6920123</v>
+        <v>6920044</v>
       </c>
       <c r="S197" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -20892,7 +20872,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>124470485</v>
+        <v>124450737</v>
       </c>
       <c r="B198" t="n">
         <v>74901</v>
@@ -20928,14 +20908,14 @@
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>380446</v>
+        <v>380210</v>
       </c>
       <c r="R198" t="n">
-        <v>6920059</v>
+        <v>6920378</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20994,7 +20974,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>124450415</v>
+        <v>124461736</v>
       </c>
       <c r="B199" t="n">
         <v>74901</v>
@@ -21034,10 +21014,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>380202</v>
+        <v>380232</v>
       </c>
       <c r="R199" t="n">
-        <v>6920332</v>
+        <v>6919808</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21096,10 +21076,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>124458476</v>
+        <v>124469907</v>
       </c>
       <c r="B200" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -21112,34 +21092,34 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>380581</v>
+        <v>380452</v>
       </c>
       <c r="R200" t="n">
-        <v>6920056</v>
+        <v>6919913</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21186,22 +21166,22 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>124451172</v>
+        <v>124466026</v>
       </c>
       <c r="B201" t="n">
-        <v>74901</v>
+        <v>79399</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -21214,34 +21194,34 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>380184</v>
+        <v>380303</v>
       </c>
       <c r="R201" t="n">
-        <v>6920434</v>
+        <v>6919598</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21276,6 +21256,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD201" t="b">
         <v>0</v>
       </c>
@@ -21288,22 +21273,22 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>124470598</v>
+        <v>124465009</v>
       </c>
       <c r="B202" t="n">
-        <v>79428</v>
+        <v>79399</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -21316,34 +21301,34 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>380506</v>
+        <v>380267</v>
       </c>
       <c r="R202" t="n">
-        <v>6920061</v>
+        <v>6919764</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21407,10 +21392,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>124455096</v>
+        <v>124459042</v>
       </c>
       <c r="B203" t="n">
-        <v>5196</v>
+        <v>74901</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -21419,43 +21404,38 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>105930</v>
+        <v>6440</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>380323</v>
+        <v>380571</v>
       </c>
       <c r="R203" t="n">
-        <v>6920260</v>
+        <v>6919993</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21514,10 +21494,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>124460258</v>
+        <v>124451172</v>
       </c>
       <c r="B204" t="n">
-        <v>79428</v>
+        <v>74901</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -21530,34 +21510,34 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>380365</v>
+        <v>380184</v>
       </c>
       <c r="R204" t="n">
-        <v>6919996</v>
+        <v>6920434</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21616,7 +21596,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>124450300</v>
+        <v>124458476</v>
       </c>
       <c r="B205" t="n">
         <v>74901</v>
@@ -21656,10 +21636,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>380182</v>
+        <v>380581</v>
       </c>
       <c r="R205" t="n">
-        <v>6920316</v>
+        <v>6920056</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21718,10 +21698,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>124457836</v>
+        <v>124469377</v>
       </c>
       <c r="B206" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -21734,34 +21714,34 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>380542</v>
+        <v>380435</v>
       </c>
       <c r="R206" t="n">
-        <v>6920184</v>
+        <v>6919916</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21808,22 +21788,22 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>124466494</v>
+        <v>124459456</v>
       </c>
       <c r="B207" t="n">
-        <v>57513</v>
+        <v>91032</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -21836,42 +21816,37 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P207" t="inlineStr">
         <is>
           <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>380344</v>
+        <v>380561</v>
       </c>
       <c r="R207" t="n">
-        <v>6919654</v>
+        <v>6919930</v>
       </c>
       <c r="S207" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -21915,22 +21890,22 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>124463365</v>
+        <v>124470737</v>
       </c>
       <c r="B208" t="n">
-        <v>79399</v>
+        <v>91030</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -21943,34 +21918,34 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>229821</v>
+        <v>5432</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>380199</v>
+        <v>380506</v>
       </c>
       <c r="R208" t="n">
-        <v>6919723</v>
+        <v>6920061</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22017,22 +21992,22 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>124451984</v>
+        <v>124465863</v>
       </c>
       <c r="B209" t="n">
-        <v>79399</v>
+        <v>78151</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -22041,38 +22016,38 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>229821</v>
+        <v>498</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Risåsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>380203</v>
+        <v>380296</v>
       </c>
       <c r="R209" t="n">
-        <v>6920482</v>
+        <v>6919585</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -22131,7 +22106,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>124469751</v>
+        <v>124470397</v>
       </c>
       <c r="B210" t="n">
         <v>74901</v>
@@ -22167,14 +22142,14 @@
       <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>380490</v>
+        <v>380506</v>
       </c>
       <c r="R210" t="n">
-        <v>6919937</v>
+        <v>6920061</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22221,22 +22196,22 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>124469088</v>
+        <v>124454665</v>
       </c>
       <c r="B211" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -22249,34 +22224,34 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>380352</v>
+        <v>380258</v>
       </c>
       <c r="R211" t="n">
-        <v>6919913</v>
+        <v>6920309</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22335,10 +22310,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>124470404</v>
+        <v>124451574</v>
       </c>
       <c r="B212" t="n">
-        <v>91030</v>
+        <v>79428</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -22351,34 +22326,34 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>380471</v>
+        <v>380184</v>
       </c>
       <c r="R212" t="n">
-        <v>6920069</v>
+        <v>6920434</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22437,10 +22412,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>124456704</v>
+        <v>124469547</v>
       </c>
       <c r="B213" t="n">
-        <v>91030</v>
+        <v>88359</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -22453,34 +22428,34 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>380385</v>
+        <v>380452</v>
       </c>
       <c r="R213" t="n">
-        <v>6920091</v>
+        <v>6919913</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22513,11 +22488,6 @@
       <c r="AA213" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC213" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -22544,10 +22514,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>124470737</v>
+        <v>124451569</v>
       </c>
       <c r="B214" t="n">
-        <v>91030</v>
+        <v>79399</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -22560,34 +22530,34 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>5432</v>
+        <v>229821</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>380506</v>
+        <v>380184</v>
       </c>
       <c r="R214" t="n">
-        <v>6920061</v>
+        <v>6920434</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22634,22 +22604,22 @@
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>124470184</v>
+        <v>124470299</v>
       </c>
       <c r="B215" t="n">
-        <v>91030</v>
+        <v>56722</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -22658,38 +22628,43 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P215" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>380516</v>
+        <v>380495</v>
       </c>
       <c r="R215" t="n">
-        <v>6920004</v>
+        <v>6920029</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22748,10 +22723,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>124464466</v>
+        <v>124464970</v>
       </c>
       <c r="B216" t="n">
-        <v>78905</v>
+        <v>57513</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -22764,37 +22739,42 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>967</v>
+        <v>100109</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P216" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>380243</v>
+        <v>380255</v>
       </c>
       <c r="R216" t="n">
-        <v>6919687</v>
+        <v>6919561</v>
       </c>
       <c r="S216" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -22850,10 +22830,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>124463640</v>
+        <v>124468469</v>
       </c>
       <c r="B217" t="n">
-        <v>79428</v>
+        <v>57513</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -22866,37 +22846,42 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P217" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>380218</v>
+        <v>380324</v>
       </c>
       <c r="R217" t="n">
-        <v>6919722</v>
+        <v>6919803</v>
       </c>
       <c r="S217" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -22952,10 +22937,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>124451574</v>
+        <v>124464321</v>
       </c>
       <c r="B218" t="n">
-        <v>79428</v>
+        <v>77738</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -22968,34 +22953,34 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>380184</v>
+        <v>380268</v>
       </c>
       <c r="R218" t="n">
-        <v>6920434</v>
+        <v>6919685</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23054,7 +23039,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>124455453</v>
+        <v>124469915</v>
       </c>
       <c r="B219" t="n">
         <v>74901</v>
@@ -23090,14 +23075,14 @@
       <c r="I219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>380326</v>
+        <v>380521</v>
       </c>
       <c r="R219" t="n">
-        <v>6920218</v>
+        <v>6919962</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23144,22 +23129,22 @@
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>124451893</v>
+        <v>124450300</v>
       </c>
       <c r="B220" t="n">
-        <v>5196</v>
+        <v>74901</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -23168,38 +23153,38 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>105930</v>
+        <v>6440</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>380227</v>
+        <v>380182</v>
       </c>
       <c r="R220" t="n">
-        <v>6920340</v>
+        <v>6920316</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23246,22 +23231,22 @@
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>124465009</v>
+        <v>124450415</v>
       </c>
       <c r="B221" t="n">
-        <v>79399</v>
+        <v>74901</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -23274,21 +23259,21 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -23298,10 +23283,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>380267</v>
+        <v>380202</v>
       </c>
       <c r="R221" t="n">
-        <v>6919764</v>
+        <v>6920332</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23336,11 +23321,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC221" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD221" t="b">
         <v>0</v>
       </c>
@@ -23353,19 +23333,19 @@
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>124451885</v>
+        <v>124456697</v>
       </c>
       <c r="B222" t="n">
         <v>91030</v>
@@ -23401,14 +23381,14 @@
       <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>380189</v>
+        <v>380443</v>
       </c>
       <c r="R222" t="n">
-        <v>6920488</v>
+        <v>6920118</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23467,10 +23447,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>124450845</v>
+        <v>124456129</v>
       </c>
       <c r="B223" t="n">
-        <v>78810</v>
+        <v>78905</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -23483,34 +23463,34 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>380205</v>
+        <v>380326</v>
       </c>
       <c r="R223" t="n">
-        <v>6920378</v>
+        <v>6920218</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23557,22 +23537,22 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>124459815</v>
+        <v>124464047</v>
       </c>
       <c r="B224" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -23585,34 +23565,34 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>380445</v>
+        <v>380267</v>
       </c>
       <c r="R224" t="n">
-        <v>6919917</v>
+        <v>6919731</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23671,10 +23651,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>124465167</v>
+        <v>124452491</v>
       </c>
       <c r="B225" t="n">
-        <v>78194</v>
+        <v>78810</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -23687,34 +23667,34 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>380244</v>
+        <v>380208</v>
       </c>
       <c r="R225" t="n">
-        <v>6919577</v>
+        <v>6920481</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23761,22 +23741,22 @@
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>124470732</v>
+        <v>124450578</v>
       </c>
       <c r="B226" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -23789,34 +23769,34 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>380372</v>
+        <v>380227</v>
       </c>
       <c r="R226" t="n">
-        <v>6920042</v>
+        <v>6920340</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23863,22 +23843,22 @@
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>124469547</v>
+        <v>124455456</v>
       </c>
       <c r="B227" t="n">
-        <v>88359</v>
+        <v>74901</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -23891,34 +23871,34 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>380452</v>
+        <v>380314</v>
       </c>
       <c r="R227" t="n">
-        <v>6919913</v>
+        <v>6920201</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23965,22 +23945,22 @@
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>124464471</v>
+        <v>124455774</v>
       </c>
       <c r="B228" t="n">
-        <v>78194</v>
+        <v>74901</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -23993,34 +23973,34 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>380243</v>
+        <v>380356</v>
       </c>
       <c r="R228" t="n">
-        <v>6919687</v>
+        <v>6920172</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24079,10 +24059,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>124455456</v>
+        <v>124451802</v>
       </c>
       <c r="B229" t="n">
-        <v>74901</v>
+        <v>79428</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -24095,21 +24075,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -24119,10 +24099,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>380314</v>
+        <v>380197</v>
       </c>
       <c r="R229" t="n">
-        <v>6920201</v>
+        <v>6920479</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24181,10 +24161,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>124452491</v>
+        <v>124464329</v>
       </c>
       <c r="B230" t="n">
-        <v>78810</v>
+        <v>78194</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -24197,34 +24177,34 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>380208</v>
+        <v>380268</v>
       </c>
       <c r="R230" t="n">
-        <v>6920481</v>
+        <v>6919685</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24283,10 +24263,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>124451837</v>
+        <v>124459060</v>
       </c>
       <c r="B231" t="n">
-        <v>78194</v>
+        <v>57513</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -24299,34 +24279,39 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>380197</v>
+        <v>380571</v>
       </c>
       <c r="R231" t="n">
-        <v>6920479</v>
+        <v>6919993</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24385,10 +24370,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>124469907</v>
+        <v>124463365</v>
       </c>
       <c r="B232" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -24401,34 +24386,34 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>380452</v>
+        <v>380199</v>
       </c>
       <c r="R232" t="n">
-        <v>6919913</v>
+        <v>6919723</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24475,22 +24460,22 @@
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>124470397</v>
+        <v>124464681</v>
       </c>
       <c r="B233" t="n">
-        <v>74901</v>
+        <v>79399</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -24503,34 +24488,34 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>380506</v>
+        <v>380264</v>
       </c>
       <c r="R233" t="n">
-        <v>6920061</v>
+        <v>6919665</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -24577,22 +24562,22 @@
       <c r="AT233" t="inlineStr"/>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>124455774</v>
+        <v>124464901</v>
       </c>
       <c r="B234" t="n">
-        <v>74901</v>
+        <v>79399</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -24605,34 +24590,34 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>380356</v>
+        <v>380249</v>
       </c>
       <c r="R234" t="n">
-        <v>6920172</v>
+        <v>6919607</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -24691,10 +24676,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>124452261</v>
+        <v>124451885</v>
       </c>
       <c r="B235" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -24707,21 +24692,21 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -24731,10 +24716,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>380227</v>
+        <v>380189</v>
       </c>
       <c r="R235" t="n">
-        <v>6920340</v>
+        <v>6920488</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -24781,22 +24766,22 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>124461736</v>
+        <v>124470234</v>
       </c>
       <c r="B236" t="n">
-        <v>74901</v>
+        <v>82597</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -24809,21 +24794,21 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -24833,10 +24818,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>380232</v>
+        <v>380506</v>
       </c>
       <c r="R236" t="n">
-        <v>6919808</v>
+        <v>6920009</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24895,10 +24880,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>124455206</v>
+        <v>124467914</v>
       </c>
       <c r="B237" t="n">
-        <v>91030</v>
+        <v>77738</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -24911,34 +24896,34 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>5432</v>
+        <v>6487</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>380311</v>
+        <v>380361</v>
       </c>
       <c r="R237" t="n">
-        <v>6920231</v>
+        <v>6919740</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -24973,6 +24958,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC237" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD237" t="b">
         <v>0</v>
       </c>
@@ -24985,22 +24975,22 @@
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>124450518</v>
+        <v>124463210</v>
       </c>
       <c r="B238" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -25013,21 +25003,21 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -25037,10 +25027,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>380202</v>
+        <v>380189</v>
       </c>
       <c r="R238" t="n">
-        <v>6920332</v>
+        <v>6919766</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -25099,10 +25089,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>124459134</v>
+        <v>124451893</v>
       </c>
       <c r="B239" t="n">
-        <v>74901</v>
+        <v>5196</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -25111,38 +25101,38 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>6440</v>
+        <v>105930</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>380559</v>
+        <v>380227</v>
       </c>
       <c r="R239" t="n">
-        <v>6919947</v>
+        <v>6920340</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -25189,22 +25179,22 @@
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>124456372</v>
+        <v>124464493</v>
       </c>
       <c r="B240" t="n">
-        <v>74901</v>
+        <v>79399</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -25217,34 +25207,34 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>380368</v>
+        <v>380243</v>
       </c>
       <c r="R240" t="n">
-        <v>6920107</v>
+        <v>6919687</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -25303,10 +25293,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>124459287</v>
+        <v>124464559</v>
       </c>
       <c r="B241" t="n">
-        <v>57513</v>
+        <v>79399</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -25319,39 +25309,34 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
-      <c r="M241" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P241" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>380561</v>
+        <v>380236</v>
       </c>
       <c r="R241" t="n">
-        <v>6919930</v>
+        <v>6919671</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -25398,22 +25383,22 @@
       <c r="AT241" t="inlineStr"/>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>124458357</v>
+        <v>124470404</v>
       </c>
       <c r="B242" t="n">
-        <v>57666</v>
+        <v>91030</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -25426,42 +25411,37 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
-      <c r="M242" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P242" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>380586</v>
+        <v>380471</v>
       </c>
       <c r="R242" t="n">
-        <v>6920100</v>
+        <v>6920069</v>
       </c>
       <c r="S242" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -25517,10 +25497,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>124470707</v>
+        <v>124470070</v>
       </c>
       <c r="B243" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -25533,42 +25513,37 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
-      <c r="M243" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>380367</v>
+        <v>380533</v>
       </c>
       <c r="R243" t="n">
-        <v>6920058</v>
+        <v>6919979</v>
       </c>
       <c r="S243" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -25624,10 +25599,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>124470806</v>
+        <v>124463640</v>
       </c>
       <c r="B244" t="n">
-        <v>57513</v>
+        <v>79428</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -25640,42 +25615,37 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
-      <c r="M244" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>380340</v>
+        <v>380218</v>
       </c>
       <c r="R244" t="n">
-        <v>6920036</v>
+        <v>6919722</v>
       </c>
       <c r="S244" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
@@ -25731,10 +25701,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>124468469</v>
+        <v>124456502</v>
       </c>
       <c r="B245" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -25747,42 +25717,37 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
-      <c r="M245" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>380324</v>
+        <v>380385</v>
       </c>
       <c r="R245" t="n">
-        <v>6919803</v>
+        <v>6920091</v>
       </c>
       <c r="S245" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -25812,6 +25777,11 @@
       <c r="AA245" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC245" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -25826,22 +25796,22 @@
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>124463210</v>
+        <v>124457836</v>
       </c>
       <c r="B246" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -25854,34 +25824,34 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>380189</v>
+        <v>380542</v>
       </c>
       <c r="R246" t="n">
-        <v>6919766</v>
+        <v>6920184</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25928,22 +25898,22 @@
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>124470299</v>
+        <v>124457866</v>
       </c>
       <c r="B247" t="n">
-        <v>56722</v>
+        <v>78151</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -25952,43 +25922,38 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>100138</v>
+        <v>498</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
-      <c r="M247" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P247" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>380495</v>
+        <v>380537</v>
       </c>
       <c r="R247" t="n">
-        <v>6920029</v>
+        <v>6920199</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -26047,10 +26012,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>124460965</v>
+        <v>124456046</v>
       </c>
       <c r="B248" t="n">
-        <v>78810</v>
+        <v>91032</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -26063,34 +26028,34 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>380307</v>
+        <v>380326</v>
       </c>
       <c r="R248" t="n">
-        <v>6919967</v>
+        <v>6920218</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -26125,6 +26090,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området.</t>
+        </is>
+      </c>
       <c r="AD248" t="b">
         <v>0</v>
       </c>
@@ -26137,22 +26107,22 @@
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>124468916</v>
+        <v>124458651</v>
       </c>
       <c r="B249" t="n">
-        <v>78151</v>
+        <v>91030</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -26161,38 +26131,38 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>498</v>
+        <v>5432</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>380343</v>
+        <v>380569</v>
       </c>
       <c r="R249" t="n">
-        <v>6919896</v>
+        <v>6920058</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -26251,10 +26221,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>124464329</v>
+        <v>124458743</v>
       </c>
       <c r="B250" t="n">
-        <v>78194</v>
+        <v>91030</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -26267,34 +26237,34 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>6437</v>
+        <v>5432</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>380268</v>
+        <v>380542</v>
       </c>
       <c r="R250" t="n">
-        <v>6919685</v>
+        <v>6920184</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -26329,6 +26299,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD250" t="b">
         <v>0</v>
       </c>
@@ -26341,22 +26316,22 @@
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>124451569</v>
+        <v>124457605</v>
       </c>
       <c r="B251" t="n">
-        <v>79399</v>
+        <v>57513</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -26369,34 +26344,39 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P251" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>380184</v>
+        <v>380542</v>
       </c>
       <c r="R251" t="n">
-        <v>6920434</v>
+        <v>6920184</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -26431,6 +26411,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC251" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området.</t>
+        </is>
+      </c>
       <c r="AD251" t="b">
         <v>0</v>
       </c>
@@ -26443,22 +26428,22 @@
       <c r="AT251" t="inlineStr"/>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>124464321</v>
+        <v>124470707</v>
       </c>
       <c r="B252" t="n">
-        <v>77738</v>
+        <v>57513</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -26471,37 +26456,42 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>6487</v>
+        <v>100109</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P252" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>380268</v>
+        <v>380367</v>
       </c>
       <c r="R252" t="n">
-        <v>6919685</v>
+        <v>6920058</v>
       </c>
       <c r="S252" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T252" t="inlineStr">
         <is>
@@ -26557,7 +26547,7 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>124461646</v>
+        <v>124460224</v>
       </c>
       <c r="B253" t="n">
         <v>57513</v>
@@ -26598,17 +26588,17 @@
       </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>380239</v>
+        <v>380374</v>
       </c>
       <c r="R253" t="n">
-        <v>6919828</v>
+        <v>6919982</v>
       </c>
       <c r="S253" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T253" t="inlineStr">
         <is>
@@ -26652,19 +26642,19 @@
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>124466302</v>
+        <v>124471016</v>
       </c>
       <c r="B254" t="n">
         <v>57513</v>
@@ -26709,13 +26699,13 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>380345</v>
+        <v>380506</v>
       </c>
       <c r="R254" t="n">
-        <v>6919632</v>
+        <v>6920061</v>
       </c>
       <c r="S254" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T254" t="inlineStr">
         <is>
@@ -26759,19 +26749,19 @@
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>124468547</v>
+        <v>124456372</v>
       </c>
       <c r="B255" t="n">
         <v>74901</v>
@@ -26807,14 +26797,14 @@
       <c r="I255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>380356</v>
+        <v>380368</v>
       </c>
       <c r="R255" t="n">
-        <v>6919817</v>
+        <v>6920107</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26873,7 +26863,7 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>124461108</v>
+        <v>124455220</v>
       </c>
       <c r="B256" t="n">
         <v>74901</v>
@@ -26913,10 +26903,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>380308</v>
+        <v>380311</v>
       </c>
       <c r="R256" t="n">
-        <v>6919925</v>
+        <v>6920231</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -26949,11 +26939,6 @@
       <c r="AA256" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC256" t="inlineStr">
-        <is>
-          <t>På basen avsågad gran. Grov stubbe</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -27082,10 +27067,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>124470234</v>
+        <v>124458172</v>
       </c>
       <c r="B258" t="n">
-        <v>82597</v>
+        <v>78151</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -27094,25 +27079,25 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>1312</v>
+        <v>498</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -27122,10 +27107,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>380506</v>
+        <v>380562</v>
       </c>
       <c r="R258" t="n">
-        <v>6920009</v>
+        <v>6920118</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -27184,10 +27169,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>124456502</v>
+        <v>124470806</v>
       </c>
       <c r="B259" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -27200,37 +27185,42 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>380385</v>
+        <v>380340</v>
       </c>
       <c r="R259" t="n">
-        <v>6920091</v>
+        <v>6920036</v>
       </c>
       <c r="S259" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T259" t="inlineStr">
         <is>
@@ -27260,11 +27250,6 @@
       <c r="AA259" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC259" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -27279,22 +27264,22 @@
       <c r="AT259" t="inlineStr"/>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>124459042</v>
+        <v>124451984</v>
       </c>
       <c r="B260" t="n">
-        <v>74901</v>
+        <v>79399</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -27307,34 +27292,34 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>380571</v>
+        <v>380203</v>
       </c>
       <c r="R260" t="n">
-        <v>6919993</v>
+        <v>6920482</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -27393,10 +27378,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>124469915</v>
+        <v>124456676</v>
       </c>
       <c r="B261" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -27409,37 +27394,42 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P261" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>380521</v>
+        <v>380434</v>
       </c>
       <c r="R261" t="n">
-        <v>6919962</v>
+        <v>6920123</v>
       </c>
       <c r="S261" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T261" t="inlineStr">
         <is>
@@ -27495,10 +27485,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>124464842</v>
+        <v>124470732</v>
       </c>
       <c r="B262" t="n">
-        <v>79428</v>
+        <v>74901</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -27511,34 +27501,34 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>380237</v>
+        <v>380372</v>
       </c>
       <c r="R262" t="n">
-        <v>6919621</v>
+        <v>6920042</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -27597,10 +27587,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>124470742</v>
+        <v>124464471</v>
       </c>
       <c r="B263" t="n">
-        <v>57513</v>
+        <v>78194</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -27613,42 +27603,37 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
-      <c r="M263" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>380369</v>
+        <v>380243</v>
       </c>
       <c r="R263" t="n">
-        <v>6920032</v>
+        <v>6919687</v>
       </c>
       <c r="S263" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T263" t="inlineStr">
         <is>
@@ -27704,10 +27689,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>124460224</v>
+        <v>124450666</v>
       </c>
       <c r="B264" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -27720,39 +27705,34 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
-      <c r="M264" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P264" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>380374</v>
+        <v>380227</v>
       </c>
       <c r="R264" t="n">
-        <v>6919982</v>
+        <v>6920340</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27811,10 +27791,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>124464651</v>
+        <v>124468916</v>
       </c>
       <c r="B265" t="n">
-        <v>79399</v>
+        <v>78151</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -27823,38 +27803,38 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>229821</v>
+        <v>498</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>380251</v>
+        <v>380343</v>
       </c>
       <c r="R265" t="n">
-        <v>6919658</v>
+        <v>6919896</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27913,10 +27893,10 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>124455022</v>
+        <v>124452423</v>
       </c>
       <c r="B266" t="n">
-        <v>79428</v>
+        <v>56725</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -27925,38 +27905,43 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>6453</v>
+        <v>102613</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P266" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>380292</v>
+        <v>380227</v>
       </c>
       <c r="R266" t="n">
-        <v>6920288</v>
+        <v>6920340</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -28003,12 +27988,12 @@
       <c r="AT266" t="inlineStr"/>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
@@ -28122,7 +28107,7 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>124464970</v>
+        <v>124464292</v>
       </c>
       <c r="B268" t="n">
         <v>57513</v>
@@ -28167,13 +28152,13 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>380255</v>
+        <v>380275</v>
       </c>
       <c r="R268" t="n">
-        <v>6919561</v>
+        <v>6919775</v>
       </c>
       <c r="S268" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T268" t="inlineStr">
         <is>
@@ -28217,22 +28202,22 @@
       <c r="AT268" t="inlineStr"/>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>124464047</v>
+        <v>124466302</v>
       </c>
       <c r="B269" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -28245,37 +28230,42 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>380267</v>
+        <v>380345</v>
       </c>
       <c r="R269" t="n">
-        <v>6919731</v>
+        <v>6919632</v>
       </c>
       <c r="S269" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T269" t="inlineStr">
         <is>
@@ -28331,10 +28321,10 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>124450578</v>
+        <v>124455134</v>
       </c>
       <c r="B270" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -28347,21 +28337,21 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
@@ -28371,10 +28361,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>380227</v>
+        <v>380311</v>
       </c>
       <c r="R270" t="n">
-        <v>6920340</v>
+        <v>6920245</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -28421,22 +28411,22 @@
       <c r="AT270" t="inlineStr"/>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>124452627</v>
+        <v>124466494</v>
       </c>
       <c r="B271" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -28449,37 +28439,42 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P271" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>380217</v>
+        <v>380344</v>
       </c>
       <c r="R271" t="n">
-        <v>6920440</v>
+        <v>6919654</v>
       </c>
       <c r="S271" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T271" t="inlineStr">
         <is>
@@ -28535,10 +28530,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>124461477</v>
+        <v>124461646</v>
       </c>
       <c r="B272" t="n">
-        <v>79399</v>
+        <v>57513</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -28551,37 +28546,42 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P272" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>380285</v>
+        <v>380239</v>
       </c>
       <c r="R272" t="n">
-        <v>6919895</v>
+        <v>6919828</v>
       </c>
       <c r="S272" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T272" t="inlineStr">
         <is>
@@ -28637,7 +28637,7 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>124588108</v>
+        <v>124588913</v>
       </c>
       <c r="B273" t="n">
         <v>57513</v>
@@ -28673,19 +28673,19 @@
       <c r="I273" t="inlineStr"/>
       <c r="M273" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P273" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>380223</v>
+        <v>380140</v>
       </c>
       <c r="R273" t="n">
-        <v>6920277</v>
+        <v>6919839</v>
       </c>
       <c r="S273" t="n">
         <v>15</v>
@@ -28744,7 +28744,7 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>124588913</v>
+        <v>124588108</v>
       </c>
       <c r="B274" t="n">
         <v>57513</v>
@@ -28780,19 +28780,19 @@
       <c r="I274" t="inlineStr"/>
       <c r="M274" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P274" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>380140</v>
+        <v>380223</v>
       </c>
       <c r="R274" t="n">
-        <v>6919839</v>
+        <v>6920277</v>
       </c>
       <c r="S274" t="n">
         <v>15</v>
@@ -28953,10 +28953,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>124871232</v>
+        <v>124870503</v>
       </c>
       <c r="B276" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -28969,37 +28969,42 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P276" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>380202</v>
+        <v>380108</v>
       </c>
       <c r="R276" t="n">
-        <v>6920072</v>
+        <v>6919741</v>
       </c>
       <c r="S276" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T276" t="inlineStr">
         <is>
@@ -29055,7 +29060,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>124870881</v>
+        <v>124870424</v>
       </c>
       <c r="B277" t="n">
         <v>57513</v>
@@ -29091,7 +29096,7 @@
       <c r="I277" t="inlineStr"/>
       <c r="M277" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P277" t="inlineStr">
@@ -29100,10 +29105,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>380067</v>
+        <v>380098</v>
       </c>
       <c r="R277" t="n">
-        <v>6919860</v>
+        <v>6919759</v>
       </c>
       <c r="S277" t="n">
         <v>15</v>
@@ -29162,10 +29167,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>124870654</v>
+        <v>124870851</v>
       </c>
       <c r="B278" t="n">
-        <v>74901</v>
+        <v>79399</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -29178,21 +29183,21 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
@@ -29202,10 +29207,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>380093</v>
+        <v>380051</v>
       </c>
       <c r="R278" t="n">
-        <v>6919795</v>
+        <v>6919850</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -29264,10 +29269,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>124870920</v>
+        <v>124870654</v>
       </c>
       <c r="B279" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -29280,34 +29285,34 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
       <c r="P279" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>380097</v>
+        <v>380093</v>
       </c>
       <c r="R279" t="n">
-        <v>6919882</v>
+        <v>6919795</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -29366,7 +29371,7 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>124870424</v>
+        <v>124871117</v>
       </c>
       <c r="B280" t="n">
         <v>57513</v>
@@ -29407,14 +29412,14 @@
       </c>
       <c r="P280" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>380098</v>
+        <v>380204</v>
       </c>
       <c r="R280" t="n">
-        <v>6919759</v>
+        <v>6920043</v>
       </c>
       <c r="S280" t="n">
         <v>15</v>
@@ -29473,10 +29478,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>124870262</v>
+        <v>124870920</v>
       </c>
       <c r="B281" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -29489,42 +29494,37 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
-      <c r="M281" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P281" t="inlineStr">
         <is>
           <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>380196</v>
+        <v>380097</v>
       </c>
       <c r="R281" t="n">
-        <v>6919970</v>
+        <v>6919882</v>
       </c>
       <c r="S281" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T281" t="inlineStr">
         <is>
@@ -29580,7 +29580,7 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>124870829</v>
+        <v>124870881</v>
       </c>
       <c r="B282" t="n">
         <v>57513</v>
@@ -29616,7 +29616,7 @@
       <c r="I282" t="inlineStr"/>
       <c r="M282" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P282" t="inlineStr">
@@ -29625,10 +29625,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>380045</v>
+        <v>380067</v>
       </c>
       <c r="R282" t="n">
-        <v>6919831</v>
+        <v>6919860</v>
       </c>
       <c r="S282" t="n">
         <v>15</v>
@@ -29687,7 +29687,7 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>124870503</v>
+        <v>124870829</v>
       </c>
       <c r="B283" t="n">
         <v>57513</v>
@@ -29732,10 +29732,10 @@
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>380108</v>
+        <v>380045</v>
       </c>
       <c r="R283" t="n">
-        <v>6919741</v>
+        <v>6919831</v>
       </c>
       <c r="S283" t="n">
         <v>15</v>
@@ -29794,7 +29794,7 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>124871057</v>
+        <v>124871081</v>
       </c>
       <c r="B284" t="n">
         <v>57513</v>
@@ -29839,10 +29839,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>380132</v>
+        <v>380173</v>
       </c>
       <c r="R284" t="n">
-        <v>6919977</v>
+        <v>6920011</v>
       </c>
       <c r="S284" t="n">
         <v>15</v>
@@ -29901,7 +29901,7 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>124871117</v>
+        <v>124870943</v>
       </c>
       <c r="B285" t="n">
         <v>57513</v>
@@ -29946,10 +29946,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>380204</v>
+        <v>380093</v>
       </c>
       <c r="R285" t="n">
-        <v>6920043</v>
+        <v>6919892</v>
       </c>
       <c r="S285" t="n">
         <v>15</v>
@@ -30008,7 +30008,7 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>124870943</v>
+        <v>124871057</v>
       </c>
       <c r="B286" t="n">
         <v>57513</v>
@@ -30053,10 +30053,10 @@
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>380093</v>
+        <v>380132</v>
       </c>
       <c r="R286" t="n">
-        <v>6919892</v>
+        <v>6919977</v>
       </c>
       <c r="S286" t="n">
         <v>15</v>
@@ -30115,10 +30115,10 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>124870851</v>
+        <v>124870262</v>
       </c>
       <c r="B287" t="n">
-        <v>79399</v>
+        <v>57513</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -30131,37 +30131,42 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I287" t="inlineStr"/>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P287" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>380051</v>
+        <v>380196</v>
       </c>
       <c r="R287" t="n">
-        <v>6919850</v>
+        <v>6919970</v>
       </c>
       <c r="S287" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T287" t="inlineStr">
         <is>
@@ -30217,10 +30222,10 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>124871081</v>
+        <v>124870693</v>
       </c>
       <c r="B288" t="n">
-        <v>57513</v>
+        <v>96354</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -30233,42 +30238,37 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I288" t="inlineStr"/>
-      <c r="M288" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P288" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>380173</v>
+        <v>380072</v>
       </c>
       <c r="R288" t="n">
-        <v>6920011</v>
+        <v>6919810</v>
       </c>
       <c r="S288" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T288" t="inlineStr">
         <is>
@@ -30324,10 +30324,10 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>124870693</v>
+        <v>124871232</v>
       </c>
       <c r="B289" t="n">
-        <v>96354</v>
+        <v>74901</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -30340,34 +30340,34 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>53</v>
+        <v>6440</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I289" t="inlineStr"/>
       <c r="P289" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>380072</v>
+        <v>380202</v>
       </c>
       <c r="R289" t="n">
-        <v>6919810</v>
+        <v>6920072</v>
       </c>
       <c r="S289" t="n">
         <v>10</v>

--- a/artfynd/A 32573-2024 artfynd.xlsx
+++ b/artfynd/A 32573-2024 artfynd.xlsx
@@ -16620,10 +16620,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>124470555</v>
+        <v>124470598</v>
       </c>
       <c r="B157" t="n">
-        <v>82597</v>
+        <v>79428</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16636,34 +16636,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>380431</v>
+        <v>380506</v>
       </c>
       <c r="R157" t="n">
-        <v>6920068</v>
+        <v>6920061</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16698,6 +16698,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
@@ -16710,22 +16715,22 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>124455206</v>
+        <v>124450902</v>
       </c>
       <c r="B158" t="n">
-        <v>91030</v>
+        <v>57529</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16738,34 +16743,39 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>380311</v>
+        <v>380227</v>
       </c>
       <c r="R158" t="n">
-        <v>6920231</v>
+        <v>6920340</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16800,6 +16810,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Troligen spillkråka.</t>
+        </is>
+      </c>
       <c r="AD158" t="b">
         <v>0</v>
       </c>
@@ -16812,22 +16827,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>124470598</v>
+        <v>124470555</v>
       </c>
       <c r="B159" t="n">
-        <v>79428</v>
+        <v>82597</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16840,34 +16855,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>380506</v>
+        <v>380431</v>
       </c>
       <c r="R159" t="n">
-        <v>6920061</v>
+        <v>6920068</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16902,11 +16917,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD159" t="b">
         <v>0</v>
       </c>
@@ -16919,22 +16929,22 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>124450902</v>
+        <v>124455206</v>
       </c>
       <c r="B160" t="n">
-        <v>57529</v>
+        <v>91030</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -16947,39 +16957,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P160" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>380227</v>
+        <v>380311</v>
       </c>
       <c r="R160" t="n">
-        <v>6920340</v>
+        <v>6920231</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17014,11 +17019,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>Troligen spillkråka.</t>
-        </is>
-      </c>
       <c r="AD160" t="b">
         <v>0</v>
       </c>
@@ -17031,12 +17031,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
@@ -19740,10 +19740,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124459287</v>
+        <v>124454876</v>
       </c>
       <c r="B187" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -19756,39 +19756,34 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>380561</v>
+        <v>380290</v>
       </c>
       <c r="R187" t="n">
-        <v>6919930</v>
+        <v>6920272</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19835,22 +19830,22 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124469088</v>
+        <v>124465167</v>
       </c>
       <c r="B188" t="n">
-        <v>78810</v>
+        <v>78194</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -19863,34 +19858,34 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>380352</v>
+        <v>380244</v>
       </c>
       <c r="R188" t="n">
-        <v>6919913</v>
+        <v>6919577</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19937,22 +19932,22 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124470184</v>
+        <v>124451837</v>
       </c>
       <c r="B189" t="n">
-        <v>91030</v>
+        <v>78194</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -19965,34 +19960,34 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>5432</v>
+        <v>6437</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>380516</v>
+        <v>380197</v>
       </c>
       <c r="R189" t="n">
-        <v>6920004</v>
+        <v>6920479</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20051,10 +20046,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>124450518</v>
+        <v>124470485</v>
       </c>
       <c r="B190" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20067,21 +20062,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20091,10 +20086,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>380202</v>
+        <v>380446</v>
       </c>
       <c r="R190" t="n">
-        <v>6920332</v>
+        <v>6920059</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20260,10 +20255,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>124464466</v>
+        <v>124459287</v>
       </c>
       <c r="B192" t="n">
-        <v>78905</v>
+        <v>57513</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20276,34 +20271,39 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>967</v>
+        <v>100109</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>380243</v>
+        <v>380561</v>
       </c>
       <c r="R192" t="n">
-        <v>6919687</v>
+        <v>6919930</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20350,22 +20350,22 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>124454876</v>
+        <v>124469088</v>
       </c>
       <c r="B193" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -20378,34 +20378,34 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>380290</v>
+        <v>380352</v>
       </c>
       <c r="R193" t="n">
-        <v>6920272</v>
+        <v>6919913</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20464,10 +20464,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>124465167</v>
+        <v>124470184</v>
       </c>
       <c r="B194" t="n">
-        <v>78194</v>
+        <v>91030</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -20480,21 +20480,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6437</v>
+        <v>5432</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20504,10 +20504,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>380244</v>
+        <v>380516</v>
       </c>
       <c r="R194" t="n">
-        <v>6919577</v>
+        <v>6920004</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20554,22 +20554,22 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>124451837</v>
+        <v>124450518</v>
       </c>
       <c r="B195" t="n">
-        <v>78194</v>
+        <v>78810</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -20582,34 +20582,34 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>380197</v>
+        <v>380202</v>
       </c>
       <c r="R195" t="n">
-        <v>6920479</v>
+        <v>6920332</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20668,10 +20668,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>124470485</v>
+        <v>124464466</v>
       </c>
       <c r="B196" t="n">
-        <v>74901</v>
+        <v>78905</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -20684,21 +20684,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6440</v>
+        <v>967</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20708,10 +20708,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>380446</v>
+        <v>380243</v>
       </c>
       <c r="R196" t="n">
-        <v>6920059</v>
+        <v>6919687</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -22106,7 +22106,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>124470397</v>
+        <v>124454665</v>
       </c>
       <c r="B210" t="n">
         <v>74901</v>
@@ -22142,14 +22142,14 @@
       <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>380506</v>
+        <v>380258</v>
       </c>
       <c r="R210" t="n">
-        <v>6920061</v>
+        <v>6920309</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22196,22 +22196,22 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>124454665</v>
+        <v>124451574</v>
       </c>
       <c r="B211" t="n">
-        <v>74901</v>
+        <v>79428</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -22224,34 +22224,34 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>380258</v>
+        <v>380184</v>
       </c>
       <c r="R211" t="n">
-        <v>6920309</v>
+        <v>6920434</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22310,10 +22310,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>124451574</v>
+        <v>124470397</v>
       </c>
       <c r="B212" t="n">
-        <v>79428</v>
+        <v>74901</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -22326,34 +22326,34 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>380184</v>
+        <v>380506</v>
       </c>
       <c r="R212" t="n">
-        <v>6920434</v>
+        <v>6920061</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22400,12 +22400,12 @@
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
@@ -22616,10 +22616,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>124470299</v>
+        <v>124456697</v>
       </c>
       <c r="B215" t="n">
-        <v>56722</v>
+        <v>91030</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -22628,43 +22628,38 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
-      <c r="M215" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P215" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>380495</v>
+        <v>380443</v>
       </c>
       <c r="R215" t="n">
-        <v>6920029</v>
+        <v>6920118</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22723,10 +22718,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>124464970</v>
+        <v>124456129</v>
       </c>
       <c r="B216" t="n">
-        <v>57513</v>
+        <v>78905</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -22739,42 +22734,37 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>100109</v>
+        <v>967</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
-      <c r="M216" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>380255</v>
+        <v>380326</v>
       </c>
       <c r="R216" t="n">
-        <v>6919561</v>
+        <v>6920218</v>
       </c>
       <c r="S216" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -22818,22 +22808,22 @@
       <c r="AT216" t="inlineStr"/>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>124468469</v>
+        <v>124464321</v>
       </c>
       <c r="B217" t="n">
-        <v>57513</v>
+        <v>77738</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -22846,42 +22836,37 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
-      <c r="M217" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P217" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>380324</v>
+        <v>380268</v>
       </c>
       <c r="R217" t="n">
-        <v>6919803</v>
+        <v>6919685</v>
       </c>
       <c r="S217" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -22937,10 +22922,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>124464321</v>
+        <v>124469915</v>
       </c>
       <c r="B218" t="n">
-        <v>77738</v>
+        <v>74901</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -22953,21 +22938,21 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>6487</v>
+        <v>6440</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -22977,10 +22962,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>380268</v>
+        <v>380521</v>
       </c>
       <c r="R218" t="n">
-        <v>6919685</v>
+        <v>6919962</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23039,7 +23024,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>124469915</v>
+        <v>124450300</v>
       </c>
       <c r="B219" t="n">
         <v>74901</v>
@@ -23079,10 +23064,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>380521</v>
+        <v>380182</v>
       </c>
       <c r="R219" t="n">
-        <v>6919962</v>
+        <v>6920316</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23141,7 +23126,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>124450300</v>
+        <v>124450415</v>
       </c>
       <c r="B220" t="n">
         <v>74901</v>
@@ -23181,10 +23166,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>380182</v>
+        <v>380202</v>
       </c>
       <c r="R220" t="n">
-        <v>6920316</v>
+        <v>6920332</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23243,10 +23228,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>124450415</v>
+        <v>124468469</v>
       </c>
       <c r="B221" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -23259,37 +23244,42 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>380202</v>
+        <v>380324</v>
       </c>
       <c r="R221" t="n">
-        <v>6920332</v>
+        <v>6919803</v>
       </c>
       <c r="S221" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -23345,10 +23335,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>124456697</v>
+        <v>124470299</v>
       </c>
       <c r="B222" t="n">
-        <v>91030</v>
+        <v>56722</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -23357,38 +23347,43 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P222" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>380443</v>
+        <v>380495</v>
       </c>
       <c r="R222" t="n">
-        <v>6920118</v>
+        <v>6920029</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23447,10 +23442,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>124456129</v>
+        <v>124464970</v>
       </c>
       <c r="B223" t="n">
-        <v>78905</v>
+        <v>57513</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -23463,37 +23458,42 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>967</v>
+        <v>100109</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>380326</v>
+        <v>380255</v>
       </c>
       <c r="R223" t="n">
-        <v>6920218</v>
+        <v>6919561</v>
       </c>
       <c r="S223" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -23537,12 +23537,12 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
@@ -26012,10 +26012,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>124456046</v>
+        <v>124457605</v>
       </c>
       <c r="B248" t="n">
-        <v>91032</v>
+        <v>57513</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -26028,34 +26028,39 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P248" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>380326</v>
+        <v>380542</v>
       </c>
       <c r="R248" t="n">
-        <v>6920218</v>
+        <v>6920184</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -26119,10 +26124,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>124458651</v>
+        <v>124470707</v>
       </c>
       <c r="B249" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -26135,37 +26140,42 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>380569</v>
+        <v>380367</v>
       </c>
       <c r="R249" t="n">
         <v>6920058</v>
       </c>
       <c r="S249" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T249" t="inlineStr">
         <is>
@@ -26221,10 +26231,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>124458743</v>
+        <v>124460224</v>
       </c>
       <c r="B250" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -26237,34 +26247,39 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>380542</v>
+        <v>380374</v>
       </c>
       <c r="R250" t="n">
-        <v>6920184</v>
+        <v>6919982</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -26297,11 +26312,6 @@
       <c r="AA250" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC250" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -26328,7 +26338,7 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>124457605</v>
+        <v>124471016</v>
       </c>
       <c r="B251" t="n">
         <v>57513</v>
@@ -26364,19 +26374,19 @@
       <c r="I251" t="inlineStr"/>
       <c r="M251" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P251" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>380542</v>
+        <v>380506</v>
       </c>
       <c r="R251" t="n">
-        <v>6920184</v>
+        <v>6920061</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -26409,11 +26419,6 @@
       <c r="AA251" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC251" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -26440,10 +26445,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>124470707</v>
+        <v>124456046</v>
       </c>
       <c r="B252" t="n">
-        <v>57513</v>
+        <v>91032</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -26456,42 +26461,37 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
-      <c r="M252" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P252" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>380367</v>
+        <v>380326</v>
       </c>
       <c r="R252" t="n">
-        <v>6920058</v>
+        <v>6920218</v>
       </c>
       <c r="S252" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T252" t="inlineStr">
         <is>
@@ -26521,6 +26521,11 @@
       <c r="AA252" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC252" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -26535,22 +26540,22 @@
       <c r="AT252" t="inlineStr"/>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>124460224</v>
+        <v>124458651</v>
       </c>
       <c r="B253" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -26563,39 +26568,34 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
-      <c r="M253" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>380374</v>
+        <v>380569</v>
       </c>
       <c r="R253" t="n">
-        <v>6919982</v>
+        <v>6920058</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -26642,22 +26642,22 @@
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>124471016</v>
+        <v>124458743</v>
       </c>
       <c r="B254" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -26670,39 +26670,34 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
-      <c r="M254" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P254" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>380506</v>
+        <v>380542</v>
       </c>
       <c r="R254" t="n">
-        <v>6920061</v>
+        <v>6920184</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26735,6 +26730,11 @@
       <c r="AA254" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -27276,10 +27276,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>124451984</v>
+        <v>124470732</v>
       </c>
       <c r="B260" t="n">
-        <v>79399</v>
+        <v>74901</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -27292,34 +27292,34 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>380203</v>
+        <v>380372</v>
       </c>
       <c r="R260" t="n">
-        <v>6920482</v>
+        <v>6920042</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -27378,10 +27378,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>124456676</v>
+        <v>124464471</v>
       </c>
       <c r="B261" t="n">
-        <v>57513</v>
+        <v>78194</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -27394,42 +27394,37 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
-      <c r="M261" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P261" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>380434</v>
+        <v>380243</v>
       </c>
       <c r="R261" t="n">
-        <v>6920123</v>
+        <v>6919687</v>
       </c>
       <c r="S261" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T261" t="inlineStr">
         <is>
@@ -27485,7 +27480,7 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>124470732</v>
+        <v>124450666</v>
       </c>
       <c r="B262" t="n">
         <v>74901</v>
@@ -27521,14 +27516,14 @@
       <c r="I262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>380372</v>
+        <v>380227</v>
       </c>
       <c r="R262" t="n">
-        <v>6920042</v>
+        <v>6920340</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -27575,22 +27570,22 @@
       <c r="AT262" t="inlineStr"/>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>124464471</v>
+        <v>124468916</v>
       </c>
       <c r="B263" t="n">
-        <v>78194</v>
+        <v>78151</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -27599,38 +27594,38 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>6437</v>
+        <v>498</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>380243</v>
+        <v>380343</v>
       </c>
       <c r="R263" t="n">
-        <v>6919687</v>
+        <v>6919896</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -27689,10 +27684,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>124450666</v>
+        <v>124451984</v>
       </c>
       <c r="B264" t="n">
-        <v>74901</v>
+        <v>79399</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -27705,21 +27700,21 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
@@ -27729,10 +27724,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>380227</v>
+        <v>380203</v>
       </c>
       <c r="R264" t="n">
-        <v>6920340</v>
+        <v>6920482</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27779,22 +27774,22 @@
       <c r="AT264" t="inlineStr"/>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>124468916</v>
+        <v>124456676</v>
       </c>
       <c r="B265" t="n">
-        <v>78151</v>
+        <v>57513</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -27803,41 +27798,46 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>498</v>
+        <v>100109</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P265" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>380343</v>
+        <v>380434</v>
       </c>
       <c r="R265" t="n">
-        <v>6919896</v>
+        <v>6920123</v>
       </c>
       <c r="S265" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T265" t="inlineStr">
         <is>

--- a/artfynd/A 32573-2024 artfynd.xlsx
+++ b/artfynd/A 32573-2024 artfynd.xlsx
@@ -16212,10 +16212,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>124452627</v>
+        <v>124460611</v>
       </c>
       <c r="B153" t="n">
-        <v>74901</v>
+        <v>78905</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16228,34 +16228,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6440</v>
+        <v>967</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>380217</v>
+        <v>380335</v>
       </c>
       <c r="R153" t="n">
-        <v>6920440</v>
+        <v>6920000</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16302,22 +16302,22 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>124460258</v>
+        <v>124457601</v>
       </c>
       <c r="B154" t="n">
-        <v>79428</v>
+        <v>78151</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16326,38 +16326,38 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6453</v>
+        <v>498</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>380365</v>
+        <v>380544</v>
       </c>
       <c r="R154" t="n">
-        <v>6919996</v>
+        <v>6920188</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16416,10 +16416,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>124460611</v>
+        <v>124452627</v>
       </c>
       <c r="B155" t="n">
-        <v>78905</v>
+        <v>74901</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16432,34 +16432,34 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>967</v>
+        <v>6440</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>380335</v>
+        <v>380217</v>
       </c>
       <c r="R155" t="n">
-        <v>6920000</v>
+        <v>6920440</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16506,22 +16506,22 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>124457601</v>
+        <v>124460258</v>
       </c>
       <c r="B156" t="n">
-        <v>78151</v>
+        <v>79428</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16530,38 +16530,38 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>498</v>
+        <v>6453</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>380544</v>
+        <v>380365</v>
       </c>
       <c r="R156" t="n">
-        <v>6920188</v>
+        <v>6919996</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18287,10 +18287,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>124454979</v>
+        <v>124461477</v>
       </c>
       <c r="B173" t="n">
-        <v>91030</v>
+        <v>79399</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18303,34 +18303,34 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>5432</v>
+        <v>229821</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>380289</v>
+        <v>380285</v>
       </c>
       <c r="R173" t="n">
-        <v>6920290</v>
+        <v>6919895</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18365,11 +18365,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC173" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
-        </is>
-      </c>
       <c r="AD173" t="b">
         <v>0</v>
       </c>
@@ -18382,22 +18377,22 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>124459134</v>
+        <v>124454979</v>
       </c>
       <c r="B174" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18410,34 +18405,34 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>380559</v>
+        <v>380289</v>
       </c>
       <c r="R174" t="n">
-        <v>6919947</v>
+        <v>6920290</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18472,6 +18467,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD174" t="b">
         <v>0</v>
       </c>
@@ -18484,19 +18484,19 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>124455453</v>
+        <v>124459134</v>
       </c>
       <c r="B175" t="n">
         <v>74901</v>
@@ -18532,14 +18532,14 @@
       <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>380326</v>
+        <v>380559</v>
       </c>
       <c r="R175" t="n">
-        <v>6920218</v>
+        <v>6919947</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18586,22 +18586,22 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>124461477</v>
+        <v>124455453</v>
       </c>
       <c r="B176" t="n">
-        <v>79399</v>
+        <v>74901</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -18614,34 +18614,34 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>380285</v>
+        <v>380326</v>
       </c>
       <c r="R176" t="n">
-        <v>6919895</v>
+        <v>6920218</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18688,22 +18688,22 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>124465389</v>
+        <v>124458282</v>
       </c>
       <c r="B177" t="n">
-        <v>79399</v>
+        <v>78151</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -18712,25 +18712,25 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>229821</v>
+        <v>498</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18740,10 +18740,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>380244</v>
+        <v>380588</v>
       </c>
       <c r="R177" t="n">
-        <v>6919577</v>
+        <v>6920110</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18790,22 +18790,22 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>124458282</v>
+        <v>124465389</v>
       </c>
       <c r="B178" t="n">
-        <v>78151</v>
+        <v>79399</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -18814,25 +18814,25 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>498</v>
+        <v>229821</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18842,10 +18842,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>380588</v>
+        <v>380244</v>
       </c>
       <c r="R178" t="n">
-        <v>6920110</v>
+        <v>6919577</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18892,22 +18892,22 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>124451326</v>
+        <v>124452261</v>
       </c>
       <c r="B179" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -18920,29 +18920,24 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P179" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
@@ -19011,10 +19006,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>124452261</v>
+        <v>124469751</v>
       </c>
       <c r="B180" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -19027,34 +19022,34 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>380227</v>
+        <v>380490</v>
       </c>
       <c r="R180" t="n">
-        <v>6920340</v>
+        <v>6919937</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19101,22 +19096,22 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>124469751</v>
+        <v>124467947</v>
       </c>
       <c r="B181" t="n">
-        <v>74901</v>
+        <v>78194</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -19129,34 +19124,34 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>380490</v>
+        <v>380361</v>
       </c>
       <c r="R181" t="n">
-        <v>6919937</v>
+        <v>6919740</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19191,6 +19186,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD181" t="b">
         <v>0</v>
       </c>
@@ -19203,22 +19203,22 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124467947</v>
+        <v>124464842</v>
       </c>
       <c r="B182" t="n">
-        <v>78194</v>
+        <v>79428</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -19231,21 +19231,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19255,10 +19255,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>380361</v>
+        <v>380237</v>
       </c>
       <c r="R182" t="n">
-        <v>6919740</v>
+        <v>6919621</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19293,11 +19293,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC182" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD182" t="b">
         <v>0</v>
       </c>
@@ -19310,22 +19305,22 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124464842</v>
+        <v>124451326</v>
       </c>
       <c r="B183" t="n">
-        <v>79428</v>
+        <v>57513</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -19338,34 +19333,39 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>380237</v>
+        <v>380227</v>
       </c>
       <c r="R183" t="n">
-        <v>6919621</v>
+        <v>6920340</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19412,22 +19412,22 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124464651</v>
+        <v>124458357</v>
       </c>
       <c r="B184" t="n">
-        <v>79399</v>
+        <v>57666</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -19440,37 +19440,42 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P184" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>380251</v>
+        <v>380586</v>
       </c>
       <c r="R184" t="n">
-        <v>6919658</v>
+        <v>6920100</v>
       </c>
       <c r="S184" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -19526,10 +19531,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124458357</v>
+        <v>124455096</v>
       </c>
       <c r="B185" t="n">
-        <v>57666</v>
+        <v>5196</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -19538,46 +19543,46 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>103021</v>
+        <v>105930</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="M185" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>380586</v>
+        <v>380323</v>
       </c>
       <c r="R185" t="n">
-        <v>6920100</v>
+        <v>6920260</v>
       </c>
       <c r="S185" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -19633,10 +19638,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124455096</v>
+        <v>124464651</v>
       </c>
       <c r="B186" t="n">
-        <v>5196</v>
+        <v>79399</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -19645,43 +19650,38 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>105930</v>
+        <v>229821</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>380323</v>
+        <v>380251</v>
       </c>
       <c r="R186" t="n">
-        <v>6920260</v>
+        <v>6919658</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20770,10 +20770,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>124470646</v>
+        <v>124466026</v>
       </c>
       <c r="B197" t="n">
-        <v>91030</v>
+        <v>79399</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -20786,34 +20786,34 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>5432</v>
+        <v>229821</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>380402</v>
+        <v>380303</v>
       </c>
       <c r="R197" t="n">
-        <v>6920044</v>
+        <v>6919598</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20848,6 +20848,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD197" t="b">
         <v>0</v>
       </c>
@@ -20860,22 +20865,22 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>124450737</v>
+        <v>124465009</v>
       </c>
       <c r="B198" t="n">
-        <v>74901</v>
+        <v>79399</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -20888,34 +20893,34 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>380210</v>
+        <v>380267</v>
       </c>
       <c r="R198" t="n">
-        <v>6920378</v>
+        <v>6919764</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20950,6 +20955,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD198" t="b">
         <v>0</v>
       </c>
@@ -20962,22 +20972,22 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>124461736</v>
+        <v>124470646</v>
       </c>
       <c r="B199" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -20990,34 +21000,34 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>380232</v>
+        <v>380402</v>
       </c>
       <c r="R199" t="n">
-        <v>6919808</v>
+        <v>6920044</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21076,10 +21086,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>124469907</v>
+        <v>124450737</v>
       </c>
       <c r="B200" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -21092,34 +21102,34 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>380452</v>
+        <v>380210</v>
       </c>
       <c r="R200" t="n">
-        <v>6919913</v>
+        <v>6920378</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21166,22 +21176,22 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>124466026</v>
+        <v>124461736</v>
       </c>
       <c r="B201" t="n">
-        <v>79399</v>
+        <v>74901</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -21194,21 +21204,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -21218,10 +21228,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>380303</v>
+        <v>380232</v>
       </c>
       <c r="R201" t="n">
-        <v>6919598</v>
+        <v>6919808</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21256,11 +21266,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD201" t="b">
         <v>0</v>
       </c>
@@ -21273,22 +21278,22 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>124465009</v>
+        <v>124469907</v>
       </c>
       <c r="B202" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -21301,34 +21306,34 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>380267</v>
+        <v>380452</v>
       </c>
       <c r="R202" t="n">
-        <v>6919764</v>
+        <v>6919913</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21361,11 +21366,6 @@
       <c r="AA202" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -24676,10 +24676,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>124451885</v>
+        <v>124467914</v>
       </c>
       <c r="B235" t="n">
-        <v>91030</v>
+        <v>77738</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -24692,34 +24692,34 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>5432</v>
+        <v>6487</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>380189</v>
+        <v>380361</v>
       </c>
       <c r="R235" t="n">
-        <v>6920488</v>
+        <v>6919740</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -24754,6 +24754,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC235" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD235" t="b">
         <v>0</v>
       </c>
@@ -24766,22 +24771,22 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>124470234</v>
+        <v>124463210</v>
       </c>
       <c r="B236" t="n">
-        <v>82597</v>
+        <v>79428</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -24794,21 +24799,21 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -24818,10 +24823,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>380506</v>
+        <v>380189</v>
       </c>
       <c r="R236" t="n">
-        <v>6920009</v>
+        <v>6919766</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24880,10 +24885,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>124467914</v>
+        <v>124451885</v>
       </c>
       <c r="B237" t="n">
-        <v>77738</v>
+        <v>91030</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -24896,34 +24901,34 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>6487</v>
+        <v>5432</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>380361</v>
+        <v>380189</v>
       </c>
       <c r="R237" t="n">
-        <v>6919740</v>
+        <v>6920488</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -24958,11 +24963,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC237" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD237" t="b">
         <v>0</v>
       </c>
@@ -24975,22 +24975,22 @@
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>124463210</v>
+        <v>124470234</v>
       </c>
       <c r="B238" t="n">
-        <v>79428</v>
+        <v>82597</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -25003,21 +25003,21 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -25027,10 +25027,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>380189</v>
+        <v>380506</v>
       </c>
       <c r="R238" t="n">
-        <v>6919766</v>
+        <v>6920009</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -25089,10 +25089,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>124451893</v>
+        <v>124457866</v>
       </c>
       <c r="B239" t="n">
-        <v>5196</v>
+        <v>78151</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -25101,38 +25101,38 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>105930</v>
+        <v>498</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>380227</v>
+        <v>380537</v>
       </c>
       <c r="R239" t="n">
-        <v>6920340</v>
+        <v>6920199</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -25179,22 +25179,22 @@
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>124464493</v>
+        <v>124470404</v>
       </c>
       <c r="B240" t="n">
-        <v>79399</v>
+        <v>91030</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -25207,21 +25207,21 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>229821</v>
+        <v>5432</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -25231,10 +25231,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>380243</v>
+        <v>380471</v>
       </c>
       <c r="R240" t="n">
-        <v>6919687</v>
+        <v>6920069</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -25293,10 +25293,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>124464559</v>
+        <v>124470070</v>
       </c>
       <c r="B241" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -25309,21 +25309,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -25333,10 +25333,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>380236</v>
+        <v>380533</v>
       </c>
       <c r="R241" t="n">
-        <v>6919671</v>
+        <v>6919979</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -25395,10 +25395,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>124470404</v>
+        <v>124463640</v>
       </c>
       <c r="B242" t="n">
-        <v>91030</v>
+        <v>79428</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -25411,21 +25411,21 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -25435,10 +25435,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>380471</v>
+        <v>380218</v>
       </c>
       <c r="R242" t="n">
-        <v>6920069</v>
+        <v>6919722</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -25497,7 +25497,7 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>124470070</v>
+        <v>124456502</v>
       </c>
       <c r="B243" t="n">
         <v>78810</v>
@@ -25533,14 +25533,14 @@
       <c r="I243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>380533</v>
+        <v>380385</v>
       </c>
       <c r="R243" t="n">
-        <v>6919979</v>
+        <v>6920091</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -25575,6 +25575,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC243" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området.</t>
+        </is>
+      </c>
       <c r="AD243" t="b">
         <v>0</v>
       </c>
@@ -25587,22 +25592,22 @@
       <c r="AT243" t="inlineStr"/>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>124463640</v>
+        <v>124457836</v>
       </c>
       <c r="B244" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -25615,34 +25620,34 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>380218</v>
+        <v>380542</v>
       </c>
       <c r="R244" t="n">
-        <v>6919722</v>
+        <v>6920184</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25689,22 +25694,22 @@
       <c r="AT244" t="inlineStr"/>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>124456502</v>
+        <v>124464493</v>
       </c>
       <c r="B245" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -25717,34 +25722,34 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
       <c r="P245" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>380385</v>
+        <v>380243</v>
       </c>
       <c r="R245" t="n">
-        <v>6920091</v>
+        <v>6919687</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25779,11 +25784,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC245" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området.</t>
-        </is>
-      </c>
       <c r="AD245" t="b">
         <v>0</v>
       </c>
@@ -25796,22 +25796,22 @@
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>124457836</v>
+        <v>124464559</v>
       </c>
       <c r="B246" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -25824,34 +25824,34 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>380542</v>
+        <v>380236</v>
       </c>
       <c r="R246" t="n">
-        <v>6920184</v>
+        <v>6919671</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25898,22 +25898,22 @@
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>124457866</v>
+        <v>124451893</v>
       </c>
       <c r="B247" t="n">
-        <v>78151</v>
+        <v>5196</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -25922,38 +25922,38 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>498</v>
+        <v>105930</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>380537</v>
+        <v>380227</v>
       </c>
       <c r="R247" t="n">
-        <v>6920199</v>
+        <v>6920340</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -26000,22 +26000,22 @@
       <c r="AT247" t="inlineStr"/>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>124457605</v>
+        <v>124456046</v>
       </c>
       <c r="B248" t="n">
-        <v>57513</v>
+        <v>91032</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -26028,39 +26028,34 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
-      <c r="M248" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P248" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>380542</v>
+        <v>380326</v>
       </c>
       <c r="R248" t="n">
-        <v>6920184</v>
+        <v>6920218</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -26124,10 +26119,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>124470707</v>
+        <v>124458651</v>
       </c>
       <c r="B249" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -26140,42 +26135,37 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
-      <c r="M249" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>380367</v>
+        <v>380569</v>
       </c>
       <c r="R249" t="n">
         <v>6920058</v>
       </c>
       <c r="S249" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T249" t="inlineStr">
         <is>
@@ -26231,10 +26221,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>124460224</v>
+        <v>124458743</v>
       </c>
       <c r="B250" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -26247,39 +26237,34 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
-      <c r="M250" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>380374</v>
+        <v>380542</v>
       </c>
       <c r="R250" t="n">
-        <v>6919982</v>
+        <v>6920184</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -26312,6 +26297,11 @@
       <c r="AA250" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -26338,7 +26328,7 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>124471016</v>
+        <v>124457605</v>
       </c>
       <c r="B251" t="n">
         <v>57513</v>
@@ -26374,19 +26364,19 @@
       <c r="I251" t="inlineStr"/>
       <c r="M251" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P251" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>380506</v>
+        <v>380542</v>
       </c>
       <c r="R251" t="n">
-        <v>6920061</v>
+        <v>6920184</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -26419,6 +26409,11 @@
       <c r="AA251" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC251" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -26445,10 +26440,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>124456046</v>
+        <v>124470707</v>
       </c>
       <c r="B252" t="n">
-        <v>91032</v>
+        <v>57513</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -26461,37 +26456,42 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P252" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>380326</v>
+        <v>380367</v>
       </c>
       <c r="R252" t="n">
-        <v>6920218</v>
+        <v>6920058</v>
       </c>
       <c r="S252" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T252" t="inlineStr">
         <is>
@@ -26521,11 +26521,6 @@
       <c r="AA252" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC252" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -26540,22 +26535,22 @@
       <c r="AT252" t="inlineStr"/>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>124458651</v>
+        <v>124460224</v>
       </c>
       <c r="B253" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -26568,34 +26563,39 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>380569</v>
+        <v>380374</v>
       </c>
       <c r="R253" t="n">
-        <v>6920058</v>
+        <v>6919982</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -26642,22 +26642,22 @@
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>124458743</v>
+        <v>124471016</v>
       </c>
       <c r="B254" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -26670,34 +26670,39 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P254" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>380542</v>
+        <v>380506</v>
       </c>
       <c r="R254" t="n">
-        <v>6920184</v>
+        <v>6920061</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26730,11 +26735,6 @@
       <c r="AA254" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC254" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -28423,7 +28423,7 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>124466494</v>
+        <v>124461646</v>
       </c>
       <c r="B271" t="n">
         <v>57513</v>
@@ -28464,14 +28464,14 @@
       </c>
       <c r="P271" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>380344</v>
+        <v>380239</v>
       </c>
       <c r="R271" t="n">
-        <v>6919654</v>
+        <v>6919828</v>
       </c>
       <c r="S271" t="n">
         <v>15</v>
@@ -28530,7 +28530,7 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>124461646</v>
+        <v>124466494</v>
       </c>
       <c r="B272" t="n">
         <v>57513</v>
@@ -28571,14 +28571,14 @@
       </c>
       <c r="P272" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>380239</v>
+        <v>380344</v>
       </c>
       <c r="R272" t="n">
-        <v>6919828</v>
+        <v>6919654</v>
       </c>
       <c r="S272" t="n">
         <v>15</v>

--- a/artfynd/A 32573-2024 artfynd.xlsx
+++ b/artfynd/A 32573-2024 artfynd.xlsx
@@ -16105,10 +16105,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>124456704</v>
+        <v>124456129</v>
       </c>
       <c r="B152" t="n">
-        <v>91030</v>
+        <v>78905</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16121,21 +16121,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5432</v>
+        <v>967</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16145,10 +16145,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>380385</v>
+        <v>380326</v>
       </c>
       <c r="R152" t="n">
-        <v>6920091</v>
+        <v>6920218</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16181,11 +16181,6 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16212,10 +16207,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>124460611</v>
+        <v>124451984</v>
       </c>
       <c r="B153" t="n">
-        <v>78905</v>
+        <v>79399</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16228,34 +16223,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>967</v>
+        <v>229821</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>380335</v>
+        <v>380203</v>
       </c>
       <c r="R153" t="n">
-        <v>6920000</v>
+        <v>6920482</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16302,22 +16297,22 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>124457601</v>
+        <v>124451885</v>
       </c>
       <c r="B154" t="n">
-        <v>78151</v>
+        <v>91030</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16326,38 +16321,38 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>498</v>
+        <v>5432</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>380544</v>
+        <v>380189</v>
       </c>
       <c r="R154" t="n">
-        <v>6920188</v>
+        <v>6920488</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16416,10 +16411,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>124452627</v>
+        <v>124456697</v>
       </c>
       <c r="B155" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16432,34 +16427,34 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>380217</v>
+        <v>380443</v>
       </c>
       <c r="R155" t="n">
-        <v>6920440</v>
+        <v>6920118</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16518,10 +16513,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>124460258</v>
+        <v>124458743</v>
       </c>
       <c r="B156" t="n">
-        <v>79428</v>
+        <v>91030</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16534,34 +16529,34 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>380365</v>
+        <v>380542</v>
       </c>
       <c r="R156" t="n">
-        <v>6919996</v>
+        <v>6920184</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16596,6 +16591,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
@@ -16608,22 +16608,22 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>124470598</v>
+        <v>124455206</v>
       </c>
       <c r="B157" t="n">
-        <v>79428</v>
+        <v>91030</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16636,34 +16636,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>380506</v>
+        <v>380311</v>
       </c>
       <c r="R157" t="n">
-        <v>6920061</v>
+        <v>6920231</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16698,11 +16698,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
@@ -16715,22 +16710,22 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>124450902</v>
+        <v>124470397</v>
       </c>
       <c r="B158" t="n">
-        <v>57529</v>
+        <v>74901</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16743,39 +16738,34 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>380227</v>
+        <v>380506</v>
       </c>
       <c r="R158" t="n">
-        <v>6920340</v>
+        <v>6920061</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16808,11 +16798,6 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Troligen spillkråka.</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16839,10 +16824,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>124470555</v>
+        <v>124463210</v>
       </c>
       <c r="B159" t="n">
-        <v>82597</v>
+        <v>79428</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16855,21 +16840,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16879,10 +16864,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>380431</v>
+        <v>380189</v>
       </c>
       <c r="R159" t="n">
-        <v>6920068</v>
+        <v>6919766</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16941,10 +16926,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>124455206</v>
+        <v>124464329</v>
       </c>
       <c r="B160" t="n">
-        <v>91030</v>
+        <v>78194</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -16957,34 +16942,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>5432</v>
+        <v>6437</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>380311</v>
+        <v>380268</v>
       </c>
       <c r="R160" t="n">
-        <v>6920231</v>
+        <v>6919685</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17043,7 +17028,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>124470742</v>
+        <v>124464121</v>
       </c>
       <c r="B161" t="n">
         <v>57513</v>
@@ -17088,13 +17073,13 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>380369</v>
+        <v>380419</v>
       </c>
       <c r="R161" t="n">
-        <v>6920032</v>
+        <v>6919960</v>
       </c>
       <c r="S161" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -17138,22 +17123,22 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>124460965</v>
+        <v>124469547</v>
       </c>
       <c r="B162" t="n">
-        <v>78810</v>
+        <v>88359</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17166,34 +17151,34 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>380307</v>
+        <v>380452</v>
       </c>
       <c r="R162" t="n">
-        <v>6919967</v>
+        <v>6919913</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17240,22 +17225,22 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>124450845</v>
+        <v>124458172</v>
       </c>
       <c r="B163" t="n">
-        <v>78810</v>
+        <v>78151</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17264,25 +17249,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6425</v>
+        <v>498</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17292,10 +17277,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>380205</v>
+        <v>380562</v>
       </c>
       <c r="R163" t="n">
-        <v>6920378</v>
+        <v>6920118</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17354,7 +17339,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>124460951</v>
+        <v>124461736</v>
       </c>
       <c r="B164" t="n">
         <v>74901</v>
@@ -17390,14 +17375,14 @@
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>380307</v>
+        <v>380232</v>
       </c>
       <c r="R164" t="n">
-        <v>6919967</v>
+        <v>6919808</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17456,7 +17441,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>124459815</v>
+        <v>124451802</v>
       </c>
       <c r="B165" t="n">
         <v>79428</v>
@@ -17496,10 +17481,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>380445</v>
+        <v>380197</v>
       </c>
       <c r="R165" t="n">
-        <v>6919917</v>
+        <v>6920479</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17558,10 +17543,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>124458046</v>
+        <v>124451893</v>
       </c>
       <c r="B166" t="n">
-        <v>74901</v>
+        <v>5196</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17570,38 +17555,38 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6440</v>
+        <v>105930</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>380533</v>
+        <v>380227</v>
       </c>
       <c r="R166" t="n">
-        <v>6920142</v>
+        <v>6920340</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17648,22 +17633,22 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>124468547</v>
+        <v>124460965</v>
       </c>
       <c r="B167" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17676,34 +17661,34 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>380356</v>
+        <v>380307</v>
       </c>
       <c r="R167" t="n">
-        <v>6919817</v>
+        <v>6919967</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17762,10 +17747,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>124455022</v>
+        <v>124469907</v>
       </c>
       <c r="B168" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -17778,34 +17763,34 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>380292</v>
+        <v>380452</v>
       </c>
       <c r="R168" t="n">
-        <v>6920288</v>
+        <v>6919913</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17852,22 +17837,22 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>124470146</v>
+        <v>124470070</v>
       </c>
       <c r="B169" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -17880,42 +17865,37 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P169" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>380527</v>
+        <v>380533</v>
       </c>
       <c r="R169" t="n">
-        <v>6919988</v>
+        <v>6919979</v>
       </c>
       <c r="S169" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -17971,10 +17951,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>124465526</v>
+        <v>124470742</v>
       </c>
       <c r="B170" t="n">
-        <v>79399</v>
+        <v>57513</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -17987,37 +17967,42 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Risåsvallen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>380252</v>
+        <v>380369</v>
       </c>
       <c r="R170" t="n">
-        <v>6919535</v>
+        <v>6920032</v>
       </c>
       <c r="S170" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -18073,7 +18058,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>124468302</v>
+        <v>124466494</v>
       </c>
       <c r="B171" t="n">
         <v>57513</v>
@@ -18114,14 +18099,14 @@
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>380265</v>
+        <v>380344</v>
       </c>
       <c r="R171" t="n">
-        <v>6919774</v>
+        <v>6919654</v>
       </c>
       <c r="S171" t="n">
         <v>15</v>
@@ -18180,7 +18165,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>124460052</v>
+        <v>124456676</v>
       </c>
       <c r="B172" t="n">
         <v>57513</v>
@@ -18221,17 +18206,17 @@
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>380419</v>
+        <v>380434</v>
       </c>
       <c r="R172" t="n">
-        <v>6919960</v>
+        <v>6920123</v>
       </c>
       <c r="S172" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -18275,22 +18260,22 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>124461477</v>
+        <v>124470646</v>
       </c>
       <c r="B173" t="n">
-        <v>79399</v>
+        <v>91030</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18303,21 +18288,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>229821</v>
+        <v>5432</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18327,10 +18312,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>380285</v>
+        <v>380402</v>
       </c>
       <c r="R173" t="n">
-        <v>6919895</v>
+        <v>6920044</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18389,10 +18374,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>124454979</v>
+        <v>124456046</v>
       </c>
       <c r="B174" t="n">
-        <v>91030</v>
+        <v>91032</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18405,21 +18390,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>5432</v>
+        <v>5442</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18429,10 +18414,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>380289</v>
+        <v>380326</v>
       </c>
       <c r="R174" t="n">
-        <v>6920290</v>
+        <v>6920218</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18469,7 +18454,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>Miljöbilder.</t>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18496,10 +18481,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>124459134</v>
+        <v>124470184</v>
       </c>
       <c r="B175" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -18512,34 +18497,34 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>380559</v>
+        <v>380516</v>
       </c>
       <c r="R175" t="n">
-        <v>6919947</v>
+        <v>6920004</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18598,10 +18583,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>124455453</v>
+        <v>124456704</v>
       </c>
       <c r="B176" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -18614,21 +18599,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18638,10 +18623,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>380326</v>
+        <v>380385</v>
       </c>
       <c r="R176" t="n">
-        <v>6920218</v>
+        <v>6920091</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18674,6 +18659,11 @@
       <c r="AA176" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -18700,10 +18690,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>124458282</v>
+        <v>124458651</v>
       </c>
       <c r="B177" t="n">
-        <v>78151</v>
+        <v>91030</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -18712,25 +18702,25 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>498</v>
+        <v>5432</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18740,10 +18730,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>380588</v>
+        <v>380569</v>
       </c>
       <c r="R177" t="n">
-        <v>6920110</v>
+        <v>6920058</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18802,10 +18792,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>124465389</v>
+        <v>124465167</v>
       </c>
       <c r="B178" t="n">
-        <v>79399</v>
+        <v>78194</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -18818,21 +18808,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18904,10 +18894,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>124452261</v>
+        <v>124470485</v>
       </c>
       <c r="B179" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -18920,34 +18910,34 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>380227</v>
+        <v>380446</v>
       </c>
       <c r="R179" t="n">
-        <v>6920340</v>
+        <v>6920059</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18994,19 +18984,19 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>124469751</v>
+        <v>124450415</v>
       </c>
       <c r="B180" t="n">
         <v>74901</v>
@@ -19042,14 +19032,14 @@
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>380490</v>
+        <v>380202</v>
       </c>
       <c r="R180" t="n">
-        <v>6919937</v>
+        <v>6920332</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19108,10 +19098,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>124467947</v>
+        <v>124465863</v>
       </c>
       <c r="B181" t="n">
-        <v>78194</v>
+        <v>78151</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -19120,38 +19110,38 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6437</v>
+        <v>498</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>380361</v>
+        <v>380296</v>
       </c>
       <c r="R181" t="n">
-        <v>6919740</v>
+        <v>6919585</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19186,11 +19176,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD181" t="b">
         <v>0</v>
       </c>
@@ -19203,22 +19188,22 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124464842</v>
+        <v>124459456</v>
       </c>
       <c r="B182" t="n">
-        <v>79428</v>
+        <v>91032</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -19231,34 +19216,34 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>380237</v>
+        <v>380561</v>
       </c>
       <c r="R182" t="n">
-        <v>6919621</v>
+        <v>6919930</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19305,22 +19290,22 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124451326</v>
+        <v>124460951</v>
       </c>
       <c r="B183" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -19333,39 +19318,34 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>380227</v>
+        <v>380307</v>
       </c>
       <c r="R183" t="n">
-        <v>6920340</v>
+        <v>6919967</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19412,22 +19392,22 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124458357</v>
+        <v>124463640</v>
       </c>
       <c r="B184" t="n">
-        <v>57666</v>
+        <v>79428</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -19440,42 +19420,37 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P184" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>380586</v>
+        <v>380218</v>
       </c>
       <c r="R184" t="n">
-        <v>6920100</v>
+        <v>6919722</v>
       </c>
       <c r="S184" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -19531,10 +19506,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124455096</v>
+        <v>124460258</v>
       </c>
       <c r="B185" t="n">
-        <v>5196</v>
+        <v>79428</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -19543,43 +19518,38 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>105930</v>
+        <v>6453</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>380323</v>
+        <v>380365</v>
       </c>
       <c r="R185" t="n">
-        <v>6920260</v>
+        <v>6919996</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19638,10 +19608,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124464651</v>
+        <v>124455453</v>
       </c>
       <c r="B186" t="n">
-        <v>79399</v>
+        <v>74901</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -19654,34 +19624,34 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>380251</v>
+        <v>380326</v>
       </c>
       <c r="R186" t="n">
-        <v>6919658</v>
+        <v>6920218</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19728,22 +19698,22 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124454876</v>
+        <v>124464292</v>
       </c>
       <c r="B187" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -19756,34 +19726,39 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>380290</v>
+        <v>380275</v>
       </c>
       <c r="R187" t="n">
-        <v>6920272</v>
+        <v>6919775</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19830,22 +19805,22 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124465167</v>
+        <v>124464493</v>
       </c>
       <c r="B188" t="n">
-        <v>78194</v>
+        <v>79399</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -19858,21 +19833,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19882,10 +19857,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>380244</v>
+        <v>380243</v>
       </c>
       <c r="R188" t="n">
-        <v>6919577</v>
+        <v>6919687</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19932,22 +19907,22 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124451837</v>
+        <v>124459042</v>
       </c>
       <c r="B189" t="n">
-        <v>78194</v>
+        <v>74901</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -19960,34 +19935,34 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>380197</v>
+        <v>380571</v>
       </c>
       <c r="R189" t="n">
-        <v>6920479</v>
+        <v>6919993</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20046,7 +20021,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>124470485</v>
+        <v>124455220</v>
       </c>
       <c r="B190" t="n">
         <v>74901</v>
@@ -20082,14 +20057,14 @@
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>380446</v>
+        <v>380311</v>
       </c>
       <c r="R190" t="n">
-        <v>6920059</v>
+        <v>6920231</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20148,7 +20123,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>124461108</v>
+        <v>124452627</v>
       </c>
       <c r="B191" t="n">
         <v>74901</v>
@@ -20188,10 +20163,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>380308</v>
+        <v>380217</v>
       </c>
       <c r="R191" t="n">
-        <v>6919925</v>
+        <v>6920440</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20224,11 +20199,6 @@
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC191" t="inlineStr">
-        <is>
-          <t>På basen avsågad gran. Grov stubbe</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20255,10 +20225,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>124459287</v>
+        <v>124467947</v>
       </c>
       <c r="B192" t="n">
-        <v>57513</v>
+        <v>78194</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20271,39 +20241,34 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>380561</v>
+        <v>380361</v>
       </c>
       <c r="R192" t="n">
-        <v>6919930</v>
+        <v>6919740</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20336,6 +20301,11 @@
       <c r="AA192" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20362,10 +20332,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>124469088</v>
+        <v>124451574</v>
       </c>
       <c r="B193" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -20378,34 +20348,34 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>380352</v>
+        <v>380184</v>
       </c>
       <c r="R193" t="n">
-        <v>6919913</v>
+        <v>6920434</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20464,10 +20434,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>124470184</v>
+        <v>124464651</v>
       </c>
       <c r="B194" t="n">
-        <v>91030</v>
+        <v>79399</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -20480,21 +20450,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>5432</v>
+        <v>229821</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20504,10 +20474,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>380516</v>
+        <v>380251</v>
       </c>
       <c r="R194" t="n">
-        <v>6920004</v>
+        <v>6919658</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20668,7 +20638,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>124464466</v>
+        <v>124460611</v>
       </c>
       <c r="B196" t="n">
         <v>78905</v>
@@ -20704,14 +20674,14 @@
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>380243</v>
+        <v>380335</v>
       </c>
       <c r="R196" t="n">
-        <v>6919687</v>
+        <v>6920000</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20758,22 +20728,22 @@
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>124466026</v>
+        <v>124467914</v>
       </c>
       <c r="B197" t="n">
-        <v>79399</v>
+        <v>77738</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -20786,21 +20756,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20810,10 +20780,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>380303</v>
+        <v>380361</v>
       </c>
       <c r="R197" t="n">
-        <v>6919598</v>
+        <v>6919740</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20877,10 +20847,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>124465009</v>
+        <v>124459134</v>
       </c>
       <c r="B198" t="n">
-        <v>79399</v>
+        <v>74901</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -20893,34 +20863,34 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>380267</v>
+        <v>380559</v>
       </c>
       <c r="R198" t="n">
-        <v>6919764</v>
+        <v>6919947</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20955,11 +20925,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC198" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD198" t="b">
         <v>0</v>
       </c>
@@ -20972,22 +20937,22 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>124470646</v>
+        <v>124469377</v>
       </c>
       <c r="B199" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -21000,21 +20965,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -21024,10 +20989,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>380402</v>
+        <v>380435</v>
       </c>
       <c r="R199" t="n">
-        <v>6920044</v>
+        <v>6919916</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21086,10 +21051,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>124450737</v>
+        <v>124468182</v>
       </c>
       <c r="B200" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -21102,37 +21067,42 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>380210</v>
+        <v>380265</v>
       </c>
       <c r="R200" t="n">
-        <v>6920378</v>
+        <v>6919774</v>
       </c>
       <c r="S200" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -21188,10 +21158,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>124461736</v>
+        <v>124461477</v>
       </c>
       <c r="B201" t="n">
-        <v>74901</v>
+        <v>79399</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -21204,34 +21174,34 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>380232</v>
+        <v>380285</v>
       </c>
       <c r="R201" t="n">
-        <v>6919808</v>
+        <v>6919895</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21290,10 +21260,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>124469907</v>
+        <v>124465389</v>
       </c>
       <c r="B202" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -21306,34 +21276,34 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>380452</v>
+        <v>380244</v>
       </c>
       <c r="R202" t="n">
-        <v>6919913</v>
+        <v>6919577</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21392,10 +21362,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>124459042</v>
+        <v>124464559</v>
       </c>
       <c r="B203" t="n">
-        <v>74901</v>
+        <v>79399</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -21408,21 +21378,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -21432,10 +21402,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>380571</v>
+        <v>380236</v>
       </c>
       <c r="R203" t="n">
-        <v>6919993</v>
+        <v>6919671</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21494,10 +21464,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>124451172</v>
+        <v>124465009</v>
       </c>
       <c r="B204" t="n">
-        <v>74901</v>
+        <v>79399</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -21510,34 +21480,34 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>380184</v>
+        <v>380267</v>
       </c>
       <c r="R204" t="n">
-        <v>6920434</v>
+        <v>6919764</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21572,6 +21542,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD204" t="b">
         <v>0</v>
       </c>
@@ -21584,22 +21559,22 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>124458476</v>
+        <v>124461646</v>
       </c>
       <c r="B205" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -21612,37 +21587,42 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P205" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>380581</v>
+        <v>380239</v>
       </c>
       <c r="R205" t="n">
-        <v>6920056</v>
+        <v>6919828</v>
       </c>
       <c r="S205" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -21698,10 +21678,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>124469377</v>
+        <v>124470598</v>
       </c>
       <c r="B206" t="n">
-        <v>74901</v>
+        <v>79428</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -21714,34 +21694,34 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>380435</v>
+        <v>380506</v>
       </c>
       <c r="R206" t="n">
-        <v>6919916</v>
+        <v>6920061</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21776,6 +21756,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD206" t="b">
         <v>0</v>
       </c>
@@ -21788,22 +21773,22 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>124459456</v>
+        <v>124470732</v>
       </c>
       <c r="B207" t="n">
-        <v>91032</v>
+        <v>74901</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -21816,21 +21801,21 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>5442</v>
+        <v>6440</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -21840,10 +21825,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>380561</v>
+        <v>380372</v>
       </c>
       <c r="R207" t="n">
-        <v>6919930</v>
+        <v>6920042</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21890,22 +21875,22 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>124470737</v>
+        <v>124458282</v>
       </c>
       <c r="B208" t="n">
-        <v>91030</v>
+        <v>78151</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -21914,38 +21899,38 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>5432</v>
+        <v>498</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>380506</v>
+        <v>380588</v>
       </c>
       <c r="R208" t="n">
-        <v>6920061</v>
+        <v>6920110</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21992,22 +21977,22 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>124465863</v>
+        <v>124463365</v>
       </c>
       <c r="B209" t="n">
-        <v>78151</v>
+        <v>79399</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -22016,38 +22001,38 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>498</v>
+        <v>229821</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Risåsvallen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>380296</v>
+        <v>380199</v>
       </c>
       <c r="R209" t="n">
-        <v>6919585</v>
+        <v>6919723</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -22106,10 +22091,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>124454665</v>
+        <v>124469088</v>
       </c>
       <c r="B210" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -22122,34 +22107,34 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>380258</v>
+        <v>380352</v>
       </c>
       <c r="R210" t="n">
-        <v>6920309</v>
+        <v>6919913</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22208,10 +22193,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>124451574</v>
+        <v>124457866</v>
       </c>
       <c r="B211" t="n">
-        <v>79428</v>
+        <v>78151</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -22220,38 +22205,38 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6453</v>
+        <v>498</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>380184</v>
+        <v>380537</v>
       </c>
       <c r="R211" t="n">
-        <v>6920434</v>
+        <v>6920199</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22310,7 +22295,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>124470397</v>
+        <v>124451172</v>
       </c>
       <c r="B212" t="n">
         <v>74901</v>
@@ -22346,14 +22331,14 @@
       <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>380506</v>
+        <v>380184</v>
       </c>
       <c r="R212" t="n">
-        <v>6920061</v>
+        <v>6920434</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22400,22 +22385,22 @@
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>124469547</v>
+        <v>124464471</v>
       </c>
       <c r="B213" t="n">
-        <v>88359</v>
+        <v>78194</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -22428,34 +22413,34 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>510</v>
+        <v>6437</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>380452</v>
+        <v>380243</v>
       </c>
       <c r="R213" t="n">
-        <v>6919913</v>
+        <v>6919687</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22502,22 +22487,22 @@
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>124451569</v>
+        <v>124458476</v>
       </c>
       <c r="B214" t="n">
-        <v>79399</v>
+        <v>74901</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -22530,34 +22515,34 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>380184</v>
+        <v>380581</v>
       </c>
       <c r="R214" t="n">
-        <v>6920434</v>
+        <v>6920056</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22616,10 +22601,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>124456697</v>
+        <v>124471016</v>
       </c>
       <c r="B215" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -22632,34 +22617,39 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>380443</v>
+        <v>380506</v>
       </c>
       <c r="R215" t="n">
-        <v>6920118</v>
+        <v>6920061</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22706,22 +22696,22 @@
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>124456129</v>
+        <v>124464901</v>
       </c>
       <c r="B216" t="n">
-        <v>78905</v>
+        <v>79399</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -22734,34 +22724,34 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>967</v>
+        <v>229821</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>380326</v>
+        <v>380249</v>
       </c>
       <c r="R216" t="n">
-        <v>6920218</v>
+        <v>6919607</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22808,22 +22798,22 @@
       <c r="AT216" t="inlineStr"/>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>124464321</v>
+        <v>124457317</v>
       </c>
       <c r="B217" t="n">
-        <v>77738</v>
+        <v>79428</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -22836,21 +22826,21 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -22860,10 +22850,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>380268</v>
+        <v>380547</v>
       </c>
       <c r="R217" t="n">
-        <v>6919685</v>
+        <v>6920163</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22922,7 +22912,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>124469915</v>
+        <v>124455134</v>
       </c>
       <c r="B218" t="n">
         <v>74901</v>
@@ -22958,14 +22948,14 @@
       <c r="I218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>380521</v>
+        <v>380311</v>
       </c>
       <c r="R218" t="n">
-        <v>6919962</v>
+        <v>6920245</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23024,7 +23014,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>124450300</v>
+        <v>124461108</v>
       </c>
       <c r="B219" t="n">
         <v>74901</v>
@@ -23060,14 +23050,14 @@
       <c r="I219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>380182</v>
+        <v>380308</v>
       </c>
       <c r="R219" t="n">
-        <v>6920316</v>
+        <v>6919925</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23100,6 +23090,11 @@
       <c r="AA219" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>På basen avsågad gran. Grov stubbe</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -23126,10 +23121,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>124450415</v>
+        <v>124452491</v>
       </c>
       <c r="B220" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -23142,34 +23137,34 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>380202</v>
+        <v>380208</v>
       </c>
       <c r="R220" t="n">
-        <v>6920332</v>
+        <v>6920481</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23228,10 +23223,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>124468469</v>
+        <v>124457836</v>
       </c>
       <c r="B221" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -23244,42 +23239,37 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>380324</v>
+        <v>380542</v>
       </c>
       <c r="R221" t="n">
-        <v>6919803</v>
+        <v>6920184</v>
       </c>
       <c r="S221" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -23323,22 +23313,22 @@
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>124470299</v>
+        <v>124470404</v>
       </c>
       <c r="B222" t="n">
-        <v>56722</v>
+        <v>91030</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -23347,43 +23337,38 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P222" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>380495</v>
+        <v>380471</v>
       </c>
       <c r="R222" t="n">
-        <v>6920029</v>
+        <v>6920069</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23442,10 +23427,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>124464970</v>
+        <v>124450578</v>
       </c>
       <c r="B223" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -23458,42 +23443,37 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>380255</v>
+        <v>380227</v>
       </c>
       <c r="R223" t="n">
-        <v>6919561</v>
+        <v>6920340</v>
       </c>
       <c r="S223" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -23537,22 +23517,22 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>124464047</v>
+        <v>124470234</v>
       </c>
       <c r="B224" t="n">
-        <v>78810</v>
+        <v>82597</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -23565,21 +23545,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -23589,10 +23569,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>380267</v>
+        <v>380506</v>
       </c>
       <c r="R224" t="n">
-        <v>6919731</v>
+        <v>6920009</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23651,10 +23631,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>124452491</v>
+        <v>124460224</v>
       </c>
       <c r="B225" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -23667,34 +23647,39 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>380208</v>
+        <v>380374</v>
       </c>
       <c r="R225" t="n">
-        <v>6920481</v>
+        <v>6919982</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23741,22 +23726,22 @@
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>124450578</v>
+        <v>124470806</v>
       </c>
       <c r="B226" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -23769,37 +23754,42 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>380227</v>
+        <v>380340</v>
       </c>
       <c r="R226" t="n">
-        <v>6920340</v>
+        <v>6920036</v>
       </c>
       <c r="S226" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T226" t="inlineStr">
         <is>
@@ -23843,22 +23833,22 @@
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>124455456</v>
+        <v>124451326</v>
       </c>
       <c r="B227" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -23871,34 +23861,39 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P227" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>380314</v>
+        <v>380227</v>
       </c>
       <c r="R227" t="n">
-        <v>6920201</v>
+        <v>6920340</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23945,22 +23940,22 @@
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>124455774</v>
+        <v>124454979</v>
       </c>
       <c r="B228" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -23973,34 +23968,34 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>380356</v>
+        <v>380289</v>
       </c>
       <c r="R228" t="n">
-        <v>6920172</v>
+        <v>6920290</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24035,6 +24030,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC228" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD228" t="b">
         <v>0</v>
       </c>
@@ -24047,22 +24047,22 @@
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>124451802</v>
+        <v>124456372</v>
       </c>
       <c r="B229" t="n">
-        <v>79428</v>
+        <v>74901</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -24075,34 +24075,34 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>380197</v>
+        <v>380368</v>
       </c>
       <c r="R229" t="n">
-        <v>6920479</v>
+        <v>6920107</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24161,10 +24161,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>124464329</v>
+        <v>124450666</v>
       </c>
       <c r="B230" t="n">
-        <v>78194</v>
+        <v>74901</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -24177,34 +24177,34 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>380268</v>
+        <v>380227</v>
       </c>
       <c r="R230" t="n">
-        <v>6919685</v>
+        <v>6920340</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24251,22 +24251,22 @@
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>124459060</v>
+        <v>124469751</v>
       </c>
       <c r="B231" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -24279,39 +24279,34 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
-      <c r="M231" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>380571</v>
+        <v>380490</v>
       </c>
       <c r="R231" t="n">
-        <v>6919993</v>
+        <v>6919937</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24370,10 +24365,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>124463365</v>
+        <v>124470555</v>
       </c>
       <c r="B232" t="n">
-        <v>79399</v>
+        <v>82597</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -24386,21 +24381,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>229821</v>
+        <v>1312</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -24410,10 +24405,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>380199</v>
+        <v>380431</v>
       </c>
       <c r="R232" t="n">
-        <v>6919723</v>
+        <v>6920068</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24472,10 +24467,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>124464681</v>
+        <v>124464466</v>
       </c>
       <c r="B233" t="n">
-        <v>79399</v>
+        <v>78905</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -24488,21 +24483,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>229821</v>
+        <v>967</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -24512,10 +24507,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>380264</v>
+        <v>380243</v>
       </c>
       <c r="R233" t="n">
-        <v>6919665</v>
+        <v>6919687</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -24574,10 +24569,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>124464901</v>
+        <v>124455776</v>
       </c>
       <c r="B234" t="n">
-        <v>79399</v>
+        <v>57513</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -24590,34 +24585,39 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>380249</v>
+        <v>380326</v>
       </c>
       <c r="R234" t="n">
-        <v>6919607</v>
+        <v>6920218</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -24664,22 +24664,22 @@
       <c r="AT234" t="inlineStr"/>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>124467914</v>
+        <v>124470146</v>
       </c>
       <c r="B235" t="n">
-        <v>77738</v>
+        <v>57513</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -24692,37 +24692,42 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>6487</v>
+        <v>100109</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P235" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>380361</v>
+        <v>380527</v>
       </c>
       <c r="R235" t="n">
-        <v>6919740</v>
+        <v>6919988</v>
       </c>
       <c r="S235" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T235" t="inlineStr">
         <is>
@@ -24752,11 +24757,6 @@
       <c r="AA235" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC235" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -24771,19 +24771,19 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>124463210</v>
+        <v>124459815</v>
       </c>
       <c r="B236" t="n">
         <v>79428</v>
@@ -24819,14 +24819,14 @@
       <c r="I236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>380189</v>
+        <v>380445</v>
       </c>
       <c r="R236" t="n">
-        <v>6919766</v>
+        <v>6919917</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24885,10 +24885,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>124451885</v>
+        <v>124455096</v>
       </c>
       <c r="B237" t="n">
-        <v>91030</v>
+        <v>5196</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -24897,38 +24897,43 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>5432</v>
+        <v>105930</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P237" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>380189</v>
+        <v>380323</v>
       </c>
       <c r="R237" t="n">
-        <v>6920488</v>
+        <v>6920260</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -24987,10 +24992,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>124470234</v>
+        <v>124458046</v>
       </c>
       <c r="B238" t="n">
-        <v>82597</v>
+        <v>74901</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -25003,21 +25008,21 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -25027,10 +25032,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>380506</v>
+        <v>380533</v>
       </c>
       <c r="R238" t="n">
-        <v>6920009</v>
+        <v>6920142</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -25089,10 +25094,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>124457866</v>
+        <v>124454665</v>
       </c>
       <c r="B239" t="n">
-        <v>78151</v>
+        <v>74901</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -25101,25 +25106,25 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>498</v>
+        <v>6440</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -25129,10 +25134,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>380537</v>
+        <v>380258</v>
       </c>
       <c r="R239" t="n">
-        <v>6920199</v>
+        <v>6920309</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -25191,10 +25196,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>124470404</v>
+        <v>124464681</v>
       </c>
       <c r="B240" t="n">
-        <v>91030</v>
+        <v>79399</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -25207,21 +25212,21 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>5432</v>
+        <v>229821</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -25231,10 +25236,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>380471</v>
+        <v>380264</v>
       </c>
       <c r="R240" t="n">
-        <v>6920069</v>
+        <v>6919665</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -25293,10 +25298,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>124470070</v>
+        <v>124458509</v>
       </c>
       <c r="B241" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -25309,34 +25314,39 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P241" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>380533</v>
+        <v>380542</v>
       </c>
       <c r="R241" t="n">
-        <v>6919979</v>
+        <v>6920184</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -25371,6 +25381,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC241" t="inlineStr">
+        <is>
+          <t>Miljöbilder, talltita.</t>
+        </is>
+      </c>
       <c r="AD241" t="b">
         <v>0</v>
       </c>
@@ -25383,22 +25398,22 @@
       <c r="AT241" t="inlineStr"/>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>124463640</v>
+        <v>124454876</v>
       </c>
       <c r="B242" t="n">
-        <v>79428</v>
+        <v>74901</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -25411,34 +25426,34 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>380218</v>
+        <v>380290</v>
       </c>
       <c r="R242" t="n">
-        <v>6919722</v>
+        <v>6920272</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -25497,10 +25512,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>124456502</v>
+        <v>124470707</v>
       </c>
       <c r="B243" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -25513,37 +25528,42 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>380385</v>
+        <v>380367</v>
       </c>
       <c r="R243" t="n">
-        <v>6920091</v>
+        <v>6920058</v>
       </c>
       <c r="S243" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -25573,11 +25593,6 @@
       <c r="AA243" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC243" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -25592,22 +25607,22 @@
       <c r="AT243" t="inlineStr"/>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>124457836</v>
+        <v>124464970</v>
       </c>
       <c r="B244" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -25620,37 +25635,42 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>380542</v>
+        <v>380255</v>
       </c>
       <c r="R244" t="n">
-        <v>6920184</v>
+        <v>6919561</v>
       </c>
       <c r="S244" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
@@ -25694,22 +25714,22 @@
       <c r="AT244" t="inlineStr"/>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>124464493</v>
+        <v>124459060</v>
       </c>
       <c r="B245" t="n">
-        <v>79399</v>
+        <v>57513</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -25722,34 +25742,39 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P245" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>380243</v>
+        <v>380571</v>
       </c>
       <c r="R245" t="n">
-        <v>6919687</v>
+        <v>6919993</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25808,7 +25833,7 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>124464559</v>
+        <v>124466026</v>
       </c>
       <c r="B246" t="n">
         <v>79399</v>
@@ -25848,10 +25873,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>380236</v>
+        <v>380303</v>
       </c>
       <c r="R246" t="n">
-        <v>6919671</v>
+        <v>6919598</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25886,6 +25911,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC246" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD246" t="b">
         <v>0</v>
       </c>
@@ -25898,22 +25928,22 @@
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>124451893</v>
+        <v>124465526</v>
       </c>
       <c r="B247" t="n">
-        <v>5196</v>
+        <v>79399</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -25922,38 +25952,38 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>105930</v>
+        <v>229821</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Risåsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>380227</v>
+        <v>380252</v>
       </c>
       <c r="R247" t="n">
-        <v>6920340</v>
+        <v>6919535</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -26000,22 +26030,22 @@
       <c r="AT247" t="inlineStr"/>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>124456046</v>
+        <v>124455456</v>
       </c>
       <c r="B248" t="n">
-        <v>91032</v>
+        <v>74901</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -26028,21 +26058,21 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>5442</v>
+        <v>6440</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -26052,10 +26082,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>380326</v>
+        <v>380314</v>
       </c>
       <c r="R248" t="n">
-        <v>6920218</v>
+        <v>6920201</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -26090,11 +26120,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC248" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området.</t>
-        </is>
-      </c>
       <c r="AD248" t="b">
         <v>0</v>
       </c>
@@ -26107,22 +26132,22 @@
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>124458651</v>
+        <v>124450737</v>
       </c>
       <c r="B249" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -26135,34 +26160,34 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>380569</v>
+        <v>380210</v>
       </c>
       <c r="R249" t="n">
-        <v>6920058</v>
+        <v>6920378</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -26221,10 +26246,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>124458743</v>
+        <v>124469915</v>
       </c>
       <c r="B250" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -26237,34 +26262,34 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>380542</v>
+        <v>380521</v>
       </c>
       <c r="R250" t="n">
-        <v>6920184</v>
+        <v>6919962</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -26299,11 +26324,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC250" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
-        </is>
-      </c>
       <c r="AD250" t="b">
         <v>0</v>
       </c>
@@ -26316,22 +26336,22 @@
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>124457605</v>
+        <v>124468547</v>
       </c>
       <c r="B251" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -26344,39 +26364,34 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
-      <c r="M251" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P251" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>380542</v>
+        <v>380356</v>
       </c>
       <c r="R251" t="n">
-        <v>6920184</v>
+        <v>6919817</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -26411,11 +26426,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC251" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området.</t>
-        </is>
-      </c>
       <c r="AD251" t="b">
         <v>0</v>
       </c>
@@ -26428,22 +26438,22 @@
       <c r="AT251" t="inlineStr"/>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>124470707</v>
+        <v>124450902</v>
       </c>
       <c r="B252" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -26456,16 +26466,16 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -26481,17 +26491,17 @@
       </c>
       <c r="P252" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>380367</v>
+        <v>380227</v>
       </c>
       <c r="R252" t="n">
-        <v>6920058</v>
+        <v>6920340</v>
       </c>
       <c r="S252" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T252" t="inlineStr">
         <is>
@@ -26521,6 +26531,11 @@
       <c r="AA252" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC252" t="inlineStr">
+        <is>
+          <t>Troligen spillkråka.</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -26535,22 +26550,22 @@
       <c r="AT252" t="inlineStr"/>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>124460224</v>
+        <v>124464047</v>
       </c>
       <c r="B253" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -26563,39 +26578,34 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
-      <c r="M253" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>380374</v>
+        <v>380267</v>
       </c>
       <c r="R253" t="n">
-        <v>6919982</v>
+        <v>6919731</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -26642,22 +26652,22 @@
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>124471016</v>
+        <v>124450845</v>
       </c>
       <c r="B254" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -26670,39 +26680,34 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
-      <c r="M254" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P254" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>380506</v>
+        <v>380205</v>
       </c>
       <c r="R254" t="n">
-        <v>6920061</v>
+        <v>6920378</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26749,22 +26754,22 @@
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>124456372</v>
+        <v>124468916</v>
       </c>
       <c r="B255" t="n">
-        <v>74901</v>
+        <v>78151</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -26773,38 +26778,38 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>6440</v>
+        <v>498</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>380368</v>
+        <v>380343</v>
       </c>
       <c r="R255" t="n">
-        <v>6920107</v>
+        <v>6919896</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26863,10 +26868,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>124455220</v>
+        <v>124464321</v>
       </c>
       <c r="B256" t="n">
-        <v>74901</v>
+        <v>77738</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -26879,34 +26884,34 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>6440</v>
+        <v>6487</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
       <c r="P256" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>380311</v>
+        <v>380268</v>
       </c>
       <c r="R256" t="n">
-        <v>6920231</v>
+        <v>6919685</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -26965,10 +26970,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>124457317</v>
+        <v>124450300</v>
       </c>
       <c r="B257" t="n">
-        <v>79428</v>
+        <v>74901</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -26981,21 +26986,21 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -27005,10 +27010,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>380547</v>
+        <v>380182</v>
       </c>
       <c r="R257" t="n">
-        <v>6920163</v>
+        <v>6920316</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -27067,10 +27072,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>124458172</v>
+        <v>124455774</v>
       </c>
       <c r="B258" t="n">
-        <v>78151</v>
+        <v>74901</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -27079,38 +27084,38 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>498</v>
+        <v>6440</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>380562</v>
+        <v>380356</v>
       </c>
       <c r="R258" t="n">
-        <v>6920118</v>
+        <v>6920172</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -27169,7 +27174,7 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>124470806</v>
+        <v>124459287</v>
       </c>
       <c r="B259" t="n">
         <v>57513</v>
@@ -27205,7 +27210,7 @@
       <c r="I259" t="inlineStr"/>
       <c r="M259" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P259" t="inlineStr">
@@ -27214,13 +27219,13 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>380340</v>
+        <v>380561</v>
       </c>
       <c r="R259" t="n">
-        <v>6920036</v>
+        <v>6919930</v>
       </c>
       <c r="S259" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T259" t="inlineStr">
         <is>
@@ -27264,22 +27269,22 @@
       <c r="AT259" t="inlineStr"/>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>124470732</v>
+        <v>124457601</v>
       </c>
       <c r="B260" t="n">
-        <v>74901</v>
+        <v>78151</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -27288,38 +27293,38 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>6440</v>
+        <v>498</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>380372</v>
+        <v>380544</v>
       </c>
       <c r="R260" t="n">
-        <v>6920042</v>
+        <v>6920188</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -27378,10 +27383,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>124464471</v>
+        <v>124470299</v>
       </c>
       <c r="B261" t="n">
-        <v>78194</v>
+        <v>56722</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -27390,38 +27395,43 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>6437</v>
+        <v>100138</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P261" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>380243</v>
+        <v>380495</v>
       </c>
       <c r="R261" t="n">
-        <v>6919687</v>
+        <v>6920029</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -27480,10 +27490,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>124450666</v>
+        <v>124464842</v>
       </c>
       <c r="B262" t="n">
-        <v>74901</v>
+        <v>79428</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -27496,34 +27506,34 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>380227</v>
+        <v>380237</v>
       </c>
       <c r="R262" t="n">
-        <v>6920340</v>
+        <v>6919621</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -27570,22 +27580,22 @@
       <c r="AT262" t="inlineStr"/>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>124468916</v>
+        <v>124455022</v>
       </c>
       <c r="B263" t="n">
-        <v>78151</v>
+        <v>79428</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -27594,25 +27604,25 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>498</v>
+        <v>6453</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
@@ -27622,10 +27632,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>380343</v>
+        <v>380292</v>
       </c>
       <c r="R263" t="n">
-        <v>6919896</v>
+        <v>6920288</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -27684,10 +27694,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>124451984</v>
+        <v>124456502</v>
       </c>
       <c r="B264" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -27700,21 +27710,21 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
@@ -27724,10 +27734,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>380203</v>
+        <v>380385</v>
       </c>
       <c r="R264" t="n">
-        <v>6920482</v>
+        <v>6920091</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27762,6 +27772,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC264" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området.</t>
+        </is>
+      </c>
       <c r="AD264" t="b">
         <v>0</v>
       </c>
@@ -27774,22 +27789,22 @@
       <c r="AT264" t="inlineStr"/>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>124456676</v>
+        <v>124470695</v>
       </c>
       <c r="B265" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -27802,42 +27817,37 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
-      <c r="M265" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P265" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>380434</v>
+        <v>380506</v>
       </c>
       <c r="R265" t="n">
-        <v>6920123</v>
+        <v>6920061</v>
       </c>
       <c r="S265" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T265" t="inlineStr">
         <is>
@@ -27867,6 +27877,11 @@
       <c r="AA265" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC265" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -27881,22 +27896,22 @@
       <c r="AT265" t="inlineStr"/>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>124452423</v>
+        <v>124452261</v>
       </c>
       <c r="B266" t="n">
-        <v>56725</v>
+        <v>78810</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -27905,33 +27920,28 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
-      <c r="M266" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P266" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
@@ -28000,10 +28010,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>124455776</v>
+        <v>124452423</v>
       </c>
       <c r="B267" t="n">
-        <v>57513</v>
+        <v>56725</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -28012,20 +28022,20 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>100109</v>
+        <v>102613</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -28036,7 +28046,7 @@
       <c r="I267" t="inlineStr"/>
       <c r="M267" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P267" t="inlineStr">
@@ -28045,10 +28055,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>380326</v>
+        <v>380227</v>
       </c>
       <c r="R267" t="n">
-        <v>6920218</v>
+        <v>6920340</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -28107,10 +28117,10 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>124464292</v>
+        <v>124451837</v>
       </c>
       <c r="B268" t="n">
-        <v>57513</v>
+        <v>78194</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -28123,39 +28133,34 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
-      <c r="M268" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P268" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>380275</v>
+        <v>380197</v>
       </c>
       <c r="R268" t="n">
-        <v>6919775</v>
+        <v>6920479</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -28202,19 +28207,19 @@
       <c r="AT268" t="inlineStr"/>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>124466302</v>
+        <v>124468469</v>
       </c>
       <c r="B269" t="n">
         <v>57513</v>
@@ -28255,14 +28260,14 @@
       </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>380345</v>
+        <v>380324</v>
       </c>
       <c r="R269" t="n">
-        <v>6919632</v>
+        <v>6919803</v>
       </c>
       <c r="S269" t="n">
         <v>15</v>
@@ -28321,10 +28326,10 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>124455134</v>
+        <v>124466302</v>
       </c>
       <c r="B270" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -28337,37 +28342,42 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P270" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>380311</v>
+        <v>380345</v>
       </c>
       <c r="R270" t="n">
-        <v>6920245</v>
+        <v>6919632</v>
       </c>
       <c r="S270" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T270" t="inlineStr">
         <is>
@@ -28423,10 +28433,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>124461646</v>
+        <v>124458357</v>
       </c>
       <c r="B271" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -28439,27 +28449,27 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
       <c r="M271" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P271" t="inlineStr">
@@ -28468,13 +28478,13 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>380239</v>
+        <v>380586</v>
       </c>
       <c r="R271" t="n">
-        <v>6919828</v>
+        <v>6920100</v>
       </c>
       <c r="S271" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T271" t="inlineStr">
         <is>
@@ -28530,10 +28540,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>124466494</v>
+        <v>124451569</v>
       </c>
       <c r="B272" t="n">
-        <v>57513</v>
+        <v>79399</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -28546,42 +28556,37 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
-      <c r="M272" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P272" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>380344</v>
+        <v>380184</v>
       </c>
       <c r="R272" t="n">
-        <v>6919654</v>
+        <v>6920434</v>
       </c>
       <c r="S272" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T272" t="inlineStr">
         <is>
@@ -28744,10 +28749,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>124588108</v>
+        <v>124589633</v>
       </c>
       <c r="B274" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -28760,42 +28765,37 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
-      <c r="M274" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P274" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>380223</v>
+        <v>380181</v>
       </c>
       <c r="R274" t="n">
-        <v>6920277</v>
+        <v>6920018</v>
       </c>
       <c r="S274" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T274" t="inlineStr">
         <is>
@@ -28851,10 +28851,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>124589633</v>
+        <v>124588108</v>
       </c>
       <c r="B275" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -28867,37 +28867,42 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P275" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>380181</v>
+        <v>380223</v>
       </c>
       <c r="R275" t="n">
-        <v>6920018</v>
+        <v>6920277</v>
       </c>
       <c r="S275" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T275" t="inlineStr">
         <is>
@@ -28953,7 +28958,7 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>124870503</v>
+        <v>124870943</v>
       </c>
       <c r="B276" t="n">
         <v>57513</v>
@@ -28994,14 +28999,14 @@
       </c>
       <c r="P276" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>380108</v>
+        <v>380093</v>
       </c>
       <c r="R276" t="n">
-        <v>6919741</v>
+        <v>6919892</v>
       </c>
       <c r="S276" t="n">
         <v>15</v>
@@ -29060,7 +29065,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>124870424</v>
+        <v>124870829</v>
       </c>
       <c r="B277" t="n">
         <v>57513</v>
@@ -29105,10 +29110,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>380098</v>
+        <v>380045</v>
       </c>
       <c r="R277" t="n">
-        <v>6919759</v>
+        <v>6919831</v>
       </c>
       <c r="S277" t="n">
         <v>15</v>
@@ -29167,10 +29172,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>124870851</v>
+        <v>124870693</v>
       </c>
       <c r="B278" t="n">
-        <v>79399</v>
+        <v>96354</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -29183,21 +29188,21 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>229821</v>
+        <v>53</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
@@ -29207,10 +29212,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>380051</v>
+        <v>380072</v>
       </c>
       <c r="R278" t="n">
-        <v>6919850</v>
+        <v>6919810</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -29269,10 +29274,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>124870654</v>
+        <v>124870881</v>
       </c>
       <c r="B279" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -29285,37 +29290,42 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P279" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>380093</v>
+        <v>380067</v>
       </c>
       <c r="R279" t="n">
-        <v>6919795</v>
+        <v>6919860</v>
       </c>
       <c r="S279" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T279" t="inlineStr">
         <is>
@@ -29371,7 +29381,7 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>124871117</v>
+        <v>124870503</v>
       </c>
       <c r="B280" t="n">
         <v>57513</v>
@@ -29412,14 +29422,14 @@
       </c>
       <c r="P280" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>380204</v>
+        <v>380108</v>
       </c>
       <c r="R280" t="n">
-        <v>6920043</v>
+        <v>6919741</v>
       </c>
       <c r="S280" t="n">
         <v>15</v>
@@ -29478,10 +29488,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>124870920</v>
+        <v>124871232</v>
       </c>
       <c r="B281" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -29494,21 +29504,21 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
@@ -29518,10 +29528,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>380097</v>
+        <v>380202</v>
       </c>
       <c r="R281" t="n">
-        <v>6919882</v>
+        <v>6920072</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -29580,7 +29590,7 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>124870881</v>
+        <v>124871081</v>
       </c>
       <c r="B282" t="n">
         <v>57513</v>
@@ -29616,19 +29626,19 @@
       <c r="I282" t="inlineStr"/>
       <c r="M282" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P282" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>380067</v>
+        <v>380173</v>
       </c>
       <c r="R282" t="n">
-        <v>6919860</v>
+        <v>6920011</v>
       </c>
       <c r="S282" t="n">
         <v>15</v>
@@ -29687,7 +29697,7 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>124870829</v>
+        <v>124871117</v>
       </c>
       <c r="B283" t="n">
         <v>57513</v>
@@ -29728,14 +29738,14 @@
       </c>
       <c r="P283" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>380045</v>
+        <v>380204</v>
       </c>
       <c r="R283" t="n">
-        <v>6919831</v>
+        <v>6920043</v>
       </c>
       <c r="S283" t="n">
         <v>15</v>
@@ -29794,10 +29804,10 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>124871081</v>
+        <v>124870851</v>
       </c>
       <c r="B284" t="n">
-        <v>57513</v>
+        <v>79399</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -29810,42 +29820,37 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
-      <c r="M284" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P284" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>380173</v>
+        <v>380051</v>
       </c>
       <c r="R284" t="n">
-        <v>6920011</v>
+        <v>6919850</v>
       </c>
       <c r="S284" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T284" t="inlineStr">
         <is>
@@ -29901,10 +29906,10 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>124870943</v>
+        <v>124870654</v>
       </c>
       <c r="B285" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -29917,42 +29922,37 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
-      <c r="M285" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P285" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q285" t="n">
         <v>380093</v>
       </c>
       <c r="R285" t="n">
-        <v>6919892</v>
+        <v>6919795</v>
       </c>
       <c r="S285" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T285" t="inlineStr">
         <is>
@@ -30115,7 +30115,7 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>124870262</v>
+        <v>124870424</v>
       </c>
       <c r="B287" t="n">
         <v>57513</v>
@@ -30156,14 +30156,14 @@
       </c>
       <c r="P287" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>380196</v>
+        <v>380098</v>
       </c>
       <c r="R287" t="n">
-        <v>6919970</v>
+        <v>6919759</v>
       </c>
       <c r="S287" t="n">
         <v>15</v>
@@ -30222,10 +30222,10 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>124870693</v>
+        <v>124870920</v>
       </c>
       <c r="B288" t="n">
-        <v>96354</v>
+        <v>91030</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -30238,34 +30238,34 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>53</v>
+        <v>5432</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I288" t="inlineStr"/>
       <c r="P288" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>380072</v>
+        <v>380097</v>
       </c>
       <c r="R288" t="n">
-        <v>6919810</v>
+        <v>6919882</v>
       </c>
       <c r="S288" t="n">
         <v>10</v>
@@ -30324,10 +30324,10 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>124871232</v>
+        <v>124870262</v>
       </c>
       <c r="B289" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -30340,37 +30340,42 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I289" t="inlineStr"/>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P289" t="inlineStr">
         <is>
           <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>380202</v>
+        <v>380196</v>
       </c>
       <c r="R289" t="n">
-        <v>6920072</v>
+        <v>6919970</v>
       </c>
       <c r="S289" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T289" t="inlineStr">
         <is>

--- a/artfynd/A 32573-2024 artfynd.xlsx
+++ b/artfynd/A 32573-2024 artfynd.xlsx
@@ -16105,10 +16105,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>124456129</v>
+        <v>124452491</v>
       </c>
       <c r="B152" t="n">
-        <v>78905</v>
+        <v>78810</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16121,21 +16121,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16145,10 +16145,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>380326</v>
+        <v>380208</v>
       </c>
       <c r="R152" t="n">
-        <v>6920218</v>
+        <v>6920481</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16195,22 +16195,22 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>124451984</v>
+        <v>124470742</v>
       </c>
       <c r="B153" t="n">
-        <v>79399</v>
+        <v>57513</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16223,37 +16223,42 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>380203</v>
+        <v>380369</v>
       </c>
       <c r="R153" t="n">
-        <v>6920482</v>
+        <v>6920032</v>
       </c>
       <c r="S153" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16309,10 +16314,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>124451885</v>
+        <v>124456129</v>
       </c>
       <c r="B154" t="n">
-        <v>91030</v>
+        <v>78905</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16325,21 +16330,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>5432</v>
+        <v>967</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16349,10 +16354,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>380189</v>
+        <v>380326</v>
       </c>
       <c r="R154" t="n">
-        <v>6920488</v>
+        <v>6920218</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16399,22 +16404,22 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>124456697</v>
+        <v>124464471</v>
       </c>
       <c r="B155" t="n">
-        <v>91030</v>
+        <v>78194</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16427,21 +16432,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>5432</v>
+        <v>6437</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16451,10 +16456,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>380443</v>
+        <v>380243</v>
       </c>
       <c r="R155" t="n">
-        <v>6920118</v>
+        <v>6919687</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16513,10 +16518,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>124458743</v>
+        <v>124467947</v>
       </c>
       <c r="B156" t="n">
-        <v>91030</v>
+        <v>78194</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16529,34 +16534,34 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>5432</v>
+        <v>6437</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>380542</v>
+        <v>380361</v>
       </c>
       <c r="R156" t="n">
-        <v>6920184</v>
+        <v>6919740</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16593,7 +16598,7 @@
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Miljöbilder.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16620,10 +16625,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>124455206</v>
+        <v>124455774</v>
       </c>
       <c r="B157" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16636,34 +16641,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>380311</v>
+        <v>380356</v>
       </c>
       <c r="R157" t="n">
-        <v>6920231</v>
+        <v>6920172</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16722,10 +16727,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>124470397</v>
+        <v>124468916</v>
       </c>
       <c r="B158" t="n">
-        <v>74901</v>
+        <v>78151</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16734,38 +16739,38 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6440</v>
+        <v>498</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>380506</v>
+        <v>380343</v>
       </c>
       <c r="R158" t="n">
-        <v>6920061</v>
+        <v>6919896</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16812,22 +16817,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>124463210</v>
+        <v>124464047</v>
       </c>
       <c r="B159" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16840,21 +16845,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16864,10 +16869,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>380189</v>
+        <v>380267</v>
       </c>
       <c r="R159" t="n">
-        <v>6919766</v>
+        <v>6919731</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16926,10 +16931,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>124464329</v>
+        <v>124459060</v>
       </c>
       <c r="B160" t="n">
-        <v>78194</v>
+        <v>57513</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -16942,34 +16947,39 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>380268</v>
+        <v>380571</v>
       </c>
       <c r="R160" t="n">
-        <v>6919685</v>
+        <v>6919993</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17028,10 +17038,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>124464121</v>
+        <v>124470184</v>
       </c>
       <c r="B161" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17044,39 +17054,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>380419</v>
+        <v>380516</v>
       </c>
       <c r="R161" t="n">
-        <v>6919960</v>
+        <v>6920004</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17123,22 +17128,22 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>124469547</v>
+        <v>124470146</v>
       </c>
       <c r="B162" t="n">
-        <v>88359</v>
+        <v>57513</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17151,37 +17156,42 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>380452</v>
+        <v>380527</v>
       </c>
       <c r="R162" t="n">
-        <v>6919913</v>
+        <v>6919988</v>
       </c>
       <c r="S162" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -17225,22 +17235,22 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>124458172</v>
+        <v>124461108</v>
       </c>
       <c r="B163" t="n">
-        <v>78151</v>
+        <v>74901</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17249,38 +17259,38 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>498</v>
+        <v>6440</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>380562</v>
+        <v>380308</v>
       </c>
       <c r="R163" t="n">
-        <v>6920118</v>
+        <v>6919925</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17313,6 +17323,11 @@
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>På basen avsågad gran. Grov stubbe</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17339,10 +17354,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>124461736</v>
+        <v>124450902</v>
       </c>
       <c r="B164" t="n">
-        <v>74901</v>
+        <v>57529</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17355,34 +17370,39 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>380232</v>
+        <v>380227</v>
       </c>
       <c r="R164" t="n">
-        <v>6919808</v>
+        <v>6920340</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17417,6 +17437,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>Troligen spillkråka.</t>
+        </is>
+      </c>
       <c r="AD164" t="b">
         <v>0</v>
       </c>
@@ -17429,22 +17454,22 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>124451802</v>
+        <v>124454876</v>
       </c>
       <c r="B165" t="n">
-        <v>79428</v>
+        <v>74901</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17457,21 +17482,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17481,10 +17506,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>380197</v>
+        <v>380290</v>
       </c>
       <c r="R165" t="n">
-        <v>6920479</v>
+        <v>6920272</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17543,10 +17568,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>124451893</v>
+        <v>124468547</v>
       </c>
       <c r="B166" t="n">
-        <v>5196</v>
+        <v>74901</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17555,25 +17580,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>105930</v>
+        <v>6440</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17583,10 +17608,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>380227</v>
+        <v>380356</v>
       </c>
       <c r="R166" t="n">
-        <v>6920340</v>
+        <v>6919817</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17633,19 +17658,19 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>124460965</v>
+        <v>124457836</v>
       </c>
       <c r="B167" t="n">
         <v>78810</v>
@@ -17681,14 +17706,14 @@
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>380307</v>
+        <v>380542</v>
       </c>
       <c r="R167" t="n">
-        <v>6919967</v>
+        <v>6920184</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17735,22 +17760,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>124469907</v>
+        <v>124451837</v>
       </c>
       <c r="B168" t="n">
-        <v>78810</v>
+        <v>78194</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -17763,34 +17788,34 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>380452</v>
+        <v>380197</v>
       </c>
       <c r="R168" t="n">
-        <v>6919913</v>
+        <v>6920479</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17837,22 +17862,22 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>124470070</v>
+        <v>124455456</v>
       </c>
       <c r="B169" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -17865,34 +17890,34 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>380533</v>
+        <v>380314</v>
       </c>
       <c r="R169" t="n">
-        <v>6919979</v>
+        <v>6920201</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17951,10 +17976,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>124470742</v>
+        <v>124461736</v>
       </c>
       <c r="B170" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -17967,42 +17992,37 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>380369</v>
+        <v>380232</v>
       </c>
       <c r="R170" t="n">
-        <v>6920032</v>
+        <v>6919808</v>
       </c>
       <c r="S170" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -18058,7 +18078,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>124466494</v>
+        <v>124461646</v>
       </c>
       <c r="B171" t="n">
         <v>57513</v>
@@ -18099,14 +18119,14 @@
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>380344</v>
+        <v>380239</v>
       </c>
       <c r="R171" t="n">
-        <v>6919654</v>
+        <v>6919828</v>
       </c>
       <c r="S171" t="n">
         <v>15</v>
@@ -18165,10 +18185,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>124456676</v>
+        <v>124458282</v>
       </c>
       <c r="B172" t="n">
-        <v>57513</v>
+        <v>78151</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18177,46 +18197,41 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P172" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>380434</v>
+        <v>380588</v>
       </c>
       <c r="R172" t="n">
-        <v>6920123</v>
+        <v>6920110</v>
       </c>
       <c r="S172" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -18272,10 +18287,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>124470646</v>
+        <v>124470234</v>
       </c>
       <c r="B173" t="n">
-        <v>91030</v>
+        <v>82597</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18288,34 +18303,34 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>380402</v>
+        <v>380506</v>
       </c>
       <c r="R173" t="n">
-        <v>6920044</v>
+        <v>6920009</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18374,10 +18389,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>124456046</v>
+        <v>124454979</v>
       </c>
       <c r="B174" t="n">
-        <v>91032</v>
+        <v>91030</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18390,21 +18405,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>5442</v>
+        <v>5432</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18414,10 +18429,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>380326</v>
+        <v>380289</v>
       </c>
       <c r="R174" t="n">
-        <v>6920218</v>
+        <v>6920290</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18454,7 +18469,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>Miljöbilder för området.</t>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18481,10 +18496,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>124470184</v>
+        <v>124450666</v>
       </c>
       <c r="B175" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -18497,34 +18512,34 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>380516</v>
+        <v>380227</v>
       </c>
       <c r="R175" t="n">
-        <v>6920004</v>
+        <v>6920340</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18571,22 +18586,22 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>124456704</v>
+        <v>124468182</v>
       </c>
       <c r="B176" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -18599,37 +18614,42 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>380385</v>
+        <v>380265</v>
       </c>
       <c r="R176" t="n">
-        <v>6920091</v>
+        <v>6919774</v>
       </c>
       <c r="S176" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -18659,11 +18679,6 @@
       <c r="AA176" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -18678,19 +18693,19 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>124458651</v>
+        <v>124456832</v>
       </c>
       <c r="B177" t="n">
         <v>91030</v>
@@ -18730,10 +18745,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>380569</v>
+        <v>380443</v>
       </c>
       <c r="R177" t="n">
-        <v>6920058</v>
+        <v>6920118</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18792,10 +18807,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>124465167</v>
+        <v>124458743</v>
       </c>
       <c r="B178" t="n">
-        <v>78194</v>
+        <v>91030</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -18808,34 +18823,34 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6437</v>
+        <v>5432</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>380244</v>
+        <v>380542</v>
       </c>
       <c r="R178" t="n">
-        <v>6919577</v>
+        <v>6920184</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18868,6 +18883,11 @@
       <c r="AA178" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -18894,10 +18914,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>124470485</v>
+        <v>124455206</v>
       </c>
       <c r="B179" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -18910,34 +18930,34 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>380446</v>
+        <v>380311</v>
       </c>
       <c r="R179" t="n">
-        <v>6920059</v>
+        <v>6920231</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18996,10 +19016,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>124450415</v>
+        <v>124450845</v>
       </c>
       <c r="B180" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -19012,21 +19032,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19036,10 +19056,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>380202</v>
+        <v>380205</v>
       </c>
       <c r="R180" t="n">
-        <v>6920332</v>
+        <v>6920378</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19098,10 +19118,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>124465863</v>
+        <v>124464842</v>
       </c>
       <c r="B181" t="n">
-        <v>78151</v>
+        <v>79428</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -19110,38 +19130,38 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>498</v>
+        <v>6453</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Risåsvallen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>380296</v>
+        <v>380237</v>
       </c>
       <c r="R181" t="n">
-        <v>6919585</v>
+        <v>6919621</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19200,10 +19220,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124459456</v>
+        <v>124450300</v>
       </c>
       <c r="B182" t="n">
-        <v>91032</v>
+        <v>74901</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -19216,34 +19236,34 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>5442</v>
+        <v>6440</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>380561</v>
+        <v>380182</v>
       </c>
       <c r="R182" t="n">
-        <v>6919930</v>
+        <v>6920316</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19290,22 +19310,22 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124460951</v>
+        <v>124460258</v>
       </c>
       <c r="B183" t="n">
-        <v>74901</v>
+        <v>79428</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -19318,21 +19338,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19342,10 +19362,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>380307</v>
+        <v>380365</v>
       </c>
       <c r="R183" t="n">
-        <v>6919967</v>
+        <v>6919996</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19404,10 +19424,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124463640</v>
+        <v>124451326</v>
       </c>
       <c r="B184" t="n">
-        <v>79428</v>
+        <v>57513</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -19420,34 +19440,39 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>380218</v>
+        <v>380227</v>
       </c>
       <c r="R184" t="n">
-        <v>6919722</v>
+        <v>6920340</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19494,22 +19519,22 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124460258</v>
+        <v>124469377</v>
       </c>
       <c r="B185" t="n">
-        <v>79428</v>
+        <v>74901</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -19522,21 +19547,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19546,10 +19571,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>380365</v>
+        <v>380435</v>
       </c>
       <c r="R185" t="n">
-        <v>6919996</v>
+        <v>6919916</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19608,7 +19633,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124455453</v>
+        <v>124458046</v>
       </c>
       <c r="B186" t="n">
         <v>74901</v>
@@ -19644,14 +19669,14 @@
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>380326</v>
+        <v>380533</v>
       </c>
       <c r="R186" t="n">
-        <v>6920218</v>
+        <v>6920142</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19698,22 +19723,22 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124464292</v>
+        <v>124464329</v>
       </c>
       <c r="B187" t="n">
-        <v>57513</v>
+        <v>78194</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -19726,39 +19751,34 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P187" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>380275</v>
+        <v>380268</v>
       </c>
       <c r="R187" t="n">
-        <v>6919775</v>
+        <v>6919685</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19805,12 +19825,12 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
@@ -19919,7 +19939,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124459042</v>
+        <v>124451172</v>
       </c>
       <c r="B189" t="n">
         <v>74901</v>
@@ -19955,14 +19975,14 @@
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>380571</v>
+        <v>380184</v>
       </c>
       <c r="R189" t="n">
-        <v>6919993</v>
+        <v>6920434</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20021,10 +20041,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>124455220</v>
+        <v>124460052</v>
       </c>
       <c r="B190" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20037,34 +20057,39 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>380311</v>
+        <v>380419</v>
       </c>
       <c r="R190" t="n">
-        <v>6920231</v>
+        <v>6919960</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20111,19 +20136,19 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>124452627</v>
+        <v>124470732</v>
       </c>
       <c r="B191" t="n">
         <v>74901</v>
@@ -20159,14 +20184,14 @@
       <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>380217</v>
+        <v>380372</v>
       </c>
       <c r="R191" t="n">
-        <v>6920440</v>
+        <v>6920042</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20225,10 +20250,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>124467947</v>
+        <v>124455453</v>
       </c>
       <c r="B192" t="n">
-        <v>78194</v>
+        <v>74901</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20241,34 +20266,34 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>380361</v>
+        <v>380326</v>
       </c>
       <c r="R192" t="n">
-        <v>6919740</v>
+        <v>6920218</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20301,11 +20326,6 @@
       <c r="AA192" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20332,10 +20352,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>124451574</v>
+        <v>124451569</v>
       </c>
       <c r="B193" t="n">
-        <v>79428</v>
+        <v>79399</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -20348,21 +20368,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20434,10 +20454,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>124464651</v>
+        <v>124459456</v>
       </c>
       <c r="B194" t="n">
-        <v>79399</v>
+        <v>91032</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -20450,34 +20470,34 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>229821</v>
+        <v>5442</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>380251</v>
+        <v>380561</v>
       </c>
       <c r="R194" t="n">
-        <v>6919658</v>
+        <v>6919930</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20524,22 +20544,22 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>124450518</v>
+        <v>124451885</v>
       </c>
       <c r="B195" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -20552,34 +20572,34 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>380202</v>
+        <v>380189</v>
       </c>
       <c r="R195" t="n">
-        <v>6920332</v>
+        <v>6920488</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20638,10 +20658,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>124460611</v>
+        <v>124470646</v>
       </c>
       <c r="B196" t="n">
-        <v>78905</v>
+        <v>91030</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -20654,34 +20674,34 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>967</v>
+        <v>5432</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>380335</v>
+        <v>380402</v>
       </c>
       <c r="R196" t="n">
-        <v>6920000</v>
+        <v>6920044</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20728,22 +20748,22 @@
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>124467914</v>
+        <v>124465167</v>
       </c>
       <c r="B197" t="n">
-        <v>77738</v>
+        <v>78194</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -20756,21 +20776,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20780,10 +20800,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>380361</v>
+        <v>380244</v>
       </c>
       <c r="R197" t="n">
-        <v>6919740</v>
+        <v>6919577</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20816,11 +20836,6 @@
       <c r="AA197" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC197" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -20847,10 +20862,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>124459134</v>
+        <v>124470695</v>
       </c>
       <c r="B198" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -20863,21 +20878,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -20887,10 +20902,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>380559</v>
+        <v>380506</v>
       </c>
       <c r="R198" t="n">
-        <v>6919947</v>
+        <v>6920061</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20925,6 +20940,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD198" t="b">
         <v>0</v>
       </c>
@@ -20937,22 +20957,22 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>124469377</v>
+        <v>124458357</v>
       </c>
       <c r="B199" t="n">
-        <v>74901</v>
+        <v>57666</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -20965,37 +20985,42 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>380435</v>
+        <v>380586</v>
       </c>
       <c r="R199" t="n">
-        <v>6919916</v>
+        <v>6920100</v>
       </c>
       <c r="S199" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -21051,10 +21076,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>124468182</v>
+        <v>124451574</v>
       </c>
       <c r="B200" t="n">
-        <v>57513</v>
+        <v>79428</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -21067,42 +21092,37 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>380265</v>
+        <v>380184</v>
       </c>
       <c r="R200" t="n">
-        <v>6919774</v>
+        <v>6920434</v>
       </c>
       <c r="S200" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -21158,10 +21178,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>124461477</v>
+        <v>124459134</v>
       </c>
       <c r="B201" t="n">
-        <v>79399</v>
+        <v>74901</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -21174,34 +21194,34 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>380285</v>
+        <v>380559</v>
       </c>
       <c r="R201" t="n">
-        <v>6919895</v>
+        <v>6919947</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21260,10 +21280,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>124465389</v>
+        <v>124469088</v>
       </c>
       <c r="B202" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -21276,34 +21296,34 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>380244</v>
+        <v>380352</v>
       </c>
       <c r="R202" t="n">
-        <v>6919577</v>
+        <v>6919913</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21350,22 +21370,22 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>124464559</v>
+        <v>124464321</v>
       </c>
       <c r="B203" t="n">
-        <v>79399</v>
+        <v>77738</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -21378,21 +21398,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -21402,10 +21422,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>380236</v>
+        <v>380268</v>
       </c>
       <c r="R203" t="n">
-        <v>6919671</v>
+        <v>6919685</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21464,7 +21484,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>124465009</v>
+        <v>124464901</v>
       </c>
       <c r="B204" t="n">
         <v>79399</v>
@@ -21504,10 +21524,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>380267</v>
+        <v>380249</v>
       </c>
       <c r="R204" t="n">
-        <v>6919764</v>
+        <v>6919607</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21542,11 +21562,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD204" t="b">
         <v>0</v>
       </c>
@@ -21559,22 +21574,22 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>124461646</v>
+        <v>124469907</v>
       </c>
       <c r="B205" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -21587,42 +21602,37 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
-      <c r="M205" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>380239</v>
+        <v>380452</v>
       </c>
       <c r="R205" t="n">
-        <v>6919828</v>
+        <v>6919913</v>
       </c>
       <c r="S205" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -21666,22 +21676,22 @@
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>124470598</v>
+        <v>124466494</v>
       </c>
       <c r="B206" t="n">
-        <v>79428</v>
+        <v>57513</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -21694,37 +21704,42 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P206" t="inlineStr">
         <is>
           <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>380506</v>
+        <v>380344</v>
       </c>
       <c r="R206" t="n">
-        <v>6920061</v>
+        <v>6919654</v>
       </c>
       <c r="S206" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -21754,11 +21769,6 @@
       <c r="AA206" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC206" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -21773,22 +21783,22 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>124470732</v>
+        <v>124468469</v>
       </c>
       <c r="B207" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -21801,37 +21811,42 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>380372</v>
+        <v>380324</v>
       </c>
       <c r="R207" t="n">
-        <v>6920042</v>
+        <v>6919803</v>
       </c>
       <c r="S207" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -21887,10 +21902,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>124458282</v>
+        <v>124451893</v>
       </c>
       <c r="B208" t="n">
-        <v>78151</v>
+        <v>5196</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -21899,38 +21914,38 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>498</v>
+        <v>105930</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>380588</v>
+        <v>380227</v>
       </c>
       <c r="R208" t="n">
-        <v>6920110</v>
+        <v>6920340</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21977,22 +21992,22 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>124463365</v>
+        <v>124459815</v>
       </c>
       <c r="B209" t="n">
-        <v>79399</v>
+        <v>79428</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -22005,34 +22020,34 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>380199</v>
+        <v>380445</v>
       </c>
       <c r="R209" t="n">
-        <v>6919723</v>
+        <v>6919917</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -22091,10 +22106,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>124469088</v>
+        <v>124451984</v>
       </c>
       <c r="B210" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -22107,34 +22122,34 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>380352</v>
+        <v>380203</v>
       </c>
       <c r="R210" t="n">
-        <v>6919913</v>
+        <v>6920482</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22193,10 +22208,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>124457866</v>
+        <v>124465009</v>
       </c>
       <c r="B211" t="n">
-        <v>78151</v>
+        <v>79399</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -22205,25 +22220,25 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>498</v>
+        <v>229821</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -22233,10 +22248,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>380537</v>
+        <v>380267</v>
       </c>
       <c r="R211" t="n">
-        <v>6920199</v>
+        <v>6919764</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22271,6 +22286,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD211" t="b">
         <v>0</v>
       </c>
@@ -22283,22 +22303,22 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>124451172</v>
+        <v>124456046</v>
       </c>
       <c r="B212" t="n">
-        <v>74901</v>
+        <v>91032</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -22311,21 +22331,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6440</v>
+        <v>5442</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -22335,10 +22355,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>380184</v>
+        <v>380326</v>
       </c>
       <c r="R212" t="n">
-        <v>6920434</v>
+        <v>6920218</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22373,6 +22393,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området.</t>
+        </is>
+      </c>
       <c r="AD212" t="b">
         <v>0</v>
       </c>
@@ -22385,22 +22410,22 @@
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>124464471</v>
+        <v>124459042</v>
       </c>
       <c r="B213" t="n">
-        <v>78194</v>
+        <v>74901</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -22413,21 +22438,21 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -22437,10 +22462,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>380243</v>
+        <v>380571</v>
       </c>
       <c r="R213" t="n">
-        <v>6919687</v>
+        <v>6919993</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22601,10 +22626,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>124471016</v>
+        <v>124458172</v>
       </c>
       <c r="B215" t="n">
-        <v>57513</v>
+        <v>78151</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -22613,43 +22638,38 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
-      <c r="M215" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>380506</v>
+        <v>380562</v>
       </c>
       <c r="R215" t="n">
-        <v>6920061</v>
+        <v>6920118</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22696,22 +22716,22 @@
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>124464901</v>
+        <v>124463640</v>
       </c>
       <c r="B216" t="n">
-        <v>79399</v>
+        <v>79428</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -22724,21 +22744,21 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -22748,10 +22768,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>380249</v>
+        <v>380218</v>
       </c>
       <c r="R216" t="n">
-        <v>6919607</v>
+        <v>6919722</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22810,10 +22830,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>124457317</v>
+        <v>124460965</v>
       </c>
       <c r="B217" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -22826,34 +22846,34 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>380547</v>
+        <v>380307</v>
       </c>
       <c r="R217" t="n">
-        <v>6920163</v>
+        <v>6919967</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22912,10 +22932,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>124455134</v>
+        <v>124460224</v>
       </c>
       <c r="B218" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -22928,34 +22948,39 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>380311</v>
+        <v>380374</v>
       </c>
       <c r="R218" t="n">
-        <v>6920245</v>
+        <v>6919982</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23002,22 +23027,22 @@
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>124461108</v>
+        <v>124455022</v>
       </c>
       <c r="B219" t="n">
-        <v>74901</v>
+        <v>79428</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -23030,21 +23055,21 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -23054,10 +23079,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>380308</v>
+        <v>380292</v>
       </c>
       <c r="R219" t="n">
-        <v>6919925</v>
+        <v>6920288</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23090,11 +23115,6 @@
       <c r="AA219" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC219" t="inlineStr">
-        <is>
-          <t>På basen avsågad gran. Grov stubbe</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -23121,10 +23141,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>124452491</v>
+        <v>124464559</v>
       </c>
       <c r="B220" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -23137,34 +23157,34 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>380208</v>
+        <v>380236</v>
       </c>
       <c r="R220" t="n">
-        <v>6920481</v>
+        <v>6919671</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23223,10 +23243,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>124457836</v>
+        <v>124455776</v>
       </c>
       <c r="B221" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -23239,34 +23259,39 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>380542</v>
+        <v>380326</v>
       </c>
       <c r="R221" t="n">
-        <v>6920184</v>
+        <v>6920218</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23325,7 +23350,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>124470404</v>
+        <v>124456704</v>
       </c>
       <c r="B222" t="n">
         <v>91030</v>
@@ -23361,14 +23386,14 @@
       <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>380471</v>
+        <v>380385</v>
       </c>
       <c r="R222" t="n">
-        <v>6920069</v>
+        <v>6920091</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23403,6 +23428,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD222" t="b">
         <v>0</v>
       </c>
@@ -23415,22 +23445,22 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>124450578</v>
+        <v>124463210</v>
       </c>
       <c r="B223" t="n">
-        <v>91030</v>
+        <v>79428</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -23443,34 +23473,34 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>380227</v>
+        <v>380189</v>
       </c>
       <c r="R223" t="n">
-        <v>6920340</v>
+        <v>6919766</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23517,22 +23547,22 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>124470234</v>
+        <v>124470404</v>
       </c>
       <c r="B224" t="n">
-        <v>82597</v>
+        <v>91030</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -23545,21 +23575,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -23569,10 +23599,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>380506</v>
+        <v>380471</v>
       </c>
       <c r="R224" t="n">
-        <v>6920009</v>
+        <v>6920069</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23631,10 +23661,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>124460224</v>
+        <v>124457601</v>
       </c>
       <c r="B225" t="n">
-        <v>57513</v>
+        <v>78151</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -23643,43 +23673,38 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
-      <c r="M225" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>380374</v>
+        <v>380544</v>
       </c>
       <c r="R225" t="n">
-        <v>6919982</v>
+        <v>6920188</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23726,22 +23751,22 @@
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>124470806</v>
+        <v>124454665</v>
       </c>
       <c r="B226" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -23754,42 +23779,37 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
-      <c r="M226" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>380340</v>
+        <v>380258</v>
       </c>
       <c r="R226" t="n">
-        <v>6920036</v>
+        <v>6920309</v>
       </c>
       <c r="S226" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T226" t="inlineStr">
         <is>
@@ -23845,10 +23865,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>124451326</v>
+        <v>124470485</v>
       </c>
       <c r="B227" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -23861,39 +23881,34 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>380227</v>
+        <v>380446</v>
       </c>
       <c r="R227" t="n">
-        <v>6920340</v>
+        <v>6920059</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23940,22 +23955,22 @@
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>124454979</v>
+        <v>124457317</v>
       </c>
       <c r="B228" t="n">
-        <v>91030</v>
+        <v>79428</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -23968,34 +23983,34 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>380289</v>
+        <v>380547</v>
       </c>
       <c r="R228" t="n">
-        <v>6920290</v>
+        <v>6920163</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24030,11 +24045,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC228" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
-        </is>
-      </c>
       <c r="AD228" t="b">
         <v>0</v>
       </c>
@@ -24047,22 +24057,22 @@
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>124456372</v>
+        <v>124464466</v>
       </c>
       <c r="B229" t="n">
-        <v>74901</v>
+        <v>78905</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -24075,34 +24085,34 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6440</v>
+        <v>967</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>380368</v>
+        <v>380243</v>
       </c>
       <c r="R229" t="n">
-        <v>6920107</v>
+        <v>6919687</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24161,10 +24171,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>124450666</v>
+        <v>124469547</v>
       </c>
       <c r="B230" t="n">
-        <v>74901</v>
+        <v>88359</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -24177,34 +24187,34 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>380227</v>
+        <v>380452</v>
       </c>
       <c r="R230" t="n">
-        <v>6920340</v>
+        <v>6919913</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24263,10 +24273,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>124469751</v>
+        <v>124451802</v>
       </c>
       <c r="B231" t="n">
-        <v>74901</v>
+        <v>79428</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -24279,34 +24289,34 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>380490</v>
+        <v>380197</v>
       </c>
       <c r="R231" t="n">
-        <v>6919937</v>
+        <v>6920479</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24365,10 +24375,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>124470555</v>
+        <v>124470598</v>
       </c>
       <c r="B232" t="n">
-        <v>82597</v>
+        <v>79428</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -24381,34 +24391,34 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>380431</v>
+        <v>380506</v>
       </c>
       <c r="R232" t="n">
-        <v>6920068</v>
+        <v>6920061</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24443,6 +24453,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD232" t="b">
         <v>0</v>
       </c>
@@ -24455,22 +24470,22 @@
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>124464466</v>
+        <v>124456372</v>
       </c>
       <c r="B233" t="n">
-        <v>78905</v>
+        <v>74901</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -24483,34 +24498,34 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>967</v>
+        <v>6440</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>380243</v>
+        <v>380368</v>
       </c>
       <c r="R233" t="n">
-        <v>6919687</v>
+        <v>6920107</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -24569,10 +24584,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>124455776</v>
+        <v>124470397</v>
       </c>
       <c r="B234" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -24585,39 +24600,34 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
-      <c r="M234" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>380326</v>
+        <v>380506</v>
       </c>
       <c r="R234" t="n">
-        <v>6920218</v>
+        <v>6920061</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -24676,10 +24686,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>124470146</v>
+        <v>124461477</v>
       </c>
       <c r="B235" t="n">
-        <v>57513</v>
+        <v>79399</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -24692,42 +24702,37 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
-      <c r="M235" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>380527</v>
+        <v>380285</v>
       </c>
       <c r="R235" t="n">
-        <v>6919988</v>
+        <v>6919895</v>
       </c>
       <c r="S235" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T235" t="inlineStr">
         <is>
@@ -24783,10 +24788,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>124459815</v>
+        <v>124456676</v>
       </c>
       <c r="B236" t="n">
-        <v>79428</v>
+        <v>57513</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -24799,37 +24804,42 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>380445</v>
+        <v>380434</v>
       </c>
       <c r="R236" t="n">
-        <v>6919917</v>
+        <v>6920123</v>
       </c>
       <c r="S236" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T236" t="inlineStr">
         <is>
@@ -24885,10 +24895,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>124455096</v>
+        <v>124471016</v>
       </c>
       <c r="B237" t="n">
-        <v>5196</v>
+        <v>57513</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -24897,20 +24907,20 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>105930</v>
+        <v>100109</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -24921,19 +24931,19 @@
       <c r="I237" t="inlineStr"/>
       <c r="M237" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>380323</v>
+        <v>380506</v>
       </c>
       <c r="R237" t="n">
-        <v>6920260</v>
+        <v>6920061</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -24980,19 +24990,19 @@
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>124458046</v>
+        <v>124469751</v>
       </c>
       <c r="B238" t="n">
         <v>74901</v>
@@ -25028,14 +25038,14 @@
       <c r="I238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>380533</v>
+        <v>380490</v>
       </c>
       <c r="R238" t="n">
-        <v>6920142</v>
+        <v>6919937</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -25094,7 +25104,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>124454665</v>
+        <v>124450737</v>
       </c>
       <c r="B239" t="n">
         <v>74901</v>
@@ -25130,14 +25140,14 @@
       <c r="I239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>380258</v>
+        <v>380210</v>
       </c>
       <c r="R239" t="n">
-        <v>6920309</v>
+        <v>6920378</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -25196,10 +25206,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>124464681</v>
+        <v>124450518</v>
       </c>
       <c r="B240" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -25212,21 +25222,21 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -25236,10 +25246,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>380264</v>
+        <v>380202</v>
       </c>
       <c r="R240" t="n">
-        <v>6919665</v>
+        <v>6920332</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -25298,10 +25308,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>124458509</v>
+        <v>124469915</v>
       </c>
       <c r="B241" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -25314,39 +25324,34 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
-      <c r="M241" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P241" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>380542</v>
+        <v>380521</v>
       </c>
       <c r="R241" t="n">
-        <v>6920184</v>
+        <v>6919962</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -25381,11 +25386,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC241" t="inlineStr">
-        <is>
-          <t>Miljöbilder, talltita.</t>
-        </is>
-      </c>
       <c r="AD241" t="b">
         <v>0</v>
       </c>
@@ -25398,22 +25398,22 @@
       <c r="AT241" t="inlineStr"/>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>124454876</v>
+        <v>124464681</v>
       </c>
       <c r="B242" t="n">
-        <v>74901</v>
+        <v>79399</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -25426,34 +25426,34 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>380290</v>
+        <v>380264</v>
       </c>
       <c r="R242" t="n">
-        <v>6920272</v>
+        <v>6919665</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -25512,7 +25512,7 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>124470707</v>
+        <v>124470806</v>
       </c>
       <c r="B243" t="n">
         <v>57513</v>
@@ -25557,10 +25557,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>380367</v>
+        <v>380340</v>
       </c>
       <c r="R243" t="n">
-        <v>6920058</v>
+        <v>6920036</v>
       </c>
       <c r="S243" t="n">
         <v>15</v>
@@ -25619,10 +25619,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>124464970</v>
+        <v>124455096</v>
       </c>
       <c r="B244" t="n">
-        <v>57513</v>
+        <v>5196</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -25631,20 +25631,20 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>100109</v>
+        <v>105930</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -25655,22 +25655,22 @@
       <c r="I244" t="inlineStr"/>
       <c r="M244" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>380255</v>
+        <v>380323</v>
       </c>
       <c r="R244" t="n">
-        <v>6919561</v>
+        <v>6920260</v>
       </c>
       <c r="S244" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
@@ -25726,7 +25726,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>124459060</v>
+        <v>124466302</v>
       </c>
       <c r="B245" t="n">
         <v>57513</v>
@@ -25762,22 +25762,22 @@
       <c r="I245" t="inlineStr"/>
       <c r="M245" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>380571</v>
+        <v>380345</v>
       </c>
       <c r="R245" t="n">
-        <v>6919993</v>
+        <v>6919632</v>
       </c>
       <c r="S245" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -25833,10 +25833,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>124466026</v>
+        <v>124456502</v>
       </c>
       <c r="B246" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -25849,34 +25849,34 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>380303</v>
+        <v>380385</v>
       </c>
       <c r="R246" t="n">
-        <v>6919598</v>
+        <v>6920091</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25913,7 +25913,7 @@
       </c>
       <c r="AC246" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -25940,10 +25940,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>124465526</v>
+        <v>124470555</v>
       </c>
       <c r="B247" t="n">
-        <v>79399</v>
+        <v>82597</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -25956,34 +25956,34 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>229821</v>
+        <v>1312</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Risåsvallen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>380252</v>
+        <v>380431</v>
       </c>
       <c r="R247" t="n">
-        <v>6919535</v>
+        <v>6920068</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -26042,10 +26042,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>124455456</v>
+        <v>124470070</v>
       </c>
       <c r="B248" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -26058,34 +26058,34 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>380314</v>
+        <v>380533</v>
       </c>
       <c r="R248" t="n">
-        <v>6920201</v>
+        <v>6919979</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -26144,10 +26144,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>124450737</v>
+        <v>124452423</v>
       </c>
       <c r="B249" t="n">
-        <v>74901</v>
+        <v>56725</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -26156,38 +26156,43 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>6440</v>
+        <v>102613</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P249" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>380210</v>
+        <v>380227</v>
       </c>
       <c r="R249" t="n">
-        <v>6920378</v>
+        <v>6920340</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -26234,22 +26239,22 @@
       <c r="AT249" t="inlineStr"/>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>124469915</v>
+        <v>124459048</v>
       </c>
       <c r="B250" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -26262,34 +26267,39 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>380521</v>
+        <v>380542</v>
       </c>
       <c r="R250" t="n">
-        <v>6919962</v>
+        <v>6920184</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -26336,22 +26346,22 @@
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>124468547</v>
+        <v>124464292</v>
       </c>
       <c r="B251" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -26364,34 +26374,39 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P251" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>380356</v>
+        <v>380275</v>
       </c>
       <c r="R251" t="n">
-        <v>6919817</v>
+        <v>6919775</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -26438,22 +26453,22 @@
       <c r="AT251" t="inlineStr"/>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>124450902</v>
+        <v>124450578</v>
       </c>
       <c r="B252" t="n">
-        <v>57529</v>
+        <v>91030</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -26466,29 +26481,24 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
-      <c r="M252" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P252" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
@@ -26531,11 +26541,6 @@
       <c r="AA252" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC252" t="inlineStr">
-        <is>
-          <t>Troligen spillkråka.</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -26562,7 +26567,7 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>124464047</v>
+        <v>124452261</v>
       </c>
       <c r="B253" t="n">
         <v>78810</v>
@@ -26598,14 +26603,14 @@
       <c r="I253" t="inlineStr"/>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>380267</v>
+        <v>380227</v>
       </c>
       <c r="R253" t="n">
-        <v>6919731</v>
+        <v>6920340</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -26652,22 +26657,22 @@
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>124450845</v>
+        <v>124457866</v>
       </c>
       <c r="B254" t="n">
-        <v>78810</v>
+        <v>78151</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -26676,25 +26681,25 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>6425</v>
+        <v>498</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -26704,10 +26709,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>380205</v>
+        <v>380537</v>
       </c>
       <c r="R254" t="n">
-        <v>6920378</v>
+        <v>6920199</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26766,7 +26771,7 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>124468916</v>
+        <v>124465863</v>
       </c>
       <c r="B255" t="n">
         <v>78151</v>
@@ -26802,14 +26807,14 @@
       <c r="I255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Risåsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>380343</v>
+        <v>380296</v>
       </c>
       <c r="R255" t="n">
-        <v>6919896</v>
+        <v>6919585</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26868,10 +26873,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>124464321</v>
+        <v>124463365</v>
       </c>
       <c r="B256" t="n">
-        <v>77738</v>
+        <v>79399</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -26884,21 +26889,21 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -26908,10 +26913,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>380268</v>
+        <v>380199</v>
       </c>
       <c r="R256" t="n">
-        <v>6919685</v>
+        <v>6919723</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -26970,7 +26975,7 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>124450300</v>
+        <v>124455134</v>
       </c>
       <c r="B257" t="n">
         <v>74901</v>
@@ -27006,14 +27011,14 @@
       <c r="I257" t="inlineStr"/>
       <c r="P257" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>380182</v>
+        <v>380311</v>
       </c>
       <c r="R257" t="n">
-        <v>6920316</v>
+        <v>6920245</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -27072,7 +27077,7 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>124455774</v>
+        <v>124455220</v>
       </c>
       <c r="B258" t="n">
         <v>74901</v>
@@ -27108,14 +27113,14 @@
       <c r="I258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>380356</v>
+        <v>380311</v>
       </c>
       <c r="R258" t="n">
-        <v>6920172</v>
+        <v>6920231</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -27174,10 +27179,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>124459287</v>
+        <v>124452627</v>
       </c>
       <c r="B259" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -27190,39 +27195,34 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
-      <c r="M259" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>380561</v>
+        <v>380217</v>
       </c>
       <c r="R259" t="n">
-        <v>6919930</v>
+        <v>6920440</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -27269,22 +27269,22 @@
       <c r="AT259" t="inlineStr"/>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>124457601</v>
+        <v>124460611</v>
       </c>
       <c r="B260" t="n">
-        <v>78151</v>
+        <v>78905</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -27293,38 +27293,38 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>498</v>
+        <v>967</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>380544</v>
+        <v>380335</v>
       </c>
       <c r="R260" t="n">
-        <v>6920188</v>
+        <v>6920000</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -27371,22 +27371,22 @@
       <c r="AT260" t="inlineStr"/>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>124470299</v>
+        <v>124470707</v>
       </c>
       <c r="B261" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -27395,25 +27395,25 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -27424,17 +27424,17 @@
       </c>
       <c r="P261" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>380495</v>
+        <v>380367</v>
       </c>
       <c r="R261" t="n">
-        <v>6920029</v>
+        <v>6920058</v>
       </c>
       <c r="S261" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T261" t="inlineStr">
         <is>
@@ -27490,10 +27490,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>124464842</v>
+        <v>124465389</v>
       </c>
       <c r="B262" t="n">
-        <v>79428</v>
+        <v>79399</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -27506,21 +27506,21 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -27530,10 +27530,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>380237</v>
+        <v>380244</v>
       </c>
       <c r="R262" t="n">
-        <v>6919621</v>
+        <v>6919577</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -27580,22 +27580,22 @@
       <c r="AT262" t="inlineStr"/>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>124455022</v>
+        <v>124450415</v>
       </c>
       <c r="B263" t="n">
-        <v>79428</v>
+        <v>74901</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -27608,34 +27608,34 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>380292</v>
+        <v>380202</v>
       </c>
       <c r="R263" t="n">
-        <v>6920288</v>
+        <v>6920332</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -27694,10 +27694,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>124456502</v>
+        <v>124467914</v>
       </c>
       <c r="B264" t="n">
-        <v>78810</v>
+        <v>77738</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -27710,34 +27710,34 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>380385</v>
+        <v>380361</v>
       </c>
       <c r="R264" t="n">
-        <v>6920091</v>
+        <v>6919740</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27774,7 +27774,7 @@
       </c>
       <c r="AC264" t="inlineStr">
         <is>
-          <t>Miljöbilder för området.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -27801,10 +27801,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>124470695</v>
+        <v>124465526</v>
       </c>
       <c r="B265" t="n">
-        <v>91030</v>
+        <v>79399</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -27817,34 +27817,34 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>5432</v>
+        <v>229821</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Risåsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>380506</v>
+        <v>380252</v>
       </c>
       <c r="R265" t="n">
-        <v>6920061</v>
+        <v>6919535</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27879,11 +27879,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC265" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
-        </is>
-      </c>
       <c r="AD265" t="b">
         <v>0</v>
       </c>
@@ -27896,22 +27891,22 @@
       <c r="AT265" t="inlineStr"/>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>124452261</v>
+        <v>124460951</v>
       </c>
       <c r="B266" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -27924,34 +27919,34 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>380227</v>
+        <v>380307</v>
       </c>
       <c r="R266" t="n">
-        <v>6920340</v>
+        <v>6919967</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -27998,22 +27993,22 @@
       <c r="AT266" t="inlineStr"/>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>124452423</v>
+        <v>124470299</v>
       </c>
       <c r="B267" t="n">
-        <v>56725</v>
+        <v>56722</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -28026,39 +28021,39 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>102613</v>
+        <v>100138</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
       <c r="M267" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P267" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>380227</v>
+        <v>380495</v>
       </c>
       <c r="R267" t="n">
-        <v>6920340</v>
+        <v>6920029</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -28105,22 +28100,22 @@
       <c r="AT267" t="inlineStr"/>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>124451837</v>
+        <v>124459287</v>
       </c>
       <c r="B268" t="n">
-        <v>78194</v>
+        <v>57513</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -28133,34 +28128,39 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P268" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>380197</v>
+        <v>380561</v>
       </c>
       <c r="R268" t="n">
-        <v>6920479</v>
+        <v>6919930</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -28207,22 +28207,22 @@
       <c r="AT268" t="inlineStr"/>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>124468469</v>
+        <v>124458651</v>
       </c>
       <c r="B269" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -28235,42 +28235,37 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
-      <c r="M269" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P269" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>380324</v>
+        <v>380569</v>
       </c>
       <c r="R269" t="n">
-        <v>6919803</v>
+        <v>6920058</v>
       </c>
       <c r="S269" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T269" t="inlineStr">
         <is>
@@ -28326,10 +28321,10 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>124466302</v>
+        <v>124464651</v>
       </c>
       <c r="B270" t="n">
-        <v>57513</v>
+        <v>79399</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -28342,42 +28337,37 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
-      <c r="M270" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P270" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>380345</v>
+        <v>380251</v>
       </c>
       <c r="R270" t="n">
-        <v>6919632</v>
+        <v>6919658</v>
       </c>
       <c r="S270" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T270" t="inlineStr">
         <is>
@@ -28433,10 +28423,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>124458357</v>
+        <v>124466026</v>
       </c>
       <c r="B271" t="n">
-        <v>57666</v>
+        <v>79399</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -28449,42 +28439,37 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
-      <c r="M271" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P271" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>380586</v>
+        <v>380303</v>
       </c>
       <c r="R271" t="n">
-        <v>6920100</v>
+        <v>6919598</v>
       </c>
       <c r="S271" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T271" t="inlineStr">
         <is>
@@ -28514,6 +28499,11 @@
       <c r="AA271" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC271" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -28528,22 +28518,22 @@
       <c r="AT271" t="inlineStr"/>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>124451569</v>
+        <v>124464970</v>
       </c>
       <c r="B272" t="n">
-        <v>79399</v>
+        <v>57513</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -28556,37 +28546,42 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P272" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>380184</v>
+        <v>380255</v>
       </c>
       <c r="R272" t="n">
-        <v>6920434</v>
+        <v>6919561</v>
       </c>
       <c r="S272" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T272" t="inlineStr">
         <is>
@@ -28958,7 +28953,7 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>124870943</v>
+        <v>124870503</v>
       </c>
       <c r="B276" t="n">
         <v>57513</v>
@@ -28999,14 +28994,14 @@
       </c>
       <c r="P276" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>380093</v>
+        <v>380108</v>
       </c>
       <c r="R276" t="n">
-        <v>6919892</v>
+        <v>6919741</v>
       </c>
       <c r="S276" t="n">
         <v>15</v>
@@ -29065,7 +29060,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>124870829</v>
+        <v>124871081</v>
       </c>
       <c r="B277" t="n">
         <v>57513</v>
@@ -29106,14 +29101,14 @@
       </c>
       <c r="P277" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>380045</v>
+        <v>380173</v>
       </c>
       <c r="R277" t="n">
-        <v>6919831</v>
+        <v>6920011</v>
       </c>
       <c r="S277" t="n">
         <v>15</v>
@@ -29172,10 +29167,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>124870693</v>
+        <v>124870920</v>
       </c>
       <c r="B278" t="n">
-        <v>96354</v>
+        <v>91030</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -29188,34 +29183,34 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>53</v>
+        <v>5432</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
       <c r="P278" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>380072</v>
+        <v>380097</v>
       </c>
       <c r="R278" t="n">
-        <v>6919810</v>
+        <v>6919882</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -29274,10 +29269,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>124870881</v>
+        <v>124870851</v>
       </c>
       <c r="B279" t="n">
-        <v>57513</v>
+        <v>79399</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -29290,42 +29285,37 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
-      <c r="M279" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P279" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>380067</v>
+        <v>380051</v>
       </c>
       <c r="R279" t="n">
-        <v>6919860</v>
+        <v>6919850</v>
       </c>
       <c r="S279" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T279" t="inlineStr">
         <is>
@@ -29381,10 +29371,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>124870503</v>
+        <v>124870693</v>
       </c>
       <c r="B280" t="n">
-        <v>57513</v>
+        <v>96354</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -29397,42 +29387,37 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
-      <c r="M280" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P280" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>380108</v>
+        <v>380072</v>
       </c>
       <c r="R280" t="n">
-        <v>6919741</v>
+        <v>6919810</v>
       </c>
       <c r="S280" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T280" t="inlineStr">
         <is>
@@ -29488,10 +29473,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>124871232</v>
+        <v>124871057</v>
       </c>
       <c r="B281" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -29504,37 +29489,42 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P281" t="inlineStr">
         <is>
           <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>380202</v>
+        <v>380132</v>
       </c>
       <c r="R281" t="n">
-        <v>6920072</v>
+        <v>6919977</v>
       </c>
       <c r="S281" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T281" t="inlineStr">
         <is>
@@ -29590,10 +29580,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>124871081</v>
+        <v>124871232</v>
       </c>
       <c r="B282" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -29606,42 +29596,37 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
-      <c r="M282" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P282" t="inlineStr">
         <is>
           <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>380173</v>
+        <v>380202</v>
       </c>
       <c r="R282" t="n">
-        <v>6920011</v>
+        <v>6920072</v>
       </c>
       <c r="S282" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T282" t="inlineStr">
         <is>
@@ -29697,7 +29682,7 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>124871117</v>
+        <v>124870881</v>
       </c>
       <c r="B283" t="n">
         <v>57513</v>
@@ -29733,19 +29718,19 @@
       <c r="I283" t="inlineStr"/>
       <c r="M283" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P283" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>380204</v>
+        <v>380067</v>
       </c>
       <c r="R283" t="n">
-        <v>6920043</v>
+        <v>6919860</v>
       </c>
       <c r="S283" t="n">
         <v>15</v>
@@ -29804,10 +29789,10 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>124870851</v>
+        <v>124870262</v>
       </c>
       <c r="B284" t="n">
-        <v>79399</v>
+        <v>57513</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -29820,37 +29805,42 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P284" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>380051</v>
+        <v>380196</v>
       </c>
       <c r="R284" t="n">
-        <v>6919850</v>
+        <v>6919970</v>
       </c>
       <c r="S284" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T284" t="inlineStr">
         <is>
@@ -29906,10 +29896,10 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>124870654</v>
+        <v>124870943</v>
       </c>
       <c r="B285" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -29922,37 +29912,42 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P285" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q285" t="n">
         <v>380093</v>
       </c>
       <c r="R285" t="n">
-        <v>6919795</v>
+        <v>6919892</v>
       </c>
       <c r="S285" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T285" t="inlineStr">
         <is>
@@ -30008,7 +30003,7 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>124871057</v>
+        <v>124870829</v>
       </c>
       <c r="B286" t="n">
         <v>57513</v>
@@ -30049,14 +30044,14 @@
       </c>
       <c r="P286" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>380132</v>
+        <v>380045</v>
       </c>
       <c r="R286" t="n">
-        <v>6919977</v>
+        <v>6919831</v>
       </c>
       <c r="S286" t="n">
         <v>15</v>
@@ -30115,7 +30110,7 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>124870424</v>
+        <v>124871117</v>
       </c>
       <c r="B287" t="n">
         <v>57513</v>
@@ -30156,14 +30151,14 @@
       </c>
       <c r="P287" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>380098</v>
+        <v>380204</v>
       </c>
       <c r="R287" t="n">
-        <v>6919759</v>
+        <v>6920043</v>
       </c>
       <c r="S287" t="n">
         <v>15</v>
@@ -30222,10 +30217,10 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>124870920</v>
+        <v>124870654</v>
       </c>
       <c r="B288" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -30238,34 +30233,34 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I288" t="inlineStr"/>
       <c r="P288" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>380097</v>
+        <v>380093</v>
       </c>
       <c r="R288" t="n">
-        <v>6919882</v>
+        <v>6919795</v>
       </c>
       <c r="S288" t="n">
         <v>10</v>
@@ -30324,7 +30319,7 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>124870262</v>
+        <v>124870424</v>
       </c>
       <c r="B289" t="n">
         <v>57513</v>
@@ -30365,14 +30360,14 @@
       </c>
       <c r="P289" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>380196</v>
+        <v>380098</v>
       </c>
       <c r="R289" t="n">
-        <v>6919970</v>
+        <v>6919759</v>
       </c>
       <c r="S289" t="n">
         <v>15</v>

--- a/artfynd/A 32573-2024 artfynd.xlsx
+++ b/artfynd/A 32573-2024 artfynd.xlsx
@@ -16105,10 +16105,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>124452491</v>
+        <v>124470742</v>
       </c>
       <c r="B152" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16121,37 +16121,42 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>380208</v>
+        <v>380369</v>
       </c>
       <c r="R152" t="n">
-        <v>6920481</v>
+        <v>6920032</v>
       </c>
       <c r="S152" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16207,10 +16212,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>124470742</v>
+        <v>124456129</v>
       </c>
       <c r="B153" t="n">
-        <v>57513</v>
+        <v>78905</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16223,42 +16228,37 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100109</v>
+        <v>967</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>380369</v>
+        <v>380326</v>
       </c>
       <c r="R153" t="n">
-        <v>6920032</v>
+        <v>6920218</v>
       </c>
       <c r="S153" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16302,22 +16302,22 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>124456129</v>
+        <v>124464471</v>
       </c>
       <c r="B154" t="n">
-        <v>78905</v>
+        <v>78194</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16330,34 +16330,34 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>967</v>
+        <v>6437</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>380326</v>
+        <v>380243</v>
       </c>
       <c r="R154" t="n">
-        <v>6920218</v>
+        <v>6919687</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16404,19 +16404,19 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>124464471</v>
+        <v>124467947</v>
       </c>
       <c r="B155" t="n">
         <v>78194</v>
@@ -16456,10 +16456,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>380243</v>
+        <v>380361</v>
       </c>
       <c r="R155" t="n">
-        <v>6919687</v>
+        <v>6919740</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16494,6 +16494,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD155" t="b">
         <v>0</v>
       </c>
@@ -16506,22 +16511,22 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>124467947</v>
+        <v>124452491</v>
       </c>
       <c r="B156" t="n">
-        <v>78194</v>
+        <v>78810</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16534,34 +16539,34 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>380361</v>
+        <v>380208</v>
       </c>
       <c r="R156" t="n">
-        <v>6919740</v>
+        <v>6920481</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16596,11 +16601,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
@@ -16613,12 +16613,12 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
@@ -17772,10 +17772,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>124451837</v>
+        <v>124454979</v>
       </c>
       <c r="B168" t="n">
-        <v>78194</v>
+        <v>91030</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -17788,21 +17788,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6437</v>
+        <v>5432</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17812,10 +17812,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>380197</v>
+        <v>380289</v>
       </c>
       <c r="R168" t="n">
-        <v>6920479</v>
+        <v>6920290</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17850,6 +17850,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD168" t="b">
         <v>0</v>
       </c>
@@ -17862,22 +17867,22 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>124455456</v>
+        <v>124451837</v>
       </c>
       <c r="B169" t="n">
-        <v>74901</v>
+        <v>78194</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -17890,21 +17895,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17914,10 +17919,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>380314</v>
+        <v>380197</v>
       </c>
       <c r="R169" t="n">
-        <v>6920201</v>
+        <v>6920479</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17976,7 +17981,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>124461736</v>
+        <v>124455456</v>
       </c>
       <c r="B170" t="n">
         <v>74901</v>
@@ -18012,14 +18017,14 @@
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>380232</v>
+        <v>380314</v>
       </c>
       <c r="R170" t="n">
-        <v>6919808</v>
+        <v>6920201</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18078,10 +18083,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>124461646</v>
+        <v>124458282</v>
       </c>
       <c r="B171" t="n">
-        <v>57513</v>
+        <v>78151</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18090,46 +18095,41 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P171" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>380239</v>
+        <v>380588</v>
       </c>
       <c r="R171" t="n">
-        <v>6919828</v>
+        <v>6920110</v>
       </c>
       <c r="S171" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -18185,10 +18185,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>124458282</v>
+        <v>124461646</v>
       </c>
       <c r="B172" t="n">
-        <v>78151</v>
+        <v>57513</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18197,41 +18197,46 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>498</v>
+        <v>100109</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P172" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>380588</v>
+        <v>380239</v>
       </c>
       <c r="R172" t="n">
-        <v>6920110</v>
+        <v>6919828</v>
       </c>
       <c r="S172" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -18389,10 +18394,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>124454979</v>
+        <v>124461736</v>
       </c>
       <c r="B174" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18405,34 +18410,34 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>380289</v>
+        <v>380232</v>
       </c>
       <c r="R174" t="n">
-        <v>6920290</v>
+        <v>6919808</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18467,11 +18472,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
-        </is>
-      </c>
       <c r="AD174" t="b">
         <v>0</v>
       </c>
@@ -18484,12 +18484,12 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
@@ -19531,7 +19531,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124469377</v>
+        <v>124451172</v>
       </c>
       <c r="B185" t="n">
         <v>74901</v>
@@ -19567,14 +19567,14 @@
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>380435</v>
+        <v>380184</v>
       </c>
       <c r="R185" t="n">
-        <v>6919916</v>
+        <v>6920434</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19633,7 +19633,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124458046</v>
+        <v>124469377</v>
       </c>
       <c r="B186" t="n">
         <v>74901</v>
@@ -19669,14 +19669,14 @@
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>380533</v>
+        <v>380435</v>
       </c>
       <c r="R186" t="n">
-        <v>6920142</v>
+        <v>6919916</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19735,10 +19735,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124464329</v>
+        <v>124458046</v>
       </c>
       <c r="B187" t="n">
-        <v>78194</v>
+        <v>74901</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -19751,21 +19751,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19775,10 +19775,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>380268</v>
+        <v>380533</v>
       </c>
       <c r="R187" t="n">
-        <v>6919685</v>
+        <v>6920142</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19837,10 +19837,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124464493</v>
+        <v>124470732</v>
       </c>
       <c r="B188" t="n">
-        <v>79399</v>
+        <v>74901</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -19853,34 +19853,34 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>380243</v>
+        <v>380372</v>
       </c>
       <c r="R188" t="n">
-        <v>6919687</v>
+        <v>6920042</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19939,10 +19939,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124451172</v>
+        <v>124464329</v>
       </c>
       <c r="B189" t="n">
-        <v>74901</v>
+        <v>78194</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -19955,34 +19955,34 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>380184</v>
+        <v>380268</v>
       </c>
       <c r="R189" t="n">
-        <v>6920434</v>
+        <v>6919685</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20041,10 +20041,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>124460052</v>
+        <v>124464493</v>
       </c>
       <c r="B190" t="n">
-        <v>57513</v>
+        <v>79399</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20057,39 +20057,34 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>380419</v>
+        <v>380243</v>
       </c>
       <c r="R190" t="n">
-        <v>6919960</v>
+        <v>6919687</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20136,22 +20131,22 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>124470732</v>
+        <v>124460052</v>
       </c>
       <c r="B191" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20164,34 +20159,39 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P191" t="inlineStr">
         <is>
           <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>380372</v>
+        <v>380419</v>
       </c>
       <c r="R191" t="n">
-        <v>6920042</v>
+        <v>6919960</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20238,12 +20238,12 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
@@ -21178,10 +21178,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>124459134</v>
+        <v>124469088</v>
       </c>
       <c r="B201" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -21194,34 +21194,34 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>380559</v>
+        <v>380352</v>
       </c>
       <c r="R201" t="n">
-        <v>6919947</v>
+        <v>6919913</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21280,10 +21280,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>124469088</v>
+        <v>124459134</v>
       </c>
       <c r="B202" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -21296,34 +21296,34 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>380352</v>
+        <v>380559</v>
       </c>
       <c r="R202" t="n">
-        <v>6919913</v>
+        <v>6919947</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22208,10 +22208,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>124465009</v>
+        <v>124460965</v>
       </c>
       <c r="B211" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -22224,34 +22224,34 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>380267</v>
+        <v>380307</v>
       </c>
       <c r="R211" t="n">
-        <v>6919764</v>
+        <v>6919967</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22286,11 +22286,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC211" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD211" t="b">
         <v>0</v>
       </c>
@@ -22303,22 +22298,22 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>124456046</v>
+        <v>124465009</v>
       </c>
       <c r="B212" t="n">
-        <v>91032</v>
+        <v>79399</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -22331,34 +22326,34 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>5442</v>
+        <v>229821</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>380326</v>
+        <v>380267</v>
       </c>
       <c r="R212" t="n">
-        <v>6920218</v>
+        <v>6919764</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22395,7 +22390,7 @@
       </c>
       <c r="AC212" t="inlineStr">
         <is>
-          <t>Miljöbilder för området.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -22626,10 +22621,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>124458172</v>
+        <v>124456046</v>
       </c>
       <c r="B215" t="n">
-        <v>78151</v>
+        <v>91032</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -22638,38 +22633,38 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>498</v>
+        <v>5442</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>380562</v>
+        <v>380326</v>
       </c>
       <c r="R215" t="n">
-        <v>6920118</v>
+        <v>6920218</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22704,6 +22699,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC215" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området.</t>
+        </is>
+      </c>
       <c r="AD215" t="b">
         <v>0</v>
       </c>
@@ -22716,22 +22716,22 @@
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>124463640</v>
+        <v>124458172</v>
       </c>
       <c r="B216" t="n">
-        <v>79428</v>
+        <v>78151</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -22740,25 +22740,25 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>6453</v>
+        <v>498</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -22768,10 +22768,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>380218</v>
+        <v>380562</v>
       </c>
       <c r="R216" t="n">
-        <v>6919722</v>
+        <v>6920118</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22830,10 +22830,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>124460965</v>
+        <v>124463640</v>
       </c>
       <c r="B217" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -22846,34 +22846,34 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>380307</v>
+        <v>380218</v>
       </c>
       <c r="R217" t="n">
-        <v>6919967</v>
+        <v>6919722</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -23039,10 +23039,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>124455022</v>
+        <v>124464559</v>
       </c>
       <c r="B219" t="n">
-        <v>79428</v>
+        <v>79399</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -23055,34 +23055,34 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>380292</v>
+        <v>380236</v>
       </c>
       <c r="R219" t="n">
-        <v>6920288</v>
+        <v>6919671</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23141,10 +23141,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>124464559</v>
+        <v>124463210</v>
       </c>
       <c r="B220" t="n">
-        <v>79399</v>
+        <v>79428</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -23157,21 +23157,21 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -23181,10 +23181,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>380236</v>
+        <v>380189</v>
       </c>
       <c r="R220" t="n">
-        <v>6919671</v>
+        <v>6919766</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23457,7 +23457,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>124463210</v>
+        <v>124455022</v>
       </c>
       <c r="B223" t="n">
         <v>79428</v>
@@ -23493,14 +23493,14 @@
       <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>380189</v>
+        <v>380292</v>
       </c>
       <c r="R223" t="n">
-        <v>6919766</v>
+        <v>6920288</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -27694,10 +27694,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>124467914</v>
+        <v>124460951</v>
       </c>
       <c r="B264" t="n">
-        <v>77738</v>
+        <v>74901</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -27710,34 +27710,34 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>6487</v>
+        <v>6440</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>380361</v>
+        <v>380307</v>
       </c>
       <c r="R264" t="n">
-        <v>6919740</v>
+        <v>6919967</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27772,11 +27772,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC264" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD264" t="b">
         <v>0</v>
       </c>
@@ -27789,22 +27784,22 @@
       <c r="AT264" t="inlineStr"/>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>124465526</v>
+        <v>124459287</v>
       </c>
       <c r="B265" t="n">
-        <v>79399</v>
+        <v>57513</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -27817,34 +27812,39 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P265" t="inlineStr">
         <is>
-          <t>Risåsvallen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>380252</v>
+        <v>380561</v>
       </c>
       <c r="R265" t="n">
-        <v>6919535</v>
+        <v>6919930</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27891,22 +27891,22 @@
       <c r="AT265" t="inlineStr"/>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>124460951</v>
+        <v>124458651</v>
       </c>
       <c r="B266" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -27919,34 +27919,34 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>380307</v>
+        <v>380569</v>
       </c>
       <c r="R266" t="n">
-        <v>6919967</v>
+        <v>6920058</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -28005,10 +28005,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>124470299</v>
+        <v>124464651</v>
       </c>
       <c r="B267" t="n">
-        <v>56722</v>
+        <v>79399</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -28017,43 +28017,38 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
-      <c r="M267" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P267" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>380495</v>
+        <v>380251</v>
       </c>
       <c r="R267" t="n">
-        <v>6920029</v>
+        <v>6919658</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -28112,10 +28107,10 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>124459287</v>
+        <v>124470299</v>
       </c>
       <c r="B268" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -28124,43 +28119,43 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
       <c r="M268" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P268" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>380561</v>
+        <v>380495</v>
       </c>
       <c r="R268" t="n">
-        <v>6919930</v>
+        <v>6920029</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -28207,22 +28202,22 @@
       <c r="AT268" t="inlineStr"/>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>124458651</v>
+        <v>124467914</v>
       </c>
       <c r="B269" t="n">
-        <v>91030</v>
+        <v>77738</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -28235,21 +28230,21 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>5432</v>
+        <v>6487</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
@@ -28259,10 +28254,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>380569</v>
+        <v>380361</v>
       </c>
       <c r="R269" t="n">
-        <v>6920058</v>
+        <v>6919740</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -28297,6 +28292,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC269" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD269" t="b">
         <v>0</v>
       </c>
@@ -28309,19 +28309,19 @@
       <c r="AT269" t="inlineStr"/>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>124464651</v>
+        <v>124465526</v>
       </c>
       <c r="B270" t="n">
         <v>79399</v>
@@ -28357,14 +28357,14 @@
       <c r="I270" t="inlineStr"/>
       <c r="P270" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>380251</v>
+        <v>380252</v>
       </c>
       <c r="R270" t="n">
-        <v>6919658</v>
+        <v>6919535</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -28423,10 +28423,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>124466026</v>
+        <v>124464970</v>
       </c>
       <c r="B271" t="n">
-        <v>79399</v>
+        <v>57513</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -28439,37 +28439,42 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P271" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>380303</v>
+        <v>380255</v>
       </c>
       <c r="R271" t="n">
-        <v>6919598</v>
+        <v>6919561</v>
       </c>
       <c r="S271" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T271" t="inlineStr">
         <is>
@@ -28499,11 +28504,6 @@
       <c r="AA271" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC271" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -28518,22 +28518,22 @@
       <c r="AT271" t="inlineStr"/>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>124464970</v>
+        <v>124466026</v>
       </c>
       <c r="B272" t="n">
-        <v>57513</v>
+        <v>79399</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -28546,42 +28546,37 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
-      <c r="M272" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P272" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>380255</v>
+        <v>380303</v>
       </c>
       <c r="R272" t="n">
-        <v>6919561</v>
+        <v>6919598</v>
       </c>
       <c r="S272" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T272" t="inlineStr">
         <is>
@@ -28611,6 +28606,11 @@
       <c r="AA272" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC272" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -28625,12 +28625,12 @@
       <c r="AT272" t="inlineStr"/>
       <c r="AW272" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>

--- a/artfynd/A 32573-2024 artfynd.xlsx
+++ b/artfynd/A 32573-2024 artfynd.xlsx
@@ -16105,10 +16105,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>124470742</v>
+        <v>124469751</v>
       </c>
       <c r="B152" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16121,42 +16121,37 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>380369</v>
+        <v>380490</v>
       </c>
       <c r="R152" t="n">
-        <v>6920032</v>
+        <v>6919937</v>
       </c>
       <c r="S152" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16212,10 +16207,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>124456129</v>
+        <v>124455096</v>
       </c>
       <c r="B153" t="n">
-        <v>78905</v>
+        <v>5196</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16224,38 +16219,43 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>967</v>
+        <v>105930</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>380326</v>
+        <v>380323</v>
       </c>
       <c r="R153" t="n">
-        <v>6920218</v>
+        <v>6920260</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16302,22 +16302,22 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>124464471</v>
+        <v>124470299</v>
       </c>
       <c r="B154" t="n">
-        <v>78194</v>
+        <v>56722</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16326,38 +16326,43 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6437</v>
+        <v>100138</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>380243</v>
+        <v>380495</v>
       </c>
       <c r="R154" t="n">
-        <v>6919687</v>
+        <v>6920029</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16416,10 +16421,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>124467947</v>
+        <v>124470707</v>
       </c>
       <c r="B155" t="n">
-        <v>78194</v>
+        <v>57513</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16432,37 +16437,42 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>380361</v>
+        <v>380367</v>
       </c>
       <c r="R155" t="n">
-        <v>6919740</v>
+        <v>6920058</v>
       </c>
       <c r="S155" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16492,11 +16502,6 @@
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16511,22 +16516,22 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>124452491</v>
+        <v>124463365</v>
       </c>
       <c r="B156" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16539,34 +16544,34 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>380208</v>
+        <v>380199</v>
       </c>
       <c r="R156" t="n">
-        <v>6920481</v>
+        <v>6919723</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16625,10 +16630,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>124455774</v>
+        <v>124464559</v>
       </c>
       <c r="B157" t="n">
-        <v>74901</v>
+        <v>79399</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16641,34 +16646,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>380356</v>
+        <v>380236</v>
       </c>
       <c r="R157" t="n">
-        <v>6920172</v>
+        <v>6919671</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16727,10 +16732,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>124468916</v>
+        <v>124456046</v>
       </c>
       <c r="B158" t="n">
-        <v>78151</v>
+        <v>91032</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16739,25 +16744,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>498</v>
+        <v>5442</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16767,10 +16772,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>380343</v>
+        <v>380326</v>
       </c>
       <c r="R158" t="n">
-        <v>6919896</v>
+        <v>6920218</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16805,6 +16810,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området.</t>
+        </is>
+      </c>
       <c r="AD158" t="b">
         <v>0</v>
       </c>
@@ -16817,19 +16827,19 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>124464047</v>
+        <v>124469907</v>
       </c>
       <c r="B159" t="n">
         <v>78810</v>
@@ -16865,14 +16875,14 @@
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>380267</v>
+        <v>380452</v>
       </c>
       <c r="R159" t="n">
-        <v>6919731</v>
+        <v>6919913</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16919,19 +16929,19 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>124459060</v>
+        <v>124464292</v>
       </c>
       <c r="B160" t="n">
         <v>57513</v>
@@ -16967,7 +16977,7 @@
       <c r="I160" t="inlineStr"/>
       <c r="M160" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -16976,10 +16986,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>380571</v>
+        <v>380275</v>
       </c>
       <c r="R160" t="n">
-        <v>6919993</v>
+        <v>6919775</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17026,19 +17036,19 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>124470184</v>
+        <v>124456697</v>
       </c>
       <c r="B161" t="n">
         <v>91030</v>
@@ -17078,10 +17088,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>380516</v>
+        <v>380443</v>
       </c>
       <c r="R161" t="n">
-        <v>6920004</v>
+        <v>6920118</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17140,10 +17150,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>124470146</v>
+        <v>124450737</v>
       </c>
       <c r="B162" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17156,42 +17166,37 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>380527</v>
+        <v>380210</v>
       </c>
       <c r="R162" t="n">
-        <v>6919988</v>
+        <v>6920378</v>
       </c>
       <c r="S162" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -17247,10 +17252,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>124461108</v>
+        <v>124463640</v>
       </c>
       <c r="B163" t="n">
-        <v>74901</v>
+        <v>79428</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17263,34 +17268,34 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>380308</v>
+        <v>380218</v>
       </c>
       <c r="R163" t="n">
-        <v>6919925</v>
+        <v>6919722</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17323,11 +17328,6 @@
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>På basen avsågad gran. Grov stubbe</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17354,10 +17354,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>124450902</v>
+        <v>124470737</v>
       </c>
       <c r="B164" t="n">
-        <v>57529</v>
+        <v>91030</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17370,39 +17370,34 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>380227</v>
+        <v>380506</v>
       </c>
       <c r="R164" t="n">
-        <v>6920340</v>
+        <v>6920061</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17435,11 +17430,6 @@
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>Troligen spillkråka.</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17466,10 +17456,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>124454876</v>
+        <v>124464901</v>
       </c>
       <c r="B165" t="n">
-        <v>74901</v>
+        <v>79399</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17482,34 +17472,34 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>380290</v>
+        <v>380249</v>
       </c>
       <c r="R165" t="n">
-        <v>6920272</v>
+        <v>6919607</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17568,10 +17558,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>124468547</v>
+        <v>124461477</v>
       </c>
       <c r="B166" t="n">
-        <v>74901</v>
+        <v>79399</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17584,34 +17574,34 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>380356</v>
+        <v>380285</v>
       </c>
       <c r="R166" t="n">
-        <v>6919817</v>
+        <v>6919895</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17670,10 +17660,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>124457836</v>
+        <v>124455456</v>
       </c>
       <c r="B167" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17686,21 +17676,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17710,10 +17700,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>380542</v>
+        <v>380314</v>
       </c>
       <c r="R167" t="n">
-        <v>6920184</v>
+        <v>6920201</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17760,22 +17750,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>124454979</v>
+        <v>124454876</v>
       </c>
       <c r="B168" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -17788,21 +17778,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17812,10 +17802,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>380289</v>
+        <v>380290</v>
       </c>
       <c r="R168" t="n">
-        <v>6920290</v>
+        <v>6920272</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17850,11 +17840,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
-        </is>
-      </c>
       <c r="AD168" t="b">
         <v>0</v>
       </c>
@@ -17867,22 +17852,22 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>124451837</v>
+        <v>124470598</v>
       </c>
       <c r="B169" t="n">
-        <v>78194</v>
+        <v>79428</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -17895,34 +17880,34 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>380197</v>
+        <v>380506</v>
       </c>
       <c r="R169" t="n">
-        <v>6920479</v>
+        <v>6920061</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17957,6 +17942,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD169" t="b">
         <v>0</v>
       </c>
@@ -17969,19 +17959,19 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>124455456</v>
+        <v>124470732</v>
       </c>
       <c r="B170" t="n">
         <v>74901</v>
@@ -18017,14 +18007,14 @@
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>380314</v>
+        <v>380372</v>
       </c>
       <c r="R170" t="n">
-        <v>6920201</v>
+        <v>6920042</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18083,7 +18073,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>124458282</v>
+        <v>124468916</v>
       </c>
       <c r="B171" t="n">
         <v>78151</v>
@@ -18119,14 +18109,14 @@
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>380588</v>
+        <v>380343</v>
       </c>
       <c r="R171" t="n">
-        <v>6920110</v>
+        <v>6919896</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18185,7 +18175,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>124461646</v>
+        <v>124456676</v>
       </c>
       <c r="B172" t="n">
         <v>57513</v>
@@ -18230,10 +18220,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>380239</v>
+        <v>380434</v>
       </c>
       <c r="R172" t="n">
-        <v>6919828</v>
+        <v>6920123</v>
       </c>
       <c r="S172" t="n">
         <v>15</v>
@@ -18292,10 +18282,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>124470234</v>
+        <v>124464681</v>
       </c>
       <c r="B173" t="n">
-        <v>82597</v>
+        <v>79399</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18308,21 +18298,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1312</v>
+        <v>229821</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18332,10 +18322,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>380506</v>
+        <v>380264</v>
       </c>
       <c r="R173" t="n">
-        <v>6920009</v>
+        <v>6919665</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18394,10 +18384,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>124461736</v>
+        <v>124465009</v>
       </c>
       <c r="B174" t="n">
-        <v>74901</v>
+        <v>79399</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18410,21 +18400,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18434,10 +18424,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>380232</v>
+        <v>380267</v>
       </c>
       <c r="R174" t="n">
-        <v>6919808</v>
+        <v>6919764</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18472,6 +18462,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD174" t="b">
         <v>0</v>
       </c>
@@ -18484,22 +18479,22 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>124450666</v>
+        <v>124451885</v>
       </c>
       <c r="B175" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -18512,21 +18507,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18536,10 +18531,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>380227</v>
+        <v>380189</v>
       </c>
       <c r="R175" t="n">
-        <v>6920340</v>
+        <v>6920488</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18586,22 +18581,22 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>124468182</v>
+        <v>124460951</v>
       </c>
       <c r="B176" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -18614,42 +18609,37 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>380265</v>
+        <v>380307</v>
       </c>
       <c r="R176" t="n">
-        <v>6919774</v>
+        <v>6919967</v>
       </c>
       <c r="S176" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -18705,10 +18695,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>124456832</v>
+        <v>124469088</v>
       </c>
       <c r="B177" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -18721,34 +18711,34 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>380443</v>
+        <v>380352</v>
       </c>
       <c r="R177" t="n">
-        <v>6920118</v>
+        <v>6919913</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18807,10 +18797,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>124458743</v>
+        <v>124450666</v>
       </c>
       <c r="B178" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -18823,21 +18813,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18847,10 +18837,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>380542</v>
+        <v>380227</v>
       </c>
       <c r="R178" t="n">
-        <v>6920184</v>
+        <v>6920340</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18883,11 +18873,6 @@
       <c r="AA178" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -18914,10 +18899,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>124455206</v>
+        <v>124454665</v>
       </c>
       <c r="B179" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -18930,34 +18915,34 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>380311</v>
+        <v>380258</v>
       </c>
       <c r="R179" t="n">
-        <v>6920231</v>
+        <v>6920309</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19016,10 +19001,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>124450845</v>
+        <v>124455774</v>
       </c>
       <c r="B180" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -19032,34 +19017,34 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>380205</v>
+        <v>380356</v>
       </c>
       <c r="R180" t="n">
-        <v>6920378</v>
+        <v>6920172</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19118,7 +19103,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>124464842</v>
+        <v>124460258</v>
       </c>
       <c r="B181" t="n">
         <v>79428</v>
@@ -19154,14 +19139,14 @@
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>380237</v>
+        <v>380365</v>
       </c>
       <c r="R181" t="n">
-        <v>6919621</v>
+        <v>6919996</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19220,10 +19205,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124450300</v>
+        <v>124451802</v>
       </c>
       <c r="B182" t="n">
-        <v>74901</v>
+        <v>79428</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -19236,34 +19221,34 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>380182</v>
+        <v>380197</v>
       </c>
       <c r="R182" t="n">
-        <v>6920316</v>
+        <v>6920479</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19322,10 +19307,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124460258</v>
+        <v>124464493</v>
       </c>
       <c r="B183" t="n">
-        <v>79428</v>
+        <v>79399</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -19338,34 +19323,34 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>380365</v>
+        <v>380243</v>
       </c>
       <c r="R183" t="n">
-        <v>6919996</v>
+        <v>6919687</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19424,10 +19409,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124451326</v>
+        <v>124456129</v>
       </c>
       <c r="B184" t="n">
-        <v>57513</v>
+        <v>78905</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -19440,39 +19425,34 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>100109</v>
+        <v>967</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P184" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>380227</v>
+        <v>380326</v>
       </c>
       <c r="R184" t="n">
-        <v>6920340</v>
+        <v>6920218</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19531,10 +19511,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124451172</v>
+        <v>124460611</v>
       </c>
       <c r="B185" t="n">
-        <v>74901</v>
+        <v>78905</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -19547,34 +19527,34 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6440</v>
+        <v>967</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>380184</v>
+        <v>380335</v>
       </c>
       <c r="R185" t="n">
-        <v>6920434</v>
+        <v>6920000</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19621,22 +19601,22 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124469377</v>
+        <v>124451326</v>
       </c>
       <c r="B186" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -19649,34 +19629,39 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>380435</v>
+        <v>380227</v>
       </c>
       <c r="R186" t="n">
-        <v>6919916</v>
+        <v>6920340</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19723,19 +19708,19 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124458046</v>
+        <v>124459042</v>
       </c>
       <c r="B187" t="n">
         <v>74901</v>
@@ -19775,10 +19760,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>380533</v>
+        <v>380571</v>
       </c>
       <c r="R187" t="n">
-        <v>6920142</v>
+        <v>6919993</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19837,10 +19822,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124470732</v>
+        <v>124465167</v>
       </c>
       <c r="B188" t="n">
-        <v>74901</v>
+        <v>78194</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -19853,34 +19838,34 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>380372</v>
+        <v>380244</v>
       </c>
       <c r="R188" t="n">
-        <v>6920042</v>
+        <v>6919577</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19927,22 +19912,22 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124464329</v>
+        <v>124456372</v>
       </c>
       <c r="B189" t="n">
-        <v>78194</v>
+        <v>74901</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -19955,34 +19940,34 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>380268</v>
+        <v>380368</v>
       </c>
       <c r="R189" t="n">
-        <v>6919685</v>
+        <v>6920107</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20041,10 +20026,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>124464493</v>
+        <v>124468547</v>
       </c>
       <c r="B190" t="n">
-        <v>79399</v>
+        <v>74901</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20057,34 +20042,34 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>380243</v>
+        <v>380356</v>
       </c>
       <c r="R190" t="n">
-        <v>6919687</v>
+        <v>6919817</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20143,10 +20128,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>124460052</v>
+        <v>124464842</v>
       </c>
       <c r="B191" t="n">
-        <v>57513</v>
+        <v>79428</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20159,39 +20144,34 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>380419</v>
+        <v>380237</v>
       </c>
       <c r="R191" t="n">
-        <v>6919960</v>
+        <v>6919621</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20238,22 +20218,22 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>124455453</v>
+        <v>124470070</v>
       </c>
       <c r="B192" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20266,34 +20246,34 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>380326</v>
+        <v>380533</v>
       </c>
       <c r="R192" t="n">
-        <v>6920218</v>
+        <v>6919979</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20340,22 +20320,22 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>124451569</v>
+        <v>124470806</v>
       </c>
       <c r="B193" t="n">
-        <v>79399</v>
+        <v>57513</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -20368,37 +20348,42 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>380184</v>
+        <v>380340</v>
       </c>
       <c r="R193" t="n">
-        <v>6920434</v>
+        <v>6920036</v>
       </c>
       <c r="S193" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -20454,10 +20439,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>124459456</v>
+        <v>124469547</v>
       </c>
       <c r="B194" t="n">
-        <v>91032</v>
+        <v>88359</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -20470,21 +20455,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>5442</v>
+        <v>510</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20494,10 +20479,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>380561</v>
+        <v>380452</v>
       </c>
       <c r="R194" t="n">
-        <v>6919930</v>
+        <v>6919913</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20556,10 +20541,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>124451885</v>
+        <v>124451569</v>
       </c>
       <c r="B195" t="n">
-        <v>91030</v>
+        <v>79399</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -20572,21 +20557,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>5432</v>
+        <v>229821</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20596,10 +20581,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>380189</v>
+        <v>380184</v>
       </c>
       <c r="R195" t="n">
-        <v>6920488</v>
+        <v>6920434</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20658,10 +20643,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>124470646</v>
+        <v>124464047</v>
       </c>
       <c r="B196" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -20674,34 +20659,34 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>380402</v>
+        <v>380267</v>
       </c>
       <c r="R196" t="n">
-        <v>6920044</v>
+        <v>6919731</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20760,10 +20745,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>124465167</v>
+        <v>124450845</v>
       </c>
       <c r="B197" t="n">
-        <v>78194</v>
+        <v>78810</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -20776,21 +20761,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20800,10 +20785,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>380244</v>
+        <v>380205</v>
       </c>
       <c r="R197" t="n">
-        <v>6919577</v>
+        <v>6920378</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20850,22 +20835,22 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>124470695</v>
+        <v>124459048</v>
       </c>
       <c r="B198" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -20878,34 +20863,39 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>380506</v>
+        <v>380542</v>
       </c>
       <c r="R198" t="n">
-        <v>6920061</v>
+        <v>6920184</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20938,11 +20928,6 @@
       <c r="AA198" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC198" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -20969,10 +20954,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>124458357</v>
+        <v>124451172</v>
       </c>
       <c r="B199" t="n">
-        <v>57666</v>
+        <v>74901</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -20985,42 +20970,37 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>380586</v>
+        <v>380184</v>
       </c>
       <c r="R199" t="n">
-        <v>6920100</v>
+        <v>6920434</v>
       </c>
       <c r="S199" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -21076,10 +21056,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>124451574</v>
+        <v>124450300</v>
       </c>
       <c r="B200" t="n">
-        <v>79428</v>
+        <v>74901</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -21092,34 +21072,34 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>380184</v>
+        <v>380182</v>
       </c>
       <c r="R200" t="n">
-        <v>6920434</v>
+        <v>6920316</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21178,10 +21158,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>124469088</v>
+        <v>124455206</v>
       </c>
       <c r="B201" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -21194,34 +21174,34 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>380352</v>
+        <v>380311</v>
       </c>
       <c r="R201" t="n">
-        <v>6919913</v>
+        <v>6920231</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21280,7 +21260,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>124459134</v>
+        <v>124455453</v>
       </c>
       <c r="B202" t="n">
         <v>74901</v>
@@ -21316,14 +21296,14 @@
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>380559</v>
+        <v>380326</v>
       </c>
       <c r="R202" t="n">
-        <v>6919947</v>
+        <v>6920218</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21370,22 +21350,22 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>124464321</v>
+        <v>124451574</v>
       </c>
       <c r="B203" t="n">
-        <v>77738</v>
+        <v>79428</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -21398,34 +21378,34 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>380268</v>
+        <v>380184</v>
       </c>
       <c r="R203" t="n">
-        <v>6919685</v>
+        <v>6920434</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21484,10 +21464,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>124464901</v>
+        <v>124455022</v>
       </c>
       <c r="B204" t="n">
-        <v>79399</v>
+        <v>79428</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -21500,34 +21480,34 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>380249</v>
+        <v>380292</v>
       </c>
       <c r="R204" t="n">
-        <v>6919607</v>
+        <v>6920288</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21586,10 +21566,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>124469907</v>
+        <v>124459060</v>
       </c>
       <c r="B205" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -21602,34 +21582,39 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>380452</v>
+        <v>380571</v>
       </c>
       <c r="R205" t="n">
-        <v>6919913</v>
+        <v>6919993</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21676,22 +21661,22 @@
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>124466494</v>
+        <v>124470234</v>
       </c>
       <c r="B206" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -21704,42 +21689,37 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
-      <c r="M206" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>380344</v>
+        <v>380506</v>
       </c>
       <c r="R206" t="n">
-        <v>6919654</v>
+        <v>6920009</v>
       </c>
       <c r="S206" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -21795,7 +21775,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>124468469</v>
+        <v>124461646</v>
       </c>
       <c r="B207" t="n">
         <v>57513</v>
@@ -21840,10 +21820,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>380324</v>
+        <v>380239</v>
       </c>
       <c r="R207" t="n">
-        <v>6919803</v>
+        <v>6919828</v>
       </c>
       <c r="S207" t="n">
         <v>15</v>
@@ -21902,10 +21882,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>124451893</v>
+        <v>124470742</v>
       </c>
       <c r="B208" t="n">
-        <v>5196</v>
+        <v>57513</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -21914,20 +21894,20 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>105930</v>
+        <v>100109</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -21936,19 +21916,24 @@
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>380227</v>
+        <v>380369</v>
       </c>
       <c r="R208" t="n">
-        <v>6920340</v>
+        <v>6920032</v>
       </c>
       <c r="S208" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -21992,22 +21977,22 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>124459815</v>
+        <v>124460224</v>
       </c>
       <c r="B209" t="n">
-        <v>79428</v>
+        <v>57513</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -22020,34 +22005,39 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>380445</v>
+        <v>380374</v>
       </c>
       <c r="R209" t="n">
-        <v>6919917</v>
+        <v>6919982</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -22094,19 +22084,19 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>124451984</v>
+        <v>124466026</v>
       </c>
       <c r="B210" t="n">
         <v>79399</v>
@@ -22142,14 +22132,14 @@
       <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>380203</v>
+        <v>380303</v>
       </c>
       <c r="R210" t="n">
-        <v>6920482</v>
+        <v>6919598</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22184,6 +22174,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD210" t="b">
         <v>0</v>
       </c>
@@ -22196,22 +22191,22 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>124460965</v>
+        <v>124450578</v>
       </c>
       <c r="B211" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -22224,34 +22219,34 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>380307</v>
+        <v>380227</v>
       </c>
       <c r="R211" t="n">
-        <v>6919967</v>
+        <v>6920340</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22298,22 +22293,22 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>124465009</v>
+        <v>124464329</v>
       </c>
       <c r="B212" t="n">
-        <v>79399</v>
+        <v>78194</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -22326,21 +22321,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -22350,10 +22345,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>380267</v>
+        <v>380268</v>
       </c>
       <c r="R212" t="n">
-        <v>6919764</v>
+        <v>6919685</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22388,11 +22383,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC212" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD212" t="b">
         <v>0</v>
       </c>
@@ -22405,22 +22395,22 @@
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>124459042</v>
+        <v>124458172</v>
       </c>
       <c r="B213" t="n">
-        <v>74901</v>
+        <v>78151</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -22429,25 +22419,25 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6440</v>
+        <v>498</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -22457,10 +22447,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>380571</v>
+        <v>380562</v>
       </c>
       <c r="R213" t="n">
-        <v>6919993</v>
+        <v>6920118</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22519,10 +22509,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>124458476</v>
+        <v>124465389</v>
       </c>
       <c r="B214" t="n">
-        <v>74901</v>
+        <v>79399</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -22535,21 +22525,21 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -22559,10 +22549,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>380581</v>
+        <v>380244</v>
       </c>
       <c r="R214" t="n">
-        <v>6920056</v>
+        <v>6919577</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22609,22 +22599,22 @@
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>124456046</v>
+        <v>124460965</v>
       </c>
       <c r="B215" t="n">
-        <v>91032</v>
+        <v>78810</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -22637,34 +22627,34 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>380326</v>
+        <v>380307</v>
       </c>
       <c r="R215" t="n">
-        <v>6920218</v>
+        <v>6919967</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22699,11 +22689,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC215" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området.</t>
-        </is>
-      </c>
       <c r="AD215" t="b">
         <v>0</v>
       </c>
@@ -22716,22 +22701,22 @@
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>124458172</v>
+        <v>124455220</v>
       </c>
       <c r="B216" t="n">
-        <v>78151</v>
+        <v>74901</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -22740,38 +22725,38 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>498</v>
+        <v>6440</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>380562</v>
+        <v>380311</v>
       </c>
       <c r="R216" t="n">
-        <v>6920118</v>
+        <v>6920231</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22830,10 +22815,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>124463640</v>
+        <v>124469915</v>
       </c>
       <c r="B217" t="n">
-        <v>79428</v>
+        <v>74901</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -22846,21 +22831,21 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -22870,10 +22855,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>380218</v>
+        <v>380521</v>
       </c>
       <c r="R217" t="n">
-        <v>6919722</v>
+        <v>6919962</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22932,10 +22917,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>124460224</v>
+        <v>124463210</v>
       </c>
       <c r="B218" t="n">
-        <v>57513</v>
+        <v>79428</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -22948,39 +22933,34 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
-      <c r="M218" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>380374</v>
+        <v>380189</v>
       </c>
       <c r="R218" t="n">
-        <v>6919982</v>
+        <v>6919766</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23027,22 +23007,22 @@
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>124464559</v>
+        <v>124455776</v>
       </c>
       <c r="B219" t="n">
-        <v>79399</v>
+        <v>57513</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -23055,34 +23035,39 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>380236</v>
+        <v>380326</v>
       </c>
       <c r="R219" t="n">
-        <v>6919671</v>
+        <v>6920218</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23129,22 +23114,22 @@
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>124463210</v>
+        <v>124471016</v>
       </c>
       <c r="B220" t="n">
-        <v>79428</v>
+        <v>57513</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -23157,34 +23142,39 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>380189</v>
+        <v>380506</v>
       </c>
       <c r="R220" t="n">
-        <v>6919766</v>
+        <v>6920061</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23231,22 +23221,22 @@
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>124455776</v>
+        <v>124452423</v>
       </c>
       <c r="B221" t="n">
-        <v>57513</v>
+        <v>56725</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -23255,20 +23245,20 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>100109</v>
+        <v>102613</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -23279,7 +23269,7 @@
       <c r="I221" t="inlineStr"/>
       <c r="M221" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
@@ -23288,10 +23278,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>380326</v>
+        <v>380227</v>
       </c>
       <c r="R221" t="n">
-        <v>6920218</v>
+        <v>6920340</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23350,7 +23340,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>124456704</v>
+        <v>124470646</v>
       </c>
       <c r="B222" t="n">
         <v>91030</v>
@@ -23386,14 +23376,14 @@
       <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>380385</v>
+        <v>380402</v>
       </c>
       <c r="R222" t="n">
-        <v>6920091</v>
+        <v>6920044</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23428,11 +23418,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC222" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
-        </is>
-      </c>
       <c r="AD222" t="b">
         <v>0</v>
       </c>
@@ -23445,22 +23430,22 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>124455022</v>
+        <v>124456704</v>
       </c>
       <c r="B223" t="n">
-        <v>79428</v>
+        <v>91030</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -23473,21 +23458,21 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -23497,10 +23482,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>380292</v>
+        <v>380385</v>
       </c>
       <c r="R223" t="n">
-        <v>6920288</v>
+        <v>6920091</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23535,6 +23520,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD223" t="b">
         <v>0</v>
       </c>
@@ -23547,22 +23537,22 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>124470404</v>
+        <v>124457317</v>
       </c>
       <c r="B224" t="n">
-        <v>91030</v>
+        <v>79428</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -23575,21 +23565,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -23599,10 +23589,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>380471</v>
+        <v>380547</v>
       </c>
       <c r="R224" t="n">
-        <v>6920069</v>
+        <v>6920163</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23661,10 +23651,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>124457601</v>
+        <v>124470485</v>
       </c>
       <c r="B225" t="n">
-        <v>78151</v>
+        <v>74901</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -23673,25 +23663,25 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>498</v>
+        <v>6440</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -23701,10 +23691,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>380544</v>
+        <v>380446</v>
       </c>
       <c r="R225" t="n">
-        <v>6920188</v>
+        <v>6920059</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23763,10 +23753,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>124454665</v>
+        <v>124467947</v>
       </c>
       <c r="B226" t="n">
-        <v>74901</v>
+        <v>78194</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -23779,21 +23769,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -23803,10 +23793,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>380258</v>
+        <v>380361</v>
       </c>
       <c r="R226" t="n">
-        <v>6920309</v>
+        <v>6919740</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23841,6 +23831,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD226" t="b">
         <v>0</v>
       </c>
@@ -23853,22 +23848,22 @@
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>124470485</v>
+        <v>124458282</v>
       </c>
       <c r="B227" t="n">
-        <v>74901</v>
+        <v>78151</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -23877,25 +23872,25 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6440</v>
+        <v>498</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -23905,10 +23900,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>380446</v>
+        <v>380588</v>
       </c>
       <c r="R227" t="n">
-        <v>6920059</v>
+        <v>6920110</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23967,10 +23962,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>124457317</v>
+        <v>124468302</v>
       </c>
       <c r="B228" t="n">
-        <v>79428</v>
+        <v>57513</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -23983,37 +23978,42 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>380547</v>
+        <v>380265</v>
       </c>
       <c r="R228" t="n">
-        <v>6920163</v>
+        <v>6919774</v>
       </c>
       <c r="S228" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -24069,10 +24069,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>124464466</v>
+        <v>124464651</v>
       </c>
       <c r="B229" t="n">
-        <v>78905</v>
+        <v>79399</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -24085,21 +24085,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>967</v>
+        <v>229821</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -24109,10 +24109,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>380243</v>
+        <v>380251</v>
       </c>
       <c r="R229" t="n">
-        <v>6919687</v>
+        <v>6919658</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24171,10 +24171,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>124469547</v>
+        <v>124459456</v>
       </c>
       <c r="B230" t="n">
-        <v>88359</v>
+        <v>91032</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -24187,21 +24187,21 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>510</v>
+        <v>5442</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -24211,10 +24211,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>380452</v>
+        <v>380561</v>
       </c>
       <c r="R230" t="n">
-        <v>6919913</v>
+        <v>6919930</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24273,10 +24273,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>124451802</v>
+        <v>124455134</v>
       </c>
       <c r="B231" t="n">
-        <v>79428</v>
+        <v>74901</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -24289,21 +24289,21 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -24313,10 +24313,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>380197</v>
+        <v>380311</v>
       </c>
       <c r="R231" t="n">
-        <v>6920479</v>
+        <v>6920245</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24375,10 +24375,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>124470598</v>
+        <v>124457836</v>
       </c>
       <c r="B232" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -24391,34 +24391,34 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>380506</v>
+        <v>380542</v>
       </c>
       <c r="R232" t="n">
-        <v>6920061</v>
+        <v>6920184</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24451,11 +24451,6 @@
       <c r="AA232" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC232" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -24482,10 +24477,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>124456372</v>
+        <v>124464466</v>
       </c>
       <c r="B233" t="n">
-        <v>74901</v>
+        <v>78905</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -24498,34 +24493,34 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>6440</v>
+        <v>967</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>380368</v>
+        <v>380243</v>
       </c>
       <c r="R233" t="n">
-        <v>6920107</v>
+        <v>6919687</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -24584,10 +24579,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>124470397</v>
+        <v>124460052</v>
       </c>
       <c r="B234" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -24600,34 +24595,39 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P234" t="inlineStr">
         <is>
           <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>380506</v>
+        <v>380419</v>
       </c>
       <c r="R234" t="n">
-        <v>6920061</v>
+        <v>6919960</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -24686,10 +24686,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>124461477</v>
+        <v>124458357</v>
       </c>
       <c r="B235" t="n">
-        <v>79399</v>
+        <v>57666</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -24702,37 +24702,42 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>380285</v>
+        <v>380586</v>
       </c>
       <c r="R235" t="n">
-        <v>6919895</v>
+        <v>6920100</v>
       </c>
       <c r="S235" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T235" t="inlineStr">
         <is>
@@ -24788,10 +24793,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>124456676</v>
+        <v>124459815</v>
       </c>
       <c r="B236" t="n">
-        <v>57513</v>
+        <v>79428</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -24804,42 +24809,37 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
-      <c r="M236" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>380434</v>
+        <v>380445</v>
       </c>
       <c r="R236" t="n">
-        <v>6920123</v>
+        <v>6919917</v>
       </c>
       <c r="S236" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T236" t="inlineStr">
         <is>
@@ -24895,10 +24895,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>124471016</v>
+        <v>124461736</v>
       </c>
       <c r="B237" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -24911,39 +24911,34 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
-      <c r="M237" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>380506</v>
+        <v>380232</v>
       </c>
       <c r="R237" t="n">
-        <v>6920061</v>
+        <v>6919808</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -24990,22 +24985,22 @@
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>124469751</v>
+        <v>124464970</v>
       </c>
       <c r="B238" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -25018,37 +25013,42 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>380490</v>
+        <v>380255</v>
       </c>
       <c r="R238" t="n">
-        <v>6919937</v>
+        <v>6919561</v>
       </c>
       <c r="S238" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T238" t="inlineStr">
         <is>
@@ -25104,10 +25104,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>124450737</v>
+        <v>124466302</v>
       </c>
       <c r="B239" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -25120,37 +25120,42 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>380210</v>
+        <v>380345</v>
       </c>
       <c r="R239" t="n">
-        <v>6920378</v>
+        <v>6919632</v>
       </c>
       <c r="S239" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T239" t="inlineStr">
         <is>
@@ -25206,10 +25211,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>124450518</v>
+        <v>124451984</v>
       </c>
       <c r="B240" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -25222,34 +25227,34 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>380202</v>
+        <v>380203</v>
       </c>
       <c r="R240" t="n">
-        <v>6920332</v>
+        <v>6920482</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -25308,10 +25313,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>124469915</v>
+        <v>124465526</v>
       </c>
       <c r="B241" t="n">
-        <v>74901</v>
+        <v>79399</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -25324,34 +25329,34 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>380521</v>
+        <v>380252</v>
       </c>
       <c r="R241" t="n">
-        <v>6919962</v>
+        <v>6919535</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -25410,10 +25415,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>124464681</v>
+        <v>124464321</v>
       </c>
       <c r="B242" t="n">
-        <v>79399</v>
+        <v>77738</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -25426,21 +25431,21 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -25450,10 +25455,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>380264</v>
+        <v>380268</v>
       </c>
       <c r="R242" t="n">
-        <v>6919665</v>
+        <v>6919685</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -25512,10 +25517,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>124470806</v>
+        <v>124452627</v>
       </c>
       <c r="B243" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -25528,42 +25533,37 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
-      <c r="M243" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>380340</v>
+        <v>380217</v>
       </c>
       <c r="R243" t="n">
-        <v>6920036</v>
+        <v>6920440</v>
       </c>
       <c r="S243" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -25619,10 +25619,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>124455096</v>
+        <v>124458476</v>
       </c>
       <c r="B244" t="n">
-        <v>5196</v>
+        <v>74901</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -25631,43 +25631,38 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>105930</v>
+        <v>6440</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
-      <c r="M244" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>380323</v>
+        <v>380581</v>
       </c>
       <c r="R244" t="n">
-        <v>6920260</v>
+        <v>6920056</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25726,10 +25721,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>124466302</v>
+        <v>124452261</v>
       </c>
       <c r="B245" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -25742,42 +25737,37 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
-      <c r="M245" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>380345</v>
+        <v>380227</v>
       </c>
       <c r="R245" t="n">
-        <v>6919632</v>
+        <v>6920340</v>
       </c>
       <c r="S245" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -25821,22 +25811,22 @@
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>124456502</v>
+        <v>124465863</v>
       </c>
       <c r="B246" t="n">
-        <v>78810</v>
+        <v>78151</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -25845,38 +25835,38 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6425</v>
+        <v>498</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Risåsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>380385</v>
+        <v>380296</v>
       </c>
       <c r="R246" t="n">
-        <v>6920091</v>
+        <v>6919585</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25911,11 +25901,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC246" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området.</t>
-        </is>
-      </c>
       <c r="AD246" t="b">
         <v>0</v>
       </c>
@@ -25928,22 +25913,22 @@
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>124470555</v>
+        <v>124450902</v>
       </c>
       <c r="B247" t="n">
-        <v>82597</v>
+        <v>57529</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -25956,34 +25941,39 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>380431</v>
+        <v>380227</v>
       </c>
       <c r="R247" t="n">
-        <v>6920068</v>
+        <v>6920340</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -26018,6 +26008,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC247" t="inlineStr">
+        <is>
+          <t>Troligen spillkråka.</t>
+        </is>
+      </c>
       <c r="AD247" t="b">
         <v>0</v>
       </c>
@@ -26030,22 +26025,22 @@
       <c r="AT247" t="inlineStr"/>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>124470070</v>
+        <v>124459287</v>
       </c>
       <c r="B248" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -26058,34 +26053,39 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>380533</v>
+        <v>380561</v>
       </c>
       <c r="R248" t="n">
-        <v>6919979</v>
+        <v>6919930</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -26132,22 +26132,22 @@
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>124452423</v>
+        <v>124466494</v>
       </c>
       <c r="B249" t="n">
-        <v>56725</v>
+        <v>57513</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -26156,20 +26156,20 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>102613</v>
+        <v>100109</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -26180,22 +26180,22 @@
       <c r="I249" t="inlineStr"/>
       <c r="M249" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>380227</v>
+        <v>380344</v>
       </c>
       <c r="R249" t="n">
-        <v>6920340</v>
+        <v>6919654</v>
       </c>
       <c r="S249" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T249" t="inlineStr">
         <is>
@@ -26239,22 +26239,22 @@
       <c r="AT249" t="inlineStr"/>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>124459048</v>
+        <v>124458743</v>
       </c>
       <c r="B250" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -26267,29 +26267,24 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
-      <c r="M250" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P250" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
@@ -26332,6 +26327,11 @@
       <c r="AA250" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -26358,10 +26358,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>124464292</v>
+        <v>124470184</v>
       </c>
       <c r="B251" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -26374,39 +26374,34 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
-      <c r="M251" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P251" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>380275</v>
+        <v>380516</v>
       </c>
       <c r="R251" t="n">
-        <v>6919775</v>
+        <v>6920004</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -26453,22 +26448,22 @@
       <c r="AT251" t="inlineStr"/>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>124450578</v>
+        <v>124457601</v>
       </c>
       <c r="B252" t="n">
-        <v>91030</v>
+        <v>78151</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -26477,38 +26472,38 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>5432</v>
+        <v>498</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
       <c r="P252" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>380227</v>
+        <v>380544</v>
       </c>
       <c r="R252" t="n">
-        <v>6920340</v>
+        <v>6920188</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -26555,22 +26550,22 @@
       <c r="AT252" t="inlineStr"/>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>124452261</v>
+        <v>124470146</v>
       </c>
       <c r="B253" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -26583,37 +26578,42 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>380227</v>
+        <v>380527</v>
       </c>
       <c r="R253" t="n">
-        <v>6920340</v>
+        <v>6919988</v>
       </c>
       <c r="S253" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T253" t="inlineStr">
         <is>
@@ -26657,22 +26657,22 @@
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>124457866</v>
+        <v>124470555</v>
       </c>
       <c r="B254" t="n">
-        <v>78151</v>
+        <v>82597</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -26681,25 +26681,25 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>498</v>
+        <v>1312</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -26709,10 +26709,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>380537</v>
+        <v>380431</v>
       </c>
       <c r="R254" t="n">
-        <v>6920199</v>
+        <v>6920068</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26771,10 +26771,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>124465863</v>
+        <v>124470397</v>
       </c>
       <c r="B255" t="n">
-        <v>78151</v>
+        <v>74901</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -26783,38 +26783,38 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>498</v>
+        <v>6440</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
-          <t>Risåsvallen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>380296</v>
+        <v>380506</v>
       </c>
       <c r="R255" t="n">
-        <v>6919585</v>
+        <v>6920061</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26861,22 +26861,22 @@
       <c r="AT255" t="inlineStr"/>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>124463365</v>
+        <v>124464471</v>
       </c>
       <c r="B256" t="n">
-        <v>79399</v>
+        <v>78194</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -26889,21 +26889,21 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -26913,10 +26913,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>380199</v>
+        <v>380243</v>
       </c>
       <c r="R256" t="n">
-        <v>6919723</v>
+        <v>6919687</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -26975,7 +26975,7 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>124455134</v>
+        <v>124458046</v>
       </c>
       <c r="B257" t="n">
         <v>74901</v>
@@ -27011,14 +27011,14 @@
       <c r="I257" t="inlineStr"/>
       <c r="P257" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>380311</v>
+        <v>380533</v>
       </c>
       <c r="R257" t="n">
-        <v>6920245</v>
+        <v>6920142</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -27077,10 +27077,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>124455220</v>
+        <v>124458651</v>
       </c>
       <c r="B258" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -27093,34 +27093,34 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>380311</v>
+        <v>380569</v>
       </c>
       <c r="R258" t="n">
-        <v>6920231</v>
+        <v>6920058</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -27179,10 +27179,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>124452627</v>
+        <v>124450518</v>
       </c>
       <c r="B259" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -27195,34 +27195,34 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
       <c r="P259" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>380217</v>
+        <v>380202</v>
       </c>
       <c r="R259" t="n">
-        <v>6920440</v>
+        <v>6920332</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -27281,10 +27281,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>124460611</v>
+        <v>124467914</v>
       </c>
       <c r="B260" t="n">
-        <v>78905</v>
+        <v>77738</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -27297,34 +27297,34 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>967</v>
+        <v>6487</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>380335</v>
+        <v>380361</v>
       </c>
       <c r="R260" t="n">
-        <v>6920000</v>
+        <v>6919740</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -27357,6 +27357,11 @@
       <c r="AA260" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC260" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -27383,10 +27388,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>124470707</v>
+        <v>124459134</v>
       </c>
       <c r="B261" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -27399,42 +27404,37 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
-      <c r="M261" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P261" t="inlineStr">
         <is>
           <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>380367</v>
+        <v>380559</v>
       </c>
       <c r="R261" t="n">
-        <v>6920058</v>
+        <v>6919947</v>
       </c>
       <c r="S261" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T261" t="inlineStr">
         <is>
@@ -27490,10 +27490,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>124465389</v>
+        <v>124469377</v>
       </c>
       <c r="B262" t="n">
-        <v>79399</v>
+        <v>74901</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -27506,34 +27506,34 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>380244</v>
+        <v>380435</v>
       </c>
       <c r="R262" t="n">
-        <v>6919577</v>
+        <v>6919916</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -27580,22 +27580,22 @@
       <c r="AT262" t="inlineStr"/>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>124450415</v>
+        <v>124468469</v>
       </c>
       <c r="B263" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -27608,37 +27608,42 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P263" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>380202</v>
+        <v>380324</v>
       </c>
       <c r="R263" t="n">
-        <v>6920332</v>
+        <v>6919803</v>
       </c>
       <c r="S263" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T263" t="inlineStr">
         <is>
@@ -27694,10 +27699,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>124460951</v>
+        <v>124457866</v>
       </c>
       <c r="B264" t="n">
-        <v>74901</v>
+        <v>78151</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -27706,38 +27711,38 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>6440</v>
+        <v>498</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>380307</v>
+        <v>380537</v>
       </c>
       <c r="R264" t="n">
-        <v>6919967</v>
+        <v>6920199</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27796,10 +27801,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>124459287</v>
+        <v>124451893</v>
       </c>
       <c r="B265" t="n">
-        <v>57513</v>
+        <v>5196</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -27808,20 +27813,20 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>100109</v>
+        <v>105930</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -27830,21 +27835,16 @@
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
-      <c r="M265" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P265" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>380561</v>
+        <v>380227</v>
       </c>
       <c r="R265" t="n">
-        <v>6919930</v>
+        <v>6920340</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27903,7 +27903,7 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>124458651</v>
+        <v>124454979</v>
       </c>
       <c r="B266" t="n">
         <v>91030</v>
@@ -27939,14 +27939,14 @@
       <c r="I266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>380569</v>
+        <v>380289</v>
       </c>
       <c r="R266" t="n">
-        <v>6920058</v>
+        <v>6920290</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -27981,6 +27981,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC266" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD266" t="b">
         <v>0</v>
       </c>
@@ -27993,22 +27998,22 @@
       <c r="AT266" t="inlineStr"/>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>124464651</v>
+        <v>124451837</v>
       </c>
       <c r="B267" t="n">
-        <v>79399</v>
+        <v>78194</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -28021,34 +28026,34 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
       <c r="P267" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>380251</v>
+        <v>380197</v>
       </c>
       <c r="R267" t="n">
-        <v>6919658</v>
+        <v>6920479</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -28107,10 +28112,10 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>124470299</v>
+        <v>124456502</v>
       </c>
       <c r="B268" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -28119,43 +28124,38 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
-      <c r="M268" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P268" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>380495</v>
+        <v>380385</v>
       </c>
       <c r="R268" t="n">
-        <v>6920029</v>
+        <v>6920091</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -28190,6 +28190,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC268" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området.</t>
+        </is>
+      </c>
       <c r="AD268" t="b">
         <v>0</v>
       </c>
@@ -28202,22 +28207,22 @@
       <c r="AT268" t="inlineStr"/>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>124467914</v>
+        <v>124452491</v>
       </c>
       <c r="B269" t="n">
-        <v>77738</v>
+        <v>78810</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -28230,34 +28235,34 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
       <c r="P269" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>380361</v>
+        <v>380208</v>
       </c>
       <c r="R269" t="n">
-        <v>6919740</v>
+        <v>6920481</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -28292,11 +28297,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC269" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD269" t="b">
         <v>0</v>
       </c>
@@ -28309,22 +28309,22 @@
       <c r="AT269" t="inlineStr"/>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>124465526</v>
+        <v>124470404</v>
       </c>
       <c r="B270" t="n">
-        <v>79399</v>
+        <v>91030</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -28337,34 +28337,34 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>229821</v>
+        <v>5432</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
       <c r="P270" t="inlineStr">
         <is>
-          <t>Risåsvallen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>380252</v>
+        <v>380471</v>
       </c>
       <c r="R270" t="n">
-        <v>6919535</v>
+        <v>6920069</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -28423,10 +28423,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>124464970</v>
+        <v>124461108</v>
       </c>
       <c r="B271" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -28439,42 +28439,37 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
-      <c r="M271" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P271" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>380255</v>
+        <v>380308</v>
       </c>
       <c r="R271" t="n">
-        <v>6919561</v>
+        <v>6919925</v>
       </c>
       <c r="S271" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T271" t="inlineStr">
         <is>
@@ -28504,6 +28499,11 @@
       <c r="AA271" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC271" t="inlineStr">
+        <is>
+          <t>På basen avsågad gran. Grov stubbe</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -28530,10 +28530,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>124466026</v>
+        <v>124450415</v>
       </c>
       <c r="B272" t="n">
-        <v>79399</v>
+        <v>74901</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -28546,21 +28546,21 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
@@ -28570,10 +28570,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>380303</v>
+        <v>380202</v>
       </c>
       <c r="R272" t="n">
-        <v>6919598</v>
+        <v>6920332</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -28608,11 +28608,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC272" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD272" t="b">
         <v>0</v>
       </c>
@@ -28625,12 +28620,12 @@
       <c r="AT272" t="inlineStr"/>
       <c r="AW272" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
@@ -28744,10 +28739,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>124589633</v>
+        <v>124588108</v>
       </c>
       <c r="B274" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -28760,37 +28755,42 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P274" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>380181</v>
+        <v>380223</v>
       </c>
       <c r="R274" t="n">
-        <v>6920018</v>
+        <v>6920277</v>
       </c>
       <c r="S274" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T274" t="inlineStr">
         <is>
@@ -28846,10 +28846,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>124588108</v>
+        <v>124589633</v>
       </c>
       <c r="B275" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -28862,42 +28862,37 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
-      <c r="M275" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P275" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>380223</v>
+        <v>380181</v>
       </c>
       <c r="R275" t="n">
-        <v>6920277</v>
+        <v>6920018</v>
       </c>
       <c r="S275" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T275" t="inlineStr">
         <is>
@@ -28953,10 +28948,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>124870503</v>
+        <v>124870693</v>
       </c>
       <c r="B276" t="n">
-        <v>57513</v>
+        <v>96354</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -28969,42 +28964,37 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
-      <c r="M276" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P276" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>380108</v>
+        <v>380072</v>
       </c>
       <c r="R276" t="n">
-        <v>6919741</v>
+        <v>6919810</v>
       </c>
       <c r="S276" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T276" t="inlineStr">
         <is>
@@ -29060,10 +29050,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>124871081</v>
+        <v>124870851</v>
       </c>
       <c r="B277" t="n">
-        <v>57513</v>
+        <v>79399</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -29076,42 +29066,37 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
-      <c r="M277" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P277" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>380173</v>
+        <v>380051</v>
       </c>
       <c r="R277" t="n">
-        <v>6920011</v>
+        <v>6919850</v>
       </c>
       <c r="S277" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T277" t="inlineStr">
         <is>
@@ -29167,10 +29152,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>124870920</v>
+        <v>124871117</v>
       </c>
       <c r="B278" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -29183,37 +29168,42 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P278" t="inlineStr">
         <is>
           <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>380097</v>
+        <v>380204</v>
       </c>
       <c r="R278" t="n">
-        <v>6919882</v>
+        <v>6920043</v>
       </c>
       <c r="S278" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T278" t="inlineStr">
         <is>
@@ -29269,10 +29259,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>124870851</v>
+        <v>124871057</v>
       </c>
       <c r="B279" t="n">
-        <v>79399</v>
+        <v>57513</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -29285,37 +29275,42 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P279" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>380051</v>
+        <v>380132</v>
       </c>
       <c r="R279" t="n">
-        <v>6919850</v>
+        <v>6919977</v>
       </c>
       <c r="S279" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T279" t="inlineStr">
         <is>
@@ -29371,10 +29366,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>124870693</v>
+        <v>124871232</v>
       </c>
       <c r="B280" t="n">
-        <v>96354</v>
+        <v>74901</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -29387,34 +29382,34 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>53</v>
+        <v>6440</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
       <c r="P280" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>380072</v>
+        <v>380202</v>
       </c>
       <c r="R280" t="n">
-        <v>6919810</v>
+        <v>6920072</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -29473,7 +29468,7 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>124871057</v>
+        <v>124870503</v>
       </c>
       <c r="B281" t="n">
         <v>57513</v>
@@ -29514,14 +29509,14 @@
       </c>
       <c r="P281" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>380132</v>
+        <v>380108</v>
       </c>
       <c r="R281" t="n">
-        <v>6919977</v>
+        <v>6919741</v>
       </c>
       <c r="S281" t="n">
         <v>15</v>
@@ -29580,10 +29575,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>124871232</v>
+        <v>124870920</v>
       </c>
       <c r="B282" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -29596,21 +29591,21 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
@@ -29620,10 +29615,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>380202</v>
+        <v>380097</v>
       </c>
       <c r="R282" t="n">
-        <v>6920072</v>
+        <v>6919882</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>
@@ -29789,7 +29784,7 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>124870262</v>
+        <v>124870424</v>
       </c>
       <c r="B284" t="n">
         <v>57513</v>
@@ -29830,14 +29825,14 @@
       </c>
       <c r="P284" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>380196</v>
+        <v>380098</v>
       </c>
       <c r="R284" t="n">
-        <v>6919970</v>
+        <v>6919759</v>
       </c>
       <c r="S284" t="n">
         <v>15</v>
@@ -29896,10 +29891,10 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>124870943</v>
+        <v>124870654</v>
       </c>
       <c r="B285" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -29912,42 +29907,37 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
-      <c r="M285" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P285" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q285" t="n">
         <v>380093</v>
       </c>
       <c r="R285" t="n">
-        <v>6919892</v>
+        <v>6919795</v>
       </c>
       <c r="S285" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T285" t="inlineStr">
         <is>
@@ -30110,7 +30100,7 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>124871117</v>
+        <v>124870262</v>
       </c>
       <c r="B287" t="n">
         <v>57513</v>
@@ -30155,10 +30145,10 @@
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>380204</v>
+        <v>380196</v>
       </c>
       <c r="R287" t="n">
-        <v>6920043</v>
+        <v>6919970</v>
       </c>
       <c r="S287" t="n">
         <v>15</v>
@@ -30217,10 +30207,10 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>124870654</v>
+        <v>124870943</v>
       </c>
       <c r="B288" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -30233,37 +30223,42 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I288" t="inlineStr"/>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P288" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q288" t="n">
         <v>380093</v>
       </c>
       <c r="R288" t="n">
-        <v>6919795</v>
+        <v>6919892</v>
       </c>
       <c r="S288" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T288" t="inlineStr">
         <is>
@@ -30319,7 +30314,7 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>124870424</v>
+        <v>124871081</v>
       </c>
       <c r="B289" t="n">
         <v>57513</v>
@@ -30360,14 +30355,14 @@
       </c>
       <c r="P289" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>380098</v>
+        <v>380173</v>
       </c>
       <c r="R289" t="n">
-        <v>6919759</v>
+        <v>6920011</v>
       </c>
       <c r="S289" t="n">
         <v>15</v>

--- a/artfynd/A 32573-2024 artfynd.xlsx
+++ b/artfynd/A 32573-2024 artfynd.xlsx
@@ -17660,10 +17660,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>124455456</v>
+        <v>124468916</v>
       </c>
       <c r="B167" t="n">
-        <v>74901</v>
+        <v>78151</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17672,25 +17672,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6440</v>
+        <v>498</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17700,10 +17700,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>380314</v>
+        <v>380343</v>
       </c>
       <c r="R167" t="n">
-        <v>6920201</v>
+        <v>6919896</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17762,7 +17762,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>124454876</v>
+        <v>124455456</v>
       </c>
       <c r="B168" t="n">
         <v>74901</v>
@@ -17802,10 +17802,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>380290</v>
+        <v>380314</v>
       </c>
       <c r="R168" t="n">
-        <v>6920272</v>
+        <v>6920201</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17864,10 +17864,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>124470598</v>
+        <v>124454876</v>
       </c>
       <c r="B169" t="n">
-        <v>79428</v>
+        <v>74901</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -17880,34 +17880,34 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>380506</v>
+        <v>380290</v>
       </c>
       <c r="R169" t="n">
-        <v>6920061</v>
+        <v>6920272</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17942,11 +17942,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD169" t="b">
         <v>0</v>
       </c>
@@ -17959,22 +17954,22 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>124470732</v>
+        <v>124470598</v>
       </c>
       <c r="B170" t="n">
-        <v>74901</v>
+        <v>79428</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -17987,21 +17982,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18011,10 +18006,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>380372</v>
+        <v>380506</v>
       </c>
       <c r="R170" t="n">
-        <v>6920042</v>
+        <v>6920061</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18049,6 +18044,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD170" t="b">
         <v>0</v>
       </c>
@@ -18061,22 +18061,22 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>124468916</v>
+        <v>124470732</v>
       </c>
       <c r="B171" t="n">
-        <v>78151</v>
+        <v>74901</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18085,38 +18085,38 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>498</v>
+        <v>6440</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>380343</v>
+        <v>380372</v>
       </c>
       <c r="R171" t="n">
-        <v>6919896</v>
+        <v>6920042</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19720,10 +19720,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124459042</v>
+        <v>124469547</v>
       </c>
       <c r="B187" t="n">
-        <v>74901</v>
+        <v>88359</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -19736,34 +19736,34 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>380571</v>
+        <v>380452</v>
       </c>
       <c r="R187" t="n">
-        <v>6919993</v>
+        <v>6919913</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19810,22 +19810,22 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124465167</v>
+        <v>124459042</v>
       </c>
       <c r="B188" t="n">
-        <v>78194</v>
+        <v>74901</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -19838,21 +19838,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19862,10 +19862,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>380244</v>
+        <v>380571</v>
       </c>
       <c r="R188" t="n">
-        <v>6919577</v>
+        <v>6919993</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19912,22 +19912,22 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124456372</v>
+        <v>124465167</v>
       </c>
       <c r="B189" t="n">
-        <v>74901</v>
+        <v>78194</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -19940,34 +19940,34 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>380368</v>
+        <v>380244</v>
       </c>
       <c r="R189" t="n">
-        <v>6920107</v>
+        <v>6919577</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20014,19 +20014,19 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>124468547</v>
+        <v>124456372</v>
       </c>
       <c r="B190" t="n">
         <v>74901</v>
@@ -20062,14 +20062,14 @@
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>380356</v>
+        <v>380368</v>
       </c>
       <c r="R190" t="n">
-        <v>6919817</v>
+        <v>6920107</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20128,10 +20128,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>124464842</v>
+        <v>124468547</v>
       </c>
       <c r="B191" t="n">
-        <v>79428</v>
+        <v>74901</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20144,34 +20144,34 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>380237</v>
+        <v>380356</v>
       </c>
       <c r="R191" t="n">
-        <v>6919621</v>
+        <v>6919817</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20230,10 +20230,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>124470070</v>
+        <v>124464842</v>
       </c>
       <c r="B192" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20246,21 +20246,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20270,10 +20270,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>380533</v>
+        <v>380237</v>
       </c>
       <c r="R192" t="n">
-        <v>6919979</v>
+        <v>6919621</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20332,10 +20332,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>124470806</v>
+        <v>124470070</v>
       </c>
       <c r="B193" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -20348,42 +20348,37 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
-      <c r="M193" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>380340</v>
+        <v>380533</v>
       </c>
       <c r="R193" t="n">
-        <v>6920036</v>
+        <v>6919979</v>
       </c>
       <c r="S193" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -20439,10 +20434,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>124469547</v>
+        <v>124470806</v>
       </c>
       <c r="B194" t="n">
-        <v>88359</v>
+        <v>57513</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -20455,37 +20450,42 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P194" t="inlineStr">
         <is>
           <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>380452</v>
+        <v>380340</v>
       </c>
       <c r="R194" t="n">
-        <v>6919913</v>
+        <v>6920036</v>
       </c>
       <c r="S194" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -20529,12 +20529,12 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
@@ -23019,10 +23019,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>124455776</v>
+        <v>124452423</v>
       </c>
       <c r="B219" t="n">
-        <v>57513</v>
+        <v>56725</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -23031,20 +23031,20 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>100109</v>
+        <v>102613</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -23055,7 +23055,7 @@
       <c r="I219" t="inlineStr"/>
       <c r="M219" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
@@ -23064,10 +23064,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>380326</v>
+        <v>380227</v>
       </c>
       <c r="R219" t="n">
-        <v>6920218</v>
+        <v>6920340</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23126,7 +23126,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>124471016</v>
+        <v>124455776</v>
       </c>
       <c r="B220" t="n">
         <v>57513</v>
@@ -23162,19 +23162,19 @@
       <c r="I220" t="inlineStr"/>
       <c r="M220" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>380506</v>
+        <v>380326</v>
       </c>
       <c r="R220" t="n">
-        <v>6920061</v>
+        <v>6920218</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23233,10 +23233,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>124452423</v>
+        <v>124471016</v>
       </c>
       <c r="B221" t="n">
-        <v>56725</v>
+        <v>57513</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -23245,20 +23245,20 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>102613</v>
+        <v>100109</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -23269,19 +23269,19 @@
       <c r="I221" t="inlineStr"/>
       <c r="M221" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>380227</v>
+        <v>380506</v>
       </c>
       <c r="R221" t="n">
-        <v>6920340</v>
+        <v>6920061</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -25211,10 +25211,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>124451984</v>
+        <v>124464321</v>
       </c>
       <c r="B240" t="n">
-        <v>79399</v>
+        <v>77738</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -25227,34 +25227,34 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>380203</v>
+        <v>380268</v>
       </c>
       <c r="R240" t="n">
-        <v>6920482</v>
+        <v>6919685</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -25313,10 +25313,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>124465526</v>
+        <v>124452627</v>
       </c>
       <c r="B241" t="n">
-        <v>79399</v>
+        <v>74901</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -25329,34 +25329,34 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
-          <t>Risåsvallen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>380252</v>
+        <v>380217</v>
       </c>
       <c r="R241" t="n">
-        <v>6919535</v>
+        <v>6920440</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -25415,10 +25415,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>124464321</v>
+        <v>124458476</v>
       </c>
       <c r="B242" t="n">
-        <v>77738</v>
+        <v>74901</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -25431,21 +25431,21 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>6487</v>
+        <v>6440</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -25455,10 +25455,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>380268</v>
+        <v>380581</v>
       </c>
       <c r="R242" t="n">
-        <v>6919685</v>
+        <v>6920056</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -25517,10 +25517,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>124452627</v>
+        <v>124452261</v>
       </c>
       <c r="B243" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -25533,21 +25533,21 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -25557,10 +25557,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>380217</v>
+        <v>380227</v>
       </c>
       <c r="R243" t="n">
-        <v>6920440</v>
+        <v>6920340</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -25607,22 +25607,22 @@
       <c r="AT243" t="inlineStr"/>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>124458476</v>
+        <v>124465863</v>
       </c>
       <c r="B244" t="n">
-        <v>74901</v>
+        <v>78151</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -25631,38 +25631,38 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>6440</v>
+        <v>498</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>380581</v>
+        <v>380296</v>
       </c>
       <c r="R244" t="n">
-        <v>6920056</v>
+        <v>6919585</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25721,10 +25721,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>124452261</v>
+        <v>124450902</v>
       </c>
       <c r="B245" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -25737,24 +25737,29 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P245" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
@@ -25797,6 +25802,11 @@
       <c r="AA245" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC245" t="inlineStr">
+        <is>
+          <t>Troligen spillkråka.</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -25823,10 +25833,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>124465863</v>
+        <v>124459287</v>
       </c>
       <c r="B246" t="n">
-        <v>78151</v>
+        <v>57513</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -25835,38 +25845,43 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>498</v>
+        <v>100109</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>Risåsvallen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>380296</v>
+        <v>380561</v>
       </c>
       <c r="R246" t="n">
-        <v>6919585</v>
+        <v>6919930</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25913,22 +25928,22 @@
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>124450902</v>
+        <v>124451984</v>
       </c>
       <c r="B247" t="n">
-        <v>57529</v>
+        <v>79399</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -25941,39 +25956,34 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
-      <c r="M247" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P247" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>380227</v>
+        <v>380203</v>
       </c>
       <c r="R247" t="n">
-        <v>6920340</v>
+        <v>6920482</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -26008,11 +26018,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC247" t="inlineStr">
-        <is>
-          <t>Troligen spillkråka.</t>
-        </is>
-      </c>
       <c r="AD247" t="b">
         <v>0</v>
       </c>
@@ -26025,22 +26030,22 @@
       <c r="AT247" t="inlineStr"/>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>124459287</v>
+        <v>124465526</v>
       </c>
       <c r="B248" t="n">
-        <v>57513</v>
+        <v>79399</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -26053,39 +26058,34 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
-      <c r="M248" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Risåsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>380561</v>
+        <v>380252</v>
       </c>
       <c r="R248" t="n">
-        <v>6919930</v>
+        <v>6919535</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -26132,22 +26132,22 @@
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>124466494</v>
+        <v>124458743</v>
       </c>
       <c r="B249" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -26160,42 +26160,37 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
-      <c r="M249" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>380344</v>
+        <v>380542</v>
       </c>
       <c r="R249" t="n">
-        <v>6919654</v>
+        <v>6920184</v>
       </c>
       <c r="S249" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T249" t="inlineStr">
         <is>
@@ -26225,6 +26220,11 @@
       <c r="AA249" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC249" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -26239,19 +26239,19 @@
       <c r="AT249" t="inlineStr"/>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>124458743</v>
+        <v>124470184</v>
       </c>
       <c r="B250" t="n">
         <v>91030</v>
@@ -26287,14 +26287,14 @@
       <c r="I250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>380542</v>
+        <v>380516</v>
       </c>
       <c r="R250" t="n">
-        <v>6920184</v>
+        <v>6920004</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -26329,11 +26329,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC250" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
-        </is>
-      </c>
       <c r="AD250" t="b">
         <v>0</v>
       </c>
@@ -26346,22 +26341,22 @@
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>124470184</v>
+        <v>124466494</v>
       </c>
       <c r="B251" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -26374,37 +26369,42 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P251" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>380516</v>
+        <v>380344</v>
       </c>
       <c r="R251" t="n">
-        <v>6920004</v>
+        <v>6919654</v>
       </c>
       <c r="S251" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T251" t="inlineStr">
         <is>
@@ -26460,10 +26460,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>124457601</v>
+        <v>124470555</v>
       </c>
       <c r="B252" t="n">
-        <v>78151</v>
+        <v>82597</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -26472,25 +26472,25 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>498</v>
+        <v>1312</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -26500,10 +26500,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>380544</v>
+        <v>380431</v>
       </c>
       <c r="R252" t="n">
-        <v>6920188</v>
+        <v>6920068</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -26562,10 +26562,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>124470146</v>
+        <v>124470397</v>
       </c>
       <c r="B253" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -26578,42 +26578,37 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
-      <c r="M253" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>380527</v>
+        <v>380506</v>
       </c>
       <c r="R253" t="n">
-        <v>6919988</v>
+        <v>6920061</v>
       </c>
       <c r="S253" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T253" t="inlineStr">
         <is>
@@ -26657,22 +26652,22 @@
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>124470555</v>
+        <v>124464471</v>
       </c>
       <c r="B254" t="n">
-        <v>82597</v>
+        <v>78194</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -26685,21 +26680,21 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>1312</v>
+        <v>6437</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -26709,10 +26704,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>380431</v>
+        <v>380243</v>
       </c>
       <c r="R254" t="n">
-        <v>6920068</v>
+        <v>6919687</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26771,7 +26766,7 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>124470397</v>
+        <v>124458046</v>
       </c>
       <c r="B255" t="n">
         <v>74901</v>
@@ -26807,14 +26802,14 @@
       <c r="I255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>380506</v>
+        <v>380533</v>
       </c>
       <c r="R255" t="n">
-        <v>6920061</v>
+        <v>6920142</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26861,22 +26856,22 @@
       <c r="AT255" t="inlineStr"/>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>124464471</v>
+        <v>124458651</v>
       </c>
       <c r="B256" t="n">
-        <v>78194</v>
+        <v>91030</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -26889,21 +26884,21 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>6437</v>
+        <v>5432</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -26913,10 +26908,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>380243</v>
+        <v>380569</v>
       </c>
       <c r="R256" t="n">
-        <v>6919687</v>
+        <v>6920058</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -26975,10 +26970,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>124458046</v>
+        <v>124450518</v>
       </c>
       <c r="B257" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -26991,21 +26986,21 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -27015,10 +27010,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>380533</v>
+        <v>380202</v>
       </c>
       <c r="R257" t="n">
-        <v>6920142</v>
+        <v>6920332</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -27077,10 +27072,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>124458651</v>
+        <v>124457601</v>
       </c>
       <c r="B258" t="n">
-        <v>91030</v>
+        <v>78151</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -27089,25 +27084,25 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>5432</v>
+        <v>498</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -27117,10 +27112,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>380569</v>
+        <v>380544</v>
       </c>
       <c r="R258" t="n">
-        <v>6920058</v>
+        <v>6920188</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -27179,10 +27174,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>124450518</v>
+        <v>124470146</v>
       </c>
       <c r="B259" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -27195,37 +27190,42 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P259" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>380202</v>
+        <v>380527</v>
       </c>
       <c r="R259" t="n">
-        <v>6920332</v>
+        <v>6919988</v>
       </c>
       <c r="S259" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T259" t="inlineStr">
         <is>

--- a/artfynd/A 32573-2024 artfynd.xlsx
+++ b/artfynd/A 32573-2024 artfynd.xlsx
@@ -16105,10 +16105,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>124469751</v>
+        <v>124459048</v>
       </c>
       <c r="B152" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16121,34 +16121,39 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>380490</v>
+        <v>380542</v>
       </c>
       <c r="R152" t="n">
-        <v>6919937</v>
+        <v>6920184</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16195,22 +16200,22 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>124455096</v>
+        <v>124470806</v>
       </c>
       <c r="B153" t="n">
-        <v>5196</v>
+        <v>57513</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16219,20 +16224,20 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>105930</v>
+        <v>100109</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -16243,22 +16248,22 @@
       <c r="I153" t="inlineStr"/>
       <c r="M153" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>380323</v>
+        <v>380340</v>
       </c>
       <c r="R153" t="n">
-        <v>6920260</v>
+        <v>6920036</v>
       </c>
       <c r="S153" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16314,10 +16319,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>124470299</v>
+        <v>124465389</v>
       </c>
       <c r="B154" t="n">
-        <v>56722</v>
+        <v>79399</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16326,43 +16331,38 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P154" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>380495</v>
+        <v>380244</v>
       </c>
       <c r="R154" t="n">
-        <v>6920029</v>
+        <v>6919577</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16409,22 +16409,22 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>124470707</v>
+        <v>124454876</v>
       </c>
       <c r="B155" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16437,42 +16437,37 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>380367</v>
+        <v>380290</v>
       </c>
       <c r="R155" t="n">
-        <v>6920058</v>
+        <v>6920272</v>
       </c>
       <c r="S155" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16528,10 +16523,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>124463365</v>
+        <v>124470695</v>
       </c>
       <c r="B156" t="n">
-        <v>79399</v>
+        <v>91030</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16544,34 +16539,34 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>229821</v>
+        <v>5432</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>380199</v>
+        <v>380506</v>
       </c>
       <c r="R156" t="n">
-        <v>6919723</v>
+        <v>6920061</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16606,6 +16601,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
@@ -16618,22 +16618,22 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>124464559</v>
+        <v>124450845</v>
       </c>
       <c r="B157" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16646,21 +16646,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16670,10 +16670,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>380236</v>
+        <v>380205</v>
       </c>
       <c r="R157" t="n">
-        <v>6919671</v>
+        <v>6920378</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16732,10 +16732,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>124456046</v>
+        <v>124464842</v>
       </c>
       <c r="B158" t="n">
-        <v>91032</v>
+        <v>79428</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16748,34 +16748,34 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>380326</v>
+        <v>380237</v>
       </c>
       <c r="R158" t="n">
-        <v>6920218</v>
+        <v>6919621</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16810,11 +16810,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området.</t>
-        </is>
-      </c>
       <c r="AD158" t="b">
         <v>0</v>
       </c>
@@ -16827,22 +16822,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>124469907</v>
+        <v>124450300</v>
       </c>
       <c r="B159" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16855,34 +16850,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>380452</v>
+        <v>380182</v>
       </c>
       <c r="R159" t="n">
-        <v>6919913</v>
+        <v>6920316</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16929,22 +16924,22 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>124464292</v>
+        <v>124458651</v>
       </c>
       <c r="B160" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -16957,39 +16952,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P160" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>380275</v>
+        <v>380569</v>
       </c>
       <c r="R160" t="n">
-        <v>6919775</v>
+        <v>6920058</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17036,22 +17026,22 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>124456697</v>
+        <v>124450415</v>
       </c>
       <c r="B161" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17064,21 +17054,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17088,10 +17078,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>380443</v>
+        <v>380202</v>
       </c>
       <c r="R161" t="n">
-        <v>6920118</v>
+        <v>6920332</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17150,10 +17140,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>124450737</v>
+        <v>124455776</v>
       </c>
       <c r="B162" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17166,34 +17156,39 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>380210</v>
+        <v>380326</v>
       </c>
       <c r="R162" t="n">
-        <v>6920378</v>
+        <v>6920218</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17240,22 +17235,22 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>124463640</v>
+        <v>124460611</v>
       </c>
       <c r="B163" t="n">
-        <v>79428</v>
+        <v>78905</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17268,34 +17263,34 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6453</v>
+        <v>967</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>380218</v>
+        <v>380335</v>
       </c>
       <c r="R163" t="n">
-        <v>6919722</v>
+        <v>6920000</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17342,22 +17337,22 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>124470737</v>
+        <v>124464681</v>
       </c>
       <c r="B164" t="n">
-        <v>91030</v>
+        <v>79399</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17370,34 +17365,34 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>5432</v>
+        <v>229821</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>380506</v>
+        <v>380264</v>
       </c>
       <c r="R164" t="n">
-        <v>6920061</v>
+        <v>6919665</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17444,22 +17439,22 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>124464901</v>
+        <v>124456372</v>
       </c>
       <c r="B165" t="n">
-        <v>79399</v>
+        <v>74901</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17472,34 +17467,34 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>380249</v>
+        <v>380368</v>
       </c>
       <c r="R165" t="n">
-        <v>6919607</v>
+        <v>6920107</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17558,10 +17553,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>124461477</v>
+        <v>124469915</v>
       </c>
       <c r="B166" t="n">
-        <v>79399</v>
+        <v>74901</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17574,34 +17569,34 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>380285</v>
+        <v>380521</v>
       </c>
       <c r="R166" t="n">
-        <v>6919895</v>
+        <v>6919962</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17660,10 +17655,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>124468916</v>
+        <v>124470742</v>
       </c>
       <c r="B167" t="n">
-        <v>78151</v>
+        <v>57513</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17672,41 +17667,46 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>498</v>
+        <v>100109</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>380343</v>
+        <v>380369</v>
       </c>
       <c r="R167" t="n">
-        <v>6919896</v>
+        <v>6920032</v>
       </c>
       <c r="S167" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -17762,10 +17762,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>124455456</v>
+        <v>124451326</v>
       </c>
       <c r="B168" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -17778,34 +17778,39 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P168" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>380314</v>
+        <v>380227</v>
       </c>
       <c r="R168" t="n">
-        <v>6920201</v>
+        <v>6920340</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17852,22 +17857,22 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>124454876</v>
+        <v>124470299</v>
       </c>
       <c r="B169" t="n">
-        <v>74901</v>
+        <v>56722</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -17876,38 +17881,43 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6440</v>
+        <v>100138</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>380290</v>
+        <v>380495</v>
       </c>
       <c r="R169" t="n">
-        <v>6920272</v>
+        <v>6920029</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17966,10 +17976,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>124470598</v>
+        <v>124460224</v>
       </c>
       <c r="B170" t="n">
-        <v>79428</v>
+        <v>57513</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -17982,34 +17992,39 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
           <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>380506</v>
+        <v>380374</v>
       </c>
       <c r="R170" t="n">
-        <v>6920061</v>
+        <v>6919982</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18042,11 +18057,6 @@
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18073,7 +18083,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>124470732</v>
+        <v>124455774</v>
       </c>
       <c r="B171" t="n">
         <v>74901</v>
@@ -18113,10 +18123,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>380372</v>
+        <v>380356</v>
       </c>
       <c r="R171" t="n">
-        <v>6920042</v>
+        <v>6920172</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18175,10 +18185,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>124456676</v>
+        <v>124457836</v>
       </c>
       <c r="B172" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18191,42 +18201,37 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>380434</v>
+        <v>380542</v>
       </c>
       <c r="R172" t="n">
-        <v>6920123</v>
+        <v>6920184</v>
       </c>
       <c r="S172" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -18270,22 +18275,22 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>124464681</v>
+        <v>124461646</v>
       </c>
       <c r="B173" t="n">
-        <v>79399</v>
+        <v>57513</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18298,37 +18303,42 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P173" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>380264</v>
+        <v>380239</v>
       </c>
       <c r="R173" t="n">
-        <v>6919665</v>
+        <v>6919828</v>
       </c>
       <c r="S173" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -18384,10 +18394,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>124465009</v>
+        <v>124470146</v>
       </c>
       <c r="B174" t="n">
-        <v>79399</v>
+        <v>57513</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18400,37 +18410,42 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P174" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>380267</v>
+        <v>380527</v>
       </c>
       <c r="R174" t="n">
-        <v>6919764</v>
+        <v>6919988</v>
       </c>
       <c r="S174" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -18460,11 +18475,6 @@
       <c r="AA174" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18479,22 +18489,22 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>124451885</v>
+        <v>124468182</v>
       </c>
       <c r="B175" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -18507,37 +18517,42 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>380189</v>
+        <v>380265</v>
       </c>
       <c r="R175" t="n">
-        <v>6920488</v>
+        <v>6919774</v>
       </c>
       <c r="S175" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -18593,7 +18608,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>124460951</v>
+        <v>124470397</v>
       </c>
       <c r="B176" t="n">
         <v>74901</v>
@@ -18629,14 +18644,14 @@
       <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>380307</v>
+        <v>380506</v>
       </c>
       <c r="R176" t="n">
-        <v>6919967</v>
+        <v>6920061</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18683,22 +18698,22 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>124469088</v>
+        <v>124450666</v>
       </c>
       <c r="B177" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -18711,34 +18726,34 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>380352</v>
+        <v>380227</v>
       </c>
       <c r="R177" t="n">
-        <v>6919913</v>
+        <v>6920340</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18785,22 +18800,22 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>124450666</v>
+        <v>124464121</v>
       </c>
       <c r="B178" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -18813,34 +18828,39 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>380227</v>
+        <v>380419</v>
       </c>
       <c r="R178" t="n">
-        <v>6920340</v>
+        <v>6919960</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18899,10 +18919,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>124454665</v>
+        <v>124468469</v>
       </c>
       <c r="B179" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -18915,37 +18935,42 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P179" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>380258</v>
+        <v>380324</v>
       </c>
       <c r="R179" t="n">
-        <v>6920309</v>
+        <v>6919803</v>
       </c>
       <c r="S179" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -19001,10 +19026,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>124455774</v>
+        <v>124464559</v>
       </c>
       <c r="B180" t="n">
-        <v>74901</v>
+        <v>79399</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -19017,34 +19042,34 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>380356</v>
+        <v>380236</v>
       </c>
       <c r="R180" t="n">
-        <v>6920172</v>
+        <v>6919671</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19103,10 +19128,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>124460258</v>
+        <v>124451984</v>
       </c>
       <c r="B181" t="n">
-        <v>79428</v>
+        <v>79399</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -19119,34 +19144,34 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>380365</v>
+        <v>380203</v>
       </c>
       <c r="R181" t="n">
-        <v>6919996</v>
+        <v>6920482</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19205,7 +19230,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124451802</v>
+        <v>124463640</v>
       </c>
       <c r="B182" t="n">
         <v>79428</v>
@@ -19241,14 +19266,14 @@
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>380197</v>
+        <v>380218</v>
       </c>
       <c r="R182" t="n">
-        <v>6920479</v>
+        <v>6919722</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19307,10 +19332,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124464493</v>
+        <v>124470555</v>
       </c>
       <c r="B183" t="n">
-        <v>79399</v>
+        <v>82597</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -19323,21 +19348,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>229821</v>
+        <v>1312</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19347,10 +19372,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>380243</v>
+        <v>380431</v>
       </c>
       <c r="R183" t="n">
-        <v>6919687</v>
+        <v>6920068</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19511,10 +19536,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124460611</v>
+        <v>124457601</v>
       </c>
       <c r="B185" t="n">
-        <v>78905</v>
+        <v>78151</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -19523,38 +19548,38 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>967</v>
+        <v>498</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>380335</v>
+        <v>380544</v>
       </c>
       <c r="R185" t="n">
-        <v>6920000</v>
+        <v>6920188</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19601,22 +19626,22 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124451326</v>
+        <v>124466026</v>
       </c>
       <c r="B186" t="n">
-        <v>57513</v>
+        <v>79399</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -19629,39 +19654,34 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>380227</v>
+        <v>380303</v>
       </c>
       <c r="R186" t="n">
-        <v>6920340</v>
+        <v>6919598</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19694,6 +19714,11 @@
       <c r="AA186" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -19720,10 +19745,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124469547</v>
+        <v>124464651</v>
       </c>
       <c r="B187" t="n">
-        <v>88359</v>
+        <v>79399</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -19736,34 +19761,34 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>510</v>
+        <v>229821</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>380452</v>
+        <v>380251</v>
       </c>
       <c r="R187" t="n">
-        <v>6919913</v>
+        <v>6919658</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19810,19 +19835,19 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124459042</v>
+        <v>124450737</v>
       </c>
       <c r="B188" t="n">
         <v>74901</v>
@@ -19858,14 +19883,14 @@
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>380571</v>
+        <v>380210</v>
       </c>
       <c r="R188" t="n">
-        <v>6919993</v>
+        <v>6920378</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19924,10 +19949,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124465167</v>
+        <v>124456832</v>
       </c>
       <c r="B189" t="n">
-        <v>78194</v>
+        <v>91030</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -19940,21 +19965,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6437</v>
+        <v>5432</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19964,10 +19989,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>380244</v>
+        <v>380443</v>
       </c>
       <c r="R189" t="n">
-        <v>6919577</v>
+        <v>6920118</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20014,19 +20039,19 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>124456372</v>
+        <v>124468547</v>
       </c>
       <c r="B190" t="n">
         <v>74901</v>
@@ -20062,14 +20087,14 @@
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>380368</v>
+        <v>380356</v>
       </c>
       <c r="R190" t="n">
-        <v>6920107</v>
+        <v>6919817</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20128,10 +20153,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>124468547</v>
+        <v>124466302</v>
       </c>
       <c r="B191" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20144,37 +20169,42 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>380356</v>
+        <v>380345</v>
       </c>
       <c r="R191" t="n">
-        <v>6919817</v>
+        <v>6919632</v>
       </c>
       <c r="S191" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -20230,10 +20260,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>124464842</v>
+        <v>124451172</v>
       </c>
       <c r="B192" t="n">
-        <v>79428</v>
+        <v>74901</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20246,34 +20276,34 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>380237</v>
+        <v>380184</v>
       </c>
       <c r="R192" t="n">
-        <v>6919621</v>
+        <v>6920434</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20332,10 +20362,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>124470070</v>
+        <v>124470732</v>
       </c>
       <c r="B193" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -20348,34 +20378,34 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>380533</v>
+        <v>380372</v>
       </c>
       <c r="R193" t="n">
-        <v>6919979</v>
+        <v>6920042</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20434,10 +20464,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>124470806</v>
+        <v>124470070</v>
       </c>
       <c r="B194" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -20450,42 +20480,37 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>380340</v>
+        <v>380533</v>
       </c>
       <c r="R194" t="n">
-        <v>6920036</v>
+        <v>6919979</v>
       </c>
       <c r="S194" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -20541,10 +20566,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>124451569</v>
+        <v>124457866</v>
       </c>
       <c r="B195" t="n">
-        <v>79399</v>
+        <v>78151</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -20553,38 +20578,38 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>229821</v>
+        <v>498</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>380184</v>
+        <v>380537</v>
       </c>
       <c r="R195" t="n">
-        <v>6920434</v>
+        <v>6920199</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20643,10 +20668,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>124464047</v>
+        <v>124470646</v>
       </c>
       <c r="B196" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -20659,34 +20684,34 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>380267</v>
+        <v>380402</v>
       </c>
       <c r="R196" t="n">
-        <v>6919731</v>
+        <v>6920044</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20745,10 +20770,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>124450845</v>
+        <v>124464471</v>
       </c>
       <c r="B197" t="n">
-        <v>78810</v>
+        <v>78194</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -20761,21 +20786,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20785,10 +20810,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>380205</v>
+        <v>380243</v>
       </c>
       <c r="R197" t="n">
-        <v>6920378</v>
+        <v>6919687</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20847,10 +20872,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>124459048</v>
+        <v>124456502</v>
       </c>
       <c r="B198" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -20863,39 +20888,34 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>380542</v>
+        <v>380385</v>
       </c>
       <c r="R198" t="n">
-        <v>6920184</v>
+        <v>6920091</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20928,6 +20948,11 @@
       <c r="AA198" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -20954,10 +20979,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>124451172</v>
+        <v>124470707</v>
       </c>
       <c r="B199" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -20970,37 +20995,42 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>380184</v>
+        <v>380367</v>
       </c>
       <c r="R199" t="n">
-        <v>6920434</v>
+        <v>6920058</v>
       </c>
       <c r="S199" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -21056,10 +21086,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>124450300</v>
+        <v>124455096</v>
       </c>
       <c r="B200" t="n">
-        <v>74901</v>
+        <v>5196</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -21068,38 +21098,43 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6440</v>
+        <v>105930</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>380182</v>
+        <v>380323</v>
       </c>
       <c r="R200" t="n">
-        <v>6920316</v>
+        <v>6920260</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21158,10 +21193,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>124455206</v>
+        <v>124461477</v>
       </c>
       <c r="B201" t="n">
-        <v>91030</v>
+        <v>79399</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -21174,34 +21209,34 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>5432</v>
+        <v>229821</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>380311</v>
+        <v>380285</v>
       </c>
       <c r="R201" t="n">
-        <v>6920231</v>
+        <v>6919895</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21260,10 +21295,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>124455453</v>
+        <v>124464466</v>
       </c>
       <c r="B202" t="n">
-        <v>74901</v>
+        <v>78905</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -21276,34 +21311,34 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6440</v>
+        <v>967</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>380326</v>
+        <v>380243</v>
       </c>
       <c r="R202" t="n">
-        <v>6920218</v>
+        <v>6919687</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21350,22 +21385,22 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>124451574</v>
+        <v>124451885</v>
       </c>
       <c r="B203" t="n">
-        <v>79428</v>
+        <v>91030</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -21378,21 +21413,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -21402,10 +21437,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>380184</v>
+        <v>380189</v>
       </c>
       <c r="R203" t="n">
-        <v>6920434</v>
+        <v>6920488</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21464,10 +21499,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>124455022</v>
+        <v>124454665</v>
       </c>
       <c r="B204" t="n">
-        <v>79428</v>
+        <v>74901</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -21480,34 +21515,34 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>380292</v>
+        <v>380258</v>
       </c>
       <c r="R204" t="n">
-        <v>6920288</v>
+        <v>6920309</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21566,10 +21601,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>124459060</v>
+        <v>124452491</v>
       </c>
       <c r="B205" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -21582,39 +21617,34 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
-      <c r="M205" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>380571</v>
+        <v>380208</v>
       </c>
       <c r="R205" t="n">
-        <v>6919993</v>
+        <v>6920481</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21673,10 +21703,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>124470234</v>
+        <v>124460258</v>
       </c>
       <c r="B206" t="n">
-        <v>82597</v>
+        <v>79428</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -21689,34 +21719,34 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>380506</v>
+        <v>380365</v>
       </c>
       <c r="R206" t="n">
-        <v>6920009</v>
+        <v>6919996</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21775,7 +21805,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>124461646</v>
+        <v>124464970</v>
       </c>
       <c r="B207" t="n">
         <v>57513</v>
@@ -21820,10 +21850,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>380239</v>
+        <v>380255</v>
       </c>
       <c r="R207" t="n">
-        <v>6919828</v>
+        <v>6919561</v>
       </c>
       <c r="S207" t="n">
         <v>15</v>
@@ -21882,10 +21912,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>124470742</v>
+        <v>124469547</v>
       </c>
       <c r="B208" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -21898,42 +21928,37 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
-      <c r="M208" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P208" t="inlineStr">
         <is>
           <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>380369</v>
+        <v>380452</v>
       </c>
       <c r="R208" t="n">
-        <v>6920032</v>
+        <v>6919913</v>
       </c>
       <c r="S208" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -21977,19 +22002,19 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>124460224</v>
+        <v>124456676</v>
       </c>
       <c r="B209" t="n">
         <v>57513</v>
@@ -22030,17 +22055,17 @@
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>380374</v>
+        <v>380434</v>
       </c>
       <c r="R209" t="n">
-        <v>6919982</v>
+        <v>6920123</v>
       </c>
       <c r="S209" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -22084,22 +22109,22 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>124466026</v>
+        <v>124458357</v>
       </c>
       <c r="B210" t="n">
-        <v>79399</v>
+        <v>57666</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -22112,37 +22137,42 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P210" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>380303</v>
+        <v>380586</v>
       </c>
       <c r="R210" t="n">
-        <v>6919598</v>
+        <v>6920100</v>
       </c>
       <c r="S210" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -22172,11 +22202,6 @@
       <c r="AA210" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC210" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -22191,22 +22216,22 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>124450578</v>
+        <v>124471016</v>
       </c>
       <c r="B211" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -22219,34 +22244,39 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>380227</v>
+        <v>380506</v>
       </c>
       <c r="R211" t="n">
-        <v>6920340</v>
+        <v>6920061</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22305,10 +22335,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>124464329</v>
+        <v>124455220</v>
       </c>
       <c r="B212" t="n">
-        <v>78194</v>
+        <v>74901</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -22321,34 +22351,34 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>380268</v>
+        <v>380311</v>
       </c>
       <c r="R212" t="n">
-        <v>6919685</v>
+        <v>6920231</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22407,10 +22437,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>124458172</v>
+        <v>124452627</v>
       </c>
       <c r="B213" t="n">
-        <v>78151</v>
+        <v>74901</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -22419,38 +22449,38 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>498</v>
+        <v>6440</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>380562</v>
+        <v>380217</v>
       </c>
       <c r="R213" t="n">
-        <v>6920118</v>
+        <v>6920440</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22509,10 +22539,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>124465389</v>
+        <v>124470404</v>
       </c>
       <c r="B214" t="n">
-        <v>79399</v>
+        <v>91030</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -22525,21 +22555,21 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>229821</v>
+        <v>5432</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -22549,10 +22579,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>380244</v>
+        <v>380471</v>
       </c>
       <c r="R214" t="n">
-        <v>6919577</v>
+        <v>6920069</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22599,22 +22629,22 @@
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>124460965</v>
+        <v>124459060</v>
       </c>
       <c r="B215" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -22627,34 +22657,39 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>380307</v>
+        <v>380571</v>
       </c>
       <c r="R215" t="n">
-        <v>6919967</v>
+        <v>6919993</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22713,10 +22748,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>124455220</v>
+        <v>124458282</v>
       </c>
       <c r="B216" t="n">
-        <v>74901</v>
+        <v>78151</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -22725,38 +22760,38 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>6440</v>
+        <v>498</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>380311</v>
+        <v>380588</v>
       </c>
       <c r="R216" t="n">
-        <v>6920231</v>
+        <v>6920110</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22815,10 +22850,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>124469915</v>
+        <v>124464047</v>
       </c>
       <c r="B217" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -22831,21 +22866,21 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -22855,10 +22890,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>380521</v>
+        <v>380267</v>
       </c>
       <c r="R217" t="n">
-        <v>6919962</v>
+        <v>6919731</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22917,10 +22952,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>124463210</v>
+        <v>124470485</v>
       </c>
       <c r="B218" t="n">
-        <v>79428</v>
+        <v>74901</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -22933,21 +22968,21 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -22957,10 +22992,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>380189</v>
+        <v>380446</v>
       </c>
       <c r="R218" t="n">
-        <v>6919766</v>
+        <v>6920059</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23019,10 +23054,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>124452423</v>
+        <v>124458046</v>
       </c>
       <c r="B219" t="n">
-        <v>56725</v>
+        <v>74901</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -23031,43 +23066,38 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>102613</v>
+        <v>6440</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>380227</v>
+        <v>380533</v>
       </c>
       <c r="R219" t="n">
-        <v>6920340</v>
+        <v>6920142</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23114,22 +23144,22 @@
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>124455776</v>
+        <v>124450578</v>
       </c>
       <c r="B220" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -23142,39 +23172,34 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P220" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>380326</v>
+        <v>380227</v>
       </c>
       <c r="R220" t="n">
-        <v>6920218</v>
+        <v>6920340</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23233,10 +23258,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>124471016</v>
+        <v>124464329</v>
       </c>
       <c r="B221" t="n">
-        <v>57513</v>
+        <v>78194</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -23249,39 +23274,34 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>380506</v>
+        <v>380268</v>
       </c>
       <c r="R221" t="n">
-        <v>6920061</v>
+        <v>6919685</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23328,22 +23348,22 @@
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>124470646</v>
+        <v>124465863</v>
       </c>
       <c r="B222" t="n">
-        <v>91030</v>
+        <v>78151</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -23352,38 +23372,38 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>5432</v>
+        <v>498</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Risåsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>380402</v>
+        <v>380296</v>
       </c>
       <c r="R222" t="n">
-        <v>6920044</v>
+        <v>6919585</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23442,10 +23462,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>124456704</v>
+        <v>124470234</v>
       </c>
       <c r="B223" t="n">
-        <v>91030</v>
+        <v>82597</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -23458,34 +23478,34 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>380385</v>
+        <v>380506</v>
       </c>
       <c r="R223" t="n">
-        <v>6920091</v>
+        <v>6920009</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23520,11 +23540,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC223" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
-        </is>
-      </c>
       <c r="AD223" t="b">
         <v>0</v>
       </c>
@@ -23537,22 +23552,22 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>124457317</v>
+        <v>124460965</v>
       </c>
       <c r="B224" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -23565,34 +23580,34 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>380547</v>
+        <v>380307</v>
       </c>
       <c r="R224" t="n">
-        <v>6920163</v>
+        <v>6919967</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23651,10 +23666,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>124470485</v>
+        <v>124469088</v>
       </c>
       <c r="B225" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -23667,34 +23682,34 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>380446</v>
+        <v>380352</v>
       </c>
       <c r="R225" t="n">
-        <v>6920059</v>
+        <v>6919913</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23753,10 +23768,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>124467947</v>
+        <v>124458476</v>
       </c>
       <c r="B226" t="n">
-        <v>78194</v>
+        <v>74901</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -23769,21 +23784,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -23793,10 +23808,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>380361</v>
+        <v>380581</v>
       </c>
       <c r="R226" t="n">
-        <v>6919740</v>
+        <v>6920056</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23831,11 +23846,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC226" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD226" t="b">
         <v>0</v>
       </c>
@@ -23848,22 +23858,22 @@
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>124458282</v>
+        <v>124470184</v>
       </c>
       <c r="B227" t="n">
-        <v>78151</v>
+        <v>91030</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -23872,25 +23882,25 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>498</v>
+        <v>5432</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -23900,10 +23910,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>380588</v>
+        <v>380516</v>
       </c>
       <c r="R227" t="n">
-        <v>6920110</v>
+        <v>6920004</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23962,10 +23972,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>124468302</v>
+        <v>124463365</v>
       </c>
       <c r="B228" t="n">
-        <v>57513</v>
+        <v>79399</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -23978,42 +23988,37 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>380265</v>
+        <v>380199</v>
       </c>
       <c r="R228" t="n">
-        <v>6919774</v>
+        <v>6919723</v>
       </c>
       <c r="S228" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -24069,10 +24074,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>124464651</v>
+        <v>124465167</v>
       </c>
       <c r="B229" t="n">
-        <v>79399</v>
+        <v>78194</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -24085,21 +24090,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -24109,10 +24114,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>380251</v>
+        <v>380244</v>
       </c>
       <c r="R229" t="n">
-        <v>6919658</v>
+        <v>6919577</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24159,22 +24164,22 @@
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>124459456</v>
+        <v>124469751</v>
       </c>
       <c r="B230" t="n">
-        <v>91032</v>
+        <v>74901</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -24187,34 +24192,34 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>5442</v>
+        <v>6440</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>380561</v>
+        <v>380490</v>
       </c>
       <c r="R230" t="n">
-        <v>6919930</v>
+        <v>6919937</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24261,19 +24266,19 @@
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>124455134</v>
+        <v>124469377</v>
       </c>
       <c r="B231" t="n">
         <v>74901</v>
@@ -24309,14 +24314,14 @@
       <c r="I231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>380311</v>
+        <v>380435</v>
       </c>
       <c r="R231" t="n">
-        <v>6920245</v>
+        <v>6919916</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24375,10 +24380,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>124457836</v>
+        <v>124464901</v>
       </c>
       <c r="B232" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -24391,34 +24396,34 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>380542</v>
+        <v>380249</v>
       </c>
       <c r="R232" t="n">
-        <v>6920184</v>
+        <v>6919607</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24465,22 +24470,22 @@
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>124464466</v>
+        <v>124451569</v>
       </c>
       <c r="B233" t="n">
-        <v>78905</v>
+        <v>79399</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -24493,34 +24498,34 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>967</v>
+        <v>229821</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>380243</v>
+        <v>380184</v>
       </c>
       <c r="R233" t="n">
-        <v>6919687</v>
+        <v>6920434</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -24579,10 +24584,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>124460052</v>
+        <v>124458172</v>
       </c>
       <c r="B234" t="n">
-        <v>57513</v>
+        <v>78151</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -24591,43 +24596,38 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
-      <c r="M234" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>380419</v>
+        <v>380562</v>
       </c>
       <c r="R234" t="n">
-        <v>6919960</v>
+        <v>6920118</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -24674,22 +24674,22 @@
       <c r="AT234" t="inlineStr"/>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>124458357</v>
+        <v>124460951</v>
       </c>
       <c r="B235" t="n">
-        <v>57666</v>
+        <v>74901</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -24702,42 +24702,37 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
-      <c r="M235" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>380586</v>
+        <v>380307</v>
       </c>
       <c r="R235" t="n">
-        <v>6920100</v>
+        <v>6919967</v>
       </c>
       <c r="S235" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T235" t="inlineStr">
         <is>
@@ -24793,7 +24788,7 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>124459815</v>
+        <v>124451802</v>
       </c>
       <c r="B236" t="n">
         <v>79428</v>
@@ -24833,10 +24828,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>380445</v>
+        <v>380197</v>
       </c>
       <c r="R236" t="n">
-        <v>6919917</v>
+        <v>6920479</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24895,10 +24890,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>124461736</v>
+        <v>124451574</v>
       </c>
       <c r="B237" t="n">
-        <v>74901</v>
+        <v>79428</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -24911,34 +24906,34 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>380232</v>
+        <v>380184</v>
       </c>
       <c r="R237" t="n">
-        <v>6919808</v>
+        <v>6920434</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -24997,10 +24992,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>124464970</v>
+        <v>124452423</v>
       </c>
       <c r="B238" t="n">
-        <v>57513</v>
+        <v>56725</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -25009,20 +25004,20 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>100109</v>
+        <v>102613</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -25033,22 +25028,22 @@
       <c r="I238" t="inlineStr"/>
       <c r="M238" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>380255</v>
+        <v>380227</v>
       </c>
       <c r="R238" t="n">
-        <v>6919561</v>
+        <v>6920340</v>
       </c>
       <c r="S238" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T238" t="inlineStr">
         <is>
@@ -25092,22 +25087,22 @@
       <c r="AT238" t="inlineStr"/>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>124466302</v>
+        <v>124451893</v>
       </c>
       <c r="B239" t="n">
-        <v>57513</v>
+        <v>5196</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -25116,20 +25111,20 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>100109</v>
+        <v>105930</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -25138,24 +25133,19 @@
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
-      <c r="M239" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>380345</v>
+        <v>380227</v>
       </c>
       <c r="R239" t="n">
-        <v>6919632</v>
+        <v>6920340</v>
       </c>
       <c r="S239" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T239" t="inlineStr">
         <is>
@@ -25199,22 +25189,22 @@
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>124464321</v>
+        <v>124456704</v>
       </c>
       <c r="B240" t="n">
-        <v>77738</v>
+        <v>91030</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -25227,34 +25217,34 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>6487</v>
+        <v>5432</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>380268</v>
+        <v>380385</v>
       </c>
       <c r="R240" t="n">
-        <v>6919685</v>
+        <v>6920091</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -25289,6 +25279,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC240" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD240" t="b">
         <v>0</v>
       </c>
@@ -25301,22 +25296,22 @@
       <c r="AT240" t="inlineStr"/>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>124452627</v>
+        <v>124457317</v>
       </c>
       <c r="B241" t="n">
-        <v>74901</v>
+        <v>79428</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -25329,34 +25324,34 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>380217</v>
+        <v>380547</v>
       </c>
       <c r="R241" t="n">
-        <v>6920440</v>
+        <v>6920163</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -25415,10 +25410,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>124458476</v>
+        <v>124451837</v>
       </c>
       <c r="B242" t="n">
-        <v>74901</v>
+        <v>78194</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -25431,34 +25426,34 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>380581</v>
+        <v>380197</v>
       </c>
       <c r="R242" t="n">
-        <v>6920056</v>
+        <v>6920479</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -25517,10 +25512,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>124452261</v>
+        <v>124463210</v>
       </c>
       <c r="B243" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -25533,34 +25528,34 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>380227</v>
+        <v>380189</v>
       </c>
       <c r="R243" t="n">
-        <v>6920340</v>
+        <v>6919766</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -25607,22 +25602,22 @@
       <c r="AT243" t="inlineStr"/>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>124465863</v>
+        <v>124459134</v>
       </c>
       <c r="B244" t="n">
-        <v>78151</v>
+        <v>74901</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -25631,38 +25626,38 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>498</v>
+        <v>6440</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Risåsvallen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>380296</v>
+        <v>380559</v>
       </c>
       <c r="R244" t="n">
-        <v>6919585</v>
+        <v>6919947</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25721,10 +25716,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>124450902</v>
+        <v>124455206</v>
       </c>
       <c r="B245" t="n">
-        <v>57529</v>
+        <v>91030</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -25737,39 +25732,34 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
-      <c r="M245" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P245" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>380227</v>
+        <v>380311</v>
       </c>
       <c r="R245" t="n">
-        <v>6920340</v>
+        <v>6920231</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25804,11 +25794,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC245" t="inlineStr">
-        <is>
-          <t>Troligen spillkråka.</t>
-        </is>
-      </c>
       <c r="AD245" t="b">
         <v>0</v>
       </c>
@@ -25821,22 +25806,22 @@
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>124459287</v>
+        <v>124455022</v>
       </c>
       <c r="B246" t="n">
-        <v>57513</v>
+        <v>79428</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -25849,39 +25834,34 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
-      <c r="M246" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>380561</v>
+        <v>380292</v>
       </c>
       <c r="R246" t="n">
-        <v>6919930</v>
+        <v>6920288</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25928,19 +25908,19 @@
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>124451984</v>
+        <v>124465009</v>
       </c>
       <c r="B247" t="n">
         <v>79399</v>
@@ -25976,14 +25956,14 @@
       <c r="I247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>380203</v>
+        <v>380267</v>
       </c>
       <c r="R247" t="n">
-        <v>6920482</v>
+        <v>6919764</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -26018,6 +25998,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC247" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD247" t="b">
         <v>0</v>
       </c>
@@ -26030,22 +26015,22 @@
       <c r="AT247" t="inlineStr"/>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>124465526</v>
+        <v>124450902</v>
       </c>
       <c r="B248" t="n">
-        <v>79399</v>
+        <v>57529</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -26058,34 +26043,39 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Risåsvallen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>380252</v>
+        <v>380227</v>
       </c>
       <c r="R248" t="n">
-        <v>6919535</v>
+        <v>6920340</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -26120,6 +26110,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>Troligen spillkråka.</t>
+        </is>
+      </c>
       <c r="AD248" t="b">
         <v>0</v>
       </c>
@@ -26132,22 +26127,22 @@
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>124458743</v>
+        <v>124466494</v>
       </c>
       <c r="B249" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -26160,37 +26155,42 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>380542</v>
+        <v>380344</v>
       </c>
       <c r="R249" t="n">
-        <v>6920184</v>
+        <v>6919654</v>
       </c>
       <c r="S249" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T249" t="inlineStr">
         <is>
@@ -26220,11 +26220,6 @@
       <c r="AA249" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC249" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -26239,22 +26234,22 @@
       <c r="AT249" t="inlineStr"/>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>124470184</v>
+        <v>124465526</v>
       </c>
       <c r="B250" t="n">
-        <v>91030</v>
+        <v>79399</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -26267,34 +26262,34 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>5432</v>
+        <v>229821</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>380516</v>
+        <v>380252</v>
       </c>
       <c r="R250" t="n">
-        <v>6920004</v>
+        <v>6919535</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -26353,10 +26348,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>124466494</v>
+        <v>124467914</v>
       </c>
       <c r="B251" t="n">
-        <v>57513</v>
+        <v>77738</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -26369,42 +26364,37 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
-      <c r="M251" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P251" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>380344</v>
+        <v>380361</v>
       </c>
       <c r="R251" t="n">
-        <v>6919654</v>
+        <v>6919740</v>
       </c>
       <c r="S251" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T251" t="inlineStr">
         <is>
@@ -26434,6 +26424,11 @@
       <c r="AA251" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC251" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -26448,22 +26443,22 @@
       <c r="AT251" t="inlineStr"/>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>124470555</v>
+        <v>124470598</v>
       </c>
       <c r="B252" t="n">
-        <v>82597</v>
+        <v>79428</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -26476,34 +26471,34 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
       <c r="P252" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>380431</v>
+        <v>380506</v>
       </c>
       <c r="R252" t="n">
-        <v>6920068</v>
+        <v>6920061</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -26538,6 +26533,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC252" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD252" t="b">
         <v>0</v>
       </c>
@@ -26550,22 +26550,22 @@
       <c r="AT252" t="inlineStr"/>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>124470397</v>
+        <v>124464321</v>
       </c>
       <c r="B253" t="n">
-        <v>74901</v>
+        <v>77738</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -26578,34 +26578,34 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>6440</v>
+        <v>6487</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>380506</v>
+        <v>380268</v>
       </c>
       <c r="R253" t="n">
-        <v>6920061</v>
+        <v>6919685</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -26652,22 +26652,22 @@
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>124464471</v>
+        <v>124461108</v>
       </c>
       <c r="B254" t="n">
-        <v>78194</v>
+        <v>74901</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -26680,34 +26680,34 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>380243</v>
+        <v>380308</v>
       </c>
       <c r="R254" t="n">
-        <v>6919687</v>
+        <v>6919925</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26740,6 +26740,11 @@
       <c r="AA254" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>På basen avsågad gran. Grov stubbe</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -26766,10 +26771,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>124458046</v>
+        <v>124468916</v>
       </c>
       <c r="B255" t="n">
-        <v>74901</v>
+        <v>78151</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -26778,38 +26783,38 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>6440</v>
+        <v>498</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>380533</v>
+        <v>380343</v>
       </c>
       <c r="R255" t="n">
-        <v>6920142</v>
+        <v>6919896</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26868,10 +26873,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>124458651</v>
+        <v>124464292</v>
       </c>
       <c r="B256" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -26884,34 +26889,39 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P256" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>380569</v>
+        <v>380275</v>
       </c>
       <c r="R256" t="n">
-        <v>6920058</v>
+        <v>6919775</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -26958,22 +26968,22 @@
       <c r="AT256" t="inlineStr"/>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>124450518</v>
+        <v>124454979</v>
       </c>
       <c r="B257" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -26986,34 +26996,34 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
       <c r="P257" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>380202</v>
+        <v>380289</v>
       </c>
       <c r="R257" t="n">
-        <v>6920332</v>
+        <v>6920290</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -27048,6 +27058,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC257" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD257" t="b">
         <v>0</v>
       </c>
@@ -27060,22 +27075,22 @@
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>124457601</v>
+        <v>124459456</v>
       </c>
       <c r="B258" t="n">
-        <v>78151</v>
+        <v>91032</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -27084,38 +27099,38 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>498</v>
+        <v>5442</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>380544</v>
+        <v>380561</v>
       </c>
       <c r="R258" t="n">
-        <v>6920188</v>
+        <v>6919930</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -27162,22 +27177,22 @@
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>124470146</v>
+        <v>124456046</v>
       </c>
       <c r="B259" t="n">
-        <v>57513</v>
+        <v>91032</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -27190,42 +27205,37 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
-      <c r="M259" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>380527</v>
+        <v>380326</v>
       </c>
       <c r="R259" t="n">
-        <v>6919988</v>
+        <v>6920218</v>
       </c>
       <c r="S259" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T259" t="inlineStr">
         <is>
@@ -27255,6 +27265,11 @@
       <c r="AA259" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC259" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -27269,22 +27284,22 @@
       <c r="AT259" t="inlineStr"/>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>124467914</v>
+        <v>124464493</v>
       </c>
       <c r="B260" t="n">
-        <v>77738</v>
+        <v>79399</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -27297,21 +27312,21 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
@@ -27321,10 +27336,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>380361</v>
+        <v>380243</v>
       </c>
       <c r="R260" t="n">
-        <v>6919740</v>
+        <v>6919687</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -27359,11 +27374,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC260" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD260" t="b">
         <v>0</v>
       </c>
@@ -27376,19 +27386,19 @@
       <c r="AT260" t="inlineStr"/>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>124459134</v>
+        <v>124455456</v>
       </c>
       <c r="B261" t="n">
         <v>74901</v>
@@ -27424,14 +27434,14 @@
       <c r="I261" t="inlineStr"/>
       <c r="P261" t="inlineStr">
         <is>
-          <t>Krukmakarbäcken, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>380559</v>
+        <v>380314</v>
       </c>
       <c r="R261" t="n">
-        <v>6919947</v>
+        <v>6920201</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -27490,7 +27500,7 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>124469377</v>
+        <v>124459042</v>
       </c>
       <c r="B262" t="n">
         <v>74901</v>
@@ -27526,14 +27536,14 @@
       <c r="I262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>380435</v>
+        <v>380571</v>
       </c>
       <c r="R262" t="n">
-        <v>6919916</v>
+        <v>6919993</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -27592,10 +27602,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>124468469</v>
+        <v>124455134</v>
       </c>
       <c r="B263" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -27608,42 +27618,37 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
-      <c r="M263" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>380324</v>
+        <v>380311</v>
       </c>
       <c r="R263" t="n">
-        <v>6919803</v>
+        <v>6920245</v>
       </c>
       <c r="S263" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T263" t="inlineStr">
         <is>
@@ -27699,10 +27704,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>124457866</v>
+        <v>124458743</v>
       </c>
       <c r="B264" t="n">
-        <v>78151</v>
+        <v>91030</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -27711,38 +27716,38 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>498</v>
+        <v>5432</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>380537</v>
+        <v>380542</v>
       </c>
       <c r="R264" t="n">
-        <v>6920199</v>
+        <v>6920184</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27777,6 +27782,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC264" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD264" t="b">
         <v>0</v>
       </c>
@@ -27789,22 +27799,22 @@
       <c r="AT264" t="inlineStr"/>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>124451893</v>
+        <v>124469907</v>
       </c>
       <c r="B265" t="n">
-        <v>5196</v>
+        <v>78810</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -27813,38 +27823,38 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>380227</v>
+        <v>380452</v>
       </c>
       <c r="R265" t="n">
-        <v>6920340</v>
+        <v>6919913</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27903,10 +27913,10 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>124454979</v>
+        <v>124455453</v>
       </c>
       <c r="B266" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -27919,21 +27929,21 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
@@ -27943,10 +27953,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>380289</v>
+        <v>380326</v>
       </c>
       <c r="R266" t="n">
-        <v>6920290</v>
+        <v>6920218</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -27979,11 +27989,6 @@
       <c r="AA266" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC266" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD266" t="b">
@@ -28010,10 +28015,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>124451837</v>
+        <v>124459815</v>
       </c>
       <c r="B267" t="n">
-        <v>78194</v>
+        <v>79428</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -28026,21 +28031,21 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
@@ -28050,10 +28055,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>380197</v>
+        <v>380445</v>
       </c>
       <c r="R267" t="n">
-        <v>6920479</v>
+        <v>6919917</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -28112,10 +28117,10 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>124456502</v>
+        <v>124461736</v>
       </c>
       <c r="B268" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -28128,34 +28133,34 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
       <c r="P268" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>380385</v>
+        <v>380232</v>
       </c>
       <c r="R268" t="n">
-        <v>6920091</v>
+        <v>6919808</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -28190,11 +28195,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC268" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området.</t>
-        </is>
-      </c>
       <c r="AD268" t="b">
         <v>0</v>
       </c>
@@ -28207,19 +28207,19 @@
       <c r="AT268" t="inlineStr"/>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>124452491</v>
+        <v>124452261</v>
       </c>
       <c r="B269" t="n">
         <v>78810</v>
@@ -28259,10 +28259,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>380208</v>
+        <v>380227</v>
       </c>
       <c r="R269" t="n">
-        <v>6920481</v>
+        <v>6920340</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -28309,22 +28309,22 @@
       <c r="AT269" t="inlineStr"/>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>124470404</v>
+        <v>124467947</v>
       </c>
       <c r="B270" t="n">
-        <v>91030</v>
+        <v>78194</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -28337,21 +28337,21 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>5432</v>
+        <v>6437</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
@@ -28361,10 +28361,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>380471</v>
+        <v>380361</v>
       </c>
       <c r="R270" t="n">
-        <v>6920069</v>
+        <v>6919740</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -28399,6 +28399,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC270" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD270" t="b">
         <v>0</v>
       </c>
@@ -28411,22 +28416,22 @@
       <c r="AT270" t="inlineStr"/>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>124461108</v>
+        <v>124450518</v>
       </c>
       <c r="B271" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -28439,34 +28444,34 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
       <c r="P271" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>380308</v>
+        <v>380202</v>
       </c>
       <c r="R271" t="n">
-        <v>6919925</v>
+        <v>6920332</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -28499,11 +28504,6 @@
       <c r="AA271" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC271" t="inlineStr">
-        <is>
-          <t>På basen avsågad gran. Grov stubbe</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -28530,10 +28530,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>124450415</v>
+        <v>124459287</v>
       </c>
       <c r="B272" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -28546,34 +28546,39 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P272" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>380202</v>
+        <v>380561</v>
       </c>
       <c r="R272" t="n">
-        <v>6920332</v>
+        <v>6919930</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -28620,12 +28625,12 @@
       <c r="AT272" t="inlineStr"/>
       <c r="AW272" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
@@ -29050,10 +29055,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>124870851</v>
+        <v>124871081</v>
       </c>
       <c r="B277" t="n">
-        <v>79399</v>
+        <v>57513</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -29066,37 +29071,42 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P277" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>380051</v>
+        <v>380173</v>
       </c>
       <c r="R277" t="n">
-        <v>6919850</v>
+        <v>6920011</v>
       </c>
       <c r="S277" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T277" t="inlineStr">
         <is>
@@ -29259,7 +29269,7 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>124871057</v>
+        <v>124870503</v>
       </c>
       <c r="B279" t="n">
         <v>57513</v>
@@ -29300,14 +29310,14 @@
       </c>
       <c r="P279" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>380132</v>
+        <v>380108</v>
       </c>
       <c r="R279" t="n">
-        <v>6919977</v>
+        <v>6919741</v>
       </c>
       <c r="S279" t="n">
         <v>15</v>
@@ -29366,10 +29376,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>124871232</v>
+        <v>124870881</v>
       </c>
       <c r="B280" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -29382,37 +29392,42 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P280" t="inlineStr">
         <is>
-          <t>Risåsen, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>380202</v>
+        <v>380067</v>
       </c>
       <c r="R280" t="n">
-        <v>6920072</v>
+        <v>6919860</v>
       </c>
       <c r="S280" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T280" t="inlineStr">
         <is>
@@ -29468,7 +29483,7 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>124870503</v>
+        <v>124870943</v>
       </c>
       <c r="B281" t="n">
         <v>57513</v>
@@ -29509,14 +29524,14 @@
       </c>
       <c r="P281" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>380108</v>
+        <v>380093</v>
       </c>
       <c r="R281" t="n">
-        <v>6919741</v>
+        <v>6919892</v>
       </c>
       <c r="S281" t="n">
         <v>15</v>
@@ -29575,10 +29590,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>124870920</v>
+        <v>124871057</v>
       </c>
       <c r="B282" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -29591,37 +29606,42 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P282" t="inlineStr">
         <is>
           <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>380097</v>
+        <v>380132</v>
       </c>
       <c r="R282" t="n">
-        <v>6919882</v>
+        <v>6919977</v>
       </c>
       <c r="S282" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T282" t="inlineStr">
         <is>
@@ -29677,7 +29697,7 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>124870881</v>
+        <v>124870829</v>
       </c>
       <c r="B283" t="n">
         <v>57513</v>
@@ -29713,7 +29733,7 @@
       <c r="I283" t="inlineStr"/>
       <c r="M283" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P283" t="inlineStr">
@@ -29722,10 +29742,10 @@
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>380067</v>
+        <v>380045</v>
       </c>
       <c r="R283" t="n">
-        <v>6919860</v>
+        <v>6919831</v>
       </c>
       <c r="S283" t="n">
         <v>15</v>
@@ -29784,10 +29804,10 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>124870424</v>
+        <v>124870654</v>
       </c>
       <c r="B284" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -29800,42 +29820,37 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
-      <c r="M284" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P284" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>380098</v>
+        <v>380093</v>
       </c>
       <c r="R284" t="n">
-        <v>6919759</v>
+        <v>6919795</v>
       </c>
       <c r="S284" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T284" t="inlineStr">
         <is>
@@ -29891,10 +29906,10 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>124870654</v>
+        <v>124870424</v>
       </c>
       <c r="B285" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -29907,37 +29922,42 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P285" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>380093</v>
+        <v>380098</v>
       </c>
       <c r="R285" t="n">
-        <v>6919795</v>
+        <v>6919759</v>
       </c>
       <c r="S285" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T285" t="inlineStr">
         <is>
@@ -29993,10 +30013,10 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>124870829</v>
+        <v>124870851</v>
       </c>
       <c r="B286" t="n">
-        <v>57513</v>
+        <v>79399</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -30009,42 +30029,37 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I286" t="inlineStr"/>
-      <c r="M286" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P286" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>380045</v>
+        <v>380051</v>
       </c>
       <c r="R286" t="n">
-        <v>6919831</v>
+        <v>6919850</v>
       </c>
       <c r="S286" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T286" t="inlineStr">
         <is>
@@ -30207,10 +30222,10 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>124870943</v>
+        <v>124870920</v>
       </c>
       <c r="B288" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -30223,42 +30238,37 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I288" t="inlineStr"/>
-      <c r="M288" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P288" t="inlineStr">
         <is>
           <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>380093</v>
+        <v>380097</v>
       </c>
       <c r="R288" t="n">
-        <v>6919892</v>
+        <v>6919882</v>
       </c>
       <c r="S288" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T288" t="inlineStr">
         <is>
@@ -30314,10 +30324,10 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>124871081</v>
+        <v>124871232</v>
       </c>
       <c r="B289" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -30330,42 +30340,37 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I289" t="inlineStr"/>
-      <c r="M289" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P289" t="inlineStr">
         <is>
           <t>Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>380173</v>
+        <v>380202</v>
       </c>
       <c r="R289" t="n">
-        <v>6920011</v>
+        <v>6920072</v>
       </c>
       <c r="S289" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T289" t="inlineStr">
         <is>

--- a/artfynd/A 32573-2024 artfynd.xlsx
+++ b/artfynd/A 32573-2024 artfynd.xlsx
@@ -16105,10 +16105,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>124459048</v>
+        <v>124459815</v>
       </c>
       <c r="B152" t="n">
-        <v>57513</v>
+        <v>79428</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16121,39 +16121,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>380542</v>
+        <v>380445</v>
       </c>
       <c r="R152" t="n">
-        <v>6920184</v>
+        <v>6919917</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16200,22 +16195,22 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>124470806</v>
+        <v>124470397</v>
       </c>
       <c r="B153" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16228,42 +16223,37 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>380340</v>
+        <v>380506</v>
       </c>
       <c r="R153" t="n">
-        <v>6920036</v>
+        <v>6920061</v>
       </c>
       <c r="S153" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16307,22 +16297,22 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>124465389</v>
+        <v>124461108</v>
       </c>
       <c r="B154" t="n">
-        <v>79399</v>
+        <v>74901</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16335,34 +16325,34 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>380244</v>
+        <v>380308</v>
       </c>
       <c r="R154" t="n">
-        <v>6919577</v>
+        <v>6919925</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16397,6 +16387,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>På basen avsågad gran. Grov stubbe</t>
+        </is>
+      </c>
       <c r="AD154" t="b">
         <v>0</v>
       </c>
@@ -16409,22 +16404,22 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>124454876</v>
+        <v>124458651</v>
       </c>
       <c r="B155" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16437,34 +16432,34 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Mormyren, Hjd</t>
+          <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>380290</v>
+        <v>380569</v>
       </c>
       <c r="R155" t="n">
-        <v>6920272</v>
+        <v>6920058</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16523,10 +16518,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>124470695</v>
+        <v>124460611</v>
       </c>
       <c r="B156" t="n">
-        <v>91030</v>
+        <v>78905</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16539,21 +16534,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>5432</v>
+        <v>967</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16563,10 +16558,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>380506</v>
+        <v>380335</v>
       </c>
       <c r="R156" t="n">
-        <v>6920061</v>
+        <v>6920000</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16599,11 +16594,6 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16630,10 +16620,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>124450845</v>
+        <v>124461646</v>
       </c>
       <c r="B157" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16646,37 +16636,42 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>380205</v>
+        <v>380239</v>
       </c>
       <c r="R157" t="n">
-        <v>6920378</v>
+        <v>6919828</v>
       </c>
       <c r="S157" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16732,10 +16727,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>124464842</v>
+        <v>124470742</v>
       </c>
       <c r="B158" t="n">
-        <v>79428</v>
+        <v>57513</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16748,37 +16743,42 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>380237</v>
+        <v>380369</v>
       </c>
       <c r="R158" t="n">
-        <v>6919621</v>
+        <v>6920032</v>
       </c>
       <c r="S158" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -16834,10 +16834,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>124450300</v>
+        <v>124464292</v>
       </c>
       <c r="B159" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16850,34 +16850,39 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Lill-Långtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>380182</v>
+        <v>380275</v>
       </c>
       <c r="R159" t="n">
-        <v>6920316</v>
+        <v>6919775</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16924,22 +16929,22 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>124458651</v>
+        <v>124451893</v>
       </c>
       <c r="B160" t="n">
-        <v>91030</v>
+        <v>5196</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -16948,38 +16953,38 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>5432</v>
+        <v>105930</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>380569</v>
+        <v>380227</v>
       </c>
       <c r="R160" t="n">
-        <v>6920058</v>
+        <v>6920340</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17026,22 +17031,22 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>124450415</v>
+        <v>124460052</v>
       </c>
       <c r="B161" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17054,34 +17059,39 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Lill-Långtjärnen, Hjd</t>
+          <t>Krukmakarbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>380202</v>
+        <v>380419</v>
       </c>
       <c r="R161" t="n">
-        <v>6920332</v>
+        <v>6919960</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17128,22 +17138,22 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>124455776</v>
+        <v>124451569</v>
       </c>
       <c r="B162" t="n">
-        <v>57513</v>
+        <v>79399</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17156,39 +17166,34 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>Mormyren, Hjd</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>380326</v>
+        <v>380184</v>
       </c>
       <c r="R162" t="n">
-        <v>6920218</v>
+        <v>6920434</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17235,22 +17240,22 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
     